--- a/Results/Results.out/Bovines/Data/reg_out_bv_lon_fold_sets.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_lon_fold_sets.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="483">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -80,25 +80,25 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 59, 76, 77, 133, 134, 135, 1671, 1787, 1788, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 61, 74, 75, 136, 137, 1789, 1790, 1792, 2053)</t>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 137, 1671, 1788, 1790, 1793, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 136, 1787, 1789, 1792, 1794, 1795, 1888, 2049, 2052)</t>
   </si>
   <si>
     <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(58, 60, 61, 74, 75, 76, 77, 133, 134, 136, 137, 1788, 1789, 1790, 1792, 1793, 1794, 2049, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 135, 1671, 1787, 1795, 1888, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 61, 76, 77, 133, 135, 136, 137, 1788, 1790, 1793, 1794, 1795, 2049, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 74, 75, 134, 1671, 1787, 1789, 1792, 1888, 2051)</t>
+    <t xml:space="preserve">c(51, 59, 75, 76, 77, 134, 135, 137, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 61, 74, 133, 136, 1671, 1787, 2049, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 75, 77, 135, 136, 137, 1789, 1790, 1792, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 74, 76, 133, 134, 1671, 1787, 1788, 1793, 1794)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
@@ -107,934 +107,1360 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(81, 82, 122, 123, 124, 183, 185, 186, 1747, 1748, 1890, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 125, 184, 1749, 1891, 2006)</t>
+    <t xml:space="preserve">c(79, 80, 81, 82, 124, 184, 185, 1747, 1748, 1890, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 123, 125, 183, 186, 1749, 2008)</t>
   </si>
   <si>
     <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 183, 184, 185, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(79, 81, 122, 123, 124, 125, 185, 186, 1747, 1748, 1749, 1890, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 82, 183, 184, 1891, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 122, 183, 184, 185, 1748, 1749, 1890, 1891, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 82, 123, 124, 125, 186, 1747, 2006)</t>
+    <t xml:space="preserve">c(78, 79, 81, 124, 125, 183, 186, 1747, 1748, 1749, 1891, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 82, 122, 123, 184, 185, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 122, 123, 124, 125, 183, 184, 185, 1747, 1891, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 82, 186, 1748, 1749, 1890, 2006)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1833, 1834, 1979, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1832, 1980, 2145, 2147)</t>
+    <t xml:space="preserve">c(1829, 1831, 1832, 1834, 1979, 2144, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1833, 1980, 2146)</t>
   </si>
   <si>
     <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1834, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1834, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1979, 1980, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1834, 1979, 1980, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 2145, 2146, 2148)</t>
+    <t xml:space="preserve">c(1829, 1832, 1833, 1979, 1980, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1834, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1833, 1834, 1979, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1980, 2144, 2147, 2148)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(104, 105, 106, 108, 109, 111, 112, 113, 114, 117, 118, 1645, 1646, 1647, 1648, 2211, 2212, 2296, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 107, 110, 115, 116, 1676, 1677, 2213, 2297)</t>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 114, 115, 116, 117, 1645, 1647, 2213, 2297, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(112, 113, 118, 1646, 1648, 1676, 1677, 2211, 2212, 2296, 2299, 2321)</t>
   </si>
   <si>
     <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(100, 103, 105, 106, 107, 108, 110, 111, 112, 116, 117, 1645, 1647, 1648, 1676, 2211, 2212, 2213, 2296, 2297, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 104, 109, 113, 114, 115, 118, 1646, 1677, 2298, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 103, 104, 107, 108, 109, 110, 111, 112, 114, 115, 117, 118, 1645, 1647, 1648, 1676, 2211, 2297, 2298, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 105, 106, 113, 116, 1646, 1677, 2212, 2213, 2296, 2299, 2323)</t>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 107, 110, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 2212, 2297, 2298, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(105, 106, 108, 109, 111, 112, 1677, 2211, 2213, 2296, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 106, 107, 109, 111, 112, 114, 115, 116, 117, 118, 1646, 1647, 1648, 1676, 2211, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 105, 108, 110, 113, 1645, 1677, 2212, 2213, 2296, 2297, 2299)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 74, 75, 76, 77, 133, 134, 135, 136, 1787, 1788, 1790, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 61, 137, 1671, 1789, 1792, 1793, 1794, 1795)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 76, 77, 134, 135, 136, 137, 1671, 1787, 1789, 1790, 1793, 1888, 2049, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 74, 75, 133, 1788, 1792, 1794, 1795, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 61, 75, 76, 77, 133, 134, 135, 136, 1787, 1788, 1789, 1790, 1792, 1794, 1795, 1888, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 74, 137, 1671, 1793, 2049, 2050, 2053)</t>
+    <t xml:space="preserve">c(51, 59, 75, 77, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1793, 1794, 1795, 2049, 2050, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 61, 74, 76, 1671, 1792, 1888, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 76, 77, 135, 136, 137, 1671, 1787, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 61, 74, 75, 133, 134, 1788, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 61, 74, 75, 134, 136, 137, 1787, 1788, 1789, 1792, 1793, 1794, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 76, 77, 133, 135, 1671, 1790, 1795, 1888, 2049)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.2</t>
   </si>
   <si>
+    <t xml:space="preserve">c(78, 122, 123, 124, 125, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 183, 184, 185, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 82, 125, 183, 185, 186, 1747, 1748, 1749, 1890, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 122, 123, 124, 184, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 124, 125, 183, 185, 186, 1747, 1749, 1890, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 122, 123, 184, 1748, 1891, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1.1.1.2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1833, 1834, 1979, 1980, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 2144, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1833, 1834, 1979, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1832, 1980, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1.1.1.2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 106, 108, 109, 110, 111, 112, 113, 115, 117, 118, 1645, 1646, 1647, 1648, 1677, 2212, 2296, 2297, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 105, 107, 114, 116, 1676, 2211, 2213, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 106, 107, 112, 113, 114, 115, 118, 1645, 1646, 1648, 1677, 2211, 2213, 2296, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(104, 105, 108, 109, 110, 111, 116, 117, 1647, 1676, 2212, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 104, 105, 107, 108, 109, 113, 115, 117, 118, 1645, 1646, 1648, 1676, 1677, 2211, 2213, 2297, 2298, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 106, 110, 111, 112, 114, 116, 1647, 2212, 2296, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 74, 75, 77, 134, 135, 1787, 1788, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 60, 61, 76, 133, 136, 137, 1671, 1789, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 74, 75, 133, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1795, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 61, 76, 77, 134, 1793, 1794, 1888, 2049, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 61, 74, 76, 77, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1795, 1888, 2049, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 75, 1790, 1792, 1793, 1794, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 123, 125, 183, 185, 186, 1747, 1749, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 124, 184, 1748, 1890, 1891, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 122, 184, 185, 1747, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 123, 124, 125, 183, 186, 1748, 1749)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 123, 125, 183, 185, 186, 1747, 1748, 1890, 1891, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 82, 122, 124, 184, 1749, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1832, 1834, 1979, 1980, 2144, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1833, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 1834, 1979, 1980, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 1979, 1980, 2144, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1834, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 104, 105, 107, 108, 109, 111, 112, 113, 116, 117, 118, 1645, 1646, 1648, 1676, 2211, 2212, 2213, 2296, 2299, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 106, 110, 114, 115, 1647, 1677, 2297, 2298, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 105, 106, 107, 109, 110, 112, 114, 115, 116, 118, 1645, 1646, 1647, 1648, 1676, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 104, 108, 111, 113, 117, 1677, 2211, 2212, 2213, 2296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 106, 108, 109, 110, 111, 112, 114, 115, 116, 118, 1645, 1647, 1648, 2211, 2212, 2213, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 103, 104, 105, 107, 113, 117, 1646, 1676, 1677, 2296, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 74, 133, 135, 136, 1671, 1787, 1789, 1792, 1793, 1794, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 75, 76, 77, 134, 137, 1788, 1790, 1795, 1888)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 61, 75, 76, 77, 133, 135, 137, 1787, 1788, 1790, 1792, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 74, 134, 136, 1671, 1789, 1793, 1794, 1795, 1888)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 74, 76, 77, 133, 135, 136, 1671, 1787, 1790, 1792, 1888, 2049, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 75, 134, 137, 1788, 1789, 1793, 1794, 1795, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 123, 124, 125, 184, 185, 1747, 1748, 1890, 1891, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 82, 122, 183, 186, 1749, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 123, 124, 125, 183, 184, 185, 1748, 1749, 1891, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 122, 186, 1747, 1890, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 82, 122, 123, 125, 183, 184, 185, 186, 1748, 1749, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 124, 1747, 1890, 1891, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1834, 1979, 1980, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1832, 1834, 1979, 2144, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1833, 1980)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1832, 1833, 1979, 1980, 2144, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1834, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 107, 108, 109, 110, 111, 112, 113, 114, 116, 117, 1645, 1646, 1676, 1677, 2212, 2213, 2296, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 103, 104, 105, 106, 115, 118, 1647, 1648, 2211, 2297, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 106, 107, 108, 109, 110, 112, 114, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 2211, 2213, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 105, 111, 113, 115, 1677, 2212, 2296, 2297, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 104, 106, 107, 108, 110, 112, 114, 115, 116, 117, 1645, 1646, 1647, 1676, 1677, 2213, 2296, 2297, 2298, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 105, 109, 111, 113, 118, 1648, 2211, 2212, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 76, 77, 133, 134, 136, 137, 1671, 1787, 1789, 1790, 1792, 1794, 1888, 2049, 2050, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 74, 75, 135, 1788, 1793, 1795, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 75, 76, 134, 136, 137, 1671, 1787, 1790, 1795, 1888, 2049, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 77, 133, 135, 1788, 1789, 1792, 1793, 1794, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 61, 74, 75, 76, 77, 133, 134, 135, 1671, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 60, 136, 137, 1787, 2049, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 123, 124, 183, 184, 185, 186, 1747, 1749, 1891, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 122, 125, 1748, 1890, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 125, 183, 184, 186, 1748, 1890, 1891, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(122, 123, 124, 185, 1747, 1749, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 82, 122, 123, 125, 183, 185, 1747, 1748, 1890, 1891, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 124, 184, 186, 1749, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1832, 1834, 1979, 1980, 2144, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1833, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1832, 1833, 1834, 1979, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1980, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1980, 2144, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 1834, 1979, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 105, 108, 110, 111, 112, 114, 116, 117, 118, 1645, 1646, 1648, 1677, 2211, 2212, 2213, 2296, 2297, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 104, 106, 107, 109, 113, 115, 1647, 1676, 2298, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 105, 106, 107, 109, 110, 111, 112, 113, 116, 117, 118, 1646, 1647, 1648, 1677, 2297, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(104, 108, 114, 115, 1645, 1676, 2211, 2212, 2213, 2296, 2298, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 106, 108, 109, 110, 111, 113, 115, 117, 1645, 1647, 1676, 1677, 2212, 2213, 2296, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(104, 105, 107, 112, 114, 116, 118, 1646, 1648, 2211, 2297, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 74, 75, 133, 135, 136, 1671, 1787, 1788, 1789, 1792, 1793, 1795, 1888, 2049, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 76, 77, 134, 137, 1790, 1794, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 61, 74, 76, 77, 133, 136, 137, 1671, 1787, 1790, 1792, 1793, 1794, 1888, 2049, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 75, 134, 135, 1788, 1789, 1795, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 74, 75, 76, 133, 134, 136, 137, 1671, 1787, 1788, 1794, 1795, 1888, 2049, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 77, 135, 1789, 1790, 1792, 1793, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 123, 124, 184, 186, 1747, 1748, 1749, 1890, 1891, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 122, 125, 183, 185, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 123, 124, 125, 184, 1747, 1748, 1890, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 122, 183, 185, 186, 1749, 1891, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 124, 125, 183, 184, 186, 1890, 1891, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 185, 1747, 1748, 1749, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1979, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1834, 1980, 2144, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1832, 1833, 1834, 1980, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1979, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 107, 109, 110, 111, 113, 114, 117, 118, 1645, 1648, 1676, 1677, 2211, 2213, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(105, 106, 108, 112, 115, 116, 1646, 1647, 2212, 2296, 2297, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 104, 105, 106, 108, 109, 110, 114, 116, 117, 118, 1646, 1647, 1676, 2211, 2212, 2296, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 107, 111, 112, 113, 115, 1645, 1648, 1677, 2213, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 107, 108, 110, 112, 113, 118, 1645, 1646, 1647, 1648, 1677, 2211, 2212, 2213, 2298, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(105, 106, 109, 111, 114, 115, 116, 117, 1676, 2296, 2297, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 61, 75, 76, 77, 133, 134, 135, 136, 1789, 1790, 1793, 1794, 1888, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 74, 137, 1671, 1787, 1788, 1792, 1795, 2049)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 61, 74, 75, 77, 133, 134, 135, 136, 1671, 1788, 1790, 1792, 1794, 1795, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 76, 137, 1787, 1789, 1793, 1888, 2049, 2050)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 61, 74, 76, 77, 133, 134, 135, 137, 1671, 1787, 1788, 1789, 1790, 1794, 1888, 2050, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 75, 136, 1792, 1793, 1795, 2049, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 124, 125, 1747, 1748, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 123, 1749, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 123, 125, 1747, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 124, 1748, 1749)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 123, 124, 125, 1747, 1748, 1749, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 82, 122, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1833, 1979, 1980, 2144, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1832, 1834, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1980, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 1834, 1979, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1834, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 1979, 1980, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 106, 107, 109, 110, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1676, 2211, 2212, 2213, 2298, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 104, 105, 108, 111, 112, 1648, 1677, 2296, 2297, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 104, 105, 106, 108, 110, 111, 113, 114, 115, 117, 118, 1645, 1646, 1648, 1677, 2213, 2296, 2297, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 107, 109, 112, 116, 1647, 1676, 2211, 2212, 2298, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 105, 106, 107, 109, 110, 112, 114, 115, 116, 117, 1645, 1646, 1647, 1648, 1676, 1677, 2212, 2296, 2297, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 104, 108, 111, 113, 118, 2211, 2213, 2298, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 76, 77, 133, 134, 135, 137, 1671, 1787, 1788, 1790, 1792, 1794, 1888, 2049, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 74, 75, 136, 1789, 1793, 1795, 2050)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 75, 76, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1790, 1792, 1888, 2049, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 77, 1789, 1793, 1794, 1795, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 75, 76, 77, 133, 135, 136, 137, 1787, 1788, 1789, 1790, 1793, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 74, 134, 1671, 1792, 1794, 1795, 1888, 2049)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 124, 125, 1747, 1748, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(122, 123, 1749, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 82, 123, 124, 125, 1747, 1749, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 122, 1748, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 82, 122, 125, 1747, 1748, 1749, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 123, 124, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833, 1834, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1979, 1980, 2144, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1832, 1834, 1980, 2144, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1833, 1979, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1833, 1980, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1834, 1979, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 104, 105, 106, 110, 111, 113, 116, 117, 118, 1645, 1647, 1648, 1676, 1677, 2212, 2213, 2296, 2297, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 103, 107, 108, 109, 112, 114, 115, 1646, 2211, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 107, 108, 109, 114, 116, 118, 1646, 1647, 1677, 2211, 2213, 2296, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 110, 111, 112, 113, 115, 117, 1645, 1648, 1676, 2212, 2297)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 103, 105, 107, 109, 110, 111, 113, 114, 116, 118, 1645, 1646, 1647, 1676, 2211, 2213, 2296, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 104, 106, 108, 112, 115, 117, 1648, 1677, 2212, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 133, 135, 136, 1671, 1788, 1789, 1790, 1792, 1793, 2049, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 76, 77, 134, 137, 1787, 1794, 1795, 1888, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 60, 61, 74, 76, 133, 134, 136, 137, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 75, 77, 135, 1671, 1787, 2050, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 74, 75, 76, 134, 135, 136, 137, 1671, 1787, 1788, 1792, 1795, 2049, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 77, 133, 1789, 1790, 1793, 1794, 1888, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 122, 124, 184, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 82, 123, 125, 183, 185, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 122, 123, 183, 185, 186, 1747, 1748, 1890, 1891, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 124, 125, 184, 1749, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 125, 183, 184, 186, 1747, 1749, 1890, 1891, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 122, 123, 124, 185, 1748, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1832, 1833, 1979, 1980, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1834, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 1834, 1979, 1980, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1834, 1979, 2144, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1980, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 104, 106, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1647, 1648, 1676, 2296, 2298, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 105, 107, 1646, 1677, 2211, 2212, 2213, 2297, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 108, 109, 110, 111, 112, 115, 117, 1647, 1676, 1677, 2211, 2212, 2297, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 107, 113, 114, 116, 118, 1645, 1646, 1648, 2213, 2296, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 104, 105, 106, 107, 108, 111, 112, 113, 114, 115, 118, 1645, 1646, 1648, 1676, 1677, 2212, 2213, 2296, 2297)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 109, 110, 116, 117, 1647, 2211, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 134, 135, 136, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1888, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 77, 133, 137, 1671, 1795, 2049, 2050, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 75, 76, 77, 134, 136, 1671, 1787, 1788, 1789, 1790, 1792, 1794, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 135, 137, 1793, 1795, 1888, 2049, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 61, 77, 133, 136, 137, 1671, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 74, 75, 76, 134, 135, 1787, 2049, 2050)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 122, 124, 125, 186, 1749, 1890, 1891, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 123, 183, 184, 185, 1747, 1748, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 125, 183, 184, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 123, 124, 185, 186)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 122, 124, 125, 183, 184, 185, 1747, 1748, 1749, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 82, 123, 186, 1890, 1891, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1980, 2144, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 1834, 1979, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1832, 1833, 1834, 1980, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1979, 2144, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1832, 1834, 1979, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1833, 1980, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 105, 106, 107, 108, 111, 113, 115, 1645, 1646, 1647, 1676, 1677, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 109, 110, 112, 114, 116, 117, 118, 1648, 2211, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 105, 106, 107, 108, 109, 111, 113, 115, 116, 117, 118, 1646, 1647, 1648, 1676, 2211, 2213, 2296, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 104, 110, 112, 114, 1645, 1677, 2212, 2297, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 105, 107, 108, 109, 110, 111, 113, 114, 118, 1647, 1648, 1677, 2211, 2213, 2297, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(104, 106, 112, 115, 116, 117, 1645, 1646, 1676, 2212, 2296, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 61, 77, 133, 134, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 2049, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 74, 75, 76, 135, 136, 1888, 2050, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 75, 76, 77, 133, 134, 135, 136, 1788, 1789, 1790, 1793, 1794, 1795, 2049, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 74, 137, 1787, 1792, 1888, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 74, 75, 76, 77, 133, 134, 136, 137, 1787, 1788, 1789, 1792, 1888, 2049, 2050, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 61, 135, 1790, 1793, 1794, 1795, 2052, 2262)</t>
+  </si>
+  <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 123, 124, 183, 184, 186, 1748, 1890, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(122, 125, 185, 1747, 1749, 1891, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 82, 122, 124, 183, 184, 185, 186, 1747, 1749, 1890, 1891, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 123, 125, 1748, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 122, 125, 185, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 82, 123, 124, 183, 184, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1.1.1.2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1979, 1980, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1833, 1834, 2144, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1833, 1834, 1979, 1980)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1832, 1979, 1980, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1833, 1834, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1.1.1.2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 104, 105, 106, 107, 108, 109, 110, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1677, 2211, 2213, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 103, 111, 112, 113, 1676, 2212, 2296, 2297, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 104, 107, 109, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1677, 2212, 2213, 2296, 2297, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 105, 106, 108, 110, 1648, 1676, 2211, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 105, 106, 107, 109, 110, 111, 115, 116, 117, 1645, 1647, 1648, 1676, 2213, 2296, 2297, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 108, 112, 113, 114, 118, 1646, 1677, 2211, 2212, 2298, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 74, 75, 134, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 2049, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 61, 76, 77, 133, 135, 136, 1888, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 134, 135, 136, 1788, 1789, 1792, 1793, 1888, 2049, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 137, 1671, 1787, 1790, 1794, 1795, 2050, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 75, 77, 133, 134, 135, 136, 137, 1671, 1787, 1789, 1790, 1792, 1793, 1794, 2049, 2050, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 61, 74, 76, 1788, 1795, 1888, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 82, 122, 123, 125, 183, 184, 186, 1747, 1749, 1890, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 124, 185, 1748, 1891, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 122, 123, 124, 125, 183, 184, 186, 1748, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 185, 1747, 1749, 1890, 1891, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 82, 123, 124, 125, 183, 184, 1748, 1890, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 122, 185, 186, 1747, 1749, 1891, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1979, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1834, 1980, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 1833, 1834, 1979, 1980, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1834, 1979, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 1980, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 107, 108, 110, 111, 112, 113, 114, 115, 116, 1645, 1676, 1677, 2213, 2296, 2298, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(105, 106, 109, 117, 118, 1646, 1647, 1648, 2211, 2212, 2297, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 104, 105, 106, 107, 108, 111, 112, 115, 116, 1645, 1646, 1647, 1648, 1677, 2211, 2212, 2213, 2297, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 109, 110, 113, 114, 117, 118, 1676, 2296, 2298, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 109, 111, 113, 114, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2296, 2297, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 107, 108, 110, 112, 115, 2211, 2212, 2213, 2298, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 74, 75, 133, 1787, 1789, 1790, 1792, 1793, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 76, 77, 134, 135, 136, 137, 1671, 1788, 1794)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 74, 77, 133, 134, 135, 136, 1671, 1787, 1788, 1790, 1794, 1888, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 61, 75, 76, 137, 1789, 1792, 1793, 1795, 2049)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 76, 77, 133, 135, 136, 1671, 1788, 1789, 1790, 1792, 1793, 1888, 2049, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 61, 74, 75, 134, 137, 1787, 1794, 1795, 2050)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 124, 125, 183, 185, 186, 1749, 1890, 1891, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 82, 122, 123, 184, 1747, 1748, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 82, 122, 123, 124, 184, 185, 1747, 1748, 1749, 1891, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 125, 183, 186, 1890, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 123, 183, 184, 185, 186, 1747, 1748, 1749, 1890, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 124, 125, 1891, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1833, 1834, 1979, 2144, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1832, 1980, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1832, 1834, 1980, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1833, 1979, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1832, 1834, 1980, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1833, 1979, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 105, 106, 107, 109, 110, 113, 114, 116, 118, 1645, 1646, 1677, 2211, 2212, 2213, 2296, 2297, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 108, 111, 112, 115, 117, 1647, 1648, 1676, 2298, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 105, 106, 110, 111, 113, 116, 117, 1646, 1647, 1648, 1676, 1677, 2212, 2213, 2296, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(104, 107, 108, 109, 112, 114, 115, 118, 1645, 2211, 2297, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 105, 106, 108, 109, 110, 111, 113, 115, 116, 118, 1645, 1646, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 104, 107, 112, 114, 117, 1647, 1648, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 61, 74, 75, 76, 134, 135, 1671, 1787, 1788, 1789, 1790, 1792, 1795, 2049, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 77, 133, 136, 137, 1793, 1794, 1888, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 61, 74, 75, 77, 134, 136, 1671, 1787, 1789, 1792, 1793, 1795, 1888, 2049, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 76, 133, 135, 137, 1788, 1790, 1794, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 75, 76, 77, 135, 136, 1787, 1788, 1789, 1790, 1792, 1888, 2049, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 74, 133, 134, 137, 1671, 1793, 1794, 1795, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 122, 124, 125, 183, 184, 186, 1747, 1748, 1890, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 82, 123, 185, 1749, 1891, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 82, 122, 123, 125, 183, 185, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 124, 184, 186, 1747, 1748)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 122, 123, 124, 125, 183, 185, 1747, 1890, 1891, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 82, 184, 186, 1748, 1749, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1833, 1834, 1979, 1980, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1832, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1834, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1979, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1834, 1980, 2144, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1979, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 105, 107, 108, 109, 111, 112, 113, 114, 115, 118, 1646, 1647, 1676, 1677, 2211, 2213, 2298, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 106, 110, 116, 117, 1645, 1648, 2212, 2296, 2297, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 106, 107, 108, 109, 110, 111, 112, 114, 116, 117, 118, 1645, 1646, 1647, 1676, 1677, 2296, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 105, 113, 115, 1648, 2211, 2212, 2213, 2297, 2298, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 105, 106, 108, 109, 111, 115, 116, 118, 1645, 1646, 1647, 1676, 2211, 2212, 2213, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 107, 110, 112, 113, 114, 117, 1648, 1677, 2296, 2297, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 133, 134, 135, 137, 1671, 1788, 1789, 1790, 1792, 1793, 1795, 1888, 2049, 2050, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 74, 75, 76, 77, 136, 1787, 1794, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 74, 75, 133, 134, 135, 136, 137, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 76, 77, 1671, 1787, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 61, 74, 76, 77, 134, 135, 136, 137, 1671, 1787, 1793, 1795, 1888, 2049, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 75, 133, 1788, 1789, 1790, 1792, 1794, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 122, 183, 184, 185, 186, 1747, 1748, 1749, 1891, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 82, 123, 124, 125, 1890, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 123, 124, 125, 183, 1748, 1749, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 122, 184, 185, 186, 1747, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 82, 122, 124, 183, 184, 1747, 1748, 1890, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 123, 125, 185, 186, 1749, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1833, 1979, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1832, 1834, 1980, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1833, 1834, 1980, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1979, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1834, 1979, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1833, 1980, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 106, 110, 111, 113, 116, 117, 118, 1645, 1646, 1647, 1676, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 105, 107, 108, 109, 112, 114, 115, 1648, 1677, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 105, 107, 108, 109, 110, 111, 112, 113, 116, 1645, 1648, 1677, 2211, 2213, 2296, 2297, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(104, 106, 114, 115, 117, 118, 1646, 1647, 1676, 2212, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 105, 106, 108, 109, 110, 111, 112, 113, 115, 117, 1645, 1646, 1647, 1648, 1676, 2211, 2297, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 107, 114, 116, 118, 1677, 2212, 2213, 2296, 2298, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 75, 76, 77, 133, 135, 137, 1671, 1787, 1788, 1789, 1790, 1793, 1794, 2049, 2050)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 134, 136, 1792, 1795, 1888, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 61, 76, 133, 134, 137, 1671, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 74, 75, 77, 135, 136, 1787, 2049)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 76, 77, 134, 137, 1671, 1787, 1789, 1790, 1795, 1888, 2049, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 75, 133, 135, 136, 1788, 1792, 1793, 1794, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 124, 1747, 1748, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(82, 123, 125, 1749, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 122, 123, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 82, 124)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 82, 122, 124, 1747, 1749, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 123, 125, 1748)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1832, 1834, 1979, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1833, 1980)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1833, 1834, 1980, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1979)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1979, 1980, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1834, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 104, 105, 106, 107, 108, 110, 113, 115, 116, 118, 1645, 1646, 1647, 1676, 2211, 2212, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 109, 111, 112, 114, 117, 1648, 1677, 2213, 2296, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 105, 106, 107, 108, 110, 111, 112, 113, 114, 117, 118, 1646, 1647, 1648, 1677, 2212, 2296, 2297, 2298, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 109, 115, 116, 1645, 1676, 2211, 2213, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 106, 108, 109, 112, 114, 115, 116, 118, 1645, 1647, 1677, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 105, 107, 110, 111, 113, 117, 1646, 1648, 1676, 2211, 2212)</t>
+    <t xml:space="preserve">c(78, 79, 81, 82, 122, 123, 125, 183, 186, 1748, 1749, 1890, 1891, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 124, 184, 185, 1747, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 122, 183, 184, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 123, 124, 125, 185, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 82, 122, 124, 125, 184, 185, 186, 1747, 1749, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 123, 183, 1748, 1890, 1891, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1979, 1980, 2144, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1979, 1980, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1979, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 106, 107, 108, 111, 113, 114, 116, 117, 1645, 1646, 1647, 1676, 1677, 2212, 2213, 2296, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 104, 105, 109, 110, 112, 115, 118, 1648, 2211, 2297, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 105, 106, 107, 108, 109, 110, 114, 115, 116, 1645, 1646, 1648, 1677, 2211, 2212, 2213, 2296, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 111, 112, 113, 117, 118, 1647, 1676, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 104, 105, 106, 107, 109, 111, 112, 113, 114, 116, 118, 1645, 1647, 1648, 2212, 2213, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 108, 110, 115, 117, 1646, 1676, 1677, 2211, 2296, 2297, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 61, 74, 75, 76, 133, 135, 136, 137, 1788, 1789, 1790, 1792, 1794, 1888, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 77, 134, 1787, 1793, 1795, 2049, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 61, 76, 133, 136, 137, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 74, 75, 77, 134, 135, 1787, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 61, 74, 75, 76, 77, 1787, 1789, 1792, 1793, 1794, 1888, 2049, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 133, 134, 135, 136, 137, 1788, 1790, 1795, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 122, 123, 125, 184, 185, 186, 1890, 1891, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 82, 124, 183, 1747, 1748, 1749, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 124, 183, 184, 185, 186, 1747, 1749, 1890, 1891, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 82, 122, 123, 125, 1748, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 82, 122, 123, 124, 125, 183, 185, 1749, 1890, 1891, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 184, 186, 1747, 1748, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1979, 1980, 2144, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1979, 1980, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1979, 1980, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 106, 108, 109, 110, 111, 113, 114, 115, 116, 117, 1646, 1647, 1648, 1676, 2296, 2298, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(105, 107, 112, 118, 1645, 1677, 2211, 2212, 2213, 2297, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 104, 107, 109, 110, 112, 113, 114, 115, 116, 118, 1645, 1646, 1676, 1677, 2212, 2213, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 105, 106, 108, 111, 117, 1647, 1648, 2211, 2296, 2297)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 106, 109, 110, 112, 115, 116, 117, 118, 1645, 1646, 1647, 1677, 2211, 2213, 2297, 2298, 2299, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 105, 107, 108, 111, 113, 114, 1648, 1676, 2212, 2296, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 60, 61, 74, 76, 77, 1671, 2049, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 75, 1888, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 75, 76, 77, 1671, 1888, 2050, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 74, 2049, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 122, 124, 125, 1747, 1748, 1749, 1890, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 123, 1891, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 124, 125, 1747, 1748, 1749, 1890, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 82, 122, 123, 1891, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 122, 123, 124, 125, 1747, 1748, 1890, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 82, 1749, 1891, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1832, 1833, 1834, 1980, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1979, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1832, 1833, 1980, 2144, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1834, 1979, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1832, 1834, 1979, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1833, 1980, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 118, 1676, 1677, 2213, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 2211, 2212, 2296, 2297)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 118, 1676, 1677, 2211, 2212, 2296, 2297, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 2213, 2298, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 118, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 74, 75, 76, 77, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 1671, 1888, 2049, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 61, 74, 75, 76, 77, 1671, 1888, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 2049, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 61, 74, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 75, 76, 77)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 122, 124, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 82, 123, 125, 1747)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 124, 125, 1747, 1749, 1891, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(122, 123, 1748, 1890, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 82, 122, 123, 124, 1749, 1890, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 125, 1747, 1748, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1833, 1834, 1979, 1980, 2144, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1832, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1979, 2144, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1834, 1980, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1833, 1834, 1979, 1980, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1832, 2144, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 1677, 2212, 2296, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 1676, 2211, 2213, 2297, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 118, 1676, 2211, 2212, 2213, 2296, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 1677, 2297, 2298, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 118, 1677, 2213, 2296, 2297, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1676, 2211, 2212, 2298, 2299, 2323)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 59, 60, 74, 75, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1794, 1888, 2049, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 61, 76, 77, 133, 1792, 1793, 1795, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 74, 77, 133, 134, 136, 1671, 1788, 1789, 1790, 1792, 1795, 1888, 2049, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 75, 76, 135, 137, 1787, 1793, 1794, 2050, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 75, 77, 134, 135, 1671, 1787, 1788, 1789, 1790, 1792, 1794, 1795, 1888, 2049, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 74, 76, 133, 136, 137, 1793, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 1747, 1748, 1749, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(122, 123, 124, 125, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 123, 125, 1749, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 122, 124, 1747, 1748)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 123, 124, 1747, 1749, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 125, 1748, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1834, 1979, 1980, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1833, 1834, 1979, 1980, 2144, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1832, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 1979, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1834, 1980, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 104, 105, 106, 107, 110, 111, 112, 113, 114, 115, 117, 1645, 1647, 1648, 1676, 1677, 2213, 2297, 2298, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 108, 109, 116, 118, 1646, 2211, 2212, 2296, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 112, 114, 115, 117, 1645, 1646, 1647, 1648, 1676, 1677, 2213, 2296, 2297, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 107, 108, 109, 110, 111, 113, 116, 118, 2211, 2212, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 106, 107, 108, 109, 112, 113, 114, 116, 118, 1645, 1647, 1676, 1677, 2212, 2213, 2296, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 105, 110, 111, 115, 117, 1646, 1648, 2211, 2297, 2298, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 61, 74, 76, 77, 133, 134, 135, 136, 1671, 1787, 1788, 1789, 1790, 1888, 2049, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 75, 137, 1792, 1793, 1794, 1795, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 61, 74, 75, 77, 133, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 2049, 2050, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 76, 134, 135, 1795, 1888, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 61, 74, 75, 76, 77, 135, 136, 137, 1671, 1788, 1789, 1790, 1793, 1888, 2049, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 133, 134, 1787, 1792, 1794, 1795, 2050, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 82, 122, 124, 183, 186, 1748, 1749, 1890, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 123, 125, 184, 185, 1747, 1891, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 123, 125, 183, 185, 186, 1749, 1890, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 124, 184, 1747, 1748, 1891, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 82, 123, 124, 183, 184, 185, 1747, 1749, 1890, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 122, 125, 186, 1748, 1891, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 1834, 1980, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1979, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1834, 1980, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1834, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1833, 1979, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 103, 104, 105, 108, 109, 110, 111, 112, 114, 116, 118, 1645, 1646, 1647, 1676, 1677, 2212, 2213, 2296, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 106, 107, 113, 115, 117, 1648, 2211, 2297, 2298, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 105, 106, 107, 108, 109, 111, 112, 113, 114, 118, 1646, 1648, 1677, 2212, 2213, 2296, 2297, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 110, 115, 116, 117, 1645, 1647, 1676, 2211, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 105, 106, 109, 112, 113, 114, 117, 118, 1645, 1646, 1648, 1676, 1677, 2211, 2212, 2296, 2297, 2298, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 107, 108, 110, 111, 115, 116, 1647, 2213, 2323)</t>
+    <t xml:space="preserve">c(58, 59, 61, 74, 75, 77, 1671, 1888, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 60, 76, 2049, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 61, 74, 75, 76, 77, 2049, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 1671, 1888, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 76, 77, 1671, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 74, 75, 1888, 2049, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 123, 124, 125, 1749, 1890, 1891, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 1747, 1748, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 122, 1748, 1749, 1890, 1891, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(82, 123, 124, 125, 1747, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 82, 122, 124, 125, 1747, 1748, 1749, 1891, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 123, 1890, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1832, 1833, 1980, 2144, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1834, 1979, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1834, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1979, 1980, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1832, 1833, 1834, 1979, 1980, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 2212, 2213, 2296, 2297, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1677, 2211, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 1677, 2211, 2212, 2213, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 1676, 2296, 2297, 2298, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 1677, 2211, 2212, 2213, 2296, 2298, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 118, 1676, 2297, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 74, 75, 77, 1671, 1888, 2050, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 61, 76, 2049, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 74, 75, 76, 1671, 1888, 2049, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 77, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 75, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 61, 74, 76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 122, 123, 124, 125, 1748, 1749, 1890, 1891, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 82, 1747, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 123, 125, 1747, 1749, 1890, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 122, 124, 1748, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 82, 122, 124, 1748, 1749, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 123, 125, 1747, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1832, 1979, 1980, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1833, 1834, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1833, 1979, 1980, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1834, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1832, 1833, 1834, 1979, 1980, 2144, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 118, 1676, 1677, 2211, 2212, 2297, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 2213, 2296, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 118, 1676, 1677, 2211, 2297, 2298, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 2212, 2213, 2296, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 1676, 2211, 2296, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 118, 1677, 2212, 2213, 2298)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 59, 61, 74, 75, 76, 77, 133, 134, 135, 136, 1671, 1787, 1789, 1790, 1793, 1794, 1795, 2049, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 137, 1788, 1792, 1888, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 77, 133, 134, 135, 136, 137, 1671, 1788, 1789, 1792, 1793, 1794, 1795, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 74, 75, 76, 1787, 1790, 1888, 2049, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 75, 76, 77, 133, 134, 1671, 1787, 1790, 1792, 1793, 1888, 2049, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 74, 135, 136, 137, 1788, 1789, 1794, 1795, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + ADF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 122, 123, 124, 125, 183, 184, 185, 186, 1747, 1748, 1890, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 1749, 1891, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 124, 125, 183, 184, 1748, 1749, 1890, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(82, 122, 123, 185, 186, 1747, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 123, 125, 183, 184, 185, 186, 1749, 1891, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 82, 122, 124, 1747, 1748, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1979, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1833, 1834, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1979, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1833, 1834, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1833, 1834, 1980, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1979, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 106, 108, 110, 112, 114, 115, 116, 118, 1645, 1646, 1676, 2212, 2213, 2296, 2297, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(105, 107, 109, 111, 113, 117, 1647, 1648, 1677, 2211, 2298, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 103, 108, 109, 111, 112, 114, 117, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2297, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 104, 105, 106, 107, 110, 113, 115, 116, 118, 2296, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 115, 1646, 1647, 1648, 1676, 1677, 2213, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 113, 114, 116, 117, 118, 1645, 2211, 2212, 2296, 2297, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 74, 76, 134, 135, 136, 137, 1789, 1790, 1792, 1793, 1795, 1888, 2049, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 75, 77, 133, 1787, 1788, 1794, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 61, 75, 77, 133, 136, 137, 1788, 1789, 1790, 1794, 1795, 1888, 2049, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 74, 76, 134, 135, 1787, 1792, 1793, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 75, 76, 77, 133, 134, 135, 136, 137, 1790, 1793, 1794, 1888, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 74, 1787, 1788, 1789, 1792, 1795, 2049, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 123, 125, 183, 185, 186, 1747, 1890, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 124, 184, 1748, 1749, 1891, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 82, 123, 124, 183, 184, 185, 186, 1748, 1749, 1891, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 122, 125, 1747, 1890, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 122, 123, 124, 125, 183, 185, 186, 1890, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 82, 184, 1747, 1748, 1749, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1979, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1980, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1980, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1979, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1979, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 103, 105, 106, 107, 108, 112, 114, 116, 1645, 1646, 1647, 1676, 1677, 2211, 2212, 2296, 2297, 2298, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 104, 109, 110, 111, 113, 115, 117, 118, 1648, 2213, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 105, 106, 107, 108, 109, 110, 112, 113, 114, 115, 116, 118, 1646, 1647, 1677, 2211, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(104, 111, 117, 1645, 1648, 1676, 2212, 2213, 2296, 2297, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 105, 107, 108, 110, 111, 112, 113, 114, 115, 116, 1645, 1647, 1648, 1676, 1677, 2212, 2213, 2296, 2297, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 106, 109, 117, 118, 1646, 2211, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 61, 75, 76, 133, 134, 135, 136, 1788, 1789, 1790, 1793, 1794, 1888, 2049, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 74, 77, 137, 1787, 1792, 1795, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 61, 74, 75, 76, 133, 136, 137, 1788, 1789, 1790, 1792, 1793, 1795, 1888, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 77, 134, 135, 1787, 1794, 2049, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 74, 75, 133, 134, 136, 137, 1787, 1790, 1792, 1793, 1794, 1795, 1888, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 61, 76, 77, 135, 1788, 1789, 2049, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + CP_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 124, 185, 186, 1747, 1749, 1890, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 125, 183, 184, 1748, 1891, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 82, 123, 124, 125, 184, 186, 1747, 1891, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 122, 183, 185, 1748, 1749, 1890, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 124, 125, 183, 185, 186, 1747, 1749, 1890, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 122, 123, 184, 1748, 1891, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1980, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1979)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1979, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1980)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1979, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1980, 2144, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 105, 106, 108, 109, 113, 114, 115, 116, 117, 1645, 1647, 1676, 1677, 2211, 2213, 2297, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 107, 110, 111, 112, 118, 1646, 1648, 2212, 2296, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 109, 110, 112, 113, 116, 117, 1647, 1677, 2211, 2212, 2213, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(107, 108, 111, 114, 115, 118, 1645, 1646, 1648, 1676, 2296, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 105, 106, 107, 108, 109, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 2211, 2212, 2297, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 104, 110, 111, 112, 1676, 1677, 2213, 2296, 2322, 2323)</t>
+    <t xml:space="preserve">c(58, 60, 75, 76, 77, 2049, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 74, 1888, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 74, 75, 76, 77, 1888, 2049, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 2050, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 74, 77, 1888, 2049, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 75, 76, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 125, 1747, 1748, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 124, 1749, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 122, 123, 124, 125, 1747, 1748, 1890, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 82, 1749, 1891, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 122, 123, 124, 125, 1747, 1749, 1890, 1891, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 1748, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1979, 1980, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1979, 1980, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1980, 2144, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1979, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 118, 1676, 1677, 2211, 2212, 2213, 2298, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 2296, 2297, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 118, 2211, 2212, 2213, 2296, 2297, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 1676, 1677, 2298, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 118, 1676, 2211, 2212, 2296, 2297, 2298, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 1677, 2213, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 74, 77, 1888, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 61, 75, 76, 2049)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 74, 75, 77, 2049, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 76, 1888, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 61, 74, 75, 76, 2049, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 77, 1888, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 82, 122, 124, 125, 1747, 1748, 1890, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 123, 1749, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 123, 124, 125, 1749, 1890, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(82, 122, 1747, 1748, 1891, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 124, 125, 1747, 1890, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(82, 122, 123, 1748, 1749, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1979, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1980, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1980, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1979, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1979, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1980, 2144, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 118, 1677, 2211, 2213, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 1676, 2212, 2296, 2297)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 1676, 2211, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 118, 1677, 2212, 2213, 2296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 118, 2211, 2212, 2296, 2297, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 1676, 1677, 2213, 2299, 2321)</t>
   </si>
 </sst>
 </file>
@@ -2291,19 +2717,19 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="s">
         <v>62</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="s">
-        <v>63</v>
       </c>
       <c r="N17" t="n">
         <v>14</v>
       </c>
       <c r="O17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P17" t="n">
         <v>8</v>
@@ -2347,19 +2773,19 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
       </c>
       <c r="M18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N18" t="n">
         <v>14</v>
       </c>
       <c r="O18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P18" t="n">
         <v>8</v>
@@ -2403,19 +2829,19 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
       </c>
       <c r="M19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N19" t="n">
         <v>14</v>
       </c>
       <c r="O19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P19" t="n">
         <v>8</v>
@@ -2450,7 +2876,7 @@
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -2465,13 +2891,13 @@
         <v>1</v>
       </c>
       <c r="M20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N20" t="n">
         <v>9</v>
       </c>
       <c r="O20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P20" t="n">
         <v>5</v>
@@ -2506,7 +2932,7 @@
         <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -2521,13 +2947,13 @@
         <v>2</v>
       </c>
       <c r="M21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N21" t="n">
         <v>9</v>
       </c>
       <c r="O21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P21" t="n">
         <v>5</v>
@@ -2562,7 +2988,7 @@
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -2577,13 +3003,13 @@
         <v>3</v>
       </c>
       <c r="M22" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N22" t="n">
         <v>9</v>
       </c>
       <c r="O22" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P22" t="n">
         <v>5</v>
@@ -2618,7 +3044,7 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -2627,19 +3053,19 @@
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
       </c>
       <c r="M23" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N23" t="n">
         <v>23</v>
       </c>
       <c r="O23" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P23" t="n">
         <v>12</v>
@@ -2674,28 +3100,28 @@
         <v>2</v>
       </c>
       <c r="H24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="s">
+        <v>30</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="s">
         <v>76</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="s">
-        <v>62</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" t="s">
-        <v>79</v>
       </c>
       <c r="N24" t="n">
         <v>23</v>
       </c>
       <c r="O24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P24" t="n">
         <v>12</v>
@@ -2730,7 +3156,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -2739,19 +3165,19 @@
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
       </c>
       <c r="M25" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N25" t="n">
         <v>23</v>
       </c>
       <c r="O25" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="P25" t="n">
         <v>12</v>
@@ -2795,19 +3221,19 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
       </c>
       <c r="M26" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N26" t="n">
         <v>20</v>
       </c>
       <c r="O26" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P26" t="n">
         <v>10</v>
@@ -2851,19 +3277,19 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
+        <v>80</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="s">
         <v>83</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="s">
-        <v>86</v>
       </c>
       <c r="N27" t="n">
         <v>20</v>
       </c>
       <c r="O27" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P27" t="n">
         <v>10</v>
@@ -2907,19 +3333,19 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
       </c>
       <c r="M28" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N28" t="n">
         <v>20</v>
       </c>
       <c r="O28" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P28" t="n">
         <v>10</v>
@@ -2963,19 +3389,19 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N29" t="n">
         <v>14</v>
       </c>
       <c r="O29" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P29" t="n">
         <v>8</v>
@@ -3019,19 +3445,19 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
+        <v>87</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" t="s">
         <v>90</v>
-      </c>
-      <c r="L30" t="n">
-        <v>2</v>
-      </c>
-      <c r="M30" t="s">
-        <v>93</v>
       </c>
       <c r="N30" t="n">
         <v>14</v>
       </c>
       <c r="O30" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="P30" t="n">
         <v>8</v>
@@ -3075,19 +3501,19 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L31" t="n">
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="N31" t="n">
         <v>14</v>
       </c>
       <c r="O31" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P31" t="n">
         <v>8</v>
@@ -3131,19 +3557,19 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="N32" t="n">
         <v>9</v>
       </c>
       <c r="O32" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P32" t="n">
         <v>5</v>
@@ -3187,19 +3613,19 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
       </c>
       <c r="M33" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="N33" t="n">
         <v>9</v>
       </c>
       <c r="O33" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P33" t="n">
         <v>5</v>
@@ -3243,19 +3669,19 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
       </c>
       <c r="M34" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N34" t="n">
         <v>9</v>
       </c>
       <c r="O34" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="P34" t="n">
         <v>5</v>
@@ -3299,19 +3725,19 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="N35" t="n">
         <v>23</v>
       </c>
       <c r="O35" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P35" t="n">
         <v>12</v>
@@ -3355,19 +3781,19 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
       </c>
       <c r="M36" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="N36" t="n">
         <v>23</v>
       </c>
       <c r="O36" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P36" t="n">
         <v>12</v>
@@ -3411,19 +3837,19 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L37" t="n">
         <v>3</v>
       </c>
       <c r="M37" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N37" t="n">
         <v>23</v>
       </c>
       <c r="O37" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P37" t="n">
         <v>12</v>
@@ -3467,19 +3893,19 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="N38" t="n">
         <v>20</v>
       </c>
       <c r="O38" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P38" t="n">
         <v>10</v>
@@ -3523,19 +3949,19 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
       </c>
       <c r="M39" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="N39" t="n">
         <v>20</v>
       </c>
       <c r="O39" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P39" t="n">
         <v>10</v>
@@ -3579,19 +4005,19 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
       </c>
       <c r="M40" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="N40" t="n">
         <v>20</v>
       </c>
       <c r="O40" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P40" t="n">
         <v>10</v>
@@ -3635,19 +4061,19 @@
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
       </c>
       <c r="M41" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N41" t="n">
         <v>14</v>
       </c>
       <c r="O41" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="P41" t="n">
         <v>8</v>
@@ -3691,19 +4117,19 @@
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
       </c>
       <c r="M42" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N42" t="n">
         <v>14</v>
       </c>
       <c r="O42" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="P42" t="n">
         <v>8</v>
@@ -3747,19 +4173,19 @@
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="L43" t="n">
         <v>3</v>
       </c>
       <c r="M43" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="N43" t="n">
         <v>14</v>
       </c>
       <c r="O43" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="P43" t="n">
         <v>8</v>
@@ -3794,7 +4220,7 @@
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I44" t="n">
         <v>2</v>
@@ -3803,19 +4229,19 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N44" t="n">
         <v>9</v>
       </c>
       <c r="O44" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="P44" t="n">
         <v>5</v>
@@ -3850,7 +4276,7 @@
         <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
@@ -3859,19 +4285,19 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
       </c>
       <c r="M45" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="N45" t="n">
         <v>9</v>
       </c>
       <c r="O45" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="P45" t="n">
         <v>5</v>
@@ -3906,7 +4332,7 @@
         <v>2</v>
       </c>
       <c r="H46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I46" t="n">
         <v>2</v>
@@ -3915,19 +4341,19 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
       </c>
       <c r="M46" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="N46" t="n">
         <v>9</v>
       </c>
       <c r="O46" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="P46" t="n">
         <v>5</v>
@@ -3962,7 +4388,7 @@
         <v>2</v>
       </c>
       <c r="H47" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
@@ -3971,19 +4397,19 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="N47" t="n">
         <v>23</v>
       </c>
       <c r="O47" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="P47" t="n">
         <v>12</v>
@@ -4018,7 +4444,7 @@
         <v>2</v>
       </c>
       <c r="H48" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
@@ -4027,19 +4453,19 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
       </c>
       <c r="M48" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="N48" t="n">
         <v>23</v>
       </c>
       <c r="O48" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="P48" t="n">
         <v>12</v>
@@ -4074,7 +4500,7 @@
         <v>2</v>
       </c>
       <c r="H49" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I49" t="n">
         <v>2</v>
@@ -4083,19 +4509,19 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="L49" t="n">
         <v>3</v>
       </c>
       <c r="M49" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N49" t="n">
         <v>23</v>
       </c>
       <c r="O49" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="P49" t="n">
         <v>12</v>
@@ -4139,19 +4565,19 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N50" t="n">
         <v>20</v>
       </c>
       <c r="O50" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="P50" t="n">
         <v>10</v>
@@ -4195,19 +4621,19 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
       </c>
       <c r="M51" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="N51" t="n">
         <v>20</v>
       </c>
       <c r="O51" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="P51" t="n">
         <v>10</v>
@@ -4251,19 +4677,19 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
       </c>
       <c r="M52" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N52" t="n">
         <v>20</v>
       </c>
       <c r="O52" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="P52" t="n">
         <v>10</v>
@@ -4307,19 +4733,19 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="N53" t="n">
         <v>14</v>
       </c>
       <c r="O53" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="P53" t="n">
         <v>8</v>
@@ -4363,19 +4789,19 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
       </c>
       <c r="M54" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N54" t="n">
         <v>14</v>
       </c>
       <c r="O54" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="P54" t="n">
         <v>8</v>
@@ -4419,19 +4845,19 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
       </c>
       <c r="M55" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="N55" t="n">
         <v>14</v>
       </c>
       <c r="O55" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="P55" t="n">
         <v>8</v>
@@ -4475,19 +4901,19 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="N56" t="n">
         <v>9</v>
       </c>
       <c r="O56" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="P56" t="n">
         <v>5</v>
@@ -4531,19 +4957,19 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
       </c>
       <c r="M57" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N57" t="n">
         <v>9</v>
       </c>
       <c r="O57" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P57" t="n">
         <v>5</v>
@@ -4587,19 +5013,19 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
       </c>
       <c r="M58" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="N58" t="n">
         <v>9</v>
       </c>
       <c r="O58" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="P58" t="n">
         <v>5</v>
@@ -4643,19 +5069,19 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N59" t="n">
         <v>23</v>
       </c>
       <c r="O59" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="P59" t="n">
         <v>12</v>
@@ -4699,19 +5125,19 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
       </c>
       <c r="M60" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N60" t="n">
         <v>23</v>
       </c>
       <c r="O60" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="P60" t="n">
         <v>12</v>
@@ -4755,19 +5181,19 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
       </c>
       <c r="M61" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N61" t="n">
         <v>23</v>
       </c>
       <c r="O61" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="P61" t="n">
         <v>12</v>
@@ -4811,19 +5237,19 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="N62" t="n">
         <v>20</v>
       </c>
       <c r="O62" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P62" t="n">
         <v>10</v>
@@ -4867,19 +5293,19 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
       </c>
       <c r="M63" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N63" t="n">
         <v>20</v>
       </c>
       <c r="O63" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P63" t="n">
         <v>10</v>
@@ -4923,19 +5349,19 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
       </c>
       <c r="M64" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="N64" t="n">
         <v>20</v>
       </c>
       <c r="O64" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P64" t="n">
         <v>10</v>
@@ -4979,19 +5405,19 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="N65" t="n">
         <v>14</v>
       </c>
       <c r="O65" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="P65" t="n">
         <v>8</v>
@@ -5035,19 +5461,19 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
       </c>
       <c r="M66" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="N66" t="n">
         <v>14</v>
       </c>
       <c r="O66" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="P66" t="n">
         <v>8</v>
@@ -5091,19 +5517,19 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
+        <v>137</v>
+      </c>
+      <c r="L67" t="n">
+        <v>3</v>
+      </c>
+      <c r="M67" t="s">
         <v>166</v>
-      </c>
-      <c r="L67" t="n">
-        <v>3</v>
-      </c>
-      <c r="M67" t="s">
-        <v>171</v>
       </c>
       <c r="N67" t="n">
         <v>14</v>
       </c>
       <c r="O67" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="P67" t="n">
         <v>8</v>
@@ -5138,7 +5564,7 @@
         <v>2</v>
       </c>
       <c r="H68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I68" t="n">
         <v>3</v>
@@ -5147,19 +5573,19 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="N68" t="n">
         <v>9</v>
       </c>
       <c r="O68" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="P68" t="n">
         <v>5</v>
@@ -5194,7 +5620,7 @@
         <v>2</v>
       </c>
       <c r="H69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I69" t="n">
         <v>3</v>
@@ -5203,19 +5629,19 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
       </c>
       <c r="M69" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="N69" t="n">
         <v>9</v>
       </c>
       <c r="O69" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="P69" t="n">
         <v>5</v>
@@ -5250,7 +5676,7 @@
         <v>2</v>
       </c>
       <c r="H70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I70" t="n">
         <v>3</v>
@@ -5259,19 +5685,19 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
       </c>
       <c r="M70" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="N70" t="n">
         <v>9</v>
       </c>
       <c r="O70" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="P70" t="n">
         <v>5</v>
@@ -5306,7 +5732,7 @@
         <v>2</v>
       </c>
       <c r="H71" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I71" t="n">
         <v>3</v>
@@ -5315,19 +5741,19 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="N71" t="n">
         <v>23</v>
       </c>
       <c r="O71" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="P71" t="n">
         <v>12</v>
@@ -5362,7 +5788,7 @@
         <v>2</v>
       </c>
       <c r="H72" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I72" t="n">
         <v>3</v>
@@ -5371,19 +5797,19 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
       </c>
       <c r="M72" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="N72" t="n">
         <v>23</v>
       </c>
       <c r="O72" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="P72" t="n">
         <v>12</v>
@@ -5418,7 +5844,7 @@
         <v>2</v>
       </c>
       <c r="H73" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I73" t="n">
         <v>3</v>
@@ -5427,19 +5853,19 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
       </c>
       <c r="M73" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="N73" t="n">
         <v>23</v>
       </c>
       <c r="O73" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="P73" t="n">
         <v>12</v>
@@ -5483,19 +5909,19 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="N74" t="n">
         <v>20</v>
       </c>
       <c r="O74" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="P74" t="n">
         <v>10</v>
@@ -5539,19 +5965,19 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
       </c>
       <c r="M75" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="N75" t="n">
         <v>20</v>
       </c>
       <c r="O75" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="P75" t="n">
         <v>10</v>
@@ -5595,19 +6021,19 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
       </c>
       <c r="M76" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="N76" t="n">
         <v>20</v>
       </c>
       <c r="O76" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="P76" t="n">
         <v>10</v>
@@ -5651,28 +6077,28 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="N77" t="n">
         <v>10</v>
       </c>
       <c r="O77" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="P77" t="n">
         <v>5</v>
       </c>
       <c r="Q77" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="R77" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="78">
@@ -5707,28 +6133,28 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="N78" t="n">
         <v>10</v>
       </c>
       <c r="O78" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="P78" t="n">
         <v>5</v>
       </c>
       <c r="Q78" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="R78" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="79">
@@ -5763,28 +6189,28 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="N79" t="n">
         <v>10</v>
       </c>
       <c r="O79" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="P79" t="n">
         <v>5</v>
       </c>
       <c r="Q79" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="R79" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="80">
@@ -5819,19 +6245,19 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="N80" t="n">
         <v>9</v>
       </c>
       <c r="O80" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="P80" t="n">
         <v>5</v>
@@ -5875,19 +6301,19 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
       </c>
       <c r="M81" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="N81" t="n">
         <v>9</v>
       </c>
       <c r="O81" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="P81" t="n">
         <v>5</v>
@@ -5931,19 +6357,19 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
       </c>
       <c r="M82" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N82" t="n">
         <v>9</v>
       </c>
       <c r="O82" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="P82" t="n">
         <v>5</v>
@@ -5987,19 +6413,19 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="N83" t="n">
         <v>23</v>
       </c>
       <c r="O83" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="P83" t="n">
         <v>12</v>
@@ -6043,19 +6469,19 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
       </c>
       <c r="M84" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="N84" t="n">
         <v>23</v>
       </c>
       <c r="O84" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="P84" t="n">
         <v>12</v>
@@ -6099,19 +6525,19 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
       </c>
       <c r="M85" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N85" t="n">
         <v>23</v>
       </c>
       <c r="O85" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="P85" t="n">
         <v>12</v>
@@ -6155,19 +6581,19 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
       <c r="M86" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="N86" t="n">
         <v>20</v>
       </c>
       <c r="O86" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="P86" t="n">
         <v>10</v>
@@ -6211,19 +6637,19 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
       </c>
       <c r="M87" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="N87" t="n">
         <v>20</v>
       </c>
       <c r="O87" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="P87" t="n">
         <v>10</v>
@@ -6267,19 +6693,19 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
       </c>
       <c r="M88" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="N88" t="n">
         <v>20</v>
       </c>
       <c r="O88" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="P88" t="n">
         <v>10</v>
@@ -6323,28 +6749,28 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="N89" t="n">
         <v>10</v>
       </c>
       <c r="O89" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="P89" t="n">
         <v>5</v>
       </c>
       <c r="Q89" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="R89" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="90">
@@ -6379,28 +6805,28 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="N90" t="n">
         <v>10</v>
       </c>
       <c r="O90" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="P90" t="n">
         <v>5</v>
       </c>
       <c r="Q90" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="R90" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91">
@@ -6435,28 +6861,28 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="N91" t="n">
         <v>10</v>
       </c>
       <c r="O91" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="P91" t="n">
         <v>5</v>
       </c>
       <c r="Q91" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="R91" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="92">
@@ -6482,7 +6908,7 @@
         <v>2</v>
       </c>
       <c r="H92" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I92" t="n">
         <v>4</v>
@@ -6491,19 +6917,19 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="N92" t="n">
         <v>9</v>
       </c>
       <c r="O92" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="P92" t="n">
         <v>5</v>
@@ -6538,7 +6964,7 @@
         <v>2</v>
       </c>
       <c r="H93" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I93" t="n">
         <v>4</v>
@@ -6547,19 +6973,19 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
       </c>
       <c r="M93" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="N93" t="n">
         <v>9</v>
       </c>
       <c r="O93" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="P93" t="n">
         <v>5</v>
@@ -6594,7 +7020,7 @@
         <v>2</v>
       </c>
       <c r="H94" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I94" t="n">
         <v>4</v>
@@ -6603,19 +7029,19 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
       </c>
       <c r="M94" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="N94" t="n">
         <v>9</v>
       </c>
       <c r="O94" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="P94" t="n">
         <v>5</v>
@@ -6650,7 +7076,7 @@
         <v>2</v>
       </c>
       <c r="H95" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I95" t="n">
         <v>4</v>
@@ -6659,19 +7085,19 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="N95" t="n">
         <v>23</v>
       </c>
       <c r="O95" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="P95" t="n">
         <v>12</v>
@@ -6706,7 +7132,7 @@
         <v>2</v>
       </c>
       <c r="H96" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I96" t="n">
         <v>4</v>
@@ -6715,19 +7141,19 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
       </c>
       <c r="M96" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="N96" t="n">
         <v>23</v>
       </c>
       <c r="O96" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="P96" t="n">
         <v>12</v>
@@ -6762,7 +7188,7 @@
         <v>2</v>
       </c>
       <c r="H97" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I97" t="n">
         <v>4</v>
@@ -6771,19 +7197,19 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
       </c>
       <c r="M97" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="N97" t="n">
         <v>23</v>
       </c>
       <c r="O97" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="P97" t="n">
         <v>12</v>
@@ -6827,19 +7253,19 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="N98" t="n">
         <v>20</v>
       </c>
       <c r="O98" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="P98" t="n">
         <v>10</v>
@@ -6883,19 +7309,19 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
       </c>
       <c r="M99" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="N99" t="n">
         <v>20</v>
       </c>
       <c r="O99" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="P99" t="n">
         <v>10</v>
@@ -6939,19 +7365,19 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
       </c>
       <c r="M100" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="N100" t="n">
         <v>20</v>
       </c>
       <c r="O100" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="P100" t="n">
         <v>10</v>
@@ -6995,19 +7421,19 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="N101" t="n">
         <v>14</v>
       </c>
       <c r="O101" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="P101" t="n">
         <v>8</v>
@@ -7051,19 +7477,19 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
       </c>
       <c r="M102" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="N102" t="n">
         <v>14</v>
       </c>
       <c r="O102" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="P102" t="n">
         <v>8</v>
@@ -7107,19 +7533,19 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
       </c>
       <c r="M103" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="N103" t="n">
         <v>14</v>
       </c>
       <c r="O103" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="P103" t="n">
         <v>8</v>
@@ -7163,19 +7589,19 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="N104" t="n">
         <v>9</v>
       </c>
       <c r="O104" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="P104" t="n">
         <v>5</v>
@@ -7219,19 +7645,19 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
       </c>
       <c r="M105" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N105" t="n">
         <v>9</v>
       </c>
       <c r="O105" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="P105" t="n">
         <v>5</v>
@@ -7275,19 +7701,19 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
       </c>
       <c r="M106" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="N106" t="n">
         <v>9</v>
       </c>
       <c r="O106" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P106" t="n">
         <v>5</v>
@@ -7331,19 +7757,19 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="N107" t="n">
         <v>23</v>
       </c>
       <c r="O107" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="P107" t="n">
         <v>12</v>
@@ -7387,19 +7813,19 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
       </c>
       <c r="M108" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="N108" t="n">
         <v>23</v>
       </c>
       <c r="O108" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="P108" t="n">
         <v>12</v>
@@ -7443,19 +7869,19 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>166</v>
+        <v>236</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
       </c>
       <c r="M109" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="N109" t="n">
         <v>23</v>
       </c>
       <c r="O109" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P109" t="n">
         <v>12</v>
@@ -7499,19 +7925,19 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="N110" t="n">
         <v>20</v>
       </c>
       <c r="O110" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="P110" t="n">
         <v>10</v>
@@ -7555,19 +7981,19 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
       </c>
       <c r="M111" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="N111" t="n">
         <v>20</v>
       </c>
       <c r="O111" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P111" t="n">
         <v>10</v>
@@ -7611,19 +8037,19 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="N112" t="n">
         <v>20</v>
       </c>
       <c r="O112" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="P112" t="n">
         <v>10</v>
@@ -7667,19 +8093,19 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="N113" t="n">
         <v>14</v>
       </c>
       <c r="O113" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="P113" t="n">
         <v>8</v>
@@ -7723,19 +8149,19 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
       </c>
       <c r="M114" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="N114" t="n">
         <v>14</v>
       </c>
       <c r="O114" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="P114" t="n">
         <v>8</v>
@@ -7779,19 +8205,19 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
       </c>
       <c r="M115" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="N115" t="n">
         <v>14</v>
       </c>
       <c r="O115" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="P115" t="n">
         <v>8</v>
@@ -7826,7 +8252,7 @@
         <v>2</v>
       </c>
       <c r="H116" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I116" t="n">
         <v>5</v>
@@ -7835,19 +8261,19 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="N116" t="n">
         <v>9</v>
       </c>
       <c r="O116" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="P116" t="n">
         <v>5</v>
@@ -7882,7 +8308,7 @@
         <v>2</v>
       </c>
       <c r="H117" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I117" t="n">
         <v>5</v>
@@ -7891,19 +8317,19 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
       </c>
       <c r="M117" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="N117" t="n">
         <v>9</v>
       </c>
       <c r="O117" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="P117" t="n">
         <v>5</v>
@@ -7938,7 +8364,7 @@
         <v>2</v>
       </c>
       <c r="H118" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I118" t="n">
         <v>5</v>
@@ -7947,19 +8373,19 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
       </c>
       <c r="M118" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="N118" t="n">
         <v>9</v>
       </c>
       <c r="O118" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="P118" t="n">
         <v>5</v>
@@ -7994,7 +8420,7 @@
         <v>2</v>
       </c>
       <c r="H119" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I119" t="n">
         <v>5</v>
@@ -8003,19 +8429,19 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="N119" t="n">
         <v>23</v>
       </c>
       <c r="O119" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="P119" t="n">
         <v>12</v>
@@ -8050,7 +8476,7 @@
         <v>2</v>
       </c>
       <c r="H120" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I120" t="n">
         <v>5</v>
@@ -8059,19 +8485,19 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
       </c>
       <c r="M120" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="N120" t="n">
         <v>23</v>
       </c>
       <c r="O120" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="P120" t="n">
         <v>12</v>
@@ -8106,7 +8532,7 @@
         <v>2</v>
       </c>
       <c r="H121" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I121" t="n">
         <v>5</v>
@@ -8115,19 +8541,19 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
       </c>
       <c r="M121" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="N121" t="n">
         <v>23</v>
       </c>
       <c r="O121" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="P121" t="n">
         <v>12</v>
@@ -8171,28 +8597,28 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="N122" t="n">
         <v>18</v>
       </c>
       <c r="O122" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="P122" t="n">
         <v>10</v>
       </c>
       <c r="Q122" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="R122" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="123">
@@ -8227,28 +8653,28 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="N123" t="n">
         <v>18</v>
       </c>
       <c r="O123" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="P123" t="n">
         <v>10</v>
       </c>
       <c r="Q123" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="R123" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="124">
@@ -8283,28 +8709,28 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="N124" t="n">
         <v>18</v>
       </c>
       <c r="O124" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="P124" t="n">
         <v>10</v>
       </c>
       <c r="Q124" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="R124" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="125">
@@ -8339,19 +8765,19 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>62</v>
+        <v>287</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="N125" t="n">
         <v>14</v>
       </c>
       <c r="O125" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="P125" t="n">
         <v>8</v>
@@ -8395,19 +8821,19 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>62</v>
+        <v>287</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
       </c>
       <c r="M126" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="N126" t="n">
         <v>14</v>
       </c>
       <c r="O126" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="P126" t="n">
         <v>8</v>
@@ -8451,19 +8877,19 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>62</v>
+        <v>287</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
       </c>
       <c r="M127" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="N127" t="n">
         <v>14</v>
       </c>
       <c r="O127" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="P127" t="n">
         <v>8</v>
@@ -8507,28 +8933,28 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="N128" t="n">
         <v>7</v>
       </c>
       <c r="O128" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="P128" t="n">
         <v>4</v>
       </c>
       <c r="Q128" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="R128" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="129">
@@ -8563,28 +8989,28 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="N129" t="n">
         <v>7</v>
       </c>
       <c r="O129" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="P129" t="n">
         <v>4</v>
       </c>
       <c r="Q129" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="R129" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="130">
@@ -8619,28 +9045,28 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="N130" t="n">
         <v>7</v>
       </c>
       <c r="O130" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="P130" t="n">
         <v>4</v>
       </c>
       <c r="Q130" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="R130" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="131">
@@ -8675,19 +9101,19 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>62</v>
+        <v>287</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="N131" t="n">
         <v>23</v>
       </c>
       <c r="O131" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="P131" t="n">
         <v>12</v>
@@ -8731,19 +9157,19 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>62</v>
+        <v>287</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="N132" t="n">
         <v>23</v>
       </c>
       <c r="O132" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="P132" t="n">
         <v>12</v>
@@ -8787,19 +9213,19 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>62</v>
+        <v>287</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N133" t="n">
         <v>23</v>
       </c>
       <c r="O133" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="P133" t="n">
         <v>12</v>
@@ -8843,28 +9269,28 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>315</v>
+        <v>279</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="N134" t="n">
         <v>18</v>
       </c>
       <c r="O134" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="P134" t="n">
         <v>10</v>
       </c>
       <c r="Q134" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="R134" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="135">
@@ -8899,28 +9325,28 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>315</v>
+        <v>279</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="N135" t="n">
         <v>18</v>
       </c>
       <c r="O135" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="P135" t="n">
         <v>10</v>
       </c>
       <c r="Q135" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="R135" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="136">
@@ -8955,28 +9381,28 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>315</v>
+        <v>279</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="N136" t="n">
         <v>18</v>
       </c>
       <c r="O136" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="P136" t="n">
         <v>10</v>
       </c>
       <c r="Q136" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="R136" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="137">
@@ -9011,19 +9437,19 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>322</v>
+        <v>287</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="N137" t="n">
         <v>14</v>
       </c>
       <c r="O137" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="P137" t="n">
         <v>8</v>
@@ -9067,19 +9493,19 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>322</v>
+        <v>287</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="N138" t="n">
         <v>14</v>
       </c>
       <c r="O138" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="P138" t="n">
         <v>8</v>
@@ -9123,19 +9549,19 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>322</v>
+        <v>287</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="N139" t="n">
         <v>14</v>
       </c>
       <c r="O139" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="P139" t="n">
         <v>8</v>
@@ -9170,7 +9596,7 @@
         <v>2</v>
       </c>
       <c r="H140" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I140" t="n">
         <v>6</v>
@@ -9179,28 +9605,28 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>315</v>
+        <v>279</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="N140" t="n">
         <v>7</v>
       </c>
       <c r="O140" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="P140" t="n">
         <v>4</v>
       </c>
       <c r="Q140" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="R140" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="141">
@@ -9226,7 +9652,7 @@
         <v>2</v>
       </c>
       <c r="H141" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I141" t="n">
         <v>6</v>
@@ -9235,28 +9661,28 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>315</v>
+        <v>279</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="N141" t="n">
         <v>7</v>
       </c>
       <c r="O141" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="P141" t="n">
         <v>4</v>
       </c>
       <c r="Q141" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="R141" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="142">
@@ -9282,7 +9708,7 @@
         <v>2</v>
       </c>
       <c r="H142" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I142" t="n">
         <v>6</v>
@@ -9291,28 +9717,28 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>315</v>
+        <v>279</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="N142" t="n">
         <v>7</v>
       </c>
       <c r="O142" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="P142" t="n">
         <v>4</v>
       </c>
       <c r="Q142" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="R142" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="143">
@@ -9338,7 +9764,7 @@
         <v>2</v>
       </c>
       <c r="H143" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I143" t="n">
         <v>6</v>
@@ -9347,19 +9773,19 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>322</v>
+        <v>287</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="N143" t="n">
         <v>23</v>
       </c>
       <c r="O143" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="P143" t="n">
         <v>12</v>
@@ -9394,7 +9820,7 @@
         <v>2</v>
       </c>
       <c r="H144" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I144" t="n">
         <v>6</v>
@@ -9403,19 +9829,19 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>322</v>
+        <v>287</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="N144" t="n">
         <v>23</v>
       </c>
       <c r="O144" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="P144" t="n">
         <v>12</v>
@@ -9450,7 +9876,7 @@
         <v>2</v>
       </c>
       <c r="H145" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I145" t="n">
         <v>6</v>
@@ -9459,19 +9885,19 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>322</v>
+        <v>287</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="N145" t="n">
         <v>23</v>
       </c>
       <c r="O145" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="P145" t="n">
         <v>12</v>
@@ -9481,6 +9907,4038 @@
       </c>
       <c r="R145" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>289</v>
+      </c>
+      <c r="B146" t="b">
+        <v>0</v>
+      </c>
+      <c r="C146" t="s">
+        <v>18</v>
+      </c>
+      <c r="D146" t="s">
+        <v>19</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="s">
+        <v>20</v>
+      </c>
+      <c r="I146" t="n">
+        <v>7</v>
+      </c>
+      <c r="J146" t="n">
+        <v>3</v>
+      </c>
+      <c r="K146" t="s">
+        <v>331</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="s">
+        <v>332</v>
+      </c>
+      <c r="N146" t="n">
+        <v>11</v>
+      </c>
+      <c r="O146" t="s">
+        <v>333</v>
+      </c>
+      <c r="P146" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>334</v>
+      </c>
+      <c r="R146" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>290</v>
+      </c>
+      <c r="B147" t="b">
+        <v>0</v>
+      </c>
+      <c r="C147" t="s">
+        <v>18</v>
+      </c>
+      <c r="D147" t="s">
+        <v>19</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="s">
+        <v>20</v>
+      </c>
+      <c r="I147" t="n">
+        <v>7</v>
+      </c>
+      <c r="J147" t="n">
+        <v>3</v>
+      </c>
+      <c r="K147" t="s">
+        <v>331</v>
+      </c>
+      <c r="L147" t="n">
+        <v>2</v>
+      </c>
+      <c r="M147" t="s">
+        <v>335</v>
+      </c>
+      <c r="N147" t="n">
+        <v>11</v>
+      </c>
+      <c r="O147" t="s">
+        <v>336</v>
+      </c>
+      <c r="P147" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>334</v>
+      </c>
+      <c r="R147" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>291</v>
+      </c>
+      <c r="B148" t="b">
+        <v>0</v>
+      </c>
+      <c r="C148" t="s">
+        <v>18</v>
+      </c>
+      <c r="D148" t="s">
+        <v>19</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="s">
+        <v>20</v>
+      </c>
+      <c r="I148" t="n">
+        <v>7</v>
+      </c>
+      <c r="J148" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" t="s">
+        <v>331</v>
+      </c>
+      <c r="L148" t="n">
+        <v>3</v>
+      </c>
+      <c r="M148" t="s">
+        <v>337</v>
+      </c>
+      <c r="N148" t="n">
+        <v>11</v>
+      </c>
+      <c r="O148" t="s">
+        <v>338</v>
+      </c>
+      <c r="P148" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>334</v>
+      </c>
+      <c r="R148" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>295</v>
+      </c>
+      <c r="B149" t="b">
+        <v>0</v>
+      </c>
+      <c r="C149" t="s">
+        <v>18</v>
+      </c>
+      <c r="D149" t="s">
+        <v>19</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="s">
+        <v>29</v>
+      </c>
+      <c r="I149" t="n">
+        <v>7</v>
+      </c>
+      <c r="J149" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" t="s">
+        <v>339</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="s">
+        <v>340</v>
+      </c>
+      <c r="N149" t="n">
+        <v>12</v>
+      </c>
+      <c r="O149" t="s">
+        <v>341</v>
+      </c>
+      <c r="P149" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>342</v>
+      </c>
+      <c r="R149" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>296</v>
+      </c>
+      <c r="B150" t="b">
+        <v>0</v>
+      </c>
+      <c r="C150" t="s">
+        <v>18</v>
+      </c>
+      <c r="D150" t="s">
+        <v>19</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="s">
+        <v>29</v>
+      </c>
+      <c r="I150" t="n">
+        <v>7</v>
+      </c>
+      <c r="J150" t="n">
+        <v>3</v>
+      </c>
+      <c r="K150" t="s">
+        <v>339</v>
+      </c>
+      <c r="L150" t="n">
+        <v>2</v>
+      </c>
+      <c r="M150" t="s">
+        <v>343</v>
+      </c>
+      <c r="N150" t="n">
+        <v>12</v>
+      </c>
+      <c r="O150" t="s">
+        <v>344</v>
+      </c>
+      <c r="P150" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>342</v>
+      </c>
+      <c r="R150" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>297</v>
+      </c>
+      <c r="B151" t="b">
+        <v>0</v>
+      </c>
+      <c r="C151" t="s">
+        <v>18</v>
+      </c>
+      <c r="D151" t="s">
+        <v>19</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="s">
+        <v>29</v>
+      </c>
+      <c r="I151" t="n">
+        <v>7</v>
+      </c>
+      <c r="J151" t="n">
+        <v>3</v>
+      </c>
+      <c r="K151" t="s">
+        <v>339</v>
+      </c>
+      <c r="L151" t="n">
+        <v>3</v>
+      </c>
+      <c r="M151" t="s">
+        <v>345</v>
+      </c>
+      <c r="N151" t="n">
+        <v>12</v>
+      </c>
+      <c r="O151" t="s">
+        <v>346</v>
+      </c>
+      <c r="P151" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>342</v>
+      </c>
+      <c r="R151" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>301</v>
+      </c>
+      <c r="B152" t="b">
+        <v>0</v>
+      </c>
+      <c r="C152" t="s">
+        <v>18</v>
+      </c>
+      <c r="D152" t="s">
+        <v>19</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="s">
+        <v>38</v>
+      </c>
+      <c r="I152" t="n">
+        <v>7</v>
+      </c>
+      <c r="J152" t="n">
+        <v>3</v>
+      </c>
+      <c r="K152" t="s">
+        <v>331</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="s">
+        <v>347</v>
+      </c>
+      <c r="N152" t="n">
+        <v>9</v>
+      </c>
+      <c r="O152" t="s">
+        <v>348</v>
+      </c>
+      <c r="P152" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>41</v>
+      </c>
+      <c r="R152" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>302</v>
+      </c>
+      <c r="B153" t="b">
+        <v>0</v>
+      </c>
+      <c r="C153" t="s">
+        <v>18</v>
+      </c>
+      <c r="D153" t="s">
+        <v>19</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="s">
+        <v>38</v>
+      </c>
+      <c r="I153" t="n">
+        <v>7</v>
+      </c>
+      <c r="J153" t="n">
+        <v>3</v>
+      </c>
+      <c r="K153" t="s">
+        <v>331</v>
+      </c>
+      <c r="L153" t="n">
+        <v>2</v>
+      </c>
+      <c r="M153" t="s">
+        <v>349</v>
+      </c>
+      <c r="N153" t="n">
+        <v>9</v>
+      </c>
+      <c r="O153" t="s">
+        <v>350</v>
+      </c>
+      <c r="P153" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>41</v>
+      </c>
+      <c r="R153" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>303</v>
+      </c>
+      <c r="B154" t="b">
+        <v>0</v>
+      </c>
+      <c r="C154" t="s">
+        <v>18</v>
+      </c>
+      <c r="D154" t="s">
+        <v>19</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="s">
+        <v>38</v>
+      </c>
+      <c r="I154" t="n">
+        <v>7</v>
+      </c>
+      <c r="J154" t="n">
+        <v>3</v>
+      </c>
+      <c r="K154" t="s">
+        <v>331</v>
+      </c>
+      <c r="L154" t="n">
+        <v>3</v>
+      </c>
+      <c r="M154" t="s">
+        <v>351</v>
+      </c>
+      <c r="N154" t="n">
+        <v>9</v>
+      </c>
+      <c r="O154" t="s">
+        <v>352</v>
+      </c>
+      <c r="P154" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>41</v>
+      </c>
+      <c r="R154" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>307</v>
+      </c>
+      <c r="B155" t="b">
+        <v>0</v>
+      </c>
+      <c r="C155" t="s">
+        <v>18</v>
+      </c>
+      <c r="D155" t="s">
+        <v>19</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2</v>
+      </c>
+      <c r="F155" t="n">
+        <v>2</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="s">
+        <v>46</v>
+      </c>
+      <c r="I155" t="n">
+        <v>7</v>
+      </c>
+      <c r="J155" t="n">
+        <v>3</v>
+      </c>
+      <c r="K155" t="s">
+        <v>339</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="s">
+        <v>353</v>
+      </c>
+      <c r="N155" t="n">
+        <v>10</v>
+      </c>
+      <c r="O155" t="s">
+        <v>354</v>
+      </c>
+      <c r="P155" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>355</v>
+      </c>
+      <c r="R155" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>308</v>
+      </c>
+      <c r="B156" t="b">
+        <v>0</v>
+      </c>
+      <c r="C156" t="s">
+        <v>18</v>
+      </c>
+      <c r="D156" t="s">
+        <v>19</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="s">
+        <v>46</v>
+      </c>
+      <c r="I156" t="n">
+        <v>7</v>
+      </c>
+      <c r="J156" t="n">
+        <v>3</v>
+      </c>
+      <c r="K156" t="s">
+        <v>339</v>
+      </c>
+      <c r="L156" t="n">
+        <v>2</v>
+      </c>
+      <c r="M156" t="s">
+        <v>356</v>
+      </c>
+      <c r="N156" t="n">
+        <v>10</v>
+      </c>
+      <c r="O156" t="s">
+        <v>357</v>
+      </c>
+      <c r="P156" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>355</v>
+      </c>
+      <c r="R156" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>309</v>
+      </c>
+      <c r="B157" t="b">
+        <v>0</v>
+      </c>
+      <c r="C157" t="s">
+        <v>18</v>
+      </c>
+      <c r="D157" t="s">
+        <v>19</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="s">
+        <v>46</v>
+      </c>
+      <c r="I157" t="n">
+        <v>7</v>
+      </c>
+      <c r="J157" t="n">
+        <v>3</v>
+      </c>
+      <c r="K157" t="s">
+        <v>339</v>
+      </c>
+      <c r="L157" t="n">
+        <v>3</v>
+      </c>
+      <c r="M157" t="s">
+        <v>358</v>
+      </c>
+      <c r="N157" t="n">
+        <v>10</v>
+      </c>
+      <c r="O157" t="s">
+        <v>359</v>
+      </c>
+      <c r="P157" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>355</v>
+      </c>
+      <c r="R157" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>313</v>
+      </c>
+      <c r="B158" t="b">
+        <v>0</v>
+      </c>
+      <c r="C158" t="s">
+        <v>18</v>
+      </c>
+      <c r="D158" t="s">
+        <v>19</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="n">
+        <v>2</v>
+      </c>
+      <c r="H158" t="s">
+        <v>54</v>
+      </c>
+      <c r="I158" t="n">
+        <v>7</v>
+      </c>
+      <c r="J158" t="n">
+        <v>3</v>
+      </c>
+      <c r="K158" t="s">
+        <v>331</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="s">
+        <v>360</v>
+      </c>
+      <c r="N158" t="n">
+        <v>11</v>
+      </c>
+      <c r="O158" t="s">
+        <v>361</v>
+      </c>
+      <c r="P158" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>334</v>
+      </c>
+      <c r="R158" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>314</v>
+      </c>
+      <c r="B159" t="b">
+        <v>0</v>
+      </c>
+      <c r="C159" t="s">
+        <v>18</v>
+      </c>
+      <c r="D159" t="s">
+        <v>19</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2</v>
+      </c>
+      <c r="H159" t="s">
+        <v>54</v>
+      </c>
+      <c r="I159" t="n">
+        <v>7</v>
+      </c>
+      <c r="J159" t="n">
+        <v>3</v>
+      </c>
+      <c r="K159" t="s">
+        <v>331</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2</v>
+      </c>
+      <c r="M159" t="s">
+        <v>362</v>
+      </c>
+      <c r="N159" t="n">
+        <v>11</v>
+      </c>
+      <c r="O159" t="s">
+        <v>363</v>
+      </c>
+      <c r="P159" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>334</v>
+      </c>
+      <c r="R159" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>315</v>
+      </c>
+      <c r="B160" t="b">
+        <v>0</v>
+      </c>
+      <c r="C160" t="s">
+        <v>18</v>
+      </c>
+      <c r="D160" t="s">
+        <v>19</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" t="s">
+        <v>54</v>
+      </c>
+      <c r="I160" t="n">
+        <v>7</v>
+      </c>
+      <c r="J160" t="n">
+        <v>3</v>
+      </c>
+      <c r="K160" t="s">
+        <v>331</v>
+      </c>
+      <c r="L160" t="n">
+        <v>3</v>
+      </c>
+      <c r="M160" t="s">
+        <v>364</v>
+      </c>
+      <c r="N160" t="n">
+        <v>11</v>
+      </c>
+      <c r="O160" t="s">
+        <v>365</v>
+      </c>
+      <c r="P160" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>334</v>
+      </c>
+      <c r="R160" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>319</v>
+      </c>
+      <c r="B161" t="b">
+        <v>0</v>
+      </c>
+      <c r="C161" t="s">
+        <v>18</v>
+      </c>
+      <c r="D161" t="s">
+        <v>19</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>2</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2</v>
+      </c>
+      <c r="H161" t="s">
+        <v>61</v>
+      </c>
+      <c r="I161" t="n">
+        <v>7</v>
+      </c>
+      <c r="J161" t="n">
+        <v>3</v>
+      </c>
+      <c r="K161" t="s">
+        <v>339</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="s">
+        <v>366</v>
+      </c>
+      <c r="N161" t="n">
+        <v>12</v>
+      </c>
+      <c r="O161" t="s">
+        <v>367</v>
+      </c>
+      <c r="P161" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>342</v>
+      </c>
+      <c r="R161" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>320</v>
+      </c>
+      <c r="B162" t="b">
+        <v>0</v>
+      </c>
+      <c r="C162" t="s">
+        <v>18</v>
+      </c>
+      <c r="D162" t="s">
+        <v>19</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2</v>
+      </c>
+      <c r="H162" t="s">
+        <v>61</v>
+      </c>
+      <c r="I162" t="n">
+        <v>7</v>
+      </c>
+      <c r="J162" t="n">
+        <v>3</v>
+      </c>
+      <c r="K162" t="s">
+        <v>339</v>
+      </c>
+      <c r="L162" t="n">
+        <v>2</v>
+      </c>
+      <c r="M162" t="s">
+        <v>368</v>
+      </c>
+      <c r="N162" t="n">
+        <v>12</v>
+      </c>
+      <c r="O162" t="s">
+        <v>369</v>
+      </c>
+      <c r="P162" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>342</v>
+      </c>
+      <c r="R162" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>321</v>
+      </c>
+      <c r="B163" t="b">
+        <v>0</v>
+      </c>
+      <c r="C163" t="s">
+        <v>18</v>
+      </c>
+      <c r="D163" t="s">
+        <v>19</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" t="n">
+        <v>2</v>
+      </c>
+      <c r="H163" t="s">
+        <v>61</v>
+      </c>
+      <c r="I163" t="n">
+        <v>7</v>
+      </c>
+      <c r="J163" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" t="s">
+        <v>339</v>
+      </c>
+      <c r="L163" t="n">
+        <v>3</v>
+      </c>
+      <c r="M163" t="s">
+        <v>370</v>
+      </c>
+      <c r="N163" t="n">
+        <v>12</v>
+      </c>
+      <c r="O163" t="s">
+        <v>371</v>
+      </c>
+      <c r="P163" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>342</v>
+      </c>
+      <c r="R163" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>325</v>
+      </c>
+      <c r="B164" t="b">
+        <v>0</v>
+      </c>
+      <c r="C164" t="s">
+        <v>18</v>
+      </c>
+      <c r="D164" t="s">
+        <v>19</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+      <c r="H164" t="s">
+        <v>68</v>
+      </c>
+      <c r="I164" t="n">
+        <v>7</v>
+      </c>
+      <c r="J164" t="n">
+        <v>3</v>
+      </c>
+      <c r="K164" t="s">
+        <v>331</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="s">
+        <v>372</v>
+      </c>
+      <c r="N164" t="n">
+        <v>9</v>
+      </c>
+      <c r="O164" t="s">
+        <v>373</v>
+      </c>
+      <c r="P164" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>41</v>
+      </c>
+      <c r="R164" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>326</v>
+      </c>
+      <c r="B165" t="b">
+        <v>0</v>
+      </c>
+      <c r="C165" t="s">
+        <v>18</v>
+      </c>
+      <c r="D165" t="s">
+        <v>19</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2</v>
+      </c>
+      <c r="H165" t="s">
+        <v>68</v>
+      </c>
+      <c r="I165" t="n">
+        <v>7</v>
+      </c>
+      <c r="J165" t="n">
+        <v>3</v>
+      </c>
+      <c r="K165" t="s">
+        <v>331</v>
+      </c>
+      <c r="L165" t="n">
+        <v>2</v>
+      </c>
+      <c r="M165" t="s">
+        <v>374</v>
+      </c>
+      <c r="N165" t="n">
+        <v>9</v>
+      </c>
+      <c r="O165" t="s">
+        <v>375</v>
+      </c>
+      <c r="P165" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>41</v>
+      </c>
+      <c r="R165" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>327</v>
+      </c>
+      <c r="B166" t="b">
+        <v>0</v>
+      </c>
+      <c r="C166" t="s">
+        <v>18</v>
+      </c>
+      <c r="D166" t="s">
+        <v>19</v>
+      </c>
+      <c r="E166" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+      <c r="H166" t="s">
+        <v>68</v>
+      </c>
+      <c r="I166" t="n">
+        <v>7</v>
+      </c>
+      <c r="J166" t="n">
+        <v>3</v>
+      </c>
+      <c r="K166" t="s">
+        <v>331</v>
+      </c>
+      <c r="L166" t="n">
+        <v>3</v>
+      </c>
+      <c r="M166" t="s">
+        <v>376</v>
+      </c>
+      <c r="N166" t="n">
+        <v>9</v>
+      </c>
+      <c r="O166" t="s">
+        <v>377</v>
+      </c>
+      <c r="P166" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>41</v>
+      </c>
+      <c r="R166" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>331</v>
+      </c>
+      <c r="B167" t="b">
+        <v>0</v>
+      </c>
+      <c r="C167" t="s">
+        <v>18</v>
+      </c>
+      <c r="D167" t="s">
+        <v>19</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" t="n">
+        <v>2</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2</v>
+      </c>
+      <c r="H167" t="s">
+        <v>73</v>
+      </c>
+      <c r="I167" t="n">
+        <v>7</v>
+      </c>
+      <c r="J167" t="n">
+        <v>3</v>
+      </c>
+      <c r="K167" t="s">
+        <v>339</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="s">
+        <v>378</v>
+      </c>
+      <c r="N167" t="n">
+        <v>10</v>
+      </c>
+      <c r="O167" t="s">
+        <v>379</v>
+      </c>
+      <c r="P167" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>355</v>
+      </c>
+      <c r="R167" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>332</v>
+      </c>
+      <c r="B168" t="b">
+        <v>0</v>
+      </c>
+      <c r="C168" t="s">
+        <v>18</v>
+      </c>
+      <c r="D168" t="s">
+        <v>19</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+      <c r="H168" t="s">
+        <v>73</v>
+      </c>
+      <c r="I168" t="n">
+        <v>7</v>
+      </c>
+      <c r="J168" t="n">
+        <v>3</v>
+      </c>
+      <c r="K168" t="s">
+        <v>339</v>
+      </c>
+      <c r="L168" t="n">
+        <v>2</v>
+      </c>
+      <c r="M168" t="s">
+        <v>380</v>
+      </c>
+      <c r="N168" t="n">
+        <v>10</v>
+      </c>
+      <c r="O168" t="s">
+        <v>381</v>
+      </c>
+      <c r="P168" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>355</v>
+      </c>
+      <c r="R168" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>333</v>
+      </c>
+      <c r="B169" t="b">
+        <v>0</v>
+      </c>
+      <c r="C169" t="s">
+        <v>18</v>
+      </c>
+      <c r="D169" t="s">
+        <v>19</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2</v>
+      </c>
+      <c r="G169" t="n">
+        <v>2</v>
+      </c>
+      <c r="H169" t="s">
+        <v>73</v>
+      </c>
+      <c r="I169" t="n">
+        <v>7</v>
+      </c>
+      <c r="J169" t="n">
+        <v>3</v>
+      </c>
+      <c r="K169" t="s">
+        <v>339</v>
+      </c>
+      <c r="L169" t="n">
+        <v>3</v>
+      </c>
+      <c r="M169" t="s">
+        <v>382</v>
+      </c>
+      <c r="N169" t="n">
+        <v>10</v>
+      </c>
+      <c r="O169" t="s">
+        <v>383</v>
+      </c>
+      <c r="P169" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>355</v>
+      </c>
+      <c r="R169" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>337</v>
+      </c>
+      <c r="B170" t="b">
+        <v>0</v>
+      </c>
+      <c r="C170" t="s">
+        <v>18</v>
+      </c>
+      <c r="D170" t="s">
+        <v>19</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="s">
+        <v>20</v>
+      </c>
+      <c r="I170" t="n">
+        <v>8</v>
+      </c>
+      <c r="J170" t="n">
+        <v>3</v>
+      </c>
+      <c r="K170" t="s">
+        <v>384</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="s">
+        <v>385</v>
+      </c>
+      <c r="N170" t="n">
+        <v>11</v>
+      </c>
+      <c r="O170" t="s">
+        <v>386</v>
+      </c>
+      <c r="P170" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>334</v>
+      </c>
+      <c r="R170" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>338</v>
+      </c>
+      <c r="B171" t="b">
+        <v>0</v>
+      </c>
+      <c r="C171" t="s">
+        <v>18</v>
+      </c>
+      <c r="D171" t="s">
+        <v>19</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="s">
+        <v>20</v>
+      </c>
+      <c r="I171" t="n">
+        <v>8</v>
+      </c>
+      <c r="J171" t="n">
+        <v>3</v>
+      </c>
+      <c r="K171" t="s">
+        <v>384</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2</v>
+      </c>
+      <c r="M171" t="s">
+        <v>387</v>
+      </c>
+      <c r="N171" t="n">
+        <v>11</v>
+      </c>
+      <c r="O171" t="s">
+        <v>388</v>
+      </c>
+      <c r="P171" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>334</v>
+      </c>
+      <c r="R171" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>339</v>
+      </c>
+      <c r="B172" t="b">
+        <v>0</v>
+      </c>
+      <c r="C172" t="s">
+        <v>18</v>
+      </c>
+      <c r="D172" t="s">
+        <v>19</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="s">
+        <v>20</v>
+      </c>
+      <c r="I172" t="n">
+        <v>8</v>
+      </c>
+      <c r="J172" t="n">
+        <v>3</v>
+      </c>
+      <c r="K172" t="s">
+        <v>384</v>
+      </c>
+      <c r="L172" t="n">
+        <v>3</v>
+      </c>
+      <c r="M172" t="s">
+        <v>389</v>
+      </c>
+      <c r="N172" t="n">
+        <v>11</v>
+      </c>
+      <c r="O172" t="s">
+        <v>390</v>
+      </c>
+      <c r="P172" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>334</v>
+      </c>
+      <c r="R172" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>343</v>
+      </c>
+      <c r="B173" t="b">
+        <v>0</v>
+      </c>
+      <c r="C173" t="s">
+        <v>18</v>
+      </c>
+      <c r="D173" t="s">
+        <v>19</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="s">
+        <v>29</v>
+      </c>
+      <c r="I173" t="n">
+        <v>8</v>
+      </c>
+      <c r="J173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" t="s">
+        <v>339</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="s">
+        <v>391</v>
+      </c>
+      <c r="N173" t="n">
+        <v>12</v>
+      </c>
+      <c r="O173" t="s">
+        <v>392</v>
+      </c>
+      <c r="P173" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>342</v>
+      </c>
+      <c r="R173" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>344</v>
+      </c>
+      <c r="B174" t="b">
+        <v>0</v>
+      </c>
+      <c r="C174" t="s">
+        <v>18</v>
+      </c>
+      <c r="D174" t="s">
+        <v>19</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>2</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="s">
+        <v>29</v>
+      </c>
+      <c r="I174" t="n">
+        <v>8</v>
+      </c>
+      <c r="J174" t="n">
+        <v>3</v>
+      </c>
+      <c r="K174" t="s">
+        <v>339</v>
+      </c>
+      <c r="L174" t="n">
+        <v>2</v>
+      </c>
+      <c r="M174" t="s">
+        <v>393</v>
+      </c>
+      <c r="N174" t="n">
+        <v>12</v>
+      </c>
+      <c r="O174" t="s">
+        <v>394</v>
+      </c>
+      <c r="P174" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>342</v>
+      </c>
+      <c r="R174" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>345</v>
+      </c>
+      <c r="B175" t="b">
+        <v>0</v>
+      </c>
+      <c r="C175" t="s">
+        <v>18</v>
+      </c>
+      <c r="D175" t="s">
+        <v>19</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" t="n">
+        <v>2</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="s">
+        <v>29</v>
+      </c>
+      <c r="I175" t="n">
+        <v>8</v>
+      </c>
+      <c r="J175" t="n">
+        <v>3</v>
+      </c>
+      <c r="K175" t="s">
+        <v>339</v>
+      </c>
+      <c r="L175" t="n">
+        <v>3</v>
+      </c>
+      <c r="M175" t="s">
+        <v>395</v>
+      </c>
+      <c r="N175" t="n">
+        <v>12</v>
+      </c>
+      <c r="O175" t="s">
+        <v>396</v>
+      </c>
+      <c r="P175" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>342</v>
+      </c>
+      <c r="R175" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>349</v>
+      </c>
+      <c r="B176" t="b">
+        <v>0</v>
+      </c>
+      <c r="C176" t="s">
+        <v>18</v>
+      </c>
+      <c r="D176" t="s">
+        <v>19</v>
+      </c>
+      <c r="E176" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="s">
+        <v>38</v>
+      </c>
+      <c r="I176" t="n">
+        <v>8</v>
+      </c>
+      <c r="J176" t="n">
+        <v>3</v>
+      </c>
+      <c r="K176" t="s">
+        <v>384</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="s">
+        <v>397</v>
+      </c>
+      <c r="N176" t="n">
+        <v>9</v>
+      </c>
+      <c r="O176" t="s">
+        <v>398</v>
+      </c>
+      <c r="P176" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>41</v>
+      </c>
+      <c r="R176" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>350</v>
+      </c>
+      <c r="B177" t="b">
+        <v>0</v>
+      </c>
+      <c r="C177" t="s">
+        <v>18</v>
+      </c>
+      <c r="D177" t="s">
+        <v>19</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="s">
+        <v>38</v>
+      </c>
+      <c r="I177" t="n">
+        <v>8</v>
+      </c>
+      <c r="J177" t="n">
+        <v>3</v>
+      </c>
+      <c r="K177" t="s">
+        <v>384</v>
+      </c>
+      <c r="L177" t="n">
+        <v>2</v>
+      </c>
+      <c r="M177" t="s">
+        <v>399</v>
+      </c>
+      <c r="N177" t="n">
+        <v>9</v>
+      </c>
+      <c r="O177" t="s">
+        <v>400</v>
+      </c>
+      <c r="P177" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>41</v>
+      </c>
+      <c r="R177" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>351</v>
+      </c>
+      <c r="B178" t="b">
+        <v>0</v>
+      </c>
+      <c r="C178" t="s">
+        <v>18</v>
+      </c>
+      <c r="D178" t="s">
+        <v>19</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="s">
+        <v>38</v>
+      </c>
+      <c r="I178" t="n">
+        <v>8</v>
+      </c>
+      <c r="J178" t="n">
+        <v>3</v>
+      </c>
+      <c r="K178" t="s">
+        <v>384</v>
+      </c>
+      <c r="L178" t="n">
+        <v>3</v>
+      </c>
+      <c r="M178" t="s">
+        <v>401</v>
+      </c>
+      <c r="N178" t="n">
+        <v>9</v>
+      </c>
+      <c r="O178" t="s">
+        <v>402</v>
+      </c>
+      <c r="P178" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>41</v>
+      </c>
+      <c r="R178" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>355</v>
+      </c>
+      <c r="B179" t="b">
+        <v>0</v>
+      </c>
+      <c r="C179" t="s">
+        <v>18</v>
+      </c>
+      <c r="D179" t="s">
+        <v>19</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="s">
+        <v>46</v>
+      </c>
+      <c r="I179" t="n">
+        <v>8</v>
+      </c>
+      <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="s">
+        <v>339</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="s">
+        <v>403</v>
+      </c>
+      <c r="N179" t="n">
+        <v>10</v>
+      </c>
+      <c r="O179" t="s">
+        <v>404</v>
+      </c>
+      <c r="P179" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>355</v>
+      </c>
+      <c r="R179" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>356</v>
+      </c>
+      <c r="B180" t="b">
+        <v>0</v>
+      </c>
+      <c r="C180" t="s">
+        <v>18</v>
+      </c>
+      <c r="D180" t="s">
+        <v>19</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2</v>
+      </c>
+      <c r="F180" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="s">
+        <v>46</v>
+      </c>
+      <c r="I180" t="n">
+        <v>8</v>
+      </c>
+      <c r="J180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" t="s">
+        <v>339</v>
+      </c>
+      <c r="L180" t="n">
+        <v>2</v>
+      </c>
+      <c r="M180" t="s">
+        <v>405</v>
+      </c>
+      <c r="N180" t="n">
+        <v>10</v>
+      </c>
+      <c r="O180" t="s">
+        <v>406</v>
+      </c>
+      <c r="P180" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>355</v>
+      </c>
+      <c r="R180" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>357</v>
+      </c>
+      <c r="B181" t="b">
+        <v>0</v>
+      </c>
+      <c r="C181" t="s">
+        <v>18</v>
+      </c>
+      <c r="D181" t="s">
+        <v>19</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" t="n">
+        <v>2</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="s">
+        <v>46</v>
+      </c>
+      <c r="I181" t="n">
+        <v>8</v>
+      </c>
+      <c r="J181" t="n">
+        <v>3</v>
+      </c>
+      <c r="K181" t="s">
+        <v>339</v>
+      </c>
+      <c r="L181" t="n">
+        <v>3</v>
+      </c>
+      <c r="M181" t="s">
+        <v>407</v>
+      </c>
+      <c r="N181" t="n">
+        <v>10</v>
+      </c>
+      <c r="O181" t="s">
+        <v>408</v>
+      </c>
+      <c r="P181" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>355</v>
+      </c>
+      <c r="R181" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>361</v>
+      </c>
+      <c r="B182" t="b">
+        <v>0</v>
+      </c>
+      <c r="C182" t="s">
+        <v>18</v>
+      </c>
+      <c r="D182" t="s">
+        <v>19</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="n">
+        <v>2</v>
+      </c>
+      <c r="H182" t="s">
+        <v>54</v>
+      </c>
+      <c r="I182" t="n">
+        <v>8</v>
+      </c>
+      <c r="J182" t="n">
+        <v>3</v>
+      </c>
+      <c r="K182" t="s">
+        <v>384</v>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="s">
+        <v>409</v>
+      </c>
+      <c r="N182" t="n">
+        <v>11</v>
+      </c>
+      <c r="O182" t="s">
+        <v>410</v>
+      </c>
+      <c r="P182" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>334</v>
+      </c>
+      <c r="R182" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>362</v>
+      </c>
+      <c r="B183" t="b">
+        <v>0</v>
+      </c>
+      <c r="C183" t="s">
+        <v>18</v>
+      </c>
+      <c r="D183" t="s">
+        <v>19</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H183" t="s">
+        <v>54</v>
+      </c>
+      <c r="I183" t="n">
+        <v>8</v>
+      </c>
+      <c r="J183" t="n">
+        <v>3</v>
+      </c>
+      <c r="K183" t="s">
+        <v>384</v>
+      </c>
+      <c r="L183" t="n">
+        <v>2</v>
+      </c>
+      <c r="M183" t="s">
+        <v>411</v>
+      </c>
+      <c r="N183" t="n">
+        <v>11</v>
+      </c>
+      <c r="O183" t="s">
+        <v>412</v>
+      </c>
+      <c r="P183" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>334</v>
+      </c>
+      <c r="R183" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>363</v>
+      </c>
+      <c r="B184" t="b">
+        <v>0</v>
+      </c>
+      <c r="C184" t="s">
+        <v>18</v>
+      </c>
+      <c r="D184" t="s">
+        <v>19</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="n">
+        <v>2</v>
+      </c>
+      <c r="H184" t="s">
+        <v>54</v>
+      </c>
+      <c r="I184" t="n">
+        <v>8</v>
+      </c>
+      <c r="J184" t="n">
+        <v>3</v>
+      </c>
+      <c r="K184" t="s">
+        <v>384</v>
+      </c>
+      <c r="L184" t="n">
+        <v>3</v>
+      </c>
+      <c r="M184" t="s">
+        <v>413</v>
+      </c>
+      <c r="N184" t="n">
+        <v>11</v>
+      </c>
+      <c r="O184" t="s">
+        <v>414</v>
+      </c>
+      <c r="P184" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q184" t="s">
+        <v>334</v>
+      </c>
+      <c r="R184" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>367</v>
+      </c>
+      <c r="B185" t="b">
+        <v>0</v>
+      </c>
+      <c r="C185" t="s">
+        <v>18</v>
+      </c>
+      <c r="D185" t="s">
+        <v>19</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" t="n">
+        <v>2</v>
+      </c>
+      <c r="H185" t="s">
+        <v>61</v>
+      </c>
+      <c r="I185" t="n">
+        <v>8</v>
+      </c>
+      <c r="J185" t="n">
+        <v>3</v>
+      </c>
+      <c r="K185" t="s">
+        <v>339</v>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="s">
+        <v>415</v>
+      </c>
+      <c r="N185" t="n">
+        <v>12</v>
+      </c>
+      <c r="O185" t="s">
+        <v>416</v>
+      </c>
+      <c r="P185" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>342</v>
+      </c>
+      <c r="R185" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>368</v>
+      </c>
+      <c r="B186" t="b">
+        <v>0</v>
+      </c>
+      <c r="C186" t="s">
+        <v>18</v>
+      </c>
+      <c r="D186" t="s">
+        <v>19</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" t="n">
+        <v>2</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2</v>
+      </c>
+      <c r="H186" t="s">
+        <v>61</v>
+      </c>
+      <c r="I186" t="n">
+        <v>8</v>
+      </c>
+      <c r="J186" t="n">
+        <v>3</v>
+      </c>
+      <c r="K186" t="s">
+        <v>339</v>
+      </c>
+      <c r="L186" t="n">
+        <v>2</v>
+      </c>
+      <c r="M186" t="s">
+        <v>417</v>
+      </c>
+      <c r="N186" t="n">
+        <v>12</v>
+      </c>
+      <c r="O186" t="s">
+        <v>418</v>
+      </c>
+      <c r="P186" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>342</v>
+      </c>
+      <c r="R186" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>369</v>
+      </c>
+      <c r="B187" t="b">
+        <v>0</v>
+      </c>
+      <c r="C187" t="s">
+        <v>18</v>
+      </c>
+      <c r="D187" t="s">
+        <v>19</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="n">
+        <v>2</v>
+      </c>
+      <c r="G187" t="n">
+        <v>2</v>
+      </c>
+      <c r="H187" t="s">
+        <v>61</v>
+      </c>
+      <c r="I187" t="n">
+        <v>8</v>
+      </c>
+      <c r="J187" t="n">
+        <v>3</v>
+      </c>
+      <c r="K187" t="s">
+        <v>339</v>
+      </c>
+      <c r="L187" t="n">
+        <v>3</v>
+      </c>
+      <c r="M187" t="s">
+        <v>419</v>
+      </c>
+      <c r="N187" t="n">
+        <v>12</v>
+      </c>
+      <c r="O187" t="s">
+        <v>420</v>
+      </c>
+      <c r="P187" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>342</v>
+      </c>
+      <c r="R187" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>373</v>
+      </c>
+      <c r="B188" t="b">
+        <v>0</v>
+      </c>
+      <c r="C188" t="s">
+        <v>18</v>
+      </c>
+      <c r="D188" t="s">
+        <v>19</v>
+      </c>
+      <c r="E188" t="n">
+        <v>2</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="n">
+        <v>2</v>
+      </c>
+      <c r="H188" t="s">
+        <v>68</v>
+      </c>
+      <c r="I188" t="n">
+        <v>8</v>
+      </c>
+      <c r="J188" t="n">
+        <v>3</v>
+      </c>
+      <c r="K188" t="s">
+        <v>384</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="s">
+        <v>421</v>
+      </c>
+      <c r="N188" t="n">
+        <v>9</v>
+      </c>
+      <c r="O188" t="s">
+        <v>422</v>
+      </c>
+      <c r="P188" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>41</v>
+      </c>
+      <c r="R188" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>374</v>
+      </c>
+      <c r="B189" t="b">
+        <v>0</v>
+      </c>
+      <c r="C189" t="s">
+        <v>18</v>
+      </c>
+      <c r="D189" t="s">
+        <v>19</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" t="n">
+        <v>2</v>
+      </c>
+      <c r="H189" t="s">
+        <v>68</v>
+      </c>
+      <c r="I189" t="n">
+        <v>8</v>
+      </c>
+      <c r="J189" t="n">
+        <v>3</v>
+      </c>
+      <c r="K189" t="s">
+        <v>384</v>
+      </c>
+      <c r="L189" t="n">
+        <v>2</v>
+      </c>
+      <c r="M189" t="s">
+        <v>423</v>
+      </c>
+      <c r="N189" t="n">
+        <v>9</v>
+      </c>
+      <c r="O189" t="s">
+        <v>424</v>
+      </c>
+      <c r="P189" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>41</v>
+      </c>
+      <c r="R189" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>375</v>
+      </c>
+      <c r="B190" t="b">
+        <v>0</v>
+      </c>
+      <c r="C190" t="s">
+        <v>18</v>
+      </c>
+      <c r="D190" t="s">
+        <v>19</v>
+      </c>
+      <c r="E190" t="n">
+        <v>2</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" t="n">
+        <v>2</v>
+      </c>
+      <c r="H190" t="s">
+        <v>68</v>
+      </c>
+      <c r="I190" t="n">
+        <v>8</v>
+      </c>
+      <c r="J190" t="n">
+        <v>3</v>
+      </c>
+      <c r="K190" t="s">
+        <v>384</v>
+      </c>
+      <c r="L190" t="n">
+        <v>3</v>
+      </c>
+      <c r="M190" t="s">
+        <v>425</v>
+      </c>
+      <c r="N190" t="n">
+        <v>9</v>
+      </c>
+      <c r="O190" t="s">
+        <v>426</v>
+      </c>
+      <c r="P190" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>41</v>
+      </c>
+      <c r="R190" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>379</v>
+      </c>
+      <c r="B191" t="b">
+        <v>0</v>
+      </c>
+      <c r="C191" t="s">
+        <v>18</v>
+      </c>
+      <c r="D191" t="s">
+        <v>19</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2</v>
+      </c>
+      <c r="F191" t="n">
+        <v>2</v>
+      </c>
+      <c r="G191" t="n">
+        <v>2</v>
+      </c>
+      <c r="H191" t="s">
+        <v>73</v>
+      </c>
+      <c r="I191" t="n">
+        <v>8</v>
+      </c>
+      <c r="J191" t="n">
+        <v>3</v>
+      </c>
+      <c r="K191" t="s">
+        <v>339</v>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="s">
+        <v>427</v>
+      </c>
+      <c r="N191" t="n">
+        <v>10</v>
+      </c>
+      <c r="O191" t="s">
+        <v>428</v>
+      </c>
+      <c r="P191" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>355</v>
+      </c>
+      <c r="R191" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>380</v>
+      </c>
+      <c r="B192" t="b">
+        <v>0</v>
+      </c>
+      <c r="C192" t="s">
+        <v>18</v>
+      </c>
+      <c r="D192" t="s">
+        <v>19</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" t="n">
+        <v>2</v>
+      </c>
+      <c r="G192" t="n">
+        <v>2</v>
+      </c>
+      <c r="H192" t="s">
+        <v>73</v>
+      </c>
+      <c r="I192" t="n">
+        <v>8</v>
+      </c>
+      <c r="J192" t="n">
+        <v>3</v>
+      </c>
+      <c r="K192" t="s">
+        <v>339</v>
+      </c>
+      <c r="L192" t="n">
+        <v>2</v>
+      </c>
+      <c r="M192" t="s">
+        <v>429</v>
+      </c>
+      <c r="N192" t="n">
+        <v>10</v>
+      </c>
+      <c r="O192" t="s">
+        <v>430</v>
+      </c>
+      <c r="P192" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>355</v>
+      </c>
+      <c r="R192" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>381</v>
+      </c>
+      <c r="B193" t="b">
+        <v>0</v>
+      </c>
+      <c r="C193" t="s">
+        <v>18</v>
+      </c>
+      <c r="D193" t="s">
+        <v>19</v>
+      </c>
+      <c r="E193" t="n">
+        <v>2</v>
+      </c>
+      <c r="F193" t="n">
+        <v>2</v>
+      </c>
+      <c r="G193" t="n">
+        <v>2</v>
+      </c>
+      <c r="H193" t="s">
+        <v>73</v>
+      </c>
+      <c r="I193" t="n">
+        <v>8</v>
+      </c>
+      <c r="J193" t="n">
+        <v>3</v>
+      </c>
+      <c r="K193" t="s">
+        <v>339</v>
+      </c>
+      <c r="L193" t="n">
+        <v>3</v>
+      </c>
+      <c r="M193" t="s">
+        <v>431</v>
+      </c>
+      <c r="N193" t="n">
+        <v>10</v>
+      </c>
+      <c r="O193" t="s">
+        <v>432</v>
+      </c>
+      <c r="P193" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>355</v>
+      </c>
+      <c r="R193" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>385</v>
+      </c>
+      <c r="B194" t="b">
+        <v>0</v>
+      </c>
+      <c r="C194" t="s">
+        <v>18</v>
+      </c>
+      <c r="D194" t="s">
+        <v>19</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="s">
+        <v>20</v>
+      </c>
+      <c r="I194" t="n">
+        <v>9</v>
+      </c>
+      <c r="J194" t="n">
+        <v>3</v>
+      </c>
+      <c r="K194" t="s">
+        <v>433</v>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="s">
+        <v>434</v>
+      </c>
+      <c r="N194" t="n">
+        <v>10</v>
+      </c>
+      <c r="O194" t="s">
+        <v>435</v>
+      </c>
+      <c r="P194" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>436</v>
+      </c>
+      <c r="R194" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>386</v>
+      </c>
+      <c r="B195" t="b">
+        <v>0</v>
+      </c>
+      <c r="C195" t="s">
+        <v>18</v>
+      </c>
+      <c r="D195" t="s">
+        <v>19</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" t="s">
+        <v>20</v>
+      </c>
+      <c r="I195" t="n">
+        <v>9</v>
+      </c>
+      <c r="J195" t="n">
+        <v>3</v>
+      </c>
+      <c r="K195" t="s">
+        <v>433</v>
+      </c>
+      <c r="L195" t="n">
+        <v>2</v>
+      </c>
+      <c r="M195" t="s">
+        <v>437</v>
+      </c>
+      <c r="N195" t="n">
+        <v>10</v>
+      </c>
+      <c r="O195" t="s">
+        <v>438</v>
+      </c>
+      <c r="P195" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>436</v>
+      </c>
+      <c r="R195" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>387</v>
+      </c>
+      <c r="B196" t="b">
+        <v>0</v>
+      </c>
+      <c r="C196" t="s">
+        <v>18</v>
+      </c>
+      <c r="D196" t="s">
+        <v>19</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="s">
+        <v>20</v>
+      </c>
+      <c r="I196" t="n">
+        <v>9</v>
+      </c>
+      <c r="J196" t="n">
+        <v>3</v>
+      </c>
+      <c r="K196" t="s">
+        <v>433</v>
+      </c>
+      <c r="L196" t="n">
+        <v>3</v>
+      </c>
+      <c r="M196" t="s">
+        <v>439</v>
+      </c>
+      <c r="N196" t="n">
+        <v>10</v>
+      </c>
+      <c r="O196" t="s">
+        <v>440</v>
+      </c>
+      <c r="P196" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>436</v>
+      </c>
+      <c r="R196" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>391</v>
+      </c>
+      <c r="B197" t="b">
+        <v>0</v>
+      </c>
+      <c r="C197" t="s">
+        <v>18</v>
+      </c>
+      <c r="D197" t="s">
+        <v>19</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="s">
+        <v>29</v>
+      </c>
+      <c r="I197" t="n">
+        <v>9</v>
+      </c>
+      <c r="J197" t="n">
+        <v>3</v>
+      </c>
+      <c r="K197" t="s">
+        <v>339</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="s">
+        <v>441</v>
+      </c>
+      <c r="N197" t="n">
+        <v>12</v>
+      </c>
+      <c r="O197" t="s">
+        <v>442</v>
+      </c>
+      <c r="P197" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q197" t="s">
+        <v>342</v>
+      </c>
+      <c r="R197" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>392</v>
+      </c>
+      <c r="B198" t="b">
+        <v>0</v>
+      </c>
+      <c r="C198" t="s">
+        <v>18</v>
+      </c>
+      <c r="D198" t="s">
+        <v>19</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="s">
+        <v>29</v>
+      </c>
+      <c r="I198" t="n">
+        <v>9</v>
+      </c>
+      <c r="J198" t="n">
+        <v>3</v>
+      </c>
+      <c r="K198" t="s">
+        <v>339</v>
+      </c>
+      <c r="L198" t="n">
+        <v>2</v>
+      </c>
+      <c r="M198" t="s">
+        <v>443</v>
+      </c>
+      <c r="N198" t="n">
+        <v>12</v>
+      </c>
+      <c r="O198" t="s">
+        <v>444</v>
+      </c>
+      <c r="P198" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>342</v>
+      </c>
+      <c r="R198" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>393</v>
+      </c>
+      <c r="B199" t="b">
+        <v>0</v>
+      </c>
+      <c r="C199" t="s">
+        <v>18</v>
+      </c>
+      <c r="D199" t="s">
+        <v>19</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="s">
+        <v>29</v>
+      </c>
+      <c r="I199" t="n">
+        <v>9</v>
+      </c>
+      <c r="J199" t="n">
+        <v>3</v>
+      </c>
+      <c r="K199" t="s">
+        <v>339</v>
+      </c>
+      <c r="L199" t="n">
+        <v>3</v>
+      </c>
+      <c r="M199" t="s">
+        <v>445</v>
+      </c>
+      <c r="N199" t="n">
+        <v>12</v>
+      </c>
+      <c r="O199" t="s">
+        <v>446</v>
+      </c>
+      <c r="P199" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>342</v>
+      </c>
+      <c r="R199" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>397</v>
+      </c>
+      <c r="B200" t="b">
+        <v>0</v>
+      </c>
+      <c r="C200" t="s">
+        <v>18</v>
+      </c>
+      <c r="D200" t="s">
+        <v>19</v>
+      </c>
+      <c r="E200" t="n">
+        <v>2</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="s">
+        <v>38</v>
+      </c>
+      <c r="I200" t="n">
+        <v>9</v>
+      </c>
+      <c r="J200" t="n">
+        <v>3</v>
+      </c>
+      <c r="K200" t="s">
+        <v>433</v>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="s">
+        <v>447</v>
+      </c>
+      <c r="N200" t="n">
+        <v>7</v>
+      </c>
+      <c r="O200" t="s">
+        <v>448</v>
+      </c>
+      <c r="P200" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>296</v>
+      </c>
+      <c r="R200" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>398</v>
+      </c>
+      <c r="B201" t="b">
+        <v>0</v>
+      </c>
+      <c r="C201" t="s">
+        <v>18</v>
+      </c>
+      <c r="D201" t="s">
+        <v>19</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="s">
+        <v>38</v>
+      </c>
+      <c r="I201" t="n">
+        <v>9</v>
+      </c>
+      <c r="J201" t="n">
+        <v>3</v>
+      </c>
+      <c r="K201" t="s">
+        <v>433</v>
+      </c>
+      <c r="L201" t="n">
+        <v>2</v>
+      </c>
+      <c r="M201" t="s">
+        <v>449</v>
+      </c>
+      <c r="N201" t="n">
+        <v>7</v>
+      </c>
+      <c r="O201" t="s">
+        <v>450</v>
+      </c>
+      <c r="P201" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>296</v>
+      </c>
+      <c r="R201" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>399</v>
+      </c>
+      <c r="B202" t="b">
+        <v>0</v>
+      </c>
+      <c r="C202" t="s">
+        <v>18</v>
+      </c>
+      <c r="D202" t="s">
+        <v>19</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="s">
+        <v>38</v>
+      </c>
+      <c r="I202" t="n">
+        <v>9</v>
+      </c>
+      <c r="J202" t="n">
+        <v>3</v>
+      </c>
+      <c r="K202" t="s">
+        <v>433</v>
+      </c>
+      <c r="L202" t="n">
+        <v>3</v>
+      </c>
+      <c r="M202" t="s">
+        <v>451</v>
+      </c>
+      <c r="N202" t="n">
+        <v>7</v>
+      </c>
+      <c r="O202" t="s">
+        <v>452</v>
+      </c>
+      <c r="P202" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>296</v>
+      </c>
+      <c r="R202" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>403</v>
+      </c>
+      <c r="B203" t="b">
+        <v>0</v>
+      </c>
+      <c r="C203" t="s">
+        <v>18</v>
+      </c>
+      <c r="D203" t="s">
+        <v>19</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2</v>
+      </c>
+      <c r="F203" t="n">
+        <v>2</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" t="s">
+        <v>46</v>
+      </c>
+      <c r="I203" t="n">
+        <v>9</v>
+      </c>
+      <c r="J203" t="n">
+        <v>3</v>
+      </c>
+      <c r="K203" t="s">
+        <v>339</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="s">
+        <v>453</v>
+      </c>
+      <c r="N203" t="n">
+        <v>10</v>
+      </c>
+      <c r="O203" t="s">
+        <v>454</v>
+      </c>
+      <c r="P203" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>355</v>
+      </c>
+      <c r="R203" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>404</v>
+      </c>
+      <c r="B204" t="b">
+        <v>0</v>
+      </c>
+      <c r="C204" t="s">
+        <v>18</v>
+      </c>
+      <c r="D204" t="s">
+        <v>19</v>
+      </c>
+      <c r="E204" t="n">
+        <v>2</v>
+      </c>
+      <c r="F204" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="s">
+        <v>46</v>
+      </c>
+      <c r="I204" t="n">
+        <v>9</v>
+      </c>
+      <c r="J204" t="n">
+        <v>3</v>
+      </c>
+      <c r="K204" t="s">
+        <v>339</v>
+      </c>
+      <c r="L204" t="n">
+        <v>2</v>
+      </c>
+      <c r="M204" t="s">
+        <v>455</v>
+      </c>
+      <c r="N204" t="n">
+        <v>10</v>
+      </c>
+      <c r="O204" t="s">
+        <v>456</v>
+      </c>
+      <c r="P204" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>355</v>
+      </c>
+      <c r="R204" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>405</v>
+      </c>
+      <c r="B205" t="b">
+        <v>0</v>
+      </c>
+      <c r="C205" t="s">
+        <v>18</v>
+      </c>
+      <c r="D205" t="s">
+        <v>19</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2</v>
+      </c>
+      <c r="F205" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" t="s">
+        <v>46</v>
+      </c>
+      <c r="I205" t="n">
+        <v>9</v>
+      </c>
+      <c r="J205" t="n">
+        <v>3</v>
+      </c>
+      <c r="K205" t="s">
+        <v>339</v>
+      </c>
+      <c r="L205" t="n">
+        <v>3</v>
+      </c>
+      <c r="M205" t="s">
+        <v>457</v>
+      </c>
+      <c r="N205" t="n">
+        <v>10</v>
+      </c>
+      <c r="O205" t="s">
+        <v>458</v>
+      </c>
+      <c r="P205" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>355</v>
+      </c>
+      <c r="R205" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>409</v>
+      </c>
+      <c r="B206" t="b">
+        <v>0</v>
+      </c>
+      <c r="C206" t="s">
+        <v>18</v>
+      </c>
+      <c r="D206" t="s">
+        <v>19</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="n">
+        <v>2</v>
+      </c>
+      <c r="H206" t="s">
+        <v>54</v>
+      </c>
+      <c r="I206" t="n">
+        <v>9</v>
+      </c>
+      <c r="J206" t="n">
+        <v>3</v>
+      </c>
+      <c r="K206" t="s">
+        <v>433</v>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="s">
+        <v>459</v>
+      </c>
+      <c r="N206" t="n">
+        <v>10</v>
+      </c>
+      <c r="O206" t="s">
+        <v>460</v>
+      </c>
+      <c r="P206" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>436</v>
+      </c>
+      <c r="R206" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>410</v>
+      </c>
+      <c r="B207" t="b">
+        <v>0</v>
+      </c>
+      <c r="C207" t="s">
+        <v>18</v>
+      </c>
+      <c r="D207" t="s">
+        <v>19</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="n">
+        <v>2</v>
+      </c>
+      <c r="H207" t="s">
+        <v>54</v>
+      </c>
+      <c r="I207" t="n">
+        <v>9</v>
+      </c>
+      <c r="J207" t="n">
+        <v>3</v>
+      </c>
+      <c r="K207" t="s">
+        <v>433</v>
+      </c>
+      <c r="L207" t="n">
+        <v>2</v>
+      </c>
+      <c r="M207" t="s">
+        <v>461</v>
+      </c>
+      <c r="N207" t="n">
+        <v>10</v>
+      </c>
+      <c r="O207" t="s">
+        <v>462</v>
+      </c>
+      <c r="P207" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>436</v>
+      </c>
+      <c r="R207" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>411</v>
+      </c>
+      <c r="B208" t="b">
+        <v>0</v>
+      </c>
+      <c r="C208" t="s">
+        <v>18</v>
+      </c>
+      <c r="D208" t="s">
+        <v>19</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="n">
+        <v>2</v>
+      </c>
+      <c r="H208" t="s">
+        <v>54</v>
+      </c>
+      <c r="I208" t="n">
+        <v>9</v>
+      </c>
+      <c r="J208" t="n">
+        <v>3</v>
+      </c>
+      <c r="K208" t="s">
+        <v>433</v>
+      </c>
+      <c r="L208" t="n">
+        <v>3</v>
+      </c>
+      <c r="M208" t="s">
+        <v>463</v>
+      </c>
+      <c r="N208" t="n">
+        <v>10</v>
+      </c>
+      <c r="O208" t="s">
+        <v>464</v>
+      </c>
+      <c r="P208" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>436</v>
+      </c>
+      <c r="R208" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>415</v>
+      </c>
+      <c r="B209" t="b">
+        <v>0</v>
+      </c>
+      <c r="C209" t="s">
+        <v>18</v>
+      </c>
+      <c r="D209" t="s">
+        <v>19</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2</v>
+      </c>
+      <c r="G209" t="n">
+        <v>2</v>
+      </c>
+      <c r="H209" t="s">
+        <v>61</v>
+      </c>
+      <c r="I209" t="n">
+        <v>9</v>
+      </c>
+      <c r="J209" t="n">
+        <v>3</v>
+      </c>
+      <c r="K209" t="s">
+        <v>339</v>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="s">
+        <v>465</v>
+      </c>
+      <c r="N209" t="n">
+        <v>12</v>
+      </c>
+      <c r="O209" t="s">
+        <v>466</v>
+      </c>
+      <c r="P209" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>342</v>
+      </c>
+      <c r="R209" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>416</v>
+      </c>
+      <c r="B210" t="b">
+        <v>0</v>
+      </c>
+      <c r="C210" t="s">
+        <v>18</v>
+      </c>
+      <c r="D210" t="s">
+        <v>19</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" t="n">
+        <v>2</v>
+      </c>
+      <c r="H210" t="s">
+        <v>61</v>
+      </c>
+      <c r="I210" t="n">
+        <v>9</v>
+      </c>
+      <c r="J210" t="n">
+        <v>3</v>
+      </c>
+      <c r="K210" t="s">
+        <v>339</v>
+      </c>
+      <c r="L210" t="n">
+        <v>2</v>
+      </c>
+      <c r="M210" t="s">
+        <v>467</v>
+      </c>
+      <c r="N210" t="n">
+        <v>12</v>
+      </c>
+      <c r="O210" t="s">
+        <v>468</v>
+      </c>
+      <c r="P210" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>342</v>
+      </c>
+      <c r="R210" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>417</v>
+      </c>
+      <c r="B211" t="b">
+        <v>0</v>
+      </c>
+      <c r="C211" t="s">
+        <v>18</v>
+      </c>
+      <c r="D211" t="s">
+        <v>19</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" t="n">
+        <v>2</v>
+      </c>
+      <c r="H211" t="s">
+        <v>61</v>
+      </c>
+      <c r="I211" t="n">
+        <v>9</v>
+      </c>
+      <c r="J211" t="n">
+        <v>3</v>
+      </c>
+      <c r="K211" t="s">
+        <v>339</v>
+      </c>
+      <c r="L211" t="n">
+        <v>3</v>
+      </c>
+      <c r="M211" t="s">
+        <v>469</v>
+      </c>
+      <c r="N211" t="n">
+        <v>12</v>
+      </c>
+      <c r="O211" t="s">
+        <v>470</v>
+      </c>
+      <c r="P211" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>342</v>
+      </c>
+      <c r="R211" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>421</v>
+      </c>
+      <c r="B212" t="b">
+        <v>0</v>
+      </c>
+      <c r="C212" t="s">
+        <v>18</v>
+      </c>
+      <c r="D212" t="s">
+        <v>19</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" t="n">
+        <v>2</v>
+      </c>
+      <c r="H212" t="s">
+        <v>68</v>
+      </c>
+      <c r="I212" t="n">
+        <v>9</v>
+      </c>
+      <c r="J212" t="n">
+        <v>3</v>
+      </c>
+      <c r="K212" t="s">
+        <v>433</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="s">
+        <v>471</v>
+      </c>
+      <c r="N212" t="n">
+        <v>7</v>
+      </c>
+      <c r="O212" t="s">
+        <v>472</v>
+      </c>
+      <c r="P212" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>296</v>
+      </c>
+      <c r="R212" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>422</v>
+      </c>
+      <c r="B213" t="b">
+        <v>0</v>
+      </c>
+      <c r="C213" t="s">
+        <v>18</v>
+      </c>
+      <c r="D213" t="s">
+        <v>19</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="n">
+        <v>2</v>
+      </c>
+      <c r="H213" t="s">
+        <v>68</v>
+      </c>
+      <c r="I213" t="n">
+        <v>9</v>
+      </c>
+      <c r="J213" t="n">
+        <v>3</v>
+      </c>
+      <c r="K213" t="s">
+        <v>433</v>
+      </c>
+      <c r="L213" t="n">
+        <v>2</v>
+      </c>
+      <c r="M213" t="s">
+        <v>473</v>
+      </c>
+      <c r="N213" t="n">
+        <v>7</v>
+      </c>
+      <c r="O213" t="s">
+        <v>474</v>
+      </c>
+      <c r="P213" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>296</v>
+      </c>
+      <c r="R213" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>423</v>
+      </c>
+      <c r="B214" t="b">
+        <v>0</v>
+      </c>
+      <c r="C214" t="s">
+        <v>18</v>
+      </c>
+      <c r="D214" t="s">
+        <v>19</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="n">
+        <v>2</v>
+      </c>
+      <c r="H214" t="s">
+        <v>68</v>
+      </c>
+      <c r="I214" t="n">
+        <v>9</v>
+      </c>
+      <c r="J214" t="n">
+        <v>3</v>
+      </c>
+      <c r="K214" t="s">
+        <v>433</v>
+      </c>
+      <c r="L214" t="n">
+        <v>3</v>
+      </c>
+      <c r="M214" t="s">
+        <v>475</v>
+      </c>
+      <c r="N214" t="n">
+        <v>7</v>
+      </c>
+      <c r="O214" t="s">
+        <v>476</v>
+      </c>
+      <c r="P214" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>296</v>
+      </c>
+      <c r="R214" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>427</v>
+      </c>
+      <c r="B215" t="b">
+        <v>0</v>
+      </c>
+      <c r="C215" t="s">
+        <v>18</v>
+      </c>
+      <c r="D215" t="s">
+        <v>19</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F215" t="n">
+        <v>2</v>
+      </c>
+      <c r="G215" t="n">
+        <v>2</v>
+      </c>
+      <c r="H215" t="s">
+        <v>73</v>
+      </c>
+      <c r="I215" t="n">
+        <v>9</v>
+      </c>
+      <c r="J215" t="n">
+        <v>3</v>
+      </c>
+      <c r="K215" t="s">
+        <v>339</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="s">
+        <v>477</v>
+      </c>
+      <c r="N215" t="n">
+        <v>10</v>
+      </c>
+      <c r="O215" t="s">
+        <v>478</v>
+      </c>
+      <c r="P215" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>355</v>
+      </c>
+      <c r="R215" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>428</v>
+      </c>
+      <c r="B216" t="b">
+        <v>0</v>
+      </c>
+      <c r="C216" t="s">
+        <v>18</v>
+      </c>
+      <c r="D216" t="s">
+        <v>19</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2</v>
+      </c>
+      <c r="F216" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" t="n">
+        <v>2</v>
+      </c>
+      <c r="H216" t="s">
+        <v>73</v>
+      </c>
+      <c r="I216" t="n">
+        <v>9</v>
+      </c>
+      <c r="J216" t="n">
+        <v>3</v>
+      </c>
+      <c r="K216" t="s">
+        <v>339</v>
+      </c>
+      <c r="L216" t="n">
+        <v>2</v>
+      </c>
+      <c r="M216" t="s">
+        <v>479</v>
+      </c>
+      <c r="N216" t="n">
+        <v>10</v>
+      </c>
+      <c r="O216" t="s">
+        <v>480</v>
+      </c>
+      <c r="P216" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>355</v>
+      </c>
+      <c r="R216" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>429</v>
+      </c>
+      <c r="B217" t="b">
+        <v>0</v>
+      </c>
+      <c r="C217" t="s">
+        <v>18</v>
+      </c>
+      <c r="D217" t="s">
+        <v>19</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2</v>
+      </c>
+      <c r="F217" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" t="n">
+        <v>2</v>
+      </c>
+      <c r="H217" t="s">
+        <v>73</v>
+      </c>
+      <c r="I217" t="n">
+        <v>9</v>
+      </c>
+      <c r="J217" t="n">
+        <v>3</v>
+      </c>
+      <c r="K217" t="s">
+        <v>339</v>
+      </c>
+      <c r="L217" t="n">
+        <v>3</v>
+      </c>
+      <c r="M217" t="s">
+        <v>481</v>
+      </c>
+      <c r="N217" t="n">
+        <v>10</v>
+      </c>
+      <c r="O217" t="s">
+        <v>482</v>
+      </c>
+      <c r="P217" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>355</v>
+      </c>
+      <c r="R217" t="s">
+        <v>355</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_lon_fold_sets.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_lon_fold_sets.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="426">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -77,28 +77,28 @@
     <t xml:space="preserve">1.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 137, 1671, 1788, 1790, 1793, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 136, 1787, 1789, 1792, 1794, 1795, 1888, 2049, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 75, 76, 77, 134, 135, 137, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 61, 74, 133, 136, 1671, 1787, 2049, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 75, 77, 135, 136, 137, 1789, 1790, 1792, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 74, 76, 133, 134, 1671, 1787, 1788, 1793, 1794)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 135, 137, 1787, 1788, 1792, 1793, 1795, 1888, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(134, 136, 1789, 1790, 1794, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 134, 135, 136, 1787, 1788, 1789, 1790, 1792, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 137, 1793, 1794, 1795, 1888, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(134, 135, 1787, 1788, 1790, 1792, 1794, 1795, 1888, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 136, 137, 1789, 1793, 2050)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
@@ -107,1360 +107,1189 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 124, 184, 185, 1747, 1748, 1890, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 123, 125, 183, 186, 1749, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 183, 184, 185, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 124, 125, 183, 186, 1747, 1748, 1749, 1891, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 82, 122, 123, 184, 185, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 122, 123, 124, 125, 183, 184, 185, 1747, 1891, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 82, 186, 1748, 1749, 1890, 2006)</t>
+    <t xml:space="preserve">c(79, 80, 81, 123, 124, 125, 184, 185, 186, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 183, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 122, 123, 124, 125, 183, 184, 185, 186, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 125, 183, 184, 185, 186, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 123, 124, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 124, 183, 184, 185, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 122, 123, 125, 186)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1829, 1831, 1832, 1834, 1979, 2144, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1833, 1980, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1834, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1832, 1833, 1979, 1980, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1834, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1833, 1834, 1979, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1980, 2144, 2147, 2148)</t>
+    <t xml:space="preserve">c(1828, 1833, 1834, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1980, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1834, 1980, 2144, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1833, 1980, 2144, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1834, 2145, 2148)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 114, 115, 116, 117, 1645, 1647, 2213, 2297, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(112, 113, 118, 1646, 1648, 1676, 1677, 2211, 2212, 2296, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 107, 110, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 2212, 2297, 2298, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(105, 106, 108, 109, 111, 112, 1677, 2211, 2213, 2296, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 106, 107, 109, 111, 112, 114, 115, 116, 117, 118, 1646, 1647, 1648, 1676, 2211, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 105, 108, 110, 113, 1645, 1677, 2212, 2213, 2296, 2297, 2299)</t>
+    <t xml:space="preserve">c(101, 103, 105, 106, 107, 108, 109, 110, 112, 114, 115, 1645, 1646, 1647, 1648, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 104, 111, 113, 116, 117, 118, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 104, 105, 106, 109, 110, 112, 113, 114, 115, 116, 118, 1645, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 107, 108, 111, 117, 1646, 1647, 1648, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 105, 106, 107, 108, 111, 112, 113, 114, 115, 116, 118, 1646, 1647, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 109, 110, 117, 1645, 1648, 2321)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 59, 75, 77, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1793, 1794, 1795, 2049, 2050, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 61, 74, 76, 1671, 1792, 1888, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 76, 77, 135, 136, 137, 1671, 1787, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 61, 74, 75, 133, 134, 1788, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 74, 75, 134, 136, 137, 1787, 1788, 1789, 1792, 1793, 1794, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 76, 77, 133, 135, 1671, 1790, 1795, 1888, 2049)</t>
+    <t xml:space="preserve">c(133, 134, 135, 136, 1789, 1790, 1792, 1793, 1795, 1888, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 137, 1787, 1788, 1794, 2050, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 134, 135, 136, 137, 1788, 1789, 1792, 1793, 1794, 1795, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 1787, 1790, 1888, 2050, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 136, 137, 1788, 1789, 1792, 1793, 1795, 2050, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(134, 135, 1787, 1790, 1794, 1888, 2052)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 122, 123, 124, 125, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 183, 184, 185, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 82, 125, 183, 185, 186, 1747, 1748, 1749, 1890, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 122, 123, 124, 184, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 82, 124, 125, 183, 185, 186, 1747, 1749, 1890, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 122, 123, 184, 1748, 1891, 2006, 2008)</t>
+    <t xml:space="preserve">c(79, 80, 123, 125, 183, 185, 186, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 122, 124, 184)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 122, 123, 125, 183, 185, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 124, 184, 186, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 123, 124, 185, 186, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 125, 183, 184, 1891)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1833, 1834, 1979, 1980, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1833, 1834, 1979, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1832, 1980, 2144)</t>
+    <t xml:space="preserve">c(1828, 1832, 1833, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1834, 1980, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1834, 1980, 2144, 2145)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(103, 106, 108, 109, 110, 111, 112, 113, 115, 117, 118, 1645, 1646, 1647, 1648, 1677, 2212, 2296, 2297, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 105, 107, 114, 116, 1676, 2211, 2213, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 106, 107, 112, 113, 114, 115, 118, 1645, 1646, 1648, 1677, 2211, 2213, 2296, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(104, 105, 108, 109, 110, 111, 116, 117, 1647, 1676, 2212, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 104, 105, 107, 108, 109, 113, 115, 117, 118, 1645, 1646, 1648, 1676, 1677, 2211, 2213, 2297, 2298, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 106, 110, 111, 112, 114, 116, 1647, 2212, 2296, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 74, 75, 77, 134, 135, 1787, 1788, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 61, 76, 133, 136, 137, 1671, 1789, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 74, 75, 133, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1795, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 61, 76, 77, 134, 1793, 1794, 1888, 2049, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 61, 74, 76, 77, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1795, 1888, 2049, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 75, 1790, 1792, 1793, 1794, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 123, 125, 183, 185, 186, 1747, 1749, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 124, 184, 1748, 1890, 1891, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 122, 184, 185, 1747, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 123, 124, 125, 183, 186, 1748, 1749)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 123, 125, 183, 185, 186, 1747, 1748, 1890, 1891, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 82, 122, 124, 184, 1749, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1832, 1834, 1979, 1980, 2144, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1833, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 1834, 1979, 1980, 2144)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 1979, 1980, 2144, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1834, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 104, 105, 107, 108, 109, 111, 112, 113, 116, 117, 118, 1645, 1646, 1648, 1676, 2211, 2212, 2213, 2296, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 106, 110, 114, 115, 1647, 1677, 2297, 2298, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 105, 106, 107, 109, 110, 112, 114, 115, 116, 118, 1645, 1646, 1647, 1648, 1676, 2297, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 104, 108, 111, 113, 117, 1677, 2211, 2212, 2213, 2296)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 106, 108, 109, 110, 111, 112, 114, 115, 116, 118, 1645, 1647, 1648, 2211, 2212, 2213, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 103, 104, 105, 107, 113, 117, 1646, 1676, 1677, 2296, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 74, 133, 135, 136, 1671, 1787, 1789, 1792, 1793, 1794, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 75, 76, 77, 134, 137, 1788, 1790, 1795, 1888)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 75, 76, 77, 133, 135, 137, 1787, 1788, 1790, 1792, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 74, 134, 136, 1671, 1789, 1793, 1794, 1795, 1888)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 74, 76, 77, 133, 135, 136, 1671, 1787, 1790, 1792, 1888, 2049, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 75, 134, 137, 1788, 1789, 1793, 1794, 1795, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 123, 124, 125, 184, 185, 1747, 1748, 1890, 1891, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 82, 122, 183, 186, 1749, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 82, 123, 124, 125, 183, 184, 185, 1748, 1749, 1891, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 122, 186, 1747, 1890, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 82, 122, 123, 125, 183, 184, 185, 186, 1748, 1749, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 124, 1747, 1890, 1891, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1834, 1979, 1980, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1832, 1834, 1979, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1833, 1980)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1832, 1833, 1979, 1980, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1834, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 107, 108, 109, 110, 111, 112, 113, 114, 116, 117, 1645, 1646, 1676, 1677, 2212, 2213, 2296, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 103, 104, 105, 106, 115, 118, 1647, 1648, 2211, 2297, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 106, 107, 108, 109, 110, 112, 114, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 2211, 2213, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 105, 111, 113, 115, 1677, 2212, 2296, 2297, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 104, 106, 107, 108, 110, 112, 114, 115, 116, 117, 1645, 1646, 1647, 1676, 1677, 2213, 2296, 2297, 2298, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 105, 109, 111, 113, 118, 1648, 2211, 2212, 2321, 2323)</t>
+    <t xml:space="preserve">c(100, 101, 103, 104, 105, 106, 107, 108, 109, 112, 113, 115, 116, 1645, 1647, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 110, 111, 114, 117, 118, 1646, 1648, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 106, 107, 108, 110, 112, 113, 114, 115, 117, 1646, 1647, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 105, 109, 111, 116, 118, 1645, 1648, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 106, 107, 109, 110, 111, 114, 115, 116, 117, 1646, 1647, 1648, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 105, 108, 112, 113, 118, 1645, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(134, 135, 137, 1787, 1789, 1790, 1792, 1793, 1794, 1795, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 136, 1788, 1888, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 134, 136, 1787, 1788, 1790, 1792, 1795, 2050, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(135, 137, 1789, 1793, 1794, 1888, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(134, 135, 136, 137, 1788, 1789, 1790, 1793, 1794, 1795, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 1787, 1792, 1888, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 122, 123, 124, 125, 183, 184, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 185, 186, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 122, 123, 124, 183, 184, 185, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 125, 186, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 123, 124, 183, 184, 185, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 125, 186, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1834, 1980, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1833, 1980, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1834, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 1834, 1980, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 104, 107, 109, 110, 111, 112, 113, 115, 116, 117, 118, 1646, 1647, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 105, 106, 108, 114, 1645, 1648, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 108, 109, 112, 113, 115, 116, 118, 1646, 1647, 1648, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(106, 107, 110, 111, 114, 117, 1645, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 105, 107, 108, 110, 111, 113, 115, 116, 117, 118, 1646, 1647, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 106, 109, 112, 114, 1645, 1648)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 134, 135, 137, 1788, 1789, 1792, 1794, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(136, 1787, 1790, 1793, 1795, 1888, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 134, 135, 136, 137, 1788, 1792, 1793, 1794, 1795, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 1787, 1789, 1790, 1888, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 134, 135, 136, 137, 1789, 1792, 1793, 1794, 1888, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 1787, 1788, 1790, 1795, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 122, 183, 184, 186, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(123, 124, 125, 185, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 122, 123, 183, 184, 186, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 124, 125, 185, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 122, 124, 183, 184, 186, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 123, 125, 185)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1834, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1833, 1980, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 1980, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1834, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1833, 1980, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1834, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 104, 105, 106, 109, 110, 111, 112, 113, 114, 115, 116, 118, 1648, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 107, 108, 117, 1645, 1646, 1647, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 104, 105, 107, 110, 112, 113, 114, 116, 117, 118, 1645, 1646, 1648, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 106, 108, 109, 111, 115, 1647, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 106, 107, 108, 109, 111, 112, 113, 114, 117, 118, 1648, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 105, 110, 115, 116, 1645, 1646, 1647, 2322)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 76, 77, 133, 134, 136, 137, 1671, 1787, 1789, 1790, 1792, 1794, 1888, 2049, 2050, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 74, 75, 135, 1788, 1793, 1795, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 75, 76, 134, 136, 137, 1671, 1787, 1790, 1795, 1888, 2049, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 77, 133, 135, 1788, 1789, 1792, 1793, 1794, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 61, 74, 75, 76, 77, 133, 134, 135, 1671, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 136, 137, 1787, 2049, 2050, 2051, 2052, 2262)</t>
+    <t xml:space="preserve">c(133, 134, 135, 136, 1787, 1790, 1792, 1888, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 137, 1788, 1789, 1793, 1794, 1795)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 136, 137, 1787, 1792, 1793, 1795, 1888, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(134, 135, 1788, 1789, 1790, 1794, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 134, 135, 136, 1787, 1789, 1790, 1792, 1888, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 137, 1788, 1793, 1794, 1795, 2051)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 81, 123, 124, 183, 184, 185, 186, 1747, 1749, 1891, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 82, 122, 125, 1748, 1890, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 125, 183, 184, 186, 1748, 1890, 1891, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(122, 123, 124, 185, 1747, 1749, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 82, 122, 123, 125, 183, 185, 1747, 1748, 1890, 1891, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 124, 184, 186, 1749, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1832, 1834, 1979, 1980, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1833, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1832, 1833, 1834, 1979, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1980, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1980, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 1834, 1979, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 103, 105, 108, 110, 111, 112, 114, 116, 117, 118, 1645, 1646, 1648, 1677, 2211, 2212, 2213, 2296, 2297, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 104, 106, 107, 109, 113, 115, 1647, 1676, 2298, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 105, 106, 107, 109, 110, 111, 112, 113, 116, 117, 118, 1646, 1647, 1648, 1677, 2297, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(104, 108, 114, 115, 1645, 1676, 2211, 2212, 2213, 2296, 2298, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 106, 108, 109, 110, 111, 113, 115, 117, 1645, 1647, 1676, 1677, 2212, 2213, 2296, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(104, 105, 107, 112, 114, 116, 118, 1646, 1648, 2211, 2297, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 74, 75, 133, 135, 136, 1671, 1787, 1788, 1789, 1792, 1793, 1795, 1888, 2049, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 76, 77, 134, 137, 1790, 1794, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 61, 74, 76, 77, 133, 136, 137, 1671, 1787, 1790, 1792, 1793, 1794, 1888, 2049, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 75, 134, 135, 1788, 1789, 1795, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 74, 75, 76, 133, 134, 136, 137, 1671, 1787, 1788, 1794, 1795, 1888, 2049, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 77, 135, 1789, 1790, 1792, 1793, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 123, 124, 184, 186, 1747, 1748, 1749, 1890, 1891, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 122, 125, 183, 185, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 123, 124, 125, 184, 1747, 1748, 1890, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 122, 183, 185, 186, 1749, 1891, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 124, 125, 183, 184, 186, 1890, 1891, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 185, 1747, 1748, 1749, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1979, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1834, 1980, 2144, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1832, 1833, 1834, 1980, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1979, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 107, 109, 110, 111, 113, 114, 117, 118, 1645, 1648, 1676, 1677, 2211, 2213, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(105, 106, 108, 112, 115, 116, 1646, 1647, 2212, 2296, 2297, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 104, 105, 106, 108, 109, 110, 114, 116, 117, 118, 1646, 1647, 1676, 2211, 2212, 2296, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 107, 111, 112, 113, 115, 1645, 1648, 1677, 2213, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 107, 108, 110, 112, 113, 118, 1645, 1646, 1647, 1648, 1677, 2211, 2212, 2213, 2298, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(105, 106, 109, 111, 114, 115, 116, 117, 1676, 2296, 2297, 2321)</t>
+    <t xml:space="preserve">c(80, 81, 122, 123, 125, 183, 185, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 124, 184, 186)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 123, 124, 125, 183, 184, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 185, 186, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 122, 123, 124, 125, 183, 184, 185, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 186, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 2144, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1834, 1980)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1980, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 1834, 1980, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 2144, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 106, 108, 110, 111, 112, 114, 115, 117, 118, 1645, 1648, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 104, 105, 107, 109, 113, 116, 1646, 1647)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 105, 107, 108, 110, 111, 113, 114, 115, 116, 1645, 1647, 1648, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 104, 106, 109, 112, 117, 118, 1646, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 105, 106, 108, 111, 112, 113, 114, 117, 1645, 1646, 1647, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 104, 107, 109, 110, 115, 116, 118, 1648)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 134, 135, 136, 1789, 1790, 1792, 1793, 1794, 1888, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 137, 1787, 1788, 1795, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 134, 1787, 1788, 1790, 1792, 1888, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(135, 136, 137, 1789, 1793, 1794, 1795)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 134, 136, 1788, 1789, 1794, 1888, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(135, 137, 1787, 1790, 1792, 1793, 1795)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 122, 124, 183, 185, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(123, 125, 184, 186, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 125, 183, 184, 186, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(122, 123, 124, 185, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 122, 123, 124, 125, 183, 186, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 184, 185, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1980, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1834, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 1980, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 1834, 1980, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 105, 106, 107, 108, 110, 111, 113, 114, 115, 117, 118, 1648, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 109, 112, 116, 1645, 1646, 1647, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 104, 106, 107, 108, 110, 111, 114, 115, 116, 117, 1647, 1648, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 105, 109, 112, 113, 118, 1645, 1646)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 112, 114, 118, 1645, 1648, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 111, 113, 115, 116, 117, 1646, 1647, 2322)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 61, 75, 76, 77, 133, 134, 135, 136, 1789, 1790, 1793, 1794, 1888, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 74, 137, 1671, 1787, 1788, 1792, 1795, 2049)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 61, 74, 75, 77, 133, 134, 135, 136, 1671, 1788, 1790, 1792, 1794, 1795, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 76, 137, 1787, 1789, 1793, 1888, 2049, 2050)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 61, 74, 76, 77, 133, 134, 135, 137, 1671, 1787, 1788, 1789, 1790, 1794, 1888, 2050, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 75, 136, 1792, 1793, 1795, 2049, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 124, 125, 1747, 1748, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 123, 1749, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 123, 125, 1747, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 124, 1748, 1749)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 123, 124, 125, 1747, 1748, 1749, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 82, 122, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1833, 1979, 1980, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1832, 1834, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1980, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 1834, 1979, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1834, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 1979, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 106, 107, 109, 110, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1676, 2211, 2212, 2213, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 104, 105, 108, 111, 112, 1648, 1677, 2296, 2297, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 104, 105, 106, 108, 110, 111, 113, 114, 115, 117, 118, 1645, 1646, 1648, 1677, 2213, 2296, 2297, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 107, 109, 112, 116, 1647, 1676, 2211, 2212, 2298, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 105, 106, 107, 109, 110, 112, 114, 115, 116, 117, 1645, 1646, 1647, 1648, 1676, 1677, 2212, 2296, 2297, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 104, 108, 111, 113, 118, 2211, 2213, 2298, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 76, 77, 133, 134, 135, 137, 1671, 1787, 1788, 1790, 1792, 1794, 1888, 2049, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 74, 75, 136, 1789, 1793, 1795, 2050)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 75, 76, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1790, 1792, 1888, 2049, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 77, 1789, 1793, 1794, 1795, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 75, 76, 77, 133, 135, 136, 137, 1787, 1788, 1789, 1790, 1793, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 74, 134, 1671, 1792, 1794, 1795, 1888, 2049)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 124, 125, 1747, 1748, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(122, 123, 1749, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 82, 123, 124, 125, 1747, 1749, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 122, 1748, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 82, 122, 125, 1747, 1748, 1749, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 123, 124, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833, 1834, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1979, 1980, 2144, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1832, 1834, 1980, 2144, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1833, 1979, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1833, 1980, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1834, 1979, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 104, 105, 106, 110, 111, 113, 116, 117, 118, 1645, 1647, 1648, 1676, 1677, 2212, 2213, 2296, 2297, 2298, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 103, 107, 108, 109, 112, 114, 115, 1646, 2211, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 107, 108, 109, 114, 116, 118, 1646, 1647, 1677, 2211, 2213, 2296, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 110, 111, 112, 113, 115, 117, 1645, 1648, 1676, 2212, 2297)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 103, 105, 107, 109, 110, 111, 113, 114, 116, 118, 1645, 1646, 1647, 1676, 2211, 2213, 2296, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 104, 106, 108, 112, 115, 117, 1648, 1677, 2212, 2298)</t>
+    <t xml:space="preserve">c(74, 133, 134, 135, 136, 137, 1788, 1790, 1792, 1794, 1795, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1787, 1789, 1793, 1888, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 134, 135, 1787, 1788, 1790, 1793, 1794, 1888, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 136, 137, 1789, 1792, 1795, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 134, 136, 137, 1789, 1790, 1792, 1795, 1888, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 135, 1787, 1788, 1793, 1794, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + ADF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 123, 124, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 122, 125, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 122, 123, 124, 125, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 123, 124, 125, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 122, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 122, 123, 125, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 124, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1980, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 1834, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1834, 1980, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 1834, 1980, 2144, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 105, 106, 107, 109, 110, 114, 116, 117, 118, 1646, 1647, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 108, 111, 112, 113, 115, 1645, 1648, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 104, 105, 106, 108, 109, 111, 112, 114, 115, 116, 117, 118, 1645, 1646, 1647, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 107, 110, 113, 1648, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 104, 108, 109, 110, 112, 113, 114, 116, 118, 1645, 1647, 1648, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 105, 106, 107, 111, 115, 117, 1646, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(134, 136, 137, 1787, 1788, 1789, 1790, 1793, 1794, 1888, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 135, 1792, 1795, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 134, 136, 137, 1788, 1792, 1795, 1888, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 135, 1787, 1789, 1790, 1793, 1794)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 134, 135, 137, 1788, 1792, 1793, 1794, 1795, 1888, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(136, 1787, 1789, 1790, 2050, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 123, 124, 125, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 122, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 122, 124, 125, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 123, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 122, 123, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 124, 125, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1980, 2144, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1834, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 1980, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 105, 107, 110, 111, 112, 113, 114, 115, 1645, 1646, 1647, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 104, 106, 108, 109, 116, 117, 118, 1648)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 105, 106, 108, 109, 110, 114, 115, 117, 118, 1645, 1646, 1648, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 107, 111, 112, 113, 116, 1647, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 105, 107, 108, 111, 112, 113, 118, 1645, 1646, 1647, 1648, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 106, 109, 110, 114, 115, 116, 117)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 133, 135, 136, 1671, 1788, 1789, 1790, 1792, 1793, 2049, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 76, 77, 134, 137, 1787, 1794, 1795, 1888, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 61, 74, 76, 133, 134, 136, 137, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 75, 77, 135, 1671, 1787, 2050, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 74, 75, 76, 134, 135, 136, 137, 1671, 1787, 1788, 1792, 1795, 2049, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 77, 133, 1789, 1790, 1793, 1794, 1888, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 122, 124, 184, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 82, 123, 125, 183, 185, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 82, 122, 123, 183, 185, 186, 1747, 1748, 1890, 1891, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 124, 125, 184, 1749, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 82, 125, 183, 184, 186, 1747, 1749, 1890, 1891, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 122, 123, 124, 185, 1748, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1832, 1833, 1979, 1980, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1834, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 1834, 1979, 1980, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 2144)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1834, 1979, 2144, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1980, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 104, 106, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1647, 1648, 1676, 2296, 2298, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 105, 107, 1646, 1677, 2211, 2212, 2213, 2297, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 108, 109, 110, 111, 112, 115, 117, 1647, 1676, 1677, 2211, 2212, 2297, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 107, 113, 114, 116, 118, 1645, 1646, 1648, 2213, 2296, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 105, 106, 107, 108, 111, 112, 113, 114, 115, 118, 1645, 1646, 1648, 1676, 1677, 2212, 2213, 2296, 2297)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 109, 110, 116, 117, 1647, 2211, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 134, 135, 136, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1888, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 77, 133, 137, 1671, 1795, 2049, 2050, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 75, 76, 77, 134, 136, 1671, 1787, 1788, 1789, 1790, 1792, 1794, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 135, 137, 1793, 1795, 1888, 2049, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 61, 77, 133, 136, 137, 1671, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 74, 75, 76, 134, 135, 1787, 2049, 2050)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 82, 122, 124, 125, 186, 1749, 1890, 1891, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 123, 183, 184, 185, 1747, 1748, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 125, 183, 184, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 123, 124, 185, 186)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 122, 124, 125, 183, 184, 185, 1747, 1748, 1749, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 82, 123, 186, 1890, 1891, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1980, 2144, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 1834, 1979, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1832, 1833, 1834, 1980, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1979, 2144, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1832, 1834, 1979, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1833, 1980, 2144)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 105, 106, 107, 108, 111, 113, 115, 1645, 1646, 1647, 1676, 1677, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 109, 110, 112, 114, 116, 117, 118, 1648, 2211, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 105, 106, 107, 108, 109, 111, 113, 115, 116, 117, 118, 1646, 1647, 1648, 1676, 2211, 2213, 2296, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 104, 110, 112, 114, 1645, 1677, 2212, 2297, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 105, 107, 108, 109, 110, 111, 113, 114, 118, 1647, 1648, 1677, 2211, 2213, 2297, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(104, 106, 112, 115, 116, 117, 1645, 1646, 1676, 2212, 2296, 2322)</t>
+    <t xml:space="preserve">c(74, 135, 1787, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 134, 136, 137, 1788, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 135, 137, 1787, 1792, 1793, 1794, 1795, 1888, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 134, 136, 1788, 1789, 1790, 2050)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 135, 136, 137, 1788, 1793, 1794, 1795, 1888, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 134, 1787, 1789, 1790, 1792, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + CP_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 123, 125, 185, 186, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(122, 124, 183, 184, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 122, 124, 183, 185, 186, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 123, 125, 184, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 122, 123, 124, 125, 184, 185, 186, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 183, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1834, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 1980, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1834, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1833, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 105, 106, 109, 112, 113, 114, 117, 118, 1645, 1647, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(104, 107, 108, 110, 111, 115, 116, 1646, 1648)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 105, 106, 108, 109, 110, 112, 114, 115, 117, 1645, 1646, 1647, 1648, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 107, 111, 113, 116, 118)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 105, 107, 109, 111, 112, 114, 115, 118, 1645, 1646, 1647, 1648, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 106, 108, 110, 113, 116, 117, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(135, 136, 137, 1788, 1789, 1792, 1793, 1794, 1795, 1888, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 134, 1787, 1790, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 134, 136, 137, 1787, 1788, 1790, 1793, 1794, 1795, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 135, 1789, 1792, 1888, 2050, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 134, 135, 137, 1787, 1788, 1792, 1793, 1794, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(136, 1789, 1790, 1795, 1888, 2050, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 123, 125, 184, 185, 186, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 122, 124, 183, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 123, 124, 125, 185, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(122, 183, 184, 186, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 122, 123, 124, 183, 185, 186, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 125, 184, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1834, 1980, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 1834, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1980, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1834, 1980, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 105, 106, 107, 108, 111, 112, 113, 116, 117, 118, 1645, 1646, 1647, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 104, 109, 110, 114, 115, 1648, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 106, 107, 109, 110, 111, 112, 115, 116, 117, 1645, 1647, 1648, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(104, 105, 108, 113, 114, 118, 1646, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 103, 104, 106, 107, 108, 110, 111, 112, 113, 115, 116, 1646, 1647, 1648, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 105, 109, 114, 117, 118, 1645, 2322)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(58, 60, 61, 77, 133, 134, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 2049, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 74, 75, 76, 135, 136, 1888, 2050, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 75, 76, 77, 133, 134, 135, 136, 1788, 1789, 1790, 1793, 1794, 1795, 2049, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 74, 137, 1787, 1792, 1888, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 74, 75, 76, 77, 133, 134, 136, 137, 1787, 1788, 1789, 1792, 1888, 2049, 2050, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 61, 135, 1790, 1793, 1794, 1795, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 82, 122, 123, 125, 183, 186, 1748, 1749, 1890, 1891, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 124, 184, 185, 1747, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 122, 183, 184, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 82, 123, 124, 125, 185, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 82, 122, 124, 125, 184, 185, 186, 1747, 1749, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 123, 183, 1748, 1890, 1891, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1979, 1980, 2144, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1979, 1980, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1979, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 106, 107, 108, 111, 113, 114, 116, 117, 1645, 1646, 1647, 1676, 1677, 2212, 2213, 2296, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 104, 105, 109, 110, 112, 115, 118, 1648, 2211, 2297, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 105, 106, 107, 108, 109, 110, 114, 115, 116, 1645, 1646, 1648, 1677, 2211, 2212, 2213, 2296, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 111, 112, 113, 117, 118, 1647, 1676, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 105, 106, 107, 109, 111, 112, 113, 114, 116, 118, 1645, 1647, 1648, 2212, 2213, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 108, 110, 115, 117, 1646, 1676, 1677, 2211, 2296, 2297, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 61, 74, 75, 76, 133, 135, 136, 137, 1788, 1789, 1790, 1792, 1794, 1888, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 77, 134, 1787, 1793, 1795, 2049, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 61, 76, 133, 136, 137, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 74, 75, 77, 134, 135, 1787, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 61, 74, 75, 76, 77, 1787, 1789, 1792, 1793, 1794, 1888, 2049, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 133, 134, 135, 136, 137, 1788, 1790, 1795, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 122, 123, 125, 184, 185, 186, 1890, 1891, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 82, 124, 183, 1747, 1748, 1749, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 124, 183, 184, 185, 186, 1747, 1749, 1890, 1891, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 82, 122, 123, 125, 1748, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 82, 122, 123, 124, 125, 183, 185, 1749, 1890, 1891, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 184, 186, 1747, 1748, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1979, 1980, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1979, 1980, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1979, 1980, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 106, 108, 109, 110, 111, 113, 114, 115, 116, 117, 1646, 1647, 1648, 1676, 2296, 2298, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(105, 107, 112, 118, 1645, 1677, 2211, 2212, 2213, 2297, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 104, 107, 109, 110, 112, 113, 114, 115, 116, 118, 1645, 1646, 1676, 1677, 2212, 2213, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 105, 106, 108, 111, 117, 1647, 1648, 2211, 2296, 2297)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 106, 109, 110, 112, 115, 116, 117, 118, 1645, 1646, 1647, 1677, 2211, 2213, 2297, 2298, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 105, 107, 108, 111, 113, 114, 1648, 1676, 2212, 2296, 2323)</t>
+    <t xml:space="preserve">c(133, 137, 1787, 1788, 1790, 1792, 1794, 1795, 1888, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 134, 135, 136, 1789, 1793, 2050)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(134, 135, 136, 137, 1788, 1789, 1790, 1795, 1888, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 1787, 1792, 1793, 1794, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(134, 135, 136, 137, 1788, 1789, 1792, 1793, 1795, 1888, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 1787, 1790, 1794, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + NDF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 122, 123, 125, 185, 186, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 124, 183, 184, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 123, 124, 125, 183, 185, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 122, 184, 186, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 122, 123, 125, 183, 184, 186, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 124, 185, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 2144, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1980, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1980, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1980, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 106, 108, 110, 111, 112, 113, 115, 116, 1645, 1646, 1648, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(105, 107, 109, 114, 117, 118, 1647, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 103, 105, 106, 107, 108, 109, 110, 112, 113, 114, 116, 117, 1648, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 104, 111, 115, 118, 1645, 1646, 1647)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 105, 108, 112, 113, 115, 116, 117, 118, 1646, 1647, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 106, 107, 109, 110, 111, 114, 1645, 1648)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 134, 135, 136, 1788, 1789, 1790, 1792, 1793, 1794, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 137, 1787, 1795, 1888, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 135, 136, 137, 1787, 1788, 1792, 1794, 1888, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 134, 1789, 1790, 1793, 1795, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(135, 136, 137, 1787, 1788, 1790, 1792, 1793, 1794, 1795, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 133, 134, 1789, 1888, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 122, 124, 125, 183, 185, 186, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 123, 184, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 123, 124, 184, 185, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 122, 125, 183, 186)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 122, 124, 125, 184, 186, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 123, 183, 185)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2144:2147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1980, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1980, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 106, 108, 109, 110, 111, 112, 113, 114, 116, 1647, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 105, 107, 115, 117, 118, 1645, 1646, 1648)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 109, 111, 112, 113, 114, 115, 117, 1645, 1646, 1648, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(106, 107, 108, 110, 116, 118, 1647, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 106, 107, 108, 109, 110, 112, 115, 116, 117, 118, 1645, 1646, 1647, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 105, 111, 113, 114, 1648, 2321)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 60, 61, 74, 76, 77, 1671, 2049, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 75, 1888, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 75, 76, 77, 1671, 1888, 2050, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 74, 2049, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 2052, 2053)</t>
+    <t xml:space="preserve">NA</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(79, 80, 82, 122, 124, 125, 1747, 1748, 1749, 1890, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 123, 1891, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 124, 125, 1747, 1748, 1749, 1890, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 82, 122, 123, 1891, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 122, 123, 124, 125, 1747, 1748, 1890, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 82, 1749, 1891, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1832, 1833, 1834, 1980, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1979, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1832, 1833, 1980, 2144, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1834, 1979, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1832, 1834, 1979, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1833, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 118, 1676, 1677, 2213, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 2211, 2212, 2296, 2297)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 118, 1676, 1677, 2211, 2212, 2296, 2297, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 2213, 2298, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 118, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 74, 75, 76, 77, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 1671, 1888, 2049, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 61, 74, 75, 76, 77, 1671, 1888, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 2049, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 61, 74, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 75, 76, 77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 122, 124, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 82, 123, 125, 1747)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 124, 125, 1747, 1749, 1891, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(122, 123, 1748, 1890, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 82, 122, 123, 124, 1749, 1890, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 125, 1747, 1748, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1833, 1834, 1979, 1980, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1832, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1979, 2144, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1834, 1980, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1833, 1834, 1979, 1980, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1832, 2144, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 1677, 2212, 2296, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(118, 1676, 2211, 2213, 2297, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 118, 1676, 2211, 2212, 2213, 2296, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 1677, 2297, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 118, 1677, 2213, 2296, 2297, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1676, 2211, 2212, 2298, 2299, 2323)</t>
+    <t xml:space="preserve">c(78, 122, 123, 124, 125, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 123, 124, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 122, 125, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 122, 124, 125, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 123, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1834, 1980, 2144, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1834, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 1980, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 1834, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 118)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 118, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 118)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 123, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 124, 125, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 122, 123, 125, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 124, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 122, 124, 125, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 123, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1833, 1834, 1980, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 1980, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2144, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 1834, 1980, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 118, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 118, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 118, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 2321, 2322)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(58, 59, 61, 74, 75, 77, 1671, 1888, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 76, 2049, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 61, 74, 75, 76, 77, 2049, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 1671, 1888, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 76, 77, 1671, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 74, 75, 1888, 2049, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 123, 124, 125, 1749, 1890, 1891, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 1747, 1748, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 1748, 1749, 1890, 1891, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(82, 123, 124, 125, 1747, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 82, 122, 124, 125, 1747, 1748, 1749, 1891, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 123, 1890, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1832, 1833, 1980, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1834, 1979, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1834, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1979, 1980, 2144)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1832, 1833, 1834, 1979, 1980, 2144, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 2212, 2213, 2296, 2297, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1677, 2211, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 1677, 2211, 2212, 2213, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(118, 1676, 2296, 2297, 2298, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 1677, 2211, 2212, 2213, 2296, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 118, 1676, 2297, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 74, 75, 77, 1671, 1888, 2050, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 61, 76, 2049, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 74, 75, 76, 1671, 1888, 2049, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 77, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 75, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 74, 76)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 122, 123, 124, 125, 1748, 1749, 1890, 1891, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 82, 1747, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 82, 123, 125, 1747, 1749, 1890, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 122, 124, 1748, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 82, 122, 124, 1748, 1749, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 123, 125, 1747, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1832, 1979, 1980, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1833, 1834, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1833, 1979, 1980, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1834, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1832, 1833, 1834, 1979, 1980, 2144, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 118, 1676, 1677, 2211, 2212, 2297, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 2213, 2296, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 118, 1676, 1677, 2211, 2297, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 2212, 2213, 2296, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 1676, 2211, 2296, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 118, 1677, 2212, 2213, 2298)</t>
+    <t xml:space="preserve">c(79, 80, 122, 124, 125, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 123, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 124, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 123, 125, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 122, 123, 124, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 125, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1834, 1980, 2144, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 2144, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1980, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1834, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 118, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 118, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 123, 124, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 122, 125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 123, 125, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 122, 124, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1980, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 1834, 2144, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 1834, 1980, 2144, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1834, 1980, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 118, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 118, 2321)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(58, 60, 75, 76, 77, 2049, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 74, 1888, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 74, 75, 76, 77, 1888, 2049, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 2050, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 74, 77, 1888, 2049, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 75, 76, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 125, 1747, 1748, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 124, 1749, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 122, 123, 124, 125, 1747, 1748, 1890, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 82, 1749, 1891, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 122, 123, 124, 125, 1747, 1749, 1890, 1891, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 1748, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1979, 1980, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1979, 1980, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1980, 2144, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1979, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 118, 1676, 1677, 2211, 2212, 2213, 2298, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 2296, 2297, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 118, 2211, 2212, 2213, 2296, 2297, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 1676, 1677, 2298, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 118, 1676, 2211, 2212, 2296, 2297, 2298, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 1677, 2213, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 74, 77, 1888, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 61, 75, 76, 2049)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 74, 75, 77, 2049, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 76, 1888, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 61, 74, 75, 76, 2049, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 77, 1888, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 82, 122, 124, 125, 1747, 1748, 1890, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 123, 1749, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 123, 124, 125, 1749, 1890, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(82, 122, 1747, 1748, 1891, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 124, 125, 1747, 1890, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(82, 122, 123, 1748, 1749, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1979, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1980, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1980, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1979, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1979, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1980, 2144, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 118, 1677, 2211, 2213, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 1676, 2212, 2296, 2297)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 1676, 2211, 2297, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 118, 1677, 2212, 2213, 2296)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 118, 2211, 2212, 2296, 2297, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 1676, 1677, 2213, 2299, 2321)</t>
+    <t xml:space="preserve">c(78, 79, 81, 122, 125, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 123, 124, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 125, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 123, 124)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 123, 124, 125, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 122, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1980, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1980, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115:117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 122, 124, 125, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 123, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 122, 123, 124)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(125, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 122, 123, 124, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 125, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1980, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2144:2146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1980, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1980, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 118, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116:118</t>
   </si>
 </sst>
 </file>
@@ -1886,13 +1715,13 @@
         <v>22</v>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O2" t="s">
         <v>23</v>
       </c>
       <c r="P2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="s">
         <v>24</v>
@@ -1942,13 +1771,13 @@
         <v>25</v>
       </c>
       <c r="N3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q3" t="s">
         <v>24</v>
@@ -1998,13 +1827,13 @@
         <v>27</v>
       </c>
       <c r="N4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q4" t="s">
         <v>24</v>
@@ -2054,13 +1883,13 @@
         <v>31</v>
       </c>
       <c r="N5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O5" t="s">
         <v>32</v>
       </c>
       <c r="P5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="s">
         <v>33</v>
@@ -2110,13 +1939,13 @@
         <v>34</v>
       </c>
       <c r="N6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O6" t="s">
         <v>35</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="s">
         <v>33</v>
@@ -2166,13 +1995,13 @@
         <v>36</v>
       </c>
       <c r="N7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O7" t="s">
         <v>37</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="s">
         <v>33</v>
@@ -2222,13 +2051,13 @@
         <v>39</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O8" t="s">
         <v>40</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="s">
         <v>41</v>
@@ -2278,13 +2107,13 @@
         <v>42</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O9" t="s">
         <v>43</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="s">
         <v>41</v>
@@ -2334,13 +2163,13 @@
         <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O10" t="s">
         <v>45</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="s">
         <v>41</v>
@@ -2390,13 +2219,13 @@
         <v>47</v>
       </c>
       <c r="N11" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O11" t="s">
         <v>48</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="s">
         <v>49</v>
@@ -2446,13 +2275,13 @@
         <v>50</v>
       </c>
       <c r="N12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O12" t="s">
         <v>51</v>
       </c>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q12" t="s">
         <v>49</v>
@@ -2502,13 +2331,13 @@
         <v>52</v>
       </c>
       <c r="N13" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O13" t="s">
         <v>53</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q13" t="s">
         <v>49</v>
@@ -2558,13 +2387,13 @@
         <v>55</v>
       </c>
       <c r="N14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O14" t="s">
         <v>56</v>
       </c>
       <c r="P14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q14" t="s">
         <v>24</v>
@@ -2614,13 +2443,13 @@
         <v>57</v>
       </c>
       <c r="N15" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O15" t="s">
         <v>58</v>
       </c>
       <c r="P15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q15" t="s">
         <v>24</v>
@@ -2670,13 +2499,13 @@
         <v>59</v>
       </c>
       <c r="N16" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O16" t="s">
         <v>60</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q16" t="s">
         <v>24</v>
@@ -2726,13 +2555,13 @@
         <v>62</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O17" t="s">
         <v>63</v>
       </c>
       <c r="P17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="s">
         <v>33</v>
@@ -2782,13 +2611,13 @@
         <v>64</v>
       </c>
       <c r="N18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O18" t="s">
         <v>65</v>
       </c>
       <c r="P18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="s">
         <v>33</v>
@@ -2838,13 +2667,13 @@
         <v>66</v>
       </c>
       <c r="N19" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O19" t="s">
         <v>67</v>
       </c>
       <c r="P19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="s">
         <v>33</v>
@@ -2894,13 +2723,13 @@
         <v>69</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O20" t="s">
         <v>70</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="s">
         <v>41</v>
@@ -2950,13 +2779,13 @@
         <v>71</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O21" t="s">
         <v>72</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="s">
         <v>41</v>
@@ -3003,16 +2832,16 @@
         <v>3</v>
       </c>
       <c r="M22" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q22" t="s">
         <v>41</v>
@@ -3062,13 +2891,13 @@
         <v>74</v>
       </c>
       <c r="N23" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O23" t="s">
         <v>75</v>
       </c>
       <c r="P23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q23" t="s">
         <v>49</v>
@@ -3118,13 +2947,13 @@
         <v>76</v>
       </c>
       <c r="N24" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O24" t="s">
         <v>77</v>
       </c>
       <c r="P24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q24" t="s">
         <v>49</v>
@@ -3174,13 +3003,13 @@
         <v>78</v>
       </c>
       <c r="N25" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O25" t="s">
         <v>79</v>
       </c>
       <c r="P25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q25" t="s">
         <v>49</v>
@@ -3221,22 +3050,22 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="s">
         <v>80</v>
       </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="s">
+      <c r="N26" t="n">
+        <v>12</v>
+      </c>
+      <c r="O26" t="s">
         <v>81</v>
       </c>
-      <c r="N26" t="n">
-        <v>20</v>
-      </c>
-      <c r="O26" t="s">
-        <v>82</v>
-      </c>
       <c r="P26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q26" t="s">
         <v>24</v>
@@ -3277,22 +3106,22 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
       </c>
       <c r="M27" t="s">
+        <v>82</v>
+      </c>
+      <c r="N27" t="n">
+        <v>12</v>
+      </c>
+      <c r="O27" t="s">
         <v>83</v>
       </c>
-      <c r="N27" t="n">
-        <v>20</v>
-      </c>
-      <c r="O27" t="s">
-        <v>84</v>
-      </c>
       <c r="P27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="s">
         <v>24</v>
@@ -3333,22 +3162,22 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
       </c>
       <c r="M28" t="s">
+        <v>84</v>
+      </c>
+      <c r="N28" t="n">
+        <v>12</v>
+      </c>
+      <c r="O28" t="s">
         <v>85</v>
       </c>
-      <c r="N28" t="n">
-        <v>20</v>
-      </c>
-      <c r="O28" t="s">
-        <v>86</v>
-      </c>
       <c r="P28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q28" t="s">
         <v>24</v>
@@ -3389,22 +3218,22 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
+        <v>30</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="s">
+        <v>86</v>
+      </c>
+      <c r="N29" t="n">
+        <v>10</v>
+      </c>
+      <c r="O29" t="s">
         <v>87</v>
       </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="s">
-        <v>88</v>
-      </c>
-      <c r="N29" t="n">
-        <v>14</v>
-      </c>
-      <c r="O29" t="s">
-        <v>89</v>
-      </c>
       <c r="P29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="s">
         <v>33</v>
@@ -3445,22 +3274,22 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="L30" t="n">
         <v>2</v>
       </c>
       <c r="M30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N30" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O30" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q30" t="s">
         <v>33</v>
@@ -3501,22 +3330,22 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="L31" t="n">
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N31" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O31" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q31" t="s">
         <v>33</v>
@@ -3557,22 +3386,22 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="s">
         <v>41</v>
@@ -3613,22 +3442,22 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
       </c>
       <c r="M33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q33" t="s">
         <v>41</v>
@@ -3669,22 +3498,22 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
       </c>
       <c r="M34" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q34" t="s">
         <v>41</v>
@@ -3725,22 +3554,22 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N35" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O35" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="P35" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q35" t="s">
         <v>49</v>
@@ -3781,22 +3610,22 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
       </c>
       <c r="M36" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N36" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O36" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P36" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q36" t="s">
         <v>49</v>
@@ -3837,22 +3666,22 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="L37" t="n">
         <v>3</v>
       </c>
       <c r="M37" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N37" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="P37" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q37" t="s">
         <v>49</v>
@@ -3893,22 +3722,22 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N38" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O38" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="P38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q38" t="s">
         <v>24</v>
@@ -3949,22 +3778,22 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
       </c>
       <c r="M39" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N39" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="P39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q39" t="s">
         <v>24</v>
@@ -4005,22 +3834,22 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
       </c>
       <c r="M40" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N40" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q40" t="s">
         <v>24</v>
@@ -4061,22 +3890,22 @@
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
       </c>
       <c r="M41" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N41" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O41" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q41" t="s">
         <v>33</v>
@@ -4117,22 +3946,22 @@
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
       </c>
       <c r="M42" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N42" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q42" t="s">
         <v>33</v>
@@ -4173,22 +4002,22 @@
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="L43" t="n">
         <v>3</v>
       </c>
       <c r="M43" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N43" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O43" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P43" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q43" t="s">
         <v>33</v>
@@ -4229,22 +4058,22 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N44" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O44" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q44" t="s">
         <v>41</v>
@@ -4285,22 +4114,22 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
       </c>
       <c r="M45" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O45" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="s">
         <v>41</v>
@@ -4341,22 +4170,22 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
       </c>
       <c r="M46" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N46" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O46" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="P46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q46" t="s">
         <v>41</v>
@@ -4397,22 +4226,22 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N47" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O47" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="P47" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q47" t="s">
         <v>49</v>
@@ -4453,22 +4282,22 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
       </c>
       <c r="M48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N48" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O48" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P48" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q48" t="s">
         <v>49</v>
@@ -4509,22 +4338,22 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="L49" t="n">
         <v>3</v>
       </c>
       <c r="M49" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N49" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O49" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="P49" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q49" t="s">
         <v>49</v>
@@ -4565,22 +4394,22 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
+        <v>128</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="s">
+        <v>129</v>
+      </c>
+      <c r="N50" t="n">
+        <v>12</v>
+      </c>
+      <c r="O50" t="s">
         <v>130</v>
       </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" t="s">
-        <v>131</v>
-      </c>
-      <c r="N50" t="n">
-        <v>20</v>
-      </c>
-      <c r="O50" t="s">
-        <v>132</v>
-      </c>
       <c r="P50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q50" t="s">
         <v>24</v>
@@ -4621,22 +4450,22 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
       </c>
       <c r="M51" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N51" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O51" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="P51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q51" t="s">
         <v>24</v>
@@ -4677,22 +4506,22 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
       </c>
       <c r="M52" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N52" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O52" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="P52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q52" t="s">
         <v>24</v>
@@ -4733,22 +4562,22 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
+        <v>135</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="s">
+        <v>136</v>
+      </c>
+      <c r="N53" t="n">
+        <v>10</v>
+      </c>
+      <c r="O53" t="s">
         <v>137</v>
       </c>
-      <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="s">
-        <v>138</v>
-      </c>
-      <c r="N53" t="n">
-        <v>14</v>
-      </c>
-      <c r="O53" t="s">
-        <v>139</v>
-      </c>
       <c r="P53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q53" t="s">
         <v>33</v>
@@ -4789,22 +4618,22 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
       </c>
       <c r="M54" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N54" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O54" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="P54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q54" t="s">
         <v>33</v>
@@ -4845,22 +4674,22 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
       </c>
       <c r="M55" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N55" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O55" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P55" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q55" t="s">
         <v>33</v>
@@ -4901,22 +4730,22 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N56" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O56" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q56" t="s">
         <v>41</v>
@@ -4957,22 +4786,22 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
       </c>
       <c r="M57" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N57" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="P57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q57" t="s">
         <v>41</v>
@@ -5013,22 +4842,22 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
       </c>
       <c r="M58" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N58" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O58" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q58" t="s">
         <v>41</v>
@@ -5069,22 +4898,22 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N59" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O59" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P59" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q59" t="s">
         <v>49</v>
@@ -5125,22 +4954,22 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
       </c>
       <c r="M60" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O60" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P60" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q60" t="s">
         <v>49</v>
@@ -5181,22 +5010,22 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
       </c>
       <c r="M61" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N61" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O61" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P61" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q61" t="s">
         <v>49</v>
@@ -5237,22 +5066,22 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N62" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O62" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P62" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q62" t="s">
         <v>24</v>
@@ -5293,22 +5122,22 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
       </c>
       <c r="M63" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N63" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O63" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q63" t="s">
         <v>24</v>
@@ -5349,22 +5178,22 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
       </c>
       <c r="M64" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N64" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O64" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="P64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q64" t="s">
         <v>24</v>
@@ -5405,22 +5234,22 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N65" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O65" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P65" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q65" t="s">
         <v>33</v>
@@ -5461,22 +5290,22 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
       </c>
       <c r="M66" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N66" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O66" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P66" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q66" t="s">
         <v>33</v>
@@ -5517,22 +5346,22 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
       </c>
       <c r="M67" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N67" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O67" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P67" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q67" t="s">
         <v>33</v>
@@ -5573,22 +5402,22 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N68" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O68" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q68" t="s">
         <v>41</v>
@@ -5629,22 +5458,22 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
       </c>
       <c r="M69" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N69" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O69" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="P69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q69" t="s">
         <v>41</v>
@@ -5685,22 +5514,22 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
       </c>
       <c r="M70" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="N70" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O70" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="P70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q70" t="s">
         <v>41</v>
@@ -5741,7 +5570,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
@@ -5750,13 +5579,13 @@
         <v>172</v>
       </c>
       <c r="N71" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O71" t="s">
         <v>173</v>
       </c>
       <c r="P71" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q71" t="s">
         <v>49</v>
@@ -5797,7 +5626,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
@@ -5806,13 +5635,13 @@
         <v>174</v>
       </c>
       <c r="N72" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O72" t="s">
         <v>175</v>
       </c>
       <c r="P72" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q72" t="s">
         <v>49</v>
@@ -5853,7 +5682,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -5862,13 +5691,13 @@
         <v>176</v>
       </c>
       <c r="N73" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O73" t="s">
         <v>177</v>
       </c>
       <c r="P73" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q73" t="s">
         <v>49</v>
@@ -5918,13 +5747,13 @@
         <v>179</v>
       </c>
       <c r="N74" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O74" t="s">
         <v>180</v>
       </c>
       <c r="P74" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q74" t="s">
         <v>24</v>
@@ -5974,13 +5803,13 @@
         <v>181</v>
       </c>
       <c r="N75" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O75" t="s">
         <v>182</v>
       </c>
       <c r="P75" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q75" t="s">
         <v>24</v>
@@ -6030,13 +5859,13 @@
         <v>183</v>
       </c>
       <c r="N76" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O76" t="s">
         <v>184</v>
       </c>
       <c r="P76" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q76" t="s">
         <v>24</v>
@@ -6086,13 +5915,13 @@
         <v>186</v>
       </c>
       <c r="N77" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O77" t="s">
         <v>187</v>
       </c>
       <c r="P77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q77" t="s">
         <v>188</v>
@@ -6142,13 +5971,13 @@
         <v>189</v>
       </c>
       <c r="N78" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O78" t="s">
         <v>190</v>
       </c>
       <c r="P78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q78" t="s">
         <v>188</v>
@@ -6198,13 +6027,13 @@
         <v>191</v>
       </c>
       <c r="N79" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O79" t="s">
         <v>192</v>
       </c>
       <c r="P79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q79" t="s">
         <v>188</v>
@@ -6254,13 +6083,13 @@
         <v>193</v>
       </c>
       <c r="N80" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O80" t="s">
         <v>194</v>
       </c>
       <c r="P80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q80" t="s">
         <v>41</v>
@@ -6310,13 +6139,13 @@
         <v>195</v>
       </c>
       <c r="N81" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O81" t="s">
         <v>196</v>
       </c>
       <c r="P81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q81" t="s">
         <v>41</v>
@@ -6366,13 +6195,13 @@
         <v>197</v>
       </c>
       <c r="N82" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O82" t="s">
         <v>198</v>
       </c>
       <c r="P82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q82" t="s">
         <v>41</v>
@@ -6422,13 +6251,13 @@
         <v>199</v>
       </c>
       <c r="N83" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O83" t="s">
         <v>200</v>
       </c>
       <c r="P83" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q83" t="s">
         <v>49</v>
@@ -6478,13 +6307,13 @@
         <v>201</v>
       </c>
       <c r="N84" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O84" t="s">
         <v>202</v>
       </c>
       <c r="P84" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q84" t="s">
         <v>49</v>
@@ -6534,13 +6363,13 @@
         <v>203</v>
       </c>
       <c r="N85" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O85" t="s">
         <v>204</v>
       </c>
       <c r="P85" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q85" t="s">
         <v>49</v>
@@ -6590,13 +6419,13 @@
         <v>205</v>
       </c>
       <c r="N86" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O86" t="s">
         <v>206</v>
       </c>
       <c r="P86" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q86" t="s">
         <v>24</v>
@@ -6646,13 +6475,13 @@
         <v>207</v>
       </c>
       <c r="N87" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O87" t="s">
         <v>208</v>
       </c>
       <c r="P87" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q87" t="s">
         <v>24</v>
@@ -6702,13 +6531,13 @@
         <v>209</v>
       </c>
       <c r="N88" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O88" t="s">
         <v>210</v>
       </c>
       <c r="P88" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q88" t="s">
         <v>24</v>
@@ -6758,13 +6587,13 @@
         <v>211</v>
       </c>
       <c r="N89" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O89" t="s">
         <v>212</v>
       </c>
       <c r="P89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q89" t="s">
         <v>188</v>
@@ -6814,13 +6643,13 @@
         <v>213</v>
       </c>
       <c r="N90" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O90" t="s">
         <v>214</v>
       </c>
       <c r="P90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q90" t="s">
         <v>188</v>
@@ -6870,13 +6699,13 @@
         <v>215</v>
       </c>
       <c r="N91" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O91" t="s">
         <v>216</v>
       </c>
       <c r="P91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q91" t="s">
         <v>188</v>
@@ -6923,16 +6752,16 @@
         <v>1</v>
       </c>
       <c r="M92" t="s">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="N92" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O92" t="s">
-        <v>218</v>
+        <v>147</v>
       </c>
       <c r="P92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q92" t="s">
         <v>41</v>
@@ -6979,16 +6808,16 @@
         <v>2</v>
       </c>
       <c r="M93" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N93" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O93" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="P93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q93" t="s">
         <v>41</v>
@@ -7035,16 +6864,16 @@
         <v>3</v>
       </c>
       <c r="M94" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N94" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O94" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q94" t="s">
         <v>41</v>
@@ -7091,16 +6920,16 @@
         <v>1</v>
       </c>
       <c r="M95" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N95" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O95" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P95" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q95" t="s">
         <v>49</v>
@@ -7147,16 +6976,16 @@
         <v>2</v>
       </c>
       <c r="M96" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N96" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O96" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P96" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q96" t="s">
         <v>49</v>
@@ -7203,16 +7032,16 @@
         <v>3</v>
       </c>
       <c r="M97" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N97" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O97" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P97" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q97" t="s">
         <v>49</v>
@@ -7253,22 +7082,22 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
+        <v>227</v>
+      </c>
+      <c r="L98" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" t="s">
+        <v>228</v>
+      </c>
+      <c r="N98" t="n">
+        <v>12</v>
+      </c>
+      <c r="O98" t="s">
         <v>229</v>
       </c>
-      <c r="L98" t="n">
-        <v>1</v>
-      </c>
-      <c r="M98" t="s">
-        <v>230</v>
-      </c>
-      <c r="N98" t="n">
-        <v>20</v>
-      </c>
-      <c r="O98" t="s">
-        <v>231</v>
-      </c>
       <c r="P98" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q98" t="s">
         <v>24</v>
@@ -7309,22 +7138,22 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
       </c>
       <c r="M99" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N99" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O99" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P99" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q99" t="s">
         <v>24</v>
@@ -7365,22 +7194,22 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
       </c>
       <c r="M100" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="N100" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O100" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P100" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q100" t="s">
         <v>24</v>
@@ -7421,22 +7250,22 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
+        <v>234</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" t="s">
+        <v>235</v>
+      </c>
+      <c r="N101" t="n">
+        <v>10</v>
+      </c>
+      <c r="O101" t="s">
         <v>236</v>
       </c>
-      <c r="L101" t="n">
-        <v>1</v>
-      </c>
-      <c r="M101" t="s">
-        <v>237</v>
-      </c>
-      <c r="N101" t="n">
-        <v>14</v>
-      </c>
-      <c r="O101" t="s">
-        <v>238</v>
-      </c>
       <c r="P101" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q101" t="s">
         <v>33</v>
@@ -7477,22 +7306,22 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
       </c>
       <c r="M102" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="N102" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O102" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P102" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q102" t="s">
         <v>33</v>
@@ -7533,22 +7362,22 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
       </c>
       <c r="M103" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N103" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O103" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="P103" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q103" t="s">
         <v>33</v>
@@ -7589,22 +7418,22 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N104" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O104" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q104" t="s">
         <v>41</v>
@@ -7645,22 +7474,22 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
       </c>
       <c r="M105" t="s">
-        <v>245</v>
+        <v>71</v>
       </c>
       <c r="N105" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O105" t="s">
-        <v>246</v>
+        <v>72</v>
       </c>
       <c r="P105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q105" t="s">
         <v>41</v>
@@ -7701,22 +7530,22 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
       </c>
       <c r="M106" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N106" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O106" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="P106" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q106" t="s">
         <v>41</v>
@@ -7757,22 +7586,22 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N107" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O107" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="P107" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q107" t="s">
         <v>49</v>
@@ -7813,22 +7642,22 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
       </c>
       <c r="M108" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="N108" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O108" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="P108" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q108" t="s">
         <v>49</v>
@@ -7869,22 +7698,22 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
       </c>
       <c r="M109" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N109" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O109" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="P109" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q109" t="s">
         <v>49</v>
@@ -7925,22 +7754,22 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N110" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O110" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="P110" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q110" t="s">
         <v>24</v>
@@ -7981,22 +7810,22 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
       </c>
       <c r="M111" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N111" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O111" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="P111" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q111" t="s">
         <v>24</v>
@@ -8037,22 +7866,22 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="N112" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O112" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="P112" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q112" t="s">
         <v>24</v>
@@ -8093,22 +7922,22 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="N113" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O113" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="P113" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q113" t="s">
         <v>33</v>
@@ -8149,22 +7978,22 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
       </c>
       <c r="M114" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N114" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O114" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="P114" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q114" t="s">
         <v>33</v>
@@ -8205,22 +8034,22 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
       </c>
       <c r="M115" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="N115" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O115" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="P115" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q115" t="s">
         <v>33</v>
@@ -8261,22 +8090,22 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="N116" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O116" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="P116" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q116" t="s">
         <v>41</v>
@@ -8317,22 +8146,22 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
       </c>
       <c r="M117" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="N117" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O117" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="P117" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q117" t="s">
         <v>41</v>
@@ -8373,22 +8202,22 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
       </c>
       <c r="M118" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="N118" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O118" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="P118" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q118" t="s">
         <v>41</v>
@@ -8429,22 +8258,22 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="N119" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O119" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="P119" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q119" t="s">
         <v>49</v>
@@ -8485,22 +8314,22 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
       </c>
       <c r="M120" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="N120" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O120" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="P120" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q120" t="s">
         <v>49</v>
@@ -8541,22 +8370,22 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
       </c>
       <c r="M121" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="N121" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O121" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="P121" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q121" t="s">
         <v>49</v>
@@ -8597,28 +8426,28 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="N122" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="O122" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="P122" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q122" t="s">
-        <v>282</v>
+        <v>24</v>
       </c>
       <c r="R122" t="s">
-        <v>282</v>
+        <v>24</v>
       </c>
     </row>
     <row r="123">
@@ -8653,28 +8482,28 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
+        <v>275</v>
+      </c>
+      <c r="L123" t="n">
+        <v>2</v>
+      </c>
+      <c r="M123" t="s">
+        <v>278</v>
+      </c>
+      <c r="N123" t="n">
+        <v>12</v>
+      </c>
+      <c r="O123" t="s">
         <v>279</v>
       </c>
-      <c r="L123" t="n">
-        <v>2</v>
-      </c>
-      <c r="M123" t="s">
-        <v>283</v>
-      </c>
-      <c r="N123" t="n">
-        <v>18</v>
-      </c>
-      <c r="O123" t="s">
-        <v>284</v>
-      </c>
       <c r="P123" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q123" t="s">
-        <v>282</v>
+        <v>24</v>
       </c>
       <c r="R123" t="s">
-        <v>282</v>
+        <v>24</v>
       </c>
     </row>
     <row r="124">
@@ -8709,28 +8538,28 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="N124" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="O124" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="P124" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q124" t="s">
-        <v>282</v>
+        <v>24</v>
       </c>
       <c r="R124" t="s">
-        <v>282</v>
+        <v>24</v>
       </c>
     </row>
     <row r="125">
@@ -8765,22 +8594,22 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="N125" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O125" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="P125" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q125" t="s">
         <v>33</v>
@@ -8821,22 +8650,22 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
       </c>
       <c r="M126" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N126" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O126" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="P126" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q126" t="s">
         <v>33</v>
@@ -8877,22 +8706,22 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
+        <v>282</v>
+      </c>
+      <c r="L127" t="n">
+        <v>3</v>
+      </c>
+      <c r="M127" t="s">
         <v>287</v>
       </c>
-      <c r="L127" t="n">
-        <v>3</v>
-      </c>
-      <c r="M127" t="s">
-        <v>292</v>
-      </c>
       <c r="N127" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O127" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P127" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q127" t="s">
         <v>33</v>
@@ -8933,28 +8762,28 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="N128" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O128" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="P128" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q128" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R128" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="129">
@@ -8989,28 +8818,28 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>297</v>
+        <v>97</v>
       </c>
       <c r="N129" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O129" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q129" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R129" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="130">
@@ -9045,28 +8874,28 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="N130" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O130" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="P130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q130" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R130" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="131">
@@ -9101,22 +8930,22 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="N131" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O131" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="P131" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q131" t="s">
         <v>49</v>
@@ -9157,22 +8986,22 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="N132" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O132" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="P132" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q132" t="s">
         <v>49</v>
@@ -9213,22 +9042,22 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="N133" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O133" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="P133" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q133" t="s">
         <v>49</v>
@@ -9269,28 +9098,28 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="N134" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="O134" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="P134" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q134" t="s">
-        <v>282</v>
+        <v>24</v>
       </c>
       <c r="R134" t="s">
-        <v>282</v>
+        <v>24</v>
       </c>
     </row>
     <row r="135">
@@ -9325,28 +9154,28 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="N135" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="O135" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="P135" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q135" t="s">
-        <v>282</v>
+        <v>24</v>
       </c>
       <c r="R135" t="s">
-        <v>282</v>
+        <v>24</v>
       </c>
     </row>
     <row r="136">
@@ -9381,28 +9210,28 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="N136" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="O136" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="P136" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q136" t="s">
-        <v>282</v>
+        <v>24</v>
       </c>
       <c r="R136" t="s">
-        <v>282</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137">
@@ -9437,22 +9266,22 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N137" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O137" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="P137" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q137" t="s">
         <v>33</v>
@@ -9493,22 +9322,22 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N138" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O138" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="P138" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q138" t="s">
         <v>33</v>
@@ -9549,22 +9378,22 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="N139" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O139" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="P139" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q139" t="s">
         <v>33</v>
@@ -9578,7 +9407,7 @@
         <v>277</v>
       </c>
       <c r="B140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -9605,28 +9434,28 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="N140" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O140" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="P140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q140" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R140" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="141">
@@ -9634,7 +9463,7 @@
         <v>278</v>
       </c>
       <c r="B141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -9661,28 +9490,28 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="N141" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O141" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="P141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q141" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R141" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="142">
@@ -9690,7 +9519,7 @@
         <v>279</v>
       </c>
       <c r="B142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -9717,28 +9546,28 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="N142" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O142" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="P142" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q142" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R142" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="143">
@@ -9773,22 +9602,22 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="N143" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O143" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="P143" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q143" t="s">
         <v>49</v>
@@ -9829,22 +9658,22 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="N144" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O144" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="P144" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q144" t="s">
         <v>49</v>
@@ -9885,22 +9714,22 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="N145" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O145" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P145" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q145" t="s">
         <v>49</v>
@@ -9914,7 +9743,7 @@
         <v>289</v>
       </c>
       <c r="B146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -9941,28 +9770,24 @@
         <v>3</v>
       </c>
       <c r="K146" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L146" t="n">
         <v>1</v>
       </c>
       <c r="M146" t="s">
-        <v>332</v>
-      </c>
-      <c r="N146" t="n">
-        <v>11</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N146"/>
       <c r="O146" t="s">
-        <v>333</v>
-      </c>
-      <c r="P146" t="n">
-        <v>6</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P146"/>
       <c r="Q146" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="R146" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="147">
@@ -9970,7 +9795,7 @@
         <v>290</v>
       </c>
       <c r="B147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -9997,28 +9822,24 @@
         <v>3</v>
       </c>
       <c r="K147" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L147" t="n">
         <v>2</v>
       </c>
       <c r="M147" t="s">
-        <v>335</v>
-      </c>
-      <c r="N147" t="n">
-        <v>11</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N147"/>
       <c r="O147" t="s">
-        <v>336</v>
-      </c>
-      <c r="P147" t="n">
-        <v>6</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P147"/>
       <c r="Q147" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="R147" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="148">
@@ -10026,7 +9847,7 @@
         <v>291</v>
       </c>
       <c r="B148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -10053,28 +9874,24 @@
         <v>3</v>
       </c>
       <c r="K148" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L148" t="n">
         <v>3</v>
       </c>
       <c r="M148" t="s">
-        <v>337</v>
-      </c>
-      <c r="N148" t="n">
-        <v>11</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N148"/>
       <c r="O148" t="s">
-        <v>338</v>
-      </c>
-      <c r="P148" t="n">
-        <v>6</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P148"/>
       <c r="Q148" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="R148" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="149">
@@ -10109,28 +9926,28 @@
         <v>3</v>
       </c>
       <c r="K149" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L149" t="n">
         <v>1</v>
       </c>
       <c r="M149" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="N149" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O149" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="P149" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q149" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R149" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="150">
@@ -10165,28 +9982,28 @@
         <v>3</v>
       </c>
       <c r="K150" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L150" t="n">
         <v>2</v>
       </c>
       <c r="M150" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="N150" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O150" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="P150" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q150" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R150" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="151">
@@ -10221,28 +10038,28 @@
         <v>3</v>
       </c>
       <c r="K151" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L151" t="n">
         <v>3</v>
       </c>
       <c r="M151" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="N151" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O151" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="P151" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q151" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R151" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="152">
@@ -10277,22 +10094,22 @@
         <v>3</v>
       </c>
       <c r="K152" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L152" t="n">
         <v>1</v>
       </c>
       <c r="M152" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="N152" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O152" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="P152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q152" t="s">
         <v>41</v>
@@ -10333,22 +10150,22 @@
         <v>3</v>
       </c>
       <c r="K153" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L153" t="n">
         <v>2</v>
       </c>
       <c r="M153" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="N153" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O153" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="P153" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q153" t="s">
         <v>41</v>
@@ -10389,22 +10206,22 @@
         <v>3</v>
       </c>
       <c r="K154" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L154" t="n">
         <v>3</v>
       </c>
       <c r="M154" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="N154" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O154" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="P154" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q154" t="s">
         <v>41</v>
@@ -10445,28 +10262,28 @@
         <v>3</v>
       </c>
       <c r="K155" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L155" t="n">
         <v>1</v>
       </c>
       <c r="M155" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="N155" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O155" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="P155" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q155" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R155" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="156">
@@ -10501,28 +10318,28 @@
         <v>3</v>
       </c>
       <c r="K156" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L156" t="n">
         <v>2</v>
       </c>
       <c r="M156" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="N156" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O156" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="P156" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q156" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R156" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="157">
@@ -10557,28 +10374,28 @@
         <v>3</v>
       </c>
       <c r="K157" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L157" t="n">
         <v>3</v>
       </c>
       <c r="M157" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="N157" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O157" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="P157" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q157" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R157" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="158">
@@ -10586,7 +10403,7 @@
         <v>313</v>
       </c>
       <c r="B158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C158" t="s">
         <v>18</v>
@@ -10613,28 +10430,24 @@
         <v>3</v>
       </c>
       <c r="K158" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="s">
-        <v>360</v>
-      </c>
-      <c r="N158" t="n">
-        <v>11</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N158"/>
       <c r="O158" t="s">
-        <v>361</v>
-      </c>
-      <c r="P158" t="n">
-        <v>6</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P158"/>
       <c r="Q158" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="R158" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="159">
@@ -10642,7 +10455,7 @@
         <v>314</v>
       </c>
       <c r="B159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C159" t="s">
         <v>18</v>
@@ -10669,28 +10482,24 @@
         <v>3</v>
       </c>
       <c r="K159" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L159" t="n">
         <v>2</v>
       </c>
       <c r="M159" t="s">
-        <v>362</v>
-      </c>
-      <c r="N159" t="n">
-        <v>11</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N159"/>
       <c r="O159" t="s">
-        <v>363</v>
-      </c>
-      <c r="P159" t="n">
-        <v>6</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P159"/>
       <c r="Q159" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="R159" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="160">
@@ -10698,7 +10507,7 @@
         <v>315</v>
       </c>
       <c r="B160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C160" t="s">
         <v>18</v>
@@ -10725,28 +10534,24 @@
         <v>3</v>
       </c>
       <c r="K160" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
       </c>
       <c r="M160" t="s">
-        <v>364</v>
-      </c>
-      <c r="N160" t="n">
-        <v>11</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N160"/>
       <c r="O160" t="s">
-        <v>365</v>
-      </c>
-      <c r="P160" t="n">
-        <v>6</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P160"/>
       <c r="Q160" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="R160" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="161">
@@ -10781,28 +10586,28 @@
         <v>3</v>
       </c>
       <c r="K161" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L161" t="n">
         <v>1</v>
       </c>
       <c r="M161" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="N161" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O161" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="P161" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q161" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R161" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="162">
@@ -10837,28 +10642,28 @@
         <v>3</v>
       </c>
       <c r="K162" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L162" t="n">
         <v>2</v>
       </c>
       <c r="M162" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="N162" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O162" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="P162" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q162" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R162" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="163">
@@ -10893,28 +10698,28 @@
         <v>3</v>
       </c>
       <c r="K163" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
       </c>
       <c r="M163" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="N163" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O163" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="P163" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q163" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R163" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="164">
@@ -10949,22 +10754,22 @@
         <v>3</v>
       </c>
       <c r="K164" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L164" t="n">
         <v>1</v>
       </c>
       <c r="M164" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="N164" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O164" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="P164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q164" t="s">
         <v>41</v>
@@ -11005,22 +10810,22 @@
         <v>3</v>
       </c>
       <c r="K165" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L165" t="n">
         <v>2</v>
       </c>
       <c r="M165" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="N165" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O165" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="P165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q165" t="s">
         <v>41</v>
@@ -11061,22 +10866,22 @@
         <v>3</v>
       </c>
       <c r="K166" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
       </c>
       <c r="M166" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="N166" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O166" t="s">
-        <v>377</v>
+        <v>289</v>
       </c>
       <c r="P166" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q166" t="s">
         <v>41</v>
@@ -11090,7 +10895,7 @@
         <v>331</v>
       </c>
       <c r="B167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C167" t="s">
         <v>18</v>
@@ -11117,28 +10922,28 @@
         <v>3</v>
       </c>
       <c r="K167" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L167" t="n">
         <v>1</v>
       </c>
       <c r="M167" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="N167" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O167" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="P167" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q167" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R167" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="168">
@@ -11146,7 +10951,7 @@
         <v>332</v>
       </c>
       <c r="B168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C168" t="s">
         <v>18</v>
@@ -11173,28 +10978,28 @@
         <v>3</v>
       </c>
       <c r="K168" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L168" t="n">
         <v>2</v>
       </c>
       <c r="M168" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="N168" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O168" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="P168" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q168" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R168" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="169">
@@ -11202,7 +11007,7 @@
         <v>333</v>
       </c>
       <c r="B169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C169" t="s">
         <v>18</v>
@@ -11229,28 +11034,28 @@
         <v>3</v>
       </c>
       <c r="K169" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
       </c>
       <c r="M169" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="N169" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O169" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="P169" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q169" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R169" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="170">
@@ -11258,7 +11063,7 @@
         <v>337</v>
       </c>
       <c r="B170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C170" t="s">
         <v>18</v>
@@ -11285,28 +11090,24 @@
         <v>3</v>
       </c>
       <c r="K170" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="L170" t="n">
         <v>1</v>
       </c>
       <c r="M170" t="s">
-        <v>385</v>
-      </c>
-      <c r="N170" t="n">
-        <v>11</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N170"/>
       <c r="O170" t="s">
-        <v>386</v>
-      </c>
-      <c r="P170" t="n">
-        <v>6</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P170"/>
       <c r="Q170" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="R170" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="171">
@@ -11314,7 +11115,7 @@
         <v>338</v>
       </c>
       <c r="B171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C171" t="s">
         <v>18</v>
@@ -11341,28 +11142,24 @@
         <v>3</v>
       </c>
       <c r="K171" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="L171" t="n">
         <v>2</v>
       </c>
       <c r="M171" t="s">
-        <v>387</v>
-      </c>
-      <c r="N171" t="n">
-        <v>11</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N171"/>
       <c r="O171" t="s">
-        <v>388</v>
-      </c>
-      <c r="P171" t="n">
-        <v>6</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P171"/>
       <c r="Q171" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="R171" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="172">
@@ -11370,7 +11167,7 @@
         <v>339</v>
       </c>
       <c r="B172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C172" t="s">
         <v>18</v>
@@ -11397,28 +11194,24 @@
         <v>3</v>
       </c>
       <c r="K172" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
       </c>
       <c r="M172" t="s">
-        <v>389</v>
-      </c>
-      <c r="N172" t="n">
-        <v>11</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N172"/>
       <c r="O172" t="s">
-        <v>390</v>
-      </c>
-      <c r="P172" t="n">
-        <v>6</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P172"/>
       <c r="Q172" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="R172" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="173">
@@ -11453,28 +11246,28 @@
         <v>3</v>
       </c>
       <c r="K173" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L173" t="n">
         <v>1</v>
       </c>
       <c r="M173" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="N173" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O173" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="P173" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q173" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R173" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="174">
@@ -11509,28 +11302,28 @@
         <v>3</v>
       </c>
       <c r="K174" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L174" t="n">
         <v>2</v>
       </c>
       <c r="M174" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="N174" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O174" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="P174" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q174" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R174" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="175">
@@ -11565,28 +11358,28 @@
         <v>3</v>
       </c>
       <c r="K175" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L175" t="n">
         <v>3</v>
       </c>
       <c r="M175" t="s">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="N175" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O175" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="P175" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q175" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R175" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="176">
@@ -11621,22 +11414,22 @@
         <v>3</v>
       </c>
       <c r="K176" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="L176" t="n">
         <v>1</v>
       </c>
       <c r="M176" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="N176" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O176" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="P176" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q176" t="s">
         <v>41</v>
@@ -11677,22 +11470,22 @@
         <v>3</v>
       </c>
       <c r="K177" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="L177" t="n">
         <v>2</v>
       </c>
       <c r="M177" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="N177" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O177" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="P177" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q177" t="s">
         <v>41</v>
@@ -11733,22 +11526,22 @@
         <v>3</v>
       </c>
       <c r="K178" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="L178" t="n">
         <v>3</v>
       </c>
       <c r="M178" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="N178" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O178" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="P178" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q178" t="s">
         <v>41</v>
@@ -11789,28 +11582,28 @@
         <v>3</v>
       </c>
       <c r="K179" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L179" t="n">
         <v>1</v>
       </c>
       <c r="M179" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="N179" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O179" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="P179" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q179" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R179" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="180">
@@ -11845,28 +11638,28 @@
         <v>3</v>
       </c>
       <c r="K180" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L180" t="n">
         <v>2</v>
       </c>
       <c r="M180" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="N180" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O180" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="P180" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q180" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R180" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="181">
@@ -11901,28 +11694,28 @@
         <v>3</v>
       </c>
       <c r="K181" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L181" t="n">
         <v>3</v>
       </c>
       <c r="M181" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="N181" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O181" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
       <c r="P181" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q181" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R181" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="182">
@@ -11930,7 +11723,7 @@
         <v>361</v>
       </c>
       <c r="B182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C182" t="s">
         <v>18</v>
@@ -11957,28 +11750,24 @@
         <v>3</v>
       </c>
       <c r="K182" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="L182" t="n">
         <v>1</v>
       </c>
       <c r="M182" t="s">
-        <v>409</v>
-      </c>
-      <c r="N182" t="n">
-        <v>11</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N182"/>
       <c r="O182" t="s">
-        <v>410</v>
-      </c>
-      <c r="P182" t="n">
-        <v>6</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P182"/>
       <c r="Q182" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="R182" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="183">
@@ -11986,7 +11775,7 @@
         <v>362</v>
       </c>
       <c r="B183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C183" t="s">
         <v>18</v>
@@ -12013,28 +11802,24 @@
         <v>3</v>
       </c>
       <c r="K183" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="L183" t="n">
         <v>2</v>
       </c>
       <c r="M183" t="s">
-        <v>411</v>
-      </c>
-      <c r="N183" t="n">
-        <v>11</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N183"/>
       <c r="O183" t="s">
-        <v>412</v>
-      </c>
-      <c r="P183" t="n">
-        <v>6</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P183"/>
       <c r="Q183" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="R183" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="184">
@@ -12042,7 +11827,7 @@
         <v>363</v>
       </c>
       <c r="B184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C184" t="s">
         <v>18</v>
@@ -12069,28 +11854,24 @@
         <v>3</v>
       </c>
       <c r="K184" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="L184" t="n">
         <v>3</v>
       </c>
       <c r="M184" t="s">
-        <v>413</v>
-      </c>
-      <c r="N184" t="n">
-        <v>11</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N184"/>
       <c r="O184" t="s">
-        <v>414</v>
-      </c>
-      <c r="P184" t="n">
-        <v>6</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P184"/>
       <c r="Q184" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="R184" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="185">
@@ -12125,28 +11906,28 @@
         <v>3</v>
       </c>
       <c r="K185" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L185" t="n">
         <v>1</v>
       </c>
       <c r="M185" t="s">
-        <v>415</v>
+        <v>383</v>
       </c>
       <c r="N185" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O185" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="P185" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q185" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R185" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="186">
@@ -12181,28 +11962,28 @@
         <v>3</v>
       </c>
       <c r="K186" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L186" t="n">
         <v>2</v>
       </c>
       <c r="M186" t="s">
-        <v>417</v>
+        <v>365</v>
       </c>
       <c r="N186" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O186" t="s">
-        <v>418</v>
+        <v>366</v>
       </c>
       <c r="P186" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q186" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R186" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="187">
@@ -12237,28 +12018,28 @@
         <v>3</v>
       </c>
       <c r="K187" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L187" t="n">
         <v>3</v>
       </c>
       <c r="M187" t="s">
-        <v>419</v>
+        <v>385</v>
       </c>
       <c r="N187" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O187" t="s">
-        <v>420</v>
+        <v>386</v>
       </c>
       <c r="P187" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q187" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R187" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="188">
@@ -12293,22 +12074,22 @@
         <v>3</v>
       </c>
       <c r="K188" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="L188" t="n">
         <v>1</v>
       </c>
       <c r="M188" t="s">
-        <v>421</v>
+        <v>387</v>
       </c>
       <c r="N188" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O188" t="s">
-        <v>422</v>
+        <v>388</v>
       </c>
       <c r="P188" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q188" t="s">
         <v>41</v>
@@ -12349,22 +12130,22 @@
         <v>3</v>
       </c>
       <c r="K189" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="L189" t="n">
         <v>2</v>
       </c>
       <c r="M189" t="s">
-        <v>423</v>
+        <v>389</v>
       </c>
       <c r="N189" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O189" t="s">
-        <v>424</v>
+        <v>390</v>
       </c>
       <c r="P189" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q189" t="s">
         <v>41</v>
@@ -12405,22 +12186,22 @@
         <v>3</v>
       </c>
       <c r="K190" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="L190" t="n">
         <v>3</v>
       </c>
       <c r="M190" t="s">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="N190" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O190" t="s">
-        <v>426</v>
+        <v>392</v>
       </c>
       <c r="P190" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q190" t="s">
         <v>41</v>
@@ -12434,7 +12215,7 @@
         <v>379</v>
       </c>
       <c r="B191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C191" t="s">
         <v>18</v>
@@ -12461,28 +12242,28 @@
         <v>3</v>
       </c>
       <c r="K191" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L191" t="n">
         <v>1</v>
       </c>
       <c r="M191" t="s">
-        <v>427</v>
+        <v>393</v>
       </c>
       <c r="N191" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O191" t="s">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="P191" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q191" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R191" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="192">
@@ -12490,7 +12271,7 @@
         <v>380</v>
       </c>
       <c r="B192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C192" t="s">
         <v>18</v>
@@ -12517,28 +12298,28 @@
         <v>3</v>
       </c>
       <c r="K192" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L192" t="n">
         <v>2</v>
       </c>
       <c r="M192" t="s">
-        <v>429</v>
+        <v>393</v>
       </c>
       <c r="N192" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O192" t="s">
-        <v>430</v>
+        <v>394</v>
       </c>
       <c r="P192" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q192" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R192" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="193">
@@ -12546,7 +12327,7 @@
         <v>381</v>
       </c>
       <c r="B193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C193" t="s">
         <v>18</v>
@@ -12573,28 +12354,28 @@
         <v>3</v>
       </c>
       <c r="K193" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L193" t="n">
         <v>3</v>
       </c>
       <c r="M193" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
       <c r="N193" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O193" t="s">
-        <v>432</v>
+        <v>396</v>
       </c>
       <c r="P193" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q193" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R193" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="194">
@@ -12602,7 +12383,7 @@
         <v>385</v>
       </c>
       <c r="B194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C194" t="s">
         <v>18</v>
@@ -12629,28 +12410,24 @@
         <v>3</v>
       </c>
       <c r="K194" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="L194" t="n">
         <v>1</v>
       </c>
       <c r="M194" t="s">
-        <v>434</v>
-      </c>
-      <c r="N194" t="n">
-        <v>10</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N194"/>
       <c r="O194" t="s">
-        <v>435</v>
-      </c>
-      <c r="P194" t="n">
-        <v>5</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P194"/>
       <c r="Q194" t="s">
-        <v>436</v>
+        <v>326</v>
       </c>
       <c r="R194" t="s">
-        <v>436</v>
+        <v>326</v>
       </c>
     </row>
     <row r="195">
@@ -12658,7 +12435,7 @@
         <v>386</v>
       </c>
       <c r="B195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C195" t="s">
         <v>18</v>
@@ -12685,28 +12462,24 @@
         <v>3</v>
       </c>
       <c r="K195" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="L195" t="n">
         <v>2</v>
       </c>
       <c r="M195" t="s">
-        <v>437</v>
-      </c>
-      <c r="N195" t="n">
-        <v>10</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N195"/>
       <c r="O195" t="s">
-        <v>438</v>
-      </c>
-      <c r="P195" t="n">
-        <v>5</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P195"/>
       <c r="Q195" t="s">
-        <v>436</v>
+        <v>326</v>
       </c>
       <c r="R195" t="s">
-        <v>436</v>
+        <v>326</v>
       </c>
     </row>
     <row r="196">
@@ -12714,7 +12487,7 @@
         <v>387</v>
       </c>
       <c r="B196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C196" t="s">
         <v>18</v>
@@ -12741,28 +12514,24 @@
         <v>3</v>
       </c>
       <c r="K196" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="L196" t="n">
         <v>3</v>
       </c>
       <c r="M196" t="s">
-        <v>439</v>
-      </c>
-      <c r="N196" t="n">
-        <v>10</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N196"/>
       <c r="O196" t="s">
-        <v>440</v>
-      </c>
-      <c r="P196" t="n">
-        <v>5</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P196"/>
       <c r="Q196" t="s">
-        <v>436</v>
+        <v>326</v>
       </c>
       <c r="R196" t="s">
-        <v>436</v>
+        <v>326</v>
       </c>
     </row>
     <row r="197">
@@ -12797,28 +12566,28 @@
         <v>3</v>
       </c>
       <c r="K197" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L197" t="n">
         <v>1</v>
       </c>
       <c r="M197" t="s">
-        <v>441</v>
+        <v>398</v>
       </c>
       <c r="N197" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O197" t="s">
-        <v>442</v>
+        <v>399</v>
       </c>
       <c r="P197" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q197" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R197" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="198">
@@ -12853,28 +12622,28 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L198" t="n">
         <v>2</v>
       </c>
       <c r="M198" t="s">
-        <v>443</v>
+        <v>400</v>
       </c>
       <c r="N198" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O198" t="s">
-        <v>444</v>
+        <v>401</v>
       </c>
       <c r="P198" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q198" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R198" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="199">
@@ -12909,28 +12678,28 @@
         <v>3</v>
       </c>
       <c r="K199" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L199" t="n">
         <v>3</v>
       </c>
       <c r="M199" t="s">
-        <v>445</v>
+        <v>402</v>
       </c>
       <c r="N199" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O199" t="s">
-        <v>446</v>
+        <v>403</v>
       </c>
       <c r="P199" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q199" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R199" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="200">
@@ -12965,28 +12734,28 @@
         <v>3</v>
       </c>
       <c r="K200" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="L200" t="n">
         <v>1</v>
       </c>
       <c r="M200" t="s">
-        <v>447</v>
+        <v>147</v>
       </c>
       <c r="N200" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O200" t="s">
-        <v>448</v>
+        <v>404</v>
       </c>
       <c r="P200" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q200" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R200" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="201">
@@ -13021,28 +12790,28 @@
         <v>3</v>
       </c>
       <c r="K201" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="L201" t="n">
         <v>2</v>
       </c>
       <c r="M201" t="s">
-        <v>449</v>
+        <v>405</v>
       </c>
       <c r="N201" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O201" t="s">
-        <v>450</v>
+        <v>406</v>
       </c>
       <c r="P201" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q201" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R201" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="202">
@@ -13077,28 +12846,28 @@
         <v>3</v>
       </c>
       <c r="K202" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="L202" t="n">
         <v>3</v>
       </c>
       <c r="M202" t="s">
-        <v>451</v>
+        <v>218</v>
       </c>
       <c r="N202" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O202" t="s">
-        <v>452</v>
+        <v>407</v>
       </c>
       <c r="P202" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q202" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R202" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="203">
@@ -13133,28 +12902,28 @@
         <v>3</v>
       </c>
       <c r="K203" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L203" t="n">
         <v>1</v>
       </c>
       <c r="M203" t="s">
-        <v>453</v>
+        <v>408</v>
       </c>
       <c r="N203" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O203" t="s">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="P203" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q203" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R203" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="204">
@@ -13189,28 +12958,28 @@
         <v>3</v>
       </c>
       <c r="K204" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L204" t="n">
         <v>2</v>
       </c>
       <c r="M204" t="s">
-        <v>455</v>
+        <v>408</v>
       </c>
       <c r="N204" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O204" t="s">
-        <v>456</v>
+        <v>409</v>
       </c>
       <c r="P204" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q204" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R204" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="205">
@@ -13245,28 +13014,28 @@
         <v>3</v>
       </c>
       <c r="K205" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L205" t="n">
         <v>3</v>
       </c>
       <c r="M205" t="s">
-        <v>457</v>
+        <v>358</v>
       </c>
       <c r="N205" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O205" t="s">
-        <v>458</v>
+        <v>359</v>
       </c>
       <c r="P205" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q205" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R205" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="206">
@@ -13274,7 +13043,7 @@
         <v>409</v>
       </c>
       <c r="B206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C206" t="s">
         <v>18</v>
@@ -13301,28 +13070,24 @@
         <v>3</v>
       </c>
       <c r="K206" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="s">
-        <v>459</v>
-      </c>
-      <c r="N206" t="n">
-        <v>10</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N206"/>
       <c r="O206" t="s">
-        <v>460</v>
-      </c>
-      <c r="P206" t="n">
-        <v>5</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P206"/>
       <c r="Q206" t="s">
-        <v>436</v>
+        <v>326</v>
       </c>
       <c r="R206" t="s">
-        <v>436</v>
+        <v>326</v>
       </c>
     </row>
     <row r="207">
@@ -13330,7 +13095,7 @@
         <v>410</v>
       </c>
       <c r="B207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C207" t="s">
         <v>18</v>
@@ -13357,28 +13122,24 @@
         <v>3</v>
       </c>
       <c r="K207" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="L207" t="n">
         <v>2</v>
       </c>
       <c r="M207" t="s">
-        <v>461</v>
-      </c>
-      <c r="N207" t="n">
-        <v>10</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N207"/>
       <c r="O207" t="s">
-        <v>462</v>
-      </c>
-      <c r="P207" t="n">
-        <v>5</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P207"/>
       <c r="Q207" t="s">
-        <v>436</v>
+        <v>326</v>
       </c>
       <c r="R207" t="s">
-        <v>436</v>
+        <v>326</v>
       </c>
     </row>
     <row r="208">
@@ -13386,7 +13147,7 @@
         <v>411</v>
       </c>
       <c r="B208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C208" t="s">
         <v>18</v>
@@ -13413,28 +13174,24 @@
         <v>3</v>
       </c>
       <c r="K208" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="L208" t="n">
         <v>3</v>
       </c>
       <c r="M208" t="s">
-        <v>463</v>
-      </c>
-      <c r="N208" t="n">
-        <v>10</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N208"/>
       <c r="O208" t="s">
-        <v>464</v>
-      </c>
-      <c r="P208" t="n">
-        <v>5</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="P208"/>
       <c r="Q208" t="s">
-        <v>436</v>
+        <v>326</v>
       </c>
       <c r="R208" t="s">
-        <v>436</v>
+        <v>326</v>
       </c>
     </row>
     <row r="209">
@@ -13469,28 +13226,28 @@
         <v>3</v>
       </c>
       <c r="K209" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L209" t="n">
         <v>1</v>
       </c>
       <c r="M209" t="s">
-        <v>465</v>
+        <v>410</v>
       </c>
       <c r="N209" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O209" t="s">
-        <v>466</v>
+        <v>411</v>
       </c>
       <c r="P209" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q209" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R209" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="210">
@@ -13525,28 +13282,28 @@
         <v>3</v>
       </c>
       <c r="K210" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L210" t="n">
         <v>2</v>
       </c>
       <c r="M210" t="s">
-        <v>467</v>
+        <v>412</v>
       </c>
       <c r="N210" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O210" t="s">
-        <v>468</v>
+        <v>413</v>
       </c>
       <c r="P210" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q210" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R210" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="211">
@@ -13581,28 +13338,28 @@
         <v>3</v>
       </c>
       <c r="K211" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L211" t="n">
         <v>3</v>
       </c>
       <c r="M211" t="s">
-        <v>469</v>
+        <v>414</v>
       </c>
       <c r="N211" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O211" t="s">
-        <v>470</v>
+        <v>415</v>
       </c>
       <c r="P211" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q211" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
       <c r="R211" t="s">
-        <v>342</v>
+        <v>188</v>
       </c>
     </row>
     <row r="212">
@@ -13610,7 +13367,7 @@
         <v>421</v>
       </c>
       <c r="B212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C212" t="s">
         <v>18</v>
@@ -13637,28 +13394,28 @@
         <v>3</v>
       </c>
       <c r="K212" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="L212" t="n">
         <v>1</v>
       </c>
       <c r="M212" t="s">
-        <v>471</v>
+        <v>416</v>
       </c>
       <c r="N212" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O212" t="s">
-        <v>472</v>
+        <v>417</v>
       </c>
       <c r="P212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q212" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R212" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="213">
@@ -13666,7 +13423,7 @@
         <v>422</v>
       </c>
       <c r="B213" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C213" t="s">
         <v>18</v>
@@ -13693,28 +13450,28 @@
         <v>3</v>
       </c>
       <c r="K213" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="L213" t="n">
         <v>2</v>
       </c>
       <c r="M213" t="s">
-        <v>473</v>
+        <v>418</v>
       </c>
       <c r="N213" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O213" t="s">
-        <v>474</v>
+        <v>419</v>
       </c>
       <c r="P213" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q213" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R213" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="214">
@@ -13722,7 +13479,7 @@
         <v>423</v>
       </c>
       <c r="B214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C214" t="s">
         <v>18</v>
@@ -13749,28 +13506,28 @@
         <v>3</v>
       </c>
       <c r="K214" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="L214" t="n">
         <v>3</v>
       </c>
       <c r="M214" t="s">
-        <v>475</v>
+        <v>420</v>
       </c>
       <c r="N214" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O214" t="s">
-        <v>476</v>
+        <v>421</v>
       </c>
       <c r="P214" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q214" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R214" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="215">
@@ -13778,7 +13535,7 @@
         <v>427</v>
       </c>
       <c r="B215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C215" t="s">
         <v>18</v>
@@ -13805,28 +13562,28 @@
         <v>3</v>
       </c>
       <c r="K215" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L215" t="n">
         <v>1</v>
       </c>
       <c r="M215" t="s">
-        <v>477</v>
+        <v>393</v>
       </c>
       <c r="N215" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O215" t="s">
-        <v>478</v>
+        <v>394</v>
       </c>
       <c r="P215" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q215" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R215" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="216">
@@ -13834,7 +13591,7 @@
         <v>428</v>
       </c>
       <c r="B216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C216" t="s">
         <v>18</v>
@@ -13861,28 +13618,28 @@
         <v>3</v>
       </c>
       <c r="K216" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L216" t="n">
         <v>2</v>
       </c>
       <c r="M216" t="s">
-        <v>479</v>
+        <v>422</v>
       </c>
       <c r="N216" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O216" t="s">
-        <v>480</v>
+        <v>423</v>
       </c>
       <c r="P216" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q216" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R216" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="217">
@@ -13890,7 +13647,7 @@
         <v>429</v>
       </c>
       <c r="B217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C217" t="s">
         <v>18</v>
@@ -13917,28 +13674,28 @@
         <v>3</v>
       </c>
       <c r="K217" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="L217" t="n">
         <v>3</v>
       </c>
       <c r="M217" t="s">
-        <v>481</v>
+        <v>424</v>
       </c>
       <c r="N217" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O217" t="s">
-        <v>482</v>
+        <v>425</v>
       </c>
       <c r="P217" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q217" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="R217" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_lon_fold_sets.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_lon_fold_sets.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -80,1216 +80,1393 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">c(74, 133, 135, 137, 1787, 1788, 1792, 1793, 1795, 1888, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(134, 136, 1789, 1790, 1794, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 134, 135, 136, 1787, 1788, 1789, 1790, 1792, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 137, 1793, 1794, 1795, 1888, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(134, 135, 1787, 1788, 1790, 1792, 1794, 1795, 1888, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 136, 137, 1789, 1793, 2050)</t>
+    <t xml:space="preserve">c(51, 58, 60, 61, 77, 134, 135, 136, 137, 1671, 1787, 1788, 1790, 1792, 1794, 1795, 1888, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 74, 75, 76, 133, 1789, 1793, 2049, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 61, 74, 75, 134, 135, 136, 1671, 1787, 1789, 1794, 1795, 1888, 2049, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 76, 77, 133, 137, 1788, 1790, 1792, 1793, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 74, 75, 76, 133, 134, 135, 136, 1671, 1788, 1789, 1790, 1792, 1793, 1795, 2049, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 61, 77, 137, 1787, 1794, 1888, 2050, 2053)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 123, 124, 125, 184, 185, 186, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 183, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 123, 124, 125, 183, 184, 185, 186, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 125, 183, 184, 185, 186, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 123, 124, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 124, 183, 184, 185, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 122, 123, 125, 186)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 123, 124, 183, 184, 185, 186, 1747, 1749, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 125, 1748, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 183, 184, 185, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 82, 122, 124, 125, 183, 184, 1747, 1749, 1890, 1891, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 123, 185, 186, 1748, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 123, 124, 125, 185, 186, 1749, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 122, 183, 184, 1747, 1748, 1890)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1833, 1834, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1980, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 1980, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1834, 1980, 2144, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1833, 1980, 2144, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1834, 2145, 2148)</t>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1980, 2144, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1833, 1834, 1979, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1834, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1979, 1980, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1833, 1834, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1834, 1979, 1980, 2144, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1832, 1833, 2146)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(101, 103, 105, 106, 107, 108, 109, 110, 112, 114, 115, 1645, 1646, 1647, 1648, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 104, 111, 113, 116, 117, 118, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 103, 104, 105, 106, 109, 110, 112, 113, 114, 115, 116, 118, 1645, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 107, 108, 111, 117, 1646, 1647, 1648, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 105, 106, 107, 108, 111, 112, 113, 114, 115, 116, 118, 1646, 1647, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 109, 110, 117, 1645, 1648, 2321)</t>
+    <t xml:space="preserve">c(100, 101, 103, 104, 105, 107, 108, 111, 114, 115, 117, 118, 1646, 1648, 1676, 1677, 2211, 2212, 2213, 2297, 2298, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 106, 109, 110, 112, 113, 116, 1645, 1647, 2296, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 104, 106, 107, 109, 110, 111, 112, 114, 115, 117, 1645, 1647, 1676, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 103, 105, 108, 113, 116, 118, 1646, 1648, 1677, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 105, 107, 109, 110, 111, 112, 113, 114, 115, 116, 117, 1645, 1647, 1676, 1677, 2213, 2296, 2297, 2298, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 104, 106, 108, 118, 1646, 1648, 2211, 2212, 2299, 2322)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(133, 134, 135, 136, 1789, 1790, 1792, 1793, 1795, 1888, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 137, 1787, 1788, 1794, 2050, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 134, 135, 136, 137, 1788, 1789, 1792, 1793, 1794, 1795, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 1787, 1790, 1888, 2050, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 136, 137, 1788, 1789, 1792, 1793, 1795, 2050, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(134, 135, 1787, 1790, 1794, 1888, 2052)</t>
+    <t xml:space="preserve">c(51, 59, 60, 61, 77, 134, 136, 137, 1671, 1787, 1789, 1790, 1792, 1793, 1794, 1888, 2049, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 74, 75, 76, 133, 135, 1788, 1795, 2050, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 61, 74, 75, 76, 133, 134, 136, 1671, 1787, 1788, 1789, 1792, 1793, 1794, 1795, 1888, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 77, 135, 137, 1790, 2049, 2050, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 74, 76, 77, 133, 134, 137, 1790, 1792, 1793, 1794, 1795, 1888, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 75, 135, 136, 1671, 1787, 1788, 1789, 2049, 2053)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(79, 80, 123, 125, 183, 185, 186, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 122, 124, 184)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 122, 123, 125, 183, 185, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 124, 184, 186, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 123, 124, 185, 186, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 125, 183, 184, 1891)</t>
+    <t xml:space="preserve">c(80, 81, 124, 125, 184, 185, 186, 1748, 1749, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 82, 122, 123, 183, 1747, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 122, 124, 183, 185, 186, 1747, 1748, 1890, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 82, 123, 125, 184, 1749, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 122, 124, 184, 186, 1748, 1749, 1890, 1891, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 123, 125, 183, 185, 1747, 2006)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1834, 1980, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1834, 1980, 2144, 2145)</t>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1979, 1980, 2144, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 1834, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1833, 1834, 1980, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1832, 1979, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1834, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1979, 1980, 2144, 2145, 2147)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(100, 101, 103, 104, 105, 106, 107, 108, 109, 112, 113, 115, 116, 1645, 1647, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 110, 111, 114, 117, 118, 1646, 1648, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 106, 107, 108, 110, 112, 113, 114, 115, 117, 1646, 1647, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 105, 109, 111, 116, 118, 1645, 1648, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 106, 107, 109, 110, 111, 114, 115, 116, 117, 1646, 1647, 1648, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 105, 108, 112, 113, 118, 1645, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(134, 135, 137, 1787, 1789, 1790, 1792, 1793, 1794, 1795, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 136, 1788, 1888, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 134, 136, 1787, 1788, 1790, 1792, 1795, 2050, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(135, 137, 1789, 1793, 1794, 1888, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(134, 135, 136, 137, 1788, 1789, 1790, 1793, 1794, 1795, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 1787, 1792, 1888, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 122, 123, 124, 125, 183, 184, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 185, 186, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 122, 123, 124, 183, 184, 185, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 125, 186, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 123, 124, 183, 184, 185, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 125, 186, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1834, 1980, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1833, 1980, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1834, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 1834, 1980, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 104, 107, 109, 110, 111, 112, 113, 115, 116, 117, 118, 1646, 1647, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 105, 106, 108, 114, 1645, 1648, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 108, 109, 112, 113, 115, 116, 118, 1646, 1647, 1648, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(106, 107, 110, 111, 114, 117, 1645, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 105, 107, 108, 110, 111, 113, 115, 116, 117, 118, 1646, 1647, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 106, 109, 112, 114, 1645, 1648)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 134, 135, 137, 1788, 1789, 1792, 1794, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(136, 1787, 1790, 1793, 1795, 1888, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 134, 135, 136, 137, 1788, 1792, 1793, 1794, 1795, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 1787, 1789, 1790, 1888, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 134, 135, 136, 137, 1789, 1792, 1793, 1794, 1888, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 1787, 1788, 1790, 1795, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 183, 184, 186, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(123, 124, 125, 185, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 122, 123, 183, 184, 186, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 124, 125, 185, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 122, 124, 183, 184, 186, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 123, 125, 185)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1834, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1833, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 1980, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1834, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1833, 1980, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1834, 2144, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 104, 105, 106, 109, 110, 111, 112, 113, 114, 115, 116, 118, 1648, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 107, 108, 117, 1645, 1646, 1647, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 104, 105, 107, 110, 112, 113, 114, 116, 117, 118, 1645, 1646, 1648, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 106, 108, 109, 111, 115, 1647, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 106, 107, 108, 109, 111, 112, 113, 114, 117, 118, 1648, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 105, 110, 115, 116, 1645, 1646, 1647, 2322)</t>
+    <t xml:space="preserve">c(100, 101, 102, 108, 109, 110, 111, 114, 115, 117, 118, 1645, 1646, 1676, 2211, 2212, 2213, 2296, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 104, 105, 106, 107, 112, 113, 116, 1647, 1648, 1677, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 105, 106, 107, 108, 110, 111, 112, 114, 115, 116, 117, 1645, 1646, 1647, 1648, 1676, 1677, 2212, 2213, 2297)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 104, 109, 113, 118, 2211, 2296, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 106, 107, 110, 111, 112, 113, 114, 117, 118, 1646, 1647, 1676, 1677, 2211, 2212, 2213, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 104, 105, 108, 109, 115, 116, 1645, 1648, 2296, 2297, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 74, 75, 77, 134, 135, 136, 1671, 1787, 1788, 1790, 1794, 1795, 1888, 2049, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 76, 133, 137, 1789, 1792, 1793, 2050, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 134, 136, 1671, 1787, 1788, 1789, 1790, 1793, 1794, 1795, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(76, 77, 133, 135, 137, 1792, 1888, 2049, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 61, 76, 133, 134, 135, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 2049, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 74, 75, 77, 136, 1795, 1888, 2050, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 122, 125, 184, 185, 1747, 1748, 1749, 1891, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(82, 123, 124, 183, 186, 1890, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 82, 122, 123, 124, 183, 184, 185, 186, 1747, 1749, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 125, 1748, 1891, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 82, 123, 124, 125, 183, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 122, 184, 185, 186, 1747)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1832, 1833, 1979, 1980, 2144, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1834, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1833, 1979, 1980, 2144, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1834, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1834, 1979, 1980, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1833, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 107, 108, 110, 111, 114, 115, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2296, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 105, 106, 109, 112, 113, 116, 117, 118, 2297, 2298, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 104, 106, 107, 108, 109, 110, 111, 114, 115, 116, 117, 1646, 1648, 1676, 1677, 2212, 2213, 2297, 2298, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 105, 112, 113, 118, 1645, 1647, 2211, 2296, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 104, 109, 111, 112, 114, 115, 116, 117, 118, 1645, 1646, 1647, 2211, 2212, 2213, 2296, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 105, 106, 107, 108, 110, 113, 1648, 1676, 1677, 2297, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 75, 77, 133, 134, 135, 136, 137, 1787, 1788, 1790, 1792, 1793, 1794, 1795, 2049, 2050, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 61, 74, 76, 1671, 1789, 1888, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 74, 76, 77, 133, 134, 135, 136, 137, 1788, 1792, 1793, 1794, 1888, 2049, 2050, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 75, 1671, 1787, 1789, 1790, 1795, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 74, 75, 76, 77, 134, 135, 136, 137, 1671, 1787, 1790, 1795, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 133, 1788, 1789, 1792, 1793, 1794, 1888, 2049, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 122, 123, 125, 185, 186, 1747, 1890, 1891, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 124, 183, 184, 1748, 1749, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 125, 183, 184, 186, 1890, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(122, 123, 124, 185, 1747, 1748, 1749, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 123, 125, 183, 186, 1747, 1748, 1749, 1890, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 122, 124, 184, 185, 1891, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 1833, 1834, 1979, 1980, 2144, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1833, 1979, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1832, 1834, 1980, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1833, 1834, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1832, 1979, 1980, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 105, 106, 107, 108, 109, 110, 111, 112, 117, 1645, 1647, 1648, 1676, 2211, 2213, 2296, 2297, 2298, 2299, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 104, 113, 114, 115, 116, 118, 1646, 1677, 2212, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 104, 105, 106, 108, 109, 110, 112, 116, 117, 118, 1645, 1647, 1676, 1677, 2211, 2296, 2297, 2298, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 107, 111, 113, 114, 115, 1646, 1648, 2212, 2213, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 104, 106, 107, 108, 109, 110, 111, 114, 115, 118, 1645, 1646, 1647, 1677, 2212, 2213, 2297, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 105, 112, 113, 116, 117, 1648, 1676, 2211, 2296, 2322)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">c(133, 134, 135, 136, 1787, 1790, 1792, 1888, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 137, 1788, 1789, 1793, 1794, 1795)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 136, 137, 1787, 1792, 1793, 1795, 1888, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(134, 135, 1788, 1789, 1790, 1794, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 134, 135, 136, 1787, 1789, 1790, 1792, 1888, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 137, 1788, 1793, 1794, 1795, 2051)</t>
+    <t xml:space="preserve">c(51, 58, 61, 74, 76, 77, 133, 134, 136, 137, 1671, 1787, 1788, 1789, 1790, 1793, 1795, 1888, 2049, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 75, 135, 1792, 1794, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 61, 74, 76, 77, 133, 135, 136, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1795, 1888, 2049, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 75, 134, 137, 1794, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 60, 61, 74, 76, 77, 134, 135, 136, 137, 1671, 1788, 1789, 1790, 1792, 1794, 1795, 1888, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 75, 133, 1787, 1793, 2049, 2050, 2051, 2053)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">c(80, 81, 122, 123, 125, 183, 185, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 124, 184, 186)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 123, 124, 125, 183, 184, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 185, 186, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 122, 123, 124, 125, 183, 184, 185, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 186, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1834, 1980)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1980, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 1834, 1980, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 2144, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 106, 108, 110, 111, 112, 114, 115, 117, 118, 1645, 1648, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 104, 105, 107, 109, 113, 116, 1646, 1647)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 105, 107, 108, 110, 111, 113, 114, 115, 116, 1645, 1647, 1648, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 104, 106, 109, 112, 117, 118, 1646, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 105, 106, 108, 111, 112, 113, 114, 117, 1645, 1646, 1647, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 104, 107, 109, 110, 115, 116, 118, 1648)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 134, 135, 136, 1789, 1790, 1792, 1793, 1794, 1888, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 137, 1787, 1788, 1795, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 134, 1787, 1788, 1790, 1792, 1888, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(135, 136, 137, 1789, 1793, 1794, 1795)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 134, 136, 1788, 1789, 1794, 1888, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(135, 137, 1787, 1790, 1792, 1793, 1795)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 124, 183, 185, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(123, 125, 184, 186, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 125, 183, 184, 186, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(122, 123, 124, 185, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 122, 123, 124, 125, 183, 186, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 184, 185, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 2145, 2147)</t>
+    <t xml:space="preserve">c(79, 80, 81, 82, 123, 124, 125, 184, 186, 1747, 1748, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 183, 185, 1749, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 123, 125, 183, 184, 185, 186, 1890, 1891, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 122, 124, 1747, 1748, 1749, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 122, 123, 124, 184, 186, 1747, 1749, 1890, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 125, 183, 185, 1748, 1891, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1832, 1834, 1979, 1980, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1833, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1833, 1834, 1980, 2144, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1832, 1979, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833, 1979, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1834, 1980, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 105, 106, 107, 108, 110, 112, 113, 115, 117, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2213, 2297, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 109, 111, 114, 116, 2212, 2296, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 107, 108, 111, 112, 113, 116, 118, 1646, 1647, 1648, 1676, 1677, 2211, 2213, 2296, 2297, 2298, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 105, 106, 109, 110, 114, 115, 117, 1645, 2212, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 104, 105, 106, 109, 110, 112, 113, 116, 117, 118, 1645, 1646, 1648, 1677, 2211, 2212, 2213, 2296, 2298, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 107, 108, 111, 114, 115, 1647, 1676, 2297, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 76, 77, 134, 135, 136, 137, 1788, 1789, 1792, 1793, 1795, 1888, 2049, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(75, 133, 1671, 1787, 1790, 1794, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 74, 75, 76, 77, 133, 134, 137, 1788, 1789, 1790, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 135, 136, 1671, 1787, 1792, 1793)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 75, 76, 133, 134, 136, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1795, 1888, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 61, 74, 77, 135, 137, 1794, 2049, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 82, 122, 123, 125, 185, 186, 1747, 1748, 1890, 1891, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 124, 183, 184, 1749, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 82, 122, 124, 185, 186, 1747, 1748, 1749, 1890, 1891, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 123, 125, 183, 184, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 123, 124, 125, 183, 184, 186, 1747, 1748, 1749, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 185, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 1834, 1980, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1979, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1832, 1834, 1979, 1980, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1833, 2144, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1832, 1833, 1834, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1979, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 104, 106, 108, 109, 112, 113, 114, 115, 116, 118, 1645, 1647, 1648, 1676, 1677, 2212, 2213, 2296, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 105, 107, 110, 111, 117, 1646, 2211, 2297, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 106, 107, 108, 111, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1676, 1677, 2213, 2296, 2297, 2298, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 105, 109, 110, 112, 1648, 2211, 2212, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 104, 107, 108, 110, 111, 112, 113, 114, 115, 116, 118, 1645, 1646, 1677, 2212, 2296, 2297, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 105, 106, 109, 117, 1647, 1648, 1676, 2211, 2213, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 61, 75, 76, 77, 134, 136, 1671, 1787, 1788, 1790, 1792, 1795, 1888, 2049, 2050, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 74, 133, 135, 137, 1789, 1793, 1794, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 75, 76, 133, 135, 136, 137, 1671, 1787, 1788, 1790, 1793, 1888, 2049, 2050, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 74, 77, 134, 1789, 1792, 1794, 1795, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 76, 133, 135, 136, 1671, 1787, 1788, 1789, 1793, 1794, 1888, 2049, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 75, 77, 134, 137, 1790, 1792, 1795, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 82, 123, 124, 125, 1747, 1748, 1749, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 122, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 122, 123, 124)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1834, 1980, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1832, 1833, 1979, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1832, 1833, 1834, 1980, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1979, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1979, 1980, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1833, 1834, 2144, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 108, 109, 110, 113, 114, 115, 117, 118, 1647, 1648, 1676, 2211, 2212, 2296, 2298, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(106, 107, 111, 112, 116, 1645, 1646, 1677, 2213, 2297, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 104, 105, 106, 108, 110, 111, 112, 113, 114, 116, 1645, 1646, 1648, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 107, 109, 115, 117, 118, 1647, 1676, 1677, 2211, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 104, 105, 106, 107, 108, 110, 111, 112, 113, 115, 116, 117, 118, 1646, 1648, 1676, 1677, 2211, 2212, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 109, 114, 1645, 1647, 2213, 2296, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 77, 133, 134, 136, 137, 1671, 1787, 1790, 1792, 1793, 2049, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 76, 135, 1788, 1789, 1794, 1795, 1888, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 61, 74, 77, 134, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1795, 1888, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 75, 76, 133, 135, 1794, 2049, 2050, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 76, 77, 133, 134, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1795, 2049, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 74, 75, 135, 136, 1793, 1794, 1888, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 123, 124, 125, 1748, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 1747, 1749, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 122, 125, 1747, 1748, 1749, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 123, 124, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 122, 124, 125, 1748, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 123, 1747, 1749, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1832, 1833, 1834, 1979, 1980, 2144, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1834, 1979, 1980, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1834, 1979, 1980, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 1833, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 105, 106, 109, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2297, 2298, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 107, 108, 110, 111, 112, 113, 2213, 2296, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 107, 109, 110, 111, 113, 114, 115, 116, 1645, 1647, 1648, 1676, 2211, 2212, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(106, 108, 112, 117, 118, 1646, 1677, 2213, 2296, 2297, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 107, 109, 111, 112, 113, 114, 115, 1645, 1676, 1677, 2211, 2213, 2296, 2297, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 108, 110, 116, 117, 118, 1646, 1647, 1648, 2212, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 74, 75, 76, 134, 136, 137, 1671, 1787, 1788, 1790, 1792, 1793, 1794, 1795, 2049, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 77, 133, 135, 1789, 1888, 2050)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 74, 77, 133, 135, 136, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 75, 76, 134, 137, 1671, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 60, 74, 76, 77, 133, 134, 135, 136, 1787, 1788, 1790, 1792, 1794, 1888, 2049, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 61, 75, 137, 1671, 1789, 1793, 1795, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 82, 122, 123, 124, 125, 184, 185, 186, 1748, 1749, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 183, 1747, 1890, 1891, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 122, 124, 125, 183, 185, 1890, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 123, 184, 186, 1747, 1748, 1749, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 82, 123, 124, 125, 184, 185, 1747, 1748, 1749, 1890, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 122, 183, 186, 1891, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1834, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 1979, 1980, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1832, 1833, 1834, 1980, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1979, 2144, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1832, 1833, 1834, 1979, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1980, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 107, 111, 112, 114, 115, 116, 118, 1645, 1647, 1648, 1676, 2211, 2213, 2296, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 108, 109, 110, 113, 117, 1646, 1677, 2212, 2297, 2298, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 105, 106, 108, 109, 110, 111, 112, 114, 115, 116, 117, 1647, 1648, 1677, 2211, 2213, 2296, 2297, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 104, 107, 113, 118, 1645, 1646, 1676, 2212, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 105, 106, 108, 110, 111, 112, 114, 116, 117, 118, 1645, 1646, 1648, 2212, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 104, 107, 109, 113, 115, 1647, 1676, 1677, 2211, 2213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 136, 137, 1671, 1787, 1788, 1792, 1793, 1888, 2049, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 77, 133, 134, 135, 1789, 1790, 1794, 1795, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 137, 1671, 1788, 1789, 1792, 1793, 1794, 1888, 2050, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 134, 135, 136, 1787, 1790, 1795, 2049, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 61, 74, 75, 77, 134, 136, 137, 1787, 1788, 1789, 1790, 1792, 1795, 1888, 2049, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 76, 133, 135, 1671, 1793, 1794, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 82, 122, 123, 124, 183, 185, 1748, 1749, 1890, 1891, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 125, 184, 186, 1747, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 123, 124, 125, 183, 186, 1747, 1749, 1890, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 122, 184, 185, 1748, 1891, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 82, 122, 123, 124, 183, 184, 185, 1747, 1748, 1891, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 125, 186, 1749, 1890, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1833, 1980, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1834, 1979, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1834, 1979, 1980, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 2144, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1833, 1979, 1980, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1832, 1834, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(105, 106, 107, 108, 110, 111, 112, 113, 114, 115, 116, 117, 1645, 1646, 1648, 1676, 1677, 2211, 2212, 2297, 2298, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 109, 118, 1647, 2213, 2296, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 107, 108, 109, 110, 111, 112, 113, 114, 116, 118, 1645, 1646, 1648, 1677, 2212, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(104, 105, 106, 115, 117, 1647, 1676, 2211, 2213, 2296, 2297, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 104, 105, 106, 107, 109, 110, 112, 113, 114, 116, 117, 1645, 1646, 1676, 1677, 2212, 2296, 2297, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 108, 111, 115, 118, 1647, 1648, 2211, 2213, 2298, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 75, 77, 133, 134, 135, 1788, 1789, 1790, 1792, 1795, 1888, 2049, 2050, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 74, 76, 136, 137, 1787, 1793, 1794, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 135, 137, 1787, 1789, 1792, 1794, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 134, 136, 1788, 1790, 1793, 1795, 1888, 2049, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 61, 75, 76, 77, 133, 136, 137, 1790, 1792, 1794, 1795, 1888, 2049, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 74, 134, 135, 1787, 1788, 1789, 1793, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 123, 124, 125, 183, 185, 186, 1747, 1749, 1890, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 82, 122, 184, 1748, 1891, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 82, 122, 183, 184, 185, 186, 1747, 1890, 1891, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 123, 124, 125, 1748, 1749, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 123, 124, 125, 183, 185, 186, 1748, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 122, 184, 1747, 1749, 1890, 1891, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 2145, 2147)</t>
   </si>
   <si>
     <t xml:space="preserve">c(1980, 2144, 2146, 2148)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1834, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 1834, 1980, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 105, 106, 107, 108, 110, 111, 113, 114, 115, 117, 118, 1648, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 109, 112, 116, 1645, 1646, 1647, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 104, 106, 107, 108, 110, 111, 114, 115, 116, 117, 1647, 1648, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 105, 109, 112, 113, 118, 1645, 1646)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 112, 114, 118, 1645, 1648, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 111, 113, 115, 116, 117, 1646, 1647, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 134, 135, 136, 137, 1788, 1790, 1792, 1794, 1795, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1787, 1789, 1793, 1888, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 134, 135, 1787, 1788, 1790, 1793, 1794, 1888, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 136, 137, 1789, 1792, 1795, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 134, 136, 137, 1789, 1790, 1792, 1795, 1888, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 135, 1787, 1788, 1793, 1794, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + ADF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 123, 124, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 122, 125, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 123, 124, 125, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 123, 124, 125, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 122, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 122, 123, 125, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 124, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1980, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 1834, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1834, 1980, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 1834, 1980, 2144, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 105, 106, 107, 109, 110, 114, 116, 117, 118, 1646, 1647, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 108, 111, 112, 113, 115, 1645, 1648, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 104, 105, 106, 108, 109, 111, 112, 114, 115, 116, 117, 118, 1645, 1646, 1647, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 103, 107, 110, 113, 1648, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 103, 104, 108, 109, 110, 112, 113, 114, 116, 118, 1645, 1647, 1648, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 105, 106, 107, 111, 115, 117, 1646, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(134, 136, 137, 1787, 1788, 1789, 1790, 1793, 1794, 1888, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 135, 1792, 1795, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 134, 136, 137, 1788, 1792, 1795, 1888, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 135, 1787, 1789, 1790, 1793, 1794)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 134, 135, 137, 1788, 1792, 1793, 1794, 1795, 1888, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(136, 1787, 1789, 1790, 2050, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 123, 124, 125, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 122, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 122, 124, 125, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 123, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 122, 123, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 124, 125, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1980, 2144, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1834, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 1980, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 105, 107, 110, 111, 112, 113, 114, 115, 1645, 1646, 1647, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 104, 106, 108, 109, 116, 117, 118, 1648)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 105, 106, 108, 109, 110, 114, 115, 117, 118, 1645, 1646, 1648, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 107, 111, 112, 113, 116, 1647, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 105, 107, 108, 111, 112, 113, 118, 1645, 1646, 1647, 1648, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 106, 109, 110, 114, 115, 116, 117)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 135, 1787, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 134, 136, 137, 1788, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 135, 137, 1787, 1792, 1793, 1794, 1795, 1888, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 134, 136, 1788, 1789, 1790, 2050)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 135, 136, 137, 1788, 1793, 1794, 1795, 1888, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 134, 1787, 1789, 1790, 1792, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + CP_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 123, 125, 185, 186, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(122, 124, 183, 184, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 122, 124, 183, 185, 186, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 123, 125, 184, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 122, 123, 124, 125, 184, 185, 186, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 183, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1834, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 1980, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1834, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1833, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 105, 106, 109, 112, 113, 114, 117, 118, 1645, 1647, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(104, 107, 108, 110, 111, 115, 116, 1646, 1648)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 105, 106, 108, 109, 110, 112, 114, 115, 117, 1645, 1646, 1647, 1648, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 107, 111, 113, 116, 118)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 105, 107, 109, 111, 112, 114, 115, 118, 1645, 1646, 1647, 1648, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 106, 108, 110, 113, 116, 117, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(135, 136, 137, 1788, 1789, 1792, 1793, 1794, 1795, 1888, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 134, 1787, 1790, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 134, 136, 137, 1787, 1788, 1790, 1793, 1794, 1795, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 135, 1789, 1792, 1888, 2050, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 134, 135, 137, 1787, 1788, 1792, 1793, 1794, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(136, 1789, 1790, 1795, 1888, 2050, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 123, 125, 184, 185, 186, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 122, 124, 183, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 123, 124, 125, 185, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(122, 183, 184, 186, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 122, 123, 124, 183, 185, 186, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 125, 184, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1834, 1980, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 1834, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1980, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1834, 1980, 2144, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 105, 106, 107, 108, 111, 112, 113, 116, 117, 118, 1645, 1646, 1647, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 104, 109, 110, 114, 115, 1648, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 106, 107, 109, 110, 111, 112, 115, 116, 117, 1645, 1647, 1648, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(104, 105, 108, 113, 114, 118, 1646, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 103, 104, 106, 107, 108, 110, 111, 112, 113, 115, 116, 1646, 1647, 1648, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 105, 109, 114, 117, 118, 1645, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 137, 1787, 1788, 1790, 1792, 1794, 1795, 1888, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 134, 135, 136, 1789, 1793, 2050)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(134, 135, 136, 137, 1788, 1789, 1790, 1795, 1888, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 1787, 1792, 1793, 1794, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(134, 135, 136, 137, 1788, 1789, 1792, 1793, 1795, 1888, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 1787, 1790, 1794, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 122, 123, 125, 185, 186, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 124, 183, 184, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 123, 124, 125, 183, 185, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 122, 184, 186, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 122, 123, 125, 183, 184, 186, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 124, 185, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 2144, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1980, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1980, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1980, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1980, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 106, 108, 110, 111, 112, 113, 115, 116, 1645, 1646, 1648, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(105, 107, 109, 114, 117, 118, 1647, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 103, 105, 106, 107, 108, 109, 110, 112, 113, 114, 116, 117, 1648, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 104, 111, 115, 118, 1645, 1646, 1647)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 105, 108, 112, 113, 115, 116, 117, 118, 1646, 1647, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 106, 107, 109, 110, 111, 114, 1645, 1648)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 134, 135, 136, 1788, 1789, 1790, 1792, 1793, 1794, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 137, 1787, 1795, 1888, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 135, 136, 137, 1787, 1788, 1792, 1794, 1888, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 134, 1789, 1790, 1793, 1795, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(135, 136, 137, 1787, 1788, 1790, 1792, 1793, 1794, 1795, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 133, 134, 1789, 1888, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 122, 124, 125, 183, 185, 186, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 123, 184, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 123, 124, 184, 185, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 122, 125, 183, 186)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 122, 124, 125, 184, 186, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 123, 183, 185)</t>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1980, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1979, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1980, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1979, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 104, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1676, 1677, 2297, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 105, 1648, 2211, 2212, 2213, 2296, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 105, 106, 107, 108, 111, 113, 114, 115, 116, 1645, 1647, 1677, 2211, 2212, 2213, 2296, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 103, 104, 109, 110, 112, 117, 118, 1646, 1648, 1676, 2297)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(104, 105, 106, 107, 109, 111, 113, 114, 116, 117, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 108, 110, 112, 115, 118, 1645, 2213, 2296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 61, 74, 75, 76, 133, 134, 135, 136, 137, 1787, 1789, 1794, 2049, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 77, 1788, 1790, 1792, 1793, 1795, 1888, 2050, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 61, 74, 77, 133, 134, 135, 136, 1787, 1788, 1789, 1790, 1792, 2049, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 75, 76, 137, 1793, 1794, 1795, 1888, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 61, 74, 75, 76, 136, 1788, 1789, 1790, 1794, 1795, 1888, 2049, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 77, 133, 134, 135, 137, 1787, 1792, 1793, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 122, 123, 124, 183, 185, 1747, 1749, 1890, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(82, 125, 184, 186, 1748, 1891, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 123, 124, 184, 186, 1747, 1748, 1749, 1890, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 82, 122, 125, 183, 185, 1891, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 82, 122, 124, 183, 184, 185, 186, 1748, 1749, 1890, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 123, 125, 1747, 1891, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2148)</t>
   </si>
   <si>
     <t xml:space="preserve">2144:2147</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1980, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 106, 108, 109, 110, 111, 112, 113, 114, 116, 1647, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 105, 107, 115, 117, 118, 1645, 1646, 1648)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 109, 111, 112, 113, 114, 115, 117, 1645, 1646, 1648, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(106, 107, 108, 110, 116, 118, 1647, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 106, 107, 108, 109, 110, 112, 115, 116, 117, 118, 1645, 1646, 1647, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 105, 111, 113, 114, 1648, 2321)</t>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1980, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1979, 2144, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1979, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1980, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 105, 106, 108, 110, 111, 113, 114, 117, 118, 1645, 1647, 1648, 1676, 1677, 2212, 2213, 2297, 2298, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 107, 109, 112, 115, 116, 1646, 2211, 2296, 2299, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 107, 109, 110, 111, 112, 114, 115, 116, 117, 118, 1645, 1648, 1676, 2212, 2213, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(106, 108, 113, 1646, 1647, 1677, 2211, 2296, 2297, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 105, 106, 108, 109, 111, 112, 113, 114, 116, 118, 1645, 1646, 1647, 2212, 2296, 2297, 2298, 2299, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 104, 107, 110, 115, 117, 1648, 1676, 1677, 2211, 2213, 2323)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 123, 124, 125, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 123, 124, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 122, 125, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 122, 124, 125, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 123, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1834, 1980, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1834, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 1980, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 1834, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 118)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 118, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 118)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(118, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 123, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 124, 125, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 122, 123, 125, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 124, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 122, 124, 125, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 123, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1833, 1834, 1980, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 1980, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 1834, 1980, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 118, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 118, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 118, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 2321, 2322)</t>
+    <t xml:space="preserve">c(51, 58, 59, 60, 74, 76, 77, 1888, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 75, 1671, 2049, 2050, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 61, 75, 76, 77, 1888, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 74, 1671, 2049, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 75, 76, 77, 1888, 2049, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 74, 1671, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 122, 123, 124, 1747, 1748, 1749, 1891, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 82, 125, 1890, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 123, 124, 125, 1747, 1748, 1890, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 82, 122, 1749, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 82, 122, 123, 125, 1747, 1748, 1890, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 124, 1749, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1834, 1979, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 1980, 2144, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1832, 1834, 1979, 1980, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1833, 2144, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1832, 1833, 1979, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1834, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 118, 2212, 2213, 2296, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 1676, 1677, 2211, 2297, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 118, 1676, 1677, 2211, 2296, 2297, 2298, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 2212, 2213, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 118, 1677, 2211, 2212, 2213, 2298, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 1676, 2296, 2297, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 74, 75, 76, 77, 1671, 2049, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 61, 1888, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 61, 77, 1671, 1888, 2049, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 74, 75, 76, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 61, 74, 75, 76, 77, 1671, 2049, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 1888, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 82, 122, 123, 124, 125, 1748, 1749, 1891, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 1747, 1890, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 122, 125, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 82, 123, 124, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 124, 125, 1748, 1890, 1891, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 123, 1747, 1749, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1833, 1834, 1979, 1980, 2144, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1832, 1833, 1834, 1980, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1979, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1833, 1834, 1979, 1980, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1832, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 1677, 2211, 2212, 2296, 2298, 2299, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 118, 1676, 2213, 2297, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 118, 1676, 1677, 2211, 2212, 2213, 2297, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 2296, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 118, 1676, 1677, 2211, 2296, 2298, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 2212, 2213, 2297, 2322, 2323)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(79, 80, 122, 124, 125, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 123, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 124, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 123, 125, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 122, 123, 124, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 125, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1834, 1980, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 2144, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1980, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1834, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(118, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 118, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 118, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 123, 124, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 122, 125)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 123, 125, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 122, 124, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1980, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 1834, 2144, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 1834, 1980, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1834, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 118, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 118, 2321)</t>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 77, 1888, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(75, 76, 1671, 2049, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 74, 75, 76, 77, 1671, 2049, 2050, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 61, 1888, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 76, 77, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 75, 1671, 1888, 2049, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 124, 125, 1747, 1890, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 1748, 1749, 1891, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 1747, 1748, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(123, 124, 125, 1749, 1890, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 122, 123, 124, 1748, 1749, 1890, 1891, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 82, 125, 1747, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1834, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1833, 1979, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1832, 1833, 1979, 1980, 2144, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1834, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1834, 1980, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1833, 1979, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 1676, 2211, 2212, 2213, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 118, 1677, 2296, 2297, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 1677, 2212, 2213, 2296, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 1676, 2211, 2297, 2298, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 118, 1677, 2211, 2297, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1676, 2212, 2213, 2296, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 61, 76, 1671, 1888, 2049, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 60, 74, 75, 77, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 61, 74, 77, 1888, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 75, 76, 1671, 2049)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 74, 75, 77, 1671, 1888, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 76, 2049, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 125, 1747, 1748, 1890, 1891, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(82, 122, 123, 124, 1749, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 123, 125, 1748, 1749, 1891, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 122, 124, 1747, 1890, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 122, 123, 125, 1748, 1890, 1891, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 124, 1747, 1749, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1832, 1833, 1834, 1979, 1980, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1832, 1834, 1979, 1980, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1833, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1833, 1834, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1979, 1980, 2144, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 1676, 2212, 2297, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 1677, 2211, 2213, 2296, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 1677, 2211, 2212, 2213, 2296, 2297, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 118, 1676, 2298, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 1677, 2211, 2213, 2297, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 1676, 2212, 2296, 2298, 2299)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 79, 81, 122, 125, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 123, 124, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 125, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 123, 124)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 123, 124, 125, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 122, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1980, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1980, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 2144, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(118, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115:117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 122, 124, 125, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 123, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 123, 124)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(125, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 122, 123, 124, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 125, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1980, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2144:2146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1980, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1980, 2144, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 118, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116:118</t>
+    <t xml:space="preserve">c(59, 60, 61, 75, 76, 1888, 2049, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 74, 77, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 61, 74, 75, 76, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 77, 1888, 2049, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 74, 75, 77, 1888, 2049, 2050, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 61, 76, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 123, 1748, 1890, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(122, 124, 125, 1747, 1749, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 82, 122, 123, 124, 125, 1748, 1749, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 1747, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 122, 123, 124, 125, 1749, 1890, 1891, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 82, 1747, 1748, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1979, 1980, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1979, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1980, 2144, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1979, 1980, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 2211, 2212, 2213, 2296, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 118, 1676, 1677, 2297)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 118, 1676, 2211, 2296, 2297, 2299, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 1677, 2212, 2213, 2298, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 118, 1677, 2212, 2213, 2296, 2298, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 1676, 2211, 2297, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 76, 2049, 2050, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(75, 77, 1888, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 61, 74, 75, 2049, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 76, 77, 1888, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 74, 75, 77, 1888, 2049, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 76, 2050, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 125, 1747, 1748, 1749, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(82, 122, 123, 124, 1890, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 124, 1747, 1748, 1749, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 125, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 122, 123, 125, 1747, 1890, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 124, 1748, 1749, 1891, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1979, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1979, 2144, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1980, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1980, 2144, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1979, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 1677, 2211, 2297, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2212, 2213, 2296, 2298, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 2298, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 1677, 2211, 2212, 2213, 2296, 2298, 2299, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 118, 1676, 2297, 2323)</t>
   </si>
 </sst>
 </file>
@@ -1715,13 +1892,13 @@
         <v>22</v>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O2" t="s">
         <v>23</v>
       </c>
       <c r="P2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="s">
         <v>24</v>
@@ -1771,13 +1948,13 @@
         <v>25</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
       </c>
       <c r="P3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q3" t="s">
         <v>24</v>
@@ -1827,13 +2004,13 @@
         <v>27</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O4" t="s">
         <v>28</v>
       </c>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="s">
         <v>24</v>
@@ -1883,13 +2060,13 @@
         <v>31</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O5" t="s">
         <v>32</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="s">
         <v>33</v>
@@ -1939,13 +2116,13 @@
         <v>34</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O6" t="s">
         <v>35</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="s">
         <v>33</v>
@@ -1995,13 +2172,13 @@
         <v>36</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O7" t="s">
         <v>37</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q7" t="s">
         <v>33</v>
@@ -2051,13 +2228,13 @@
         <v>39</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O8" t="s">
         <v>40</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="s">
         <v>41</v>
@@ -2107,13 +2284,13 @@
         <v>42</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O9" t="s">
         <v>43</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="s">
         <v>41</v>
@@ -2163,13 +2340,13 @@
         <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O10" t="s">
         <v>45</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="s">
         <v>41</v>
@@ -2219,13 +2396,13 @@
         <v>47</v>
       </c>
       <c r="N11" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O11" t="s">
         <v>48</v>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="s">
         <v>49</v>
@@ -2275,13 +2452,13 @@
         <v>50</v>
       </c>
       <c r="N12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O12" t="s">
         <v>51</v>
       </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="s">
         <v>49</v>
@@ -2331,13 +2508,13 @@
         <v>52</v>
       </c>
       <c r="N13" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O13" t="s">
         <v>53</v>
       </c>
       <c r="P13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="s">
         <v>49</v>
@@ -2387,13 +2564,13 @@
         <v>55</v>
       </c>
       <c r="N14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O14" t="s">
         <v>56</v>
       </c>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q14" t="s">
         <v>24</v>
@@ -2443,13 +2620,13 @@
         <v>57</v>
       </c>
       <c r="N15" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O15" t="s">
         <v>58</v>
       </c>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q15" t="s">
         <v>24</v>
@@ -2499,13 +2676,13 @@
         <v>59</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O16" t="s">
         <v>60</v>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q16" t="s">
         <v>24</v>
@@ -2555,13 +2732,13 @@
         <v>62</v>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O17" t="s">
         <v>63</v>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="s">
         <v>33</v>
@@ -2611,13 +2788,13 @@
         <v>64</v>
       </c>
       <c r="N18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O18" t="s">
         <v>65</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q18" t="s">
         <v>33</v>
@@ -2667,13 +2844,13 @@
         <v>66</v>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O19" t="s">
         <v>67</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q19" t="s">
         <v>33</v>
@@ -2723,13 +2900,13 @@
         <v>69</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O20" t="s">
         <v>70</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="s">
         <v>41</v>
@@ -2779,13 +2956,13 @@
         <v>71</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O21" t="s">
         <v>72</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="s">
         <v>41</v>
@@ -2832,16 +3009,16 @@
         <v>3</v>
       </c>
       <c r="M22" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O22" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="s">
         <v>41</v>
@@ -2873,7 +3050,7 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -2888,16 +3065,16 @@
         <v>1</v>
       </c>
       <c r="M23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N23" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q23" t="s">
         <v>49</v>
@@ -2929,7 +3106,7 @@
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -2944,16 +3121,16 @@
         <v>2</v>
       </c>
       <c r="M24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N24" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q24" t="s">
         <v>49</v>
@@ -2985,7 +3162,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -3000,16 +3177,16 @@
         <v>3</v>
       </c>
       <c r="M25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N25" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q25" t="s">
         <v>49</v>
@@ -3056,16 +3233,16 @@
         <v>1</v>
       </c>
       <c r="M26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N26" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q26" t="s">
         <v>24</v>
@@ -3112,16 +3289,16 @@
         <v>2</v>
       </c>
       <c r="M27" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="N27" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q27" t="s">
         <v>24</v>
@@ -3168,16 +3345,16 @@
         <v>3</v>
       </c>
       <c r="M28" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N28" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O28" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q28" t="s">
         <v>24</v>
@@ -3224,16 +3401,16 @@
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N29" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O29" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="P29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q29" t="s">
         <v>33</v>
@@ -3280,16 +3457,16 @@
         <v>2</v>
       </c>
       <c r="M30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N30" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="s">
         <v>33</v>
@@ -3336,16 +3513,16 @@
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N31" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O31" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P31" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q31" t="s">
         <v>33</v>
@@ -3392,16 +3569,16 @@
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q32" t="s">
         <v>41</v>
@@ -3448,16 +3625,16 @@
         <v>2</v>
       </c>
       <c r="M33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O33" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q33" t="s">
         <v>41</v>
@@ -3504,16 +3681,16 @@
         <v>3</v>
       </c>
       <c r="M34" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O34" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q34" t="s">
         <v>41</v>
@@ -3560,16 +3737,16 @@
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N35" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O35" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="P35" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q35" t="s">
         <v>49</v>
@@ -3616,16 +3793,16 @@
         <v>2</v>
       </c>
       <c r="M36" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N36" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O36" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P36" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q36" t="s">
         <v>49</v>
@@ -3672,16 +3849,16 @@
         <v>3</v>
       </c>
       <c r="M37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N37" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P37" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q37" t="s">
         <v>49</v>
@@ -3728,16 +3905,16 @@
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N38" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O38" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="P38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q38" t="s">
         <v>24</v>
@@ -3784,16 +3961,16 @@
         <v>2</v>
       </c>
       <c r="M39" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N39" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q39" t="s">
         <v>24</v>
@@ -3840,16 +4017,16 @@
         <v>3</v>
       </c>
       <c r="M40" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N40" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O40" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="P40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q40" t="s">
         <v>24</v>
@@ -3896,16 +4073,16 @@
         <v>1</v>
       </c>
       <c r="M41" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N41" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O41" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q41" t="s">
         <v>33</v>
@@ -3952,16 +4129,16 @@
         <v>2</v>
       </c>
       <c r="M42" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N42" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O42" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q42" t="s">
         <v>33</v>
@@ -4008,16 +4185,16 @@
         <v>3</v>
       </c>
       <c r="M43" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N43" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O43" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="P43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q43" t="s">
         <v>33</v>
@@ -4064,16 +4241,16 @@
         <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N44" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O44" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="P44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q44" t="s">
         <v>41</v>
@@ -4120,16 +4297,16 @@
         <v>2</v>
       </c>
       <c r="M45" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O45" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q45" t="s">
         <v>41</v>
@@ -4176,16 +4353,16 @@
         <v>3</v>
       </c>
       <c r="M46" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O46" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="P46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q46" t="s">
         <v>41</v>
@@ -4217,7 +4394,7 @@
         <v>2</v>
       </c>
       <c r="H47" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
@@ -4232,16 +4409,16 @@
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N47" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O47" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="P47" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q47" t="s">
         <v>49</v>
@@ -4273,7 +4450,7 @@
         <v>2</v>
       </c>
       <c r="H48" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
@@ -4288,16 +4465,16 @@
         <v>2</v>
       </c>
       <c r="M48" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="N48" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O48" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P48" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q48" t="s">
         <v>49</v>
@@ -4329,7 +4506,7 @@
         <v>2</v>
       </c>
       <c r="H49" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I49" t="n">
         <v>2</v>
@@ -4344,16 +4521,16 @@
         <v>3</v>
       </c>
       <c r="M49" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="N49" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O49" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="P49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q49" t="s">
         <v>49</v>
@@ -4394,22 +4571,22 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N50" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O50" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="P50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q50" t="s">
         <v>24</v>
@@ -4450,22 +4627,22 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
       </c>
       <c r="M51" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="N51" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O51" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="P51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q51" t="s">
         <v>24</v>
@@ -4506,22 +4683,22 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
       </c>
       <c r="M52" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N52" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O52" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="P52" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q52" t="s">
         <v>24</v>
@@ -4562,22 +4739,22 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N53" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O53" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="P53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q53" t="s">
         <v>33</v>
@@ -4618,22 +4795,22 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
       </c>
       <c r="M54" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N54" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O54" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="P54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q54" t="s">
         <v>33</v>
@@ -4674,22 +4851,22 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
       </c>
       <c r="M55" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N55" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O55" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q55" t="s">
         <v>33</v>
@@ -4730,22 +4907,22 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O56" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q56" t="s">
         <v>41</v>
@@ -4786,22 +4963,22 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
       </c>
       <c r="M57" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N57" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O57" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="P57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q57" t="s">
         <v>41</v>
@@ -4842,22 +5019,22 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
       </c>
       <c r="M58" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N58" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O58" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q58" t="s">
         <v>41</v>
@@ -4898,22 +5075,22 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N59" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O59" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P59" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q59" t="s">
         <v>49</v>
@@ -4954,22 +5131,22 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
       </c>
       <c r="M60" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N60" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O60" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P60" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q60" t="s">
         <v>49</v>
@@ -5010,22 +5187,22 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
       </c>
       <c r="M61" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N61" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O61" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P61" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q61" t="s">
         <v>49</v>
@@ -5066,22 +5243,22 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N62" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O62" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P62" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q62" t="s">
         <v>24</v>
@@ -5122,22 +5299,22 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
       </c>
       <c r="M63" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N63" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O63" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q63" t="s">
         <v>24</v>
@@ -5178,22 +5355,22 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
       </c>
       <c r="M64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N64" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O64" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q64" t="s">
         <v>24</v>
@@ -5234,22 +5411,22 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N65" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O65" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="P65" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q65" t="s">
         <v>33</v>
@@ -5290,22 +5467,22 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
       </c>
       <c r="M66" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N66" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O66" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P66" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q66" t="s">
         <v>33</v>
@@ -5346,22 +5523,22 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
       </c>
       <c r="M67" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O67" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q67" t="s">
         <v>33</v>
@@ -5402,22 +5579,22 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N68" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O68" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="P68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q68" t="s">
         <v>41</v>
@@ -5458,22 +5635,22 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
       </c>
       <c r="M69" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N69" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O69" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="P69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q69" t="s">
         <v>41</v>
@@ -5514,22 +5691,22 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
       </c>
       <c r="M70" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N70" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O70" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q70" t="s">
         <v>41</v>
@@ -5561,7 +5738,7 @@
         <v>2</v>
       </c>
       <c r="H71" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I71" t="n">
         <v>3</v>
@@ -5570,22 +5747,22 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N71" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O71" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P71" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q71" t="s">
         <v>49</v>
@@ -5617,7 +5794,7 @@
         <v>2</v>
       </c>
       <c r="H72" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I72" t="n">
         <v>3</v>
@@ -5626,22 +5803,22 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
       </c>
       <c r="M72" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N72" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O72" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P72" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q72" t="s">
         <v>49</v>
@@ -5673,7 +5850,7 @@
         <v>2</v>
       </c>
       <c r="H73" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I73" t="n">
         <v>3</v>
@@ -5682,22 +5859,22 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
       </c>
       <c r="M73" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N73" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O73" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P73" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q73" t="s">
         <v>49</v>
@@ -5738,22 +5915,22 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="N74" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O74" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P74" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q74" t="s">
         <v>24</v>
@@ -5794,22 +5971,22 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
       </c>
       <c r="M75" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N75" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O75" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P75" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q75" t="s">
         <v>24</v>
@@ -5850,22 +6027,22 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
       </c>
       <c r="M76" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N76" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O76" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P76" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q76" t="s">
         <v>24</v>
@@ -5906,28 +6083,28 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N77" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O77" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q77" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="R77" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="78">
@@ -5962,28 +6139,28 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N78" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O78" t="s">
+        <v>192</v>
+      </c>
+      <c r="P78" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q78" t="s">
         <v>190</v>
       </c>
-      <c r="P78" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>188</v>
-      </c>
       <c r="R78" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="79">
@@ -6018,28 +6195,28 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O79" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q79" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="R79" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="80">
@@ -6074,22 +6251,22 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N80" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O80" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q80" t="s">
         <v>41</v>
@@ -6130,22 +6307,22 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
       </c>
       <c r="M81" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N81" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O81" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q81" t="s">
         <v>41</v>
@@ -6186,22 +6363,22 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
       </c>
       <c r="M82" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N82" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O82" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q82" t="s">
         <v>41</v>
@@ -6242,22 +6419,22 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N83" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O83" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P83" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q83" t="s">
         <v>49</v>
@@ -6298,22 +6475,22 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
       </c>
       <c r="M84" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N84" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O84" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P84" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q84" t="s">
         <v>49</v>
@@ -6354,22 +6531,22 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
       </c>
       <c r="M85" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N85" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O85" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P85" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q85" t="s">
         <v>49</v>
@@ -6410,22 +6587,22 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
       <c r="M86" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N86" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O86" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="P86" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q86" t="s">
         <v>24</v>
@@ -6466,22 +6643,22 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
       </c>
       <c r="M87" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N87" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O87" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P87" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q87" t="s">
         <v>24</v>
@@ -6522,22 +6699,22 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
       </c>
       <c r="M88" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N88" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O88" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P88" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q88" t="s">
         <v>24</v>
@@ -6578,28 +6755,28 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N89" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O89" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q89" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="R89" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90">
@@ -6634,28 +6811,28 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N90" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O90" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q90" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="R90" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91">
@@ -6690,28 +6867,28 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N91" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O91" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q91" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="R91" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92">
@@ -6746,22 +6923,22 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="s">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="N92" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O92" t="s">
-        <v>147</v>
+        <v>220</v>
       </c>
       <c r="P92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q92" t="s">
         <v>41</v>
@@ -6802,22 +6979,22 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
       </c>
       <c r="M93" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N93" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O93" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="P93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q93" t="s">
         <v>41</v>
@@ -6858,22 +7035,22 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
       </c>
       <c r="M94" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N94" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O94" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="P94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q94" t="s">
         <v>41</v>
@@ -6905,7 +7082,7 @@
         <v>2</v>
       </c>
       <c r="H95" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I95" t="n">
         <v>4</v>
@@ -6914,22 +7091,22 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N95" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O95" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="P95" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q95" t="s">
         <v>49</v>
@@ -6961,7 +7138,7 @@
         <v>2</v>
       </c>
       <c r="H96" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I96" t="n">
         <v>4</v>
@@ -6970,22 +7147,22 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
       </c>
       <c r="M96" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N96" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O96" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="P96" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q96" t="s">
         <v>49</v>
@@ -7017,7 +7194,7 @@
         <v>2</v>
       </c>
       <c r="H97" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I97" t="n">
         <v>4</v>
@@ -7026,22 +7203,22 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
       </c>
       <c r="M97" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="N97" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O97" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="P97" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q97" t="s">
         <v>49</v>
@@ -7082,22 +7259,22 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="N98" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O98" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="P98" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q98" t="s">
         <v>24</v>
@@ -7138,22 +7315,22 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
       </c>
       <c r="M99" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="N99" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O99" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="P99" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q99" t="s">
         <v>24</v>
@@ -7194,22 +7371,22 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
       </c>
       <c r="M100" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N100" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O100" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="P100" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q100" t="s">
         <v>24</v>
@@ -7250,22 +7427,22 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="N101" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O101" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="P101" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q101" t="s">
         <v>33</v>
@@ -7306,22 +7483,22 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
       </c>
       <c r="M102" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N102" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O102" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="P102" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q102" t="s">
         <v>33</v>
@@ -7362,22 +7539,22 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
       </c>
       <c r="M103" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="N103" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O103" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="P103" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q103" t="s">
         <v>33</v>
@@ -7418,22 +7595,22 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="N104" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O104" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="P104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q104" t="s">
         <v>41</v>
@@ -7474,22 +7651,22 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
       </c>
       <c r="M105" t="s">
-        <v>71</v>
+        <v>247</v>
       </c>
       <c r="N105" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O105" t="s">
-        <v>72</v>
+        <v>248</v>
       </c>
       <c r="P105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q105" t="s">
         <v>41</v>
@@ -7530,22 +7707,22 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
       </c>
       <c r="M106" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="N106" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O106" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="P106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q106" t="s">
         <v>41</v>
@@ -7586,22 +7763,22 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="N107" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O107" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="P107" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q107" t="s">
         <v>49</v>
@@ -7642,22 +7819,22 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
       </c>
       <c r="M108" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="N108" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O108" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="P108" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q108" t="s">
         <v>49</v>
@@ -7698,22 +7875,22 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
       </c>
       <c r="M109" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="N109" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O109" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="P109" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q109" t="s">
         <v>49</v>
@@ -7754,22 +7931,22 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="N110" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O110" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="P110" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q110" t="s">
         <v>24</v>
@@ -7810,22 +7987,22 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
       </c>
       <c r="M111" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="N111" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O111" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="P111" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q111" t="s">
         <v>24</v>
@@ -7866,22 +8043,22 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="N112" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="O112" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="P112" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q112" t="s">
         <v>24</v>
@@ -7922,22 +8099,22 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="N113" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O113" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="P113" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q113" t="s">
         <v>33</v>
@@ -7978,22 +8155,22 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
       </c>
       <c r="M114" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="N114" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O114" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="P114" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q114" t="s">
         <v>33</v>
@@ -8034,22 +8211,22 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
       </c>
       <c r="M115" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="N115" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O115" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="P115" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q115" t="s">
         <v>33</v>
@@ -8090,22 +8267,22 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="N116" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O116" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="P116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q116" t="s">
         <v>41</v>
@@ -8146,22 +8323,22 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
       </c>
       <c r="M117" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="N117" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O117" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="P117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q117" t="s">
         <v>41</v>
@@ -8202,22 +8379,22 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
       </c>
       <c r="M118" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="N118" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O118" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="P118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q118" t="s">
         <v>41</v>
@@ -8249,7 +8426,7 @@
         <v>2</v>
       </c>
       <c r="H119" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I119" t="n">
         <v>5</v>
@@ -8258,22 +8435,22 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="N119" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O119" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="P119" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q119" t="s">
         <v>49</v>
@@ -8305,7 +8482,7 @@
         <v>2</v>
       </c>
       <c r="H120" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I120" t="n">
         <v>5</v>
@@ -8314,22 +8491,22 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
       </c>
       <c r="M120" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="N120" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O120" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="P120" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q120" t="s">
         <v>49</v>
@@ -8361,7 +8538,7 @@
         <v>2</v>
       </c>
       <c r="H121" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I121" t="n">
         <v>5</v>
@@ -8370,22 +8547,22 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
       </c>
       <c r="M121" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="N121" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O121" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="P121" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q121" t="s">
         <v>49</v>
@@ -8426,28 +8603,28 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="N122" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O122" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="P122" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q122" t="s">
-        <v>24</v>
+        <v>284</v>
       </c>
       <c r="R122" t="s">
-        <v>24</v>
+        <v>284</v>
       </c>
     </row>
     <row r="123">
@@ -8482,28 +8659,28 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="N123" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O123" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="P123" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q123" t="s">
-        <v>24</v>
+        <v>284</v>
       </c>
       <c r="R123" t="s">
-        <v>24</v>
+        <v>284</v>
       </c>
     </row>
     <row r="124">
@@ -8538,28 +8715,28 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="N124" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O124" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="P124" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q124" t="s">
-        <v>24</v>
+        <v>284</v>
       </c>
       <c r="R124" t="s">
-        <v>24</v>
+        <v>284</v>
       </c>
     </row>
     <row r="125">
@@ -8594,22 +8771,22 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="N125" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O125" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="P125" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q125" t="s">
         <v>33</v>
@@ -8650,22 +8827,22 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
       </c>
       <c r="M126" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="N126" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O126" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="P126" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q126" t="s">
         <v>33</v>
@@ -8706,22 +8883,22 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
       </c>
       <c r="M127" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="N127" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O127" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="P127" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q127" t="s">
         <v>33</v>
@@ -8762,28 +8939,28 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="N128" t="n">
+        <v>7</v>
+      </c>
+      <c r="O128" t="s">
+        <v>297</v>
+      </c>
+      <c r="P128" t="n">
         <v>4</v>
       </c>
-      <c r="O128" t="s">
-        <v>290</v>
-      </c>
-      <c r="P128" t="n">
-        <v>3</v>
-      </c>
       <c r="Q128" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="R128" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="129">
@@ -8818,28 +8995,28 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>97</v>
+        <v>299</v>
       </c>
       <c r="N129" t="n">
+        <v>7</v>
+      </c>
+      <c r="O129" t="s">
+        <v>300</v>
+      </c>
+      <c r="P129" t="n">
         <v>4</v>
       </c>
-      <c r="O129" t="s">
-        <v>292</v>
-      </c>
-      <c r="P129" t="n">
-        <v>3</v>
-      </c>
       <c r="Q129" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="R129" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="130">
@@ -8874,28 +9051,28 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="N130" t="n">
+        <v>7</v>
+      </c>
+      <c r="O130" t="s">
+        <v>302</v>
+      </c>
+      <c r="P130" t="n">
         <v>4</v>
       </c>
-      <c r="O130" t="s">
-        <v>294</v>
-      </c>
-      <c r="P130" t="n">
-        <v>3</v>
-      </c>
       <c r="Q130" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="R130" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="131">
@@ -8930,22 +9107,22 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="N131" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O131" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="P131" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q131" t="s">
         <v>49</v>
@@ -8986,22 +9163,22 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="N132" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O132" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="P132" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q132" t="s">
         <v>49</v>
@@ -9042,22 +9219,22 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="N133" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O133" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="P133" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q133" t="s">
         <v>49</v>
@@ -9098,28 +9275,28 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="N134" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O134" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="P134" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q134" t="s">
-        <v>24</v>
+        <v>284</v>
       </c>
       <c r="R134" t="s">
-        <v>24</v>
+        <v>284</v>
       </c>
     </row>
     <row r="135">
@@ -9154,28 +9331,28 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="N135" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O135" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="P135" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q135" t="s">
-        <v>24</v>
+        <v>284</v>
       </c>
       <c r="R135" t="s">
-        <v>24</v>
+        <v>284</v>
       </c>
     </row>
     <row r="136">
@@ -9210,28 +9387,28 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="N136" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O136" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="P136" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q136" t="s">
-        <v>24</v>
+        <v>284</v>
       </c>
       <c r="R136" t="s">
-        <v>24</v>
+        <v>284</v>
       </c>
     </row>
     <row r="137">
@@ -9266,22 +9443,22 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="N137" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O137" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="P137" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q137" t="s">
         <v>33</v>
@@ -9322,22 +9499,22 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="N138" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O138" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="P138" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q138" t="s">
         <v>33</v>
@@ -9378,22 +9555,22 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="N139" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O139" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="P139" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q139" t="s">
         <v>33</v>
@@ -9407,7 +9584,7 @@
         <v>277</v>
       </c>
       <c r="B140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
@@ -9434,28 +9611,28 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="N140" t="n">
+        <v>7</v>
+      </c>
+      <c r="O140" t="s">
+        <v>322</v>
+      </c>
+      <c r="P140" t="n">
         <v>4</v>
       </c>
-      <c r="O140" t="s">
-        <v>314</v>
-      </c>
-      <c r="P140" t="n">
-        <v>3</v>
-      </c>
       <c r="Q140" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="R140" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="141">
@@ -9463,7 +9640,7 @@
         <v>278</v>
       </c>
       <c r="B141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C141" t="s">
         <v>18</v>
@@ -9490,28 +9667,28 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="N141" t="n">
+        <v>7</v>
+      </c>
+      <c r="O141" t="s">
+        <v>324</v>
+      </c>
+      <c r="P141" t="n">
         <v>4</v>
       </c>
-      <c r="O141" t="s">
-        <v>316</v>
-      </c>
-      <c r="P141" t="n">
-        <v>3</v>
-      </c>
       <c r="Q141" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="R141" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="142">
@@ -9519,7 +9696,7 @@
         <v>279</v>
       </c>
       <c r="B142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C142" t="s">
         <v>18</v>
@@ -9546,28 +9723,28 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="N142" t="n">
+        <v>7</v>
+      </c>
+      <c r="O142" t="s">
+        <v>326</v>
+      </c>
+      <c r="P142" t="n">
         <v>4</v>
       </c>
-      <c r="O142" t="s">
-        <v>318</v>
-      </c>
-      <c r="P142" t="n">
-        <v>3</v>
-      </c>
       <c r="Q142" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="R142" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="143">
@@ -9593,7 +9770,7 @@
         <v>2</v>
       </c>
       <c r="H143" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I143" t="n">
         <v>6</v>
@@ -9602,22 +9779,22 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="N143" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O143" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="P143" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q143" t="s">
         <v>49</v>
@@ -9649,7 +9826,7 @@
         <v>2</v>
       </c>
       <c r="H144" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I144" t="n">
         <v>6</v>
@@ -9658,22 +9835,22 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="N144" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O144" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="P144" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q144" t="s">
         <v>49</v>
@@ -9705,7 +9882,7 @@
         <v>2</v>
       </c>
       <c r="H145" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I145" t="n">
         <v>6</v>
@@ -9714,22 +9891,22 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="N145" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O145" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="P145" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q145" t="s">
         <v>49</v>
@@ -9743,7 +9920,7 @@
         <v>289</v>
       </c>
       <c r="B146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C146" t="s">
         <v>18</v>
@@ -9770,24 +9947,28 @@
         <v>3</v>
       </c>
       <c r="K146" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="L146" t="n">
         <v>1</v>
       </c>
       <c r="M146" t="s">
-        <v>326</v>
-      </c>
-      <c r="N146"/>
+        <v>334</v>
+      </c>
+      <c r="N146" t="n">
+        <v>11</v>
+      </c>
       <c r="O146" t="s">
-        <v>326</v>
-      </c>
-      <c r="P146"/>
+        <v>335</v>
+      </c>
+      <c r="P146" t="n">
+        <v>6</v>
+      </c>
       <c r="Q146" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="R146" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="147">
@@ -9795,7 +9976,7 @@
         <v>290</v>
       </c>
       <c r="B147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C147" t="s">
         <v>18</v>
@@ -9822,24 +10003,28 @@
         <v>3</v>
       </c>
       <c r="K147" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="L147" t="n">
         <v>2</v>
       </c>
       <c r="M147" t="s">
-        <v>326</v>
-      </c>
-      <c r="N147"/>
+        <v>337</v>
+      </c>
+      <c r="N147" t="n">
+        <v>11</v>
+      </c>
       <c r="O147" t="s">
-        <v>326</v>
-      </c>
-      <c r="P147"/>
+        <v>338</v>
+      </c>
+      <c r="P147" t="n">
+        <v>6</v>
+      </c>
       <c r="Q147" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="R147" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="148">
@@ -9847,7 +10032,7 @@
         <v>291</v>
       </c>
       <c r="B148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C148" t="s">
         <v>18</v>
@@ -9874,24 +10059,28 @@
         <v>3</v>
       </c>
       <c r="K148" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="L148" t="n">
         <v>3</v>
       </c>
       <c r="M148" t="s">
-        <v>326</v>
-      </c>
-      <c r="N148"/>
+        <v>339</v>
+      </c>
+      <c r="N148" t="n">
+        <v>11</v>
+      </c>
       <c r="O148" t="s">
-        <v>326</v>
-      </c>
-      <c r="P148"/>
+        <v>340</v>
+      </c>
+      <c r="P148" t="n">
+        <v>6</v>
+      </c>
       <c r="Q148" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="R148" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="149">
@@ -9926,28 +10115,28 @@
         <v>3</v>
       </c>
       <c r="K149" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L149" t="n">
         <v>1</v>
       </c>
       <c r="M149" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="N149" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O149" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="P149" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q149" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R149" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="150">
@@ -9982,28 +10171,28 @@
         <v>3</v>
       </c>
       <c r="K150" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L150" t="n">
         <v>2</v>
       </c>
       <c r="M150" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="N150" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O150" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="P150" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q150" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R150" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="151">
@@ -10038,28 +10227,28 @@
         <v>3</v>
       </c>
       <c r="K151" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L151" t="n">
         <v>3</v>
       </c>
       <c r="M151" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="N151" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O151" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="P151" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q151" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R151" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="152">
@@ -10094,22 +10283,22 @@
         <v>3</v>
       </c>
       <c r="K152" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="L152" t="n">
         <v>1</v>
       </c>
       <c r="M152" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="N152" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O152" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="P152" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q152" t="s">
         <v>41</v>
@@ -10150,22 +10339,22 @@
         <v>3</v>
       </c>
       <c r="K153" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="L153" t="n">
         <v>2</v>
       </c>
       <c r="M153" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="N153" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O153" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="P153" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q153" t="s">
         <v>41</v>
@@ -10206,22 +10395,22 @@
         <v>3</v>
       </c>
       <c r="K154" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="L154" t="n">
         <v>3</v>
       </c>
       <c r="M154" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="N154" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O154" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="P154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q154" t="s">
         <v>41</v>
@@ -10262,28 +10451,28 @@
         <v>3</v>
       </c>
       <c r="K155" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L155" t="n">
         <v>1</v>
       </c>
       <c r="M155" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="N155" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O155" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="P155" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q155" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R155" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="156">
@@ -10318,28 +10507,28 @@
         <v>3</v>
       </c>
       <c r="K156" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L156" t="n">
         <v>2</v>
       </c>
       <c r="M156" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="N156" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O156" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="P156" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q156" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R156" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="157">
@@ -10374,28 +10563,28 @@
         <v>3</v>
       </c>
       <c r="K157" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L157" t="n">
         <v>3</v>
       </c>
       <c r="M157" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="N157" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O157" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="P157" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q157" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R157" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="158">
@@ -10403,7 +10592,7 @@
         <v>313</v>
       </c>
       <c r="B158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C158" t="s">
         <v>18</v>
@@ -10430,24 +10619,28 @@
         <v>3</v>
       </c>
       <c r="K158" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="s">
-        <v>326</v>
-      </c>
-      <c r="N158"/>
+        <v>362</v>
+      </c>
+      <c r="N158" t="n">
+        <v>11</v>
+      </c>
       <c r="O158" t="s">
-        <v>326</v>
-      </c>
-      <c r="P158"/>
+        <v>363</v>
+      </c>
+      <c r="P158" t="n">
+        <v>6</v>
+      </c>
       <c r="Q158" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="R158" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="159">
@@ -10455,7 +10648,7 @@
         <v>314</v>
       </c>
       <c r="B159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C159" t="s">
         <v>18</v>
@@ -10482,24 +10675,28 @@
         <v>3</v>
       </c>
       <c r="K159" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="L159" t="n">
         <v>2</v>
       </c>
       <c r="M159" t="s">
-        <v>326</v>
-      </c>
-      <c r="N159"/>
+        <v>364</v>
+      </c>
+      <c r="N159" t="n">
+        <v>11</v>
+      </c>
       <c r="O159" t="s">
-        <v>326</v>
-      </c>
-      <c r="P159"/>
+        <v>365</v>
+      </c>
+      <c r="P159" t="n">
+        <v>6</v>
+      </c>
       <c r="Q159" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="R159" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="160">
@@ -10507,7 +10704,7 @@
         <v>315</v>
       </c>
       <c r="B160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C160" t="s">
         <v>18</v>
@@ -10534,24 +10731,28 @@
         <v>3</v>
       </c>
       <c r="K160" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
       </c>
       <c r="M160" t="s">
-        <v>326</v>
-      </c>
-      <c r="N160"/>
+        <v>366</v>
+      </c>
+      <c r="N160" t="n">
+        <v>11</v>
+      </c>
       <c r="O160" t="s">
-        <v>326</v>
-      </c>
-      <c r="P160"/>
+        <v>367</v>
+      </c>
+      <c r="P160" t="n">
+        <v>6</v>
+      </c>
       <c r="Q160" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="R160" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="161">
@@ -10586,28 +10787,28 @@
         <v>3</v>
       </c>
       <c r="K161" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L161" t="n">
         <v>1</v>
       </c>
       <c r="M161" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="N161" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O161" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="P161" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q161" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R161" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="162">
@@ -10642,28 +10843,28 @@
         <v>3</v>
       </c>
       <c r="K162" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L162" t="n">
         <v>2</v>
       </c>
       <c r="M162" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="N162" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O162" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="P162" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q162" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R162" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="163">
@@ -10698,28 +10899,28 @@
         <v>3</v>
       </c>
       <c r="K163" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
       </c>
       <c r="M163" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="N163" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O163" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="P163" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q163" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R163" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="164">
@@ -10754,22 +10955,22 @@
         <v>3</v>
       </c>
       <c r="K164" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="L164" t="n">
         <v>1</v>
       </c>
       <c r="M164" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="N164" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O164" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="P164" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q164" t="s">
         <v>41</v>
@@ -10810,22 +11011,22 @@
         <v>3</v>
       </c>
       <c r="K165" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="L165" t="n">
         <v>2</v>
       </c>
       <c r="M165" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="N165" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O165" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="P165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q165" t="s">
         <v>41</v>
@@ -10866,22 +11067,22 @@
         <v>3</v>
       </c>
       <c r="K166" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
       </c>
       <c r="M166" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="N166" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O166" t="s">
-        <v>289</v>
+        <v>379</v>
       </c>
       <c r="P166" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q166" t="s">
         <v>41</v>
@@ -10895,7 +11096,7 @@
         <v>331</v>
       </c>
       <c r="B167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C167" t="s">
         <v>18</v>
@@ -10913,7 +11114,7 @@
         <v>2</v>
       </c>
       <c r="H167" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I167" t="n">
         <v>7</v>
@@ -10922,28 +11123,28 @@
         <v>3</v>
       </c>
       <c r="K167" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L167" t="n">
         <v>1</v>
       </c>
       <c r="M167" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="N167" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O167" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="P167" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q167" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R167" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="168">
@@ -10951,7 +11152,7 @@
         <v>332</v>
       </c>
       <c r="B168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C168" t="s">
         <v>18</v>
@@ -10969,7 +11170,7 @@
         <v>2</v>
       </c>
       <c r="H168" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I168" t="n">
         <v>7</v>
@@ -10978,28 +11179,28 @@
         <v>3</v>
       </c>
       <c r="K168" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L168" t="n">
         <v>2</v>
       </c>
       <c r="M168" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="N168" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O168" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="P168" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q168" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R168" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="169">
@@ -11007,7 +11208,7 @@
         <v>333</v>
       </c>
       <c r="B169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C169" t="s">
         <v>18</v>
@@ -11025,7 +11226,7 @@
         <v>2</v>
       </c>
       <c r="H169" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I169" t="n">
         <v>7</v>
@@ -11034,28 +11235,28 @@
         <v>3</v>
       </c>
       <c r="K169" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
       </c>
       <c r="M169" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="N169" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O169" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="P169" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q169" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R169" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="170">
@@ -11063,7 +11264,7 @@
         <v>337</v>
       </c>
       <c r="B170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C170" t="s">
         <v>18</v>
@@ -11090,24 +11291,28 @@
         <v>3</v>
       </c>
       <c r="K170" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="L170" t="n">
         <v>1</v>
       </c>
       <c r="M170" t="s">
-        <v>326</v>
-      </c>
-      <c r="N170"/>
+        <v>387</v>
+      </c>
+      <c r="N170" t="n">
+        <v>11</v>
+      </c>
       <c r="O170" t="s">
-        <v>326</v>
-      </c>
-      <c r="P170"/>
+        <v>388</v>
+      </c>
+      <c r="P170" t="n">
+        <v>6</v>
+      </c>
       <c r="Q170" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="R170" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="171">
@@ -11115,7 +11320,7 @@
         <v>338</v>
       </c>
       <c r="B171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C171" t="s">
         <v>18</v>
@@ -11142,24 +11347,28 @@
         <v>3</v>
       </c>
       <c r="K171" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="L171" t="n">
         <v>2</v>
       </c>
       <c r="M171" t="s">
-        <v>326</v>
-      </c>
-      <c r="N171"/>
+        <v>389</v>
+      </c>
+      <c r="N171" t="n">
+        <v>11</v>
+      </c>
       <c r="O171" t="s">
-        <v>326</v>
-      </c>
-      <c r="P171"/>
+        <v>390</v>
+      </c>
+      <c r="P171" t="n">
+        <v>6</v>
+      </c>
       <c r="Q171" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="R171" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="172">
@@ -11167,7 +11376,7 @@
         <v>339</v>
       </c>
       <c r="B172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C172" t="s">
         <v>18</v>
@@ -11194,24 +11403,28 @@
         <v>3</v>
       </c>
       <c r="K172" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
       </c>
       <c r="M172" t="s">
-        <v>326</v>
-      </c>
-      <c r="N172"/>
+        <v>391</v>
+      </c>
+      <c r="N172" t="n">
+        <v>11</v>
+      </c>
       <c r="O172" t="s">
-        <v>326</v>
-      </c>
-      <c r="P172"/>
+        <v>392</v>
+      </c>
+      <c r="P172" t="n">
+        <v>6</v>
+      </c>
       <c r="Q172" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="R172" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="173">
@@ -11246,28 +11459,28 @@
         <v>3</v>
       </c>
       <c r="K173" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L173" t="n">
         <v>1</v>
       </c>
       <c r="M173" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="N173" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O173" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="P173" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q173" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R173" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="174">
@@ -11302,28 +11515,28 @@
         <v>3</v>
       </c>
       <c r="K174" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L174" t="n">
         <v>2</v>
       </c>
       <c r="M174" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="N174" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O174" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="P174" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q174" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R174" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="175">
@@ -11358,28 +11571,28 @@
         <v>3</v>
       </c>
       <c r="K175" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L175" t="n">
         <v>3</v>
       </c>
       <c r="M175" t="s">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="N175" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O175" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="P175" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q175" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R175" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="176">
@@ -11414,22 +11627,22 @@
         <v>3</v>
       </c>
       <c r="K176" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="L176" t="n">
         <v>1</v>
       </c>
       <c r="M176" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="N176" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O176" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="P176" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q176" t="s">
         <v>41</v>
@@ -11470,22 +11683,22 @@
         <v>3</v>
       </c>
       <c r="K177" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="L177" t="n">
         <v>2</v>
       </c>
       <c r="M177" t="s">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="N177" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O177" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="P177" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q177" t="s">
         <v>41</v>
@@ -11526,22 +11739,22 @@
         <v>3</v>
       </c>
       <c r="K178" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="L178" t="n">
         <v>3</v>
       </c>
       <c r="M178" t="s">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="N178" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O178" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="P178" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q178" t="s">
         <v>41</v>
@@ -11582,28 +11795,28 @@
         <v>3</v>
       </c>
       <c r="K179" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L179" t="n">
         <v>1</v>
       </c>
       <c r="M179" t="s">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="N179" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O179" t="s">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="P179" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q179" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R179" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="180">
@@ -11638,28 +11851,28 @@
         <v>3</v>
       </c>
       <c r="K180" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L180" t="n">
         <v>2</v>
       </c>
       <c r="M180" t="s">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="N180" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O180" t="s">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="P180" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q180" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R180" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="181">
@@ -11694,28 +11907,28 @@
         <v>3</v>
       </c>
       <c r="K181" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L181" t="n">
         <v>3</v>
       </c>
       <c r="M181" t="s">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="N181" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O181" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="P181" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q181" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R181" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="182">
@@ -11723,7 +11936,7 @@
         <v>361</v>
       </c>
       <c r="B182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C182" t="s">
         <v>18</v>
@@ -11750,24 +11963,28 @@
         <v>3</v>
       </c>
       <c r="K182" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="L182" t="n">
         <v>1</v>
       </c>
       <c r="M182" t="s">
-        <v>326</v>
-      </c>
-      <c r="N182"/>
+        <v>411</v>
+      </c>
+      <c r="N182" t="n">
+        <v>11</v>
+      </c>
       <c r="O182" t="s">
-        <v>326</v>
-      </c>
-      <c r="P182"/>
+        <v>412</v>
+      </c>
+      <c r="P182" t="n">
+        <v>6</v>
+      </c>
       <c r="Q182" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="R182" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="183">
@@ -11775,7 +11992,7 @@
         <v>362</v>
       </c>
       <c r="B183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C183" t="s">
         <v>18</v>
@@ -11802,24 +12019,28 @@
         <v>3</v>
       </c>
       <c r="K183" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="L183" t="n">
         <v>2</v>
       </c>
       <c r="M183" t="s">
-        <v>326</v>
-      </c>
-      <c r="N183"/>
+        <v>413</v>
+      </c>
+      <c r="N183" t="n">
+        <v>11</v>
+      </c>
       <c r="O183" t="s">
-        <v>326</v>
-      </c>
-      <c r="P183"/>
+        <v>414</v>
+      </c>
+      <c r="P183" t="n">
+        <v>6</v>
+      </c>
       <c r="Q183" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="R183" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="184">
@@ -11827,7 +12048,7 @@
         <v>363</v>
       </c>
       <c r="B184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C184" t="s">
         <v>18</v>
@@ -11854,24 +12075,28 @@
         <v>3</v>
       </c>
       <c r="K184" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="L184" t="n">
         <v>3</v>
       </c>
       <c r="M184" t="s">
-        <v>326</v>
-      </c>
-      <c r="N184"/>
+        <v>415</v>
+      </c>
+      <c r="N184" t="n">
+        <v>11</v>
+      </c>
       <c r="O184" t="s">
-        <v>326</v>
-      </c>
-      <c r="P184"/>
+        <v>416</v>
+      </c>
+      <c r="P184" t="n">
+        <v>6</v>
+      </c>
       <c r="Q184" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="R184" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="185">
@@ -11906,28 +12131,28 @@
         <v>3</v>
       </c>
       <c r="K185" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L185" t="n">
         <v>1</v>
       </c>
       <c r="M185" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="N185" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O185" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="P185" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q185" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R185" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="186">
@@ -11962,28 +12187,28 @@
         <v>3</v>
       </c>
       <c r="K186" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L186" t="n">
         <v>2</v>
       </c>
       <c r="M186" t="s">
-        <v>365</v>
+        <v>419</v>
       </c>
       <c r="N186" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O186" t="s">
-        <v>366</v>
+        <v>420</v>
       </c>
       <c r="P186" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q186" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R186" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="187">
@@ -12018,28 +12243,28 @@
         <v>3</v>
       </c>
       <c r="K187" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L187" t="n">
         <v>3</v>
       </c>
       <c r="M187" t="s">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="N187" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O187" t="s">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="P187" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q187" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R187" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="188">
@@ -12074,22 +12299,22 @@
         <v>3</v>
       </c>
       <c r="K188" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="L188" t="n">
         <v>1</v>
       </c>
       <c r="M188" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="N188" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O188" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="P188" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q188" t="s">
         <v>41</v>
@@ -12130,22 +12355,22 @@
         <v>3</v>
       </c>
       <c r="K189" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="L189" t="n">
         <v>2</v>
       </c>
       <c r="M189" t="s">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="N189" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O189" t="s">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="P189" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q189" t="s">
         <v>41</v>
@@ -12186,22 +12411,22 @@
         <v>3</v>
       </c>
       <c r="K190" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="L190" t="n">
         <v>3</v>
       </c>
       <c r="M190" t="s">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="N190" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O190" t="s">
-        <v>392</v>
+        <v>428</v>
       </c>
       <c r="P190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q190" t="s">
         <v>41</v>
@@ -12215,7 +12440,7 @@
         <v>379</v>
       </c>
       <c r="B191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C191" t="s">
         <v>18</v>
@@ -12233,7 +12458,7 @@
         <v>2</v>
       </c>
       <c r="H191" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I191" t="n">
         <v>8</v>
@@ -12242,28 +12467,28 @@
         <v>3</v>
       </c>
       <c r="K191" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L191" t="n">
         <v>1</v>
       </c>
       <c r="M191" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="N191" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O191" t="s">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="P191" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q191" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R191" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="192">
@@ -12271,7 +12496,7 @@
         <v>380</v>
       </c>
       <c r="B192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C192" t="s">
         <v>18</v>
@@ -12289,7 +12514,7 @@
         <v>2</v>
       </c>
       <c r="H192" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I192" t="n">
         <v>8</v>
@@ -12298,28 +12523,28 @@
         <v>3</v>
       </c>
       <c r="K192" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L192" t="n">
         <v>2</v>
       </c>
       <c r="M192" t="s">
-        <v>393</v>
+        <v>431</v>
       </c>
       <c r="N192" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O192" t="s">
-        <v>394</v>
+        <v>432</v>
       </c>
       <c r="P192" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q192" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R192" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="193">
@@ -12327,7 +12552,7 @@
         <v>381</v>
       </c>
       <c r="B193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C193" t="s">
         <v>18</v>
@@ -12345,7 +12570,7 @@
         <v>2</v>
       </c>
       <c r="H193" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I193" t="n">
         <v>8</v>
@@ -12354,28 +12579,28 @@
         <v>3</v>
       </c>
       <c r="K193" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L193" t="n">
         <v>3</v>
       </c>
       <c r="M193" t="s">
-        <v>395</v>
+        <v>433</v>
       </c>
       <c r="N193" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O193" t="s">
-        <v>396</v>
+        <v>434</v>
       </c>
       <c r="P193" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q193" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R193" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="194">
@@ -12383,7 +12608,7 @@
         <v>385</v>
       </c>
       <c r="B194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C194" t="s">
         <v>18</v>
@@ -12410,24 +12635,28 @@
         <v>3</v>
       </c>
       <c r="K194" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="L194" t="n">
         <v>1</v>
       </c>
       <c r="M194" t="s">
-        <v>326</v>
-      </c>
-      <c r="N194"/>
+        <v>436</v>
+      </c>
+      <c r="N194" t="n">
+        <v>10</v>
+      </c>
       <c r="O194" t="s">
-        <v>326</v>
-      </c>
-      <c r="P194"/>
+        <v>437</v>
+      </c>
+      <c r="P194" t="n">
+        <v>5</v>
+      </c>
       <c r="Q194" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
       <c r="R194" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
     </row>
     <row r="195">
@@ -12435,7 +12664,7 @@
         <v>386</v>
       </c>
       <c r="B195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C195" t="s">
         <v>18</v>
@@ -12462,24 +12691,28 @@
         <v>3</v>
       </c>
       <c r="K195" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="L195" t="n">
         <v>2</v>
       </c>
       <c r="M195" t="s">
-        <v>326</v>
-      </c>
-      <c r="N195"/>
+        <v>439</v>
+      </c>
+      <c r="N195" t="n">
+        <v>10</v>
+      </c>
       <c r="O195" t="s">
-        <v>326</v>
-      </c>
-      <c r="P195"/>
+        <v>440</v>
+      </c>
+      <c r="P195" t="n">
+        <v>5</v>
+      </c>
       <c r="Q195" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
       <c r="R195" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
     </row>
     <row r="196">
@@ -12487,7 +12720,7 @@
         <v>387</v>
       </c>
       <c r="B196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C196" t="s">
         <v>18</v>
@@ -12514,24 +12747,28 @@
         <v>3</v>
       </c>
       <c r="K196" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="L196" t="n">
         <v>3</v>
       </c>
       <c r="M196" t="s">
-        <v>326</v>
-      </c>
-      <c r="N196"/>
+        <v>441</v>
+      </c>
+      <c r="N196" t="n">
+        <v>10</v>
+      </c>
       <c r="O196" t="s">
-        <v>326</v>
-      </c>
-      <c r="P196"/>
+        <v>442</v>
+      </c>
+      <c r="P196" t="n">
+        <v>5</v>
+      </c>
       <c r="Q196" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
       <c r="R196" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197">
@@ -12566,28 +12803,28 @@
         <v>3</v>
       </c>
       <c r="K197" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L197" t="n">
         <v>1</v>
       </c>
       <c r="M197" t="s">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="N197" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O197" t="s">
-        <v>399</v>
+        <v>444</v>
       </c>
       <c r="P197" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q197" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R197" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="198">
@@ -12622,28 +12859,28 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L198" t="n">
         <v>2</v>
       </c>
       <c r="M198" t="s">
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="N198" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O198" t="s">
-        <v>401</v>
+        <v>446</v>
       </c>
       <c r="P198" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q198" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R198" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="199">
@@ -12678,28 +12915,28 @@
         <v>3</v>
       </c>
       <c r="K199" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L199" t="n">
         <v>3</v>
       </c>
       <c r="M199" t="s">
-        <v>402</v>
+        <v>447</v>
       </c>
       <c r="N199" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O199" t="s">
-        <v>403</v>
+        <v>448</v>
       </c>
       <c r="P199" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q199" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R199" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="200">
@@ -12734,28 +12971,28 @@
         <v>3</v>
       </c>
       <c r="K200" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="L200" t="n">
         <v>1</v>
       </c>
       <c r="M200" t="s">
-        <v>147</v>
+        <v>449</v>
       </c>
       <c r="N200" t="n">
+        <v>7</v>
+      </c>
+      <c r="O200" t="s">
+        <v>450</v>
+      </c>
+      <c r="P200" t="n">
         <v>4</v>
       </c>
-      <c r="O200" t="s">
-        <v>404</v>
-      </c>
-      <c r="P200" t="n">
-        <v>3</v>
-      </c>
       <c r="Q200" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="R200" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="201">
@@ -12790,28 +13027,28 @@
         <v>3</v>
       </c>
       <c r="K201" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="L201" t="n">
         <v>2</v>
       </c>
       <c r="M201" t="s">
-        <v>405</v>
+        <v>451</v>
       </c>
       <c r="N201" t="n">
+        <v>7</v>
+      </c>
+      <c r="O201" t="s">
+        <v>452</v>
+      </c>
+      <c r="P201" t="n">
         <v>4</v>
       </c>
-      <c r="O201" t="s">
-        <v>406</v>
-      </c>
-      <c r="P201" t="n">
-        <v>3</v>
-      </c>
       <c r="Q201" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="R201" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="202">
@@ -12846,28 +13083,28 @@
         <v>3</v>
       </c>
       <c r="K202" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="L202" t="n">
         <v>3</v>
       </c>
       <c r="M202" t="s">
-        <v>218</v>
+        <v>453</v>
       </c>
       <c r="N202" t="n">
+        <v>7</v>
+      </c>
+      <c r="O202" t="s">
+        <v>454</v>
+      </c>
+      <c r="P202" t="n">
         <v>4</v>
       </c>
-      <c r="O202" t="s">
-        <v>407</v>
-      </c>
-      <c r="P202" t="n">
-        <v>3</v>
-      </c>
       <c r="Q202" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="R202" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="203">
@@ -12902,28 +13139,28 @@
         <v>3</v>
       </c>
       <c r="K203" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L203" t="n">
         <v>1</v>
       </c>
       <c r="M203" t="s">
-        <v>408</v>
+        <v>455</v>
       </c>
       <c r="N203" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O203" t="s">
-        <v>409</v>
+        <v>456</v>
       </c>
       <c r="P203" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q203" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R203" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="204">
@@ -12958,28 +13195,28 @@
         <v>3</v>
       </c>
       <c r="K204" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L204" t="n">
         <v>2</v>
       </c>
       <c r="M204" t="s">
-        <v>408</v>
+        <v>457</v>
       </c>
       <c r="N204" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O204" t="s">
-        <v>409</v>
+        <v>458</v>
       </c>
       <c r="P204" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q204" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R204" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="205">
@@ -13014,28 +13251,28 @@
         <v>3</v>
       </c>
       <c r="K205" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L205" t="n">
         <v>3</v>
       </c>
       <c r="M205" t="s">
-        <v>358</v>
+        <v>459</v>
       </c>
       <c r="N205" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O205" t="s">
-        <v>359</v>
+        <v>460</v>
       </c>
       <c r="P205" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q205" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R205" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="206">
@@ -13043,7 +13280,7 @@
         <v>409</v>
       </c>
       <c r="B206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C206" t="s">
         <v>18</v>
@@ -13070,24 +13307,28 @@
         <v>3</v>
       </c>
       <c r="K206" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="s">
-        <v>326</v>
-      </c>
-      <c r="N206"/>
+        <v>461</v>
+      </c>
+      <c r="N206" t="n">
+        <v>10</v>
+      </c>
       <c r="O206" t="s">
-        <v>326</v>
-      </c>
-      <c r="P206"/>
+        <v>462</v>
+      </c>
+      <c r="P206" t="n">
+        <v>5</v>
+      </c>
       <c r="Q206" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
       <c r="R206" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
     </row>
     <row r="207">
@@ -13095,7 +13336,7 @@
         <v>410</v>
       </c>
       <c r="B207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C207" t="s">
         <v>18</v>
@@ -13122,24 +13363,28 @@
         <v>3</v>
       </c>
       <c r="K207" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="L207" t="n">
         <v>2</v>
       </c>
       <c r="M207" t="s">
-        <v>326</v>
-      </c>
-      <c r="N207"/>
+        <v>463</v>
+      </c>
+      <c r="N207" t="n">
+        <v>10</v>
+      </c>
       <c r="O207" t="s">
-        <v>326</v>
-      </c>
-      <c r="P207"/>
+        <v>464</v>
+      </c>
+      <c r="P207" t="n">
+        <v>5</v>
+      </c>
       <c r="Q207" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
       <c r="R207" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
     </row>
     <row r="208">
@@ -13147,7 +13392,7 @@
         <v>411</v>
       </c>
       <c r="B208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C208" t="s">
         <v>18</v>
@@ -13174,24 +13419,28 @@
         <v>3</v>
       </c>
       <c r="K208" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="L208" t="n">
         <v>3</v>
       </c>
       <c r="M208" t="s">
-        <v>326</v>
-      </c>
-      <c r="N208"/>
+        <v>465</v>
+      </c>
+      <c r="N208" t="n">
+        <v>10</v>
+      </c>
       <c r="O208" t="s">
-        <v>326</v>
-      </c>
-      <c r="P208"/>
+        <v>466</v>
+      </c>
+      <c r="P208" t="n">
+        <v>5</v>
+      </c>
       <c r="Q208" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
       <c r="R208" t="s">
-        <v>326</v>
+        <v>438</v>
       </c>
     </row>
     <row r="209">
@@ -13226,28 +13475,28 @@
         <v>3</v>
       </c>
       <c r="K209" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L209" t="n">
         <v>1</v>
       </c>
       <c r="M209" t="s">
-        <v>410</v>
+        <v>467</v>
       </c>
       <c r="N209" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O209" t="s">
-        <v>411</v>
+        <v>468</v>
       </c>
       <c r="P209" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q209" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R209" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="210">
@@ -13282,28 +13531,28 @@
         <v>3</v>
       </c>
       <c r="K210" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L210" t="n">
         <v>2</v>
       </c>
       <c r="M210" t="s">
-        <v>412</v>
+        <v>469</v>
       </c>
       <c r="N210" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O210" t="s">
-        <v>413</v>
+        <v>470</v>
       </c>
       <c r="P210" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q210" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R210" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="211">
@@ -13338,28 +13587,28 @@
         <v>3</v>
       </c>
       <c r="K211" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L211" t="n">
         <v>3</v>
       </c>
       <c r="M211" t="s">
-        <v>414</v>
+        <v>471</v>
       </c>
       <c r="N211" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O211" t="s">
-        <v>415</v>
+        <v>472</v>
       </c>
       <c r="P211" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q211" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="R211" t="s">
-        <v>188</v>
+        <v>344</v>
       </c>
     </row>
     <row r="212">
@@ -13367,7 +13616,7 @@
         <v>421</v>
       </c>
       <c r="B212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C212" t="s">
         <v>18</v>
@@ -13394,28 +13643,28 @@
         <v>3</v>
       </c>
       <c r="K212" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="L212" t="n">
         <v>1</v>
       </c>
       <c r="M212" t="s">
-        <v>416</v>
+        <v>473</v>
       </c>
       <c r="N212" t="n">
+        <v>7</v>
+      </c>
+      <c r="O212" t="s">
+        <v>474</v>
+      </c>
+      <c r="P212" t="n">
         <v>4</v>
       </c>
-      <c r="O212" t="s">
-        <v>417</v>
-      </c>
-      <c r="P212" t="n">
-        <v>3</v>
-      </c>
       <c r="Q212" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="R212" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="213">
@@ -13423,7 +13672,7 @@
         <v>422</v>
       </c>
       <c r="B213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C213" t="s">
         <v>18</v>
@@ -13450,28 +13699,28 @@
         <v>3</v>
       </c>
       <c r="K213" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="L213" t="n">
         <v>2</v>
       </c>
       <c r="M213" t="s">
-        <v>418</v>
+        <v>475</v>
       </c>
       <c r="N213" t="n">
+        <v>7</v>
+      </c>
+      <c r="O213" t="s">
+        <v>476</v>
+      </c>
+      <c r="P213" t="n">
         <v>4</v>
       </c>
-      <c r="O213" t="s">
-        <v>419</v>
-      </c>
-      <c r="P213" t="n">
-        <v>3</v>
-      </c>
       <c r="Q213" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="R213" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="214">
@@ -13479,7 +13728,7 @@
         <v>423</v>
       </c>
       <c r="B214" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C214" t="s">
         <v>18</v>
@@ -13506,28 +13755,28 @@
         <v>3</v>
       </c>
       <c r="K214" t="s">
-        <v>397</v>
+        <v>435</v>
       </c>
       <c r="L214" t="n">
         <v>3</v>
       </c>
       <c r="M214" t="s">
-        <v>420</v>
+        <v>477</v>
       </c>
       <c r="N214" t="n">
+        <v>7</v>
+      </c>
+      <c r="O214" t="s">
+        <v>478</v>
+      </c>
+      <c r="P214" t="n">
         <v>4</v>
       </c>
-      <c r="O214" t="s">
-        <v>421</v>
-      </c>
-      <c r="P214" t="n">
-        <v>3</v>
-      </c>
       <c r="Q214" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="R214" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="215">
@@ -13535,7 +13784,7 @@
         <v>427</v>
       </c>
       <c r="B215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C215" t="s">
         <v>18</v>
@@ -13553,7 +13802,7 @@
         <v>2</v>
       </c>
       <c r="H215" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I215" t="n">
         <v>9</v>
@@ -13562,28 +13811,28 @@
         <v>3</v>
       </c>
       <c r="K215" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L215" t="n">
         <v>1</v>
       </c>
       <c r="M215" t="s">
-        <v>393</v>
+        <v>479</v>
       </c>
       <c r="N215" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O215" t="s">
-        <v>394</v>
+        <v>480</v>
       </c>
       <c r="P215" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q215" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R215" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="216">
@@ -13591,7 +13840,7 @@
         <v>428</v>
       </c>
       <c r="B216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C216" t="s">
         <v>18</v>
@@ -13609,7 +13858,7 @@
         <v>2</v>
       </c>
       <c r="H216" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I216" t="n">
         <v>9</v>
@@ -13618,28 +13867,28 @@
         <v>3</v>
       </c>
       <c r="K216" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L216" t="n">
         <v>2</v>
       </c>
       <c r="M216" t="s">
-        <v>422</v>
+        <v>481</v>
       </c>
       <c r="N216" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O216" t="s">
-        <v>423</v>
+        <v>482</v>
       </c>
       <c r="P216" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q216" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R216" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="217">
@@ -13647,7 +13896,7 @@
         <v>429</v>
       </c>
       <c r="B217" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C217" t="s">
         <v>18</v>
@@ -13665,7 +13914,7 @@
         <v>2</v>
       </c>
       <c r="H217" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I217" t="n">
         <v>9</v>
@@ -13674,28 +13923,28 @@
         <v>3</v>
       </c>
       <c r="K217" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="L217" t="n">
         <v>3</v>
       </c>
       <c r="M217" t="s">
-        <v>424</v>
+        <v>483</v>
       </c>
       <c r="N217" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O217" t="s">
-        <v>425</v>
+        <v>484</v>
       </c>
       <c r="P217" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q217" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="R217" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_lon_fold_sets.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_lon_fold_sets.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="483">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -80,25 +80,25 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 77, 134, 135, 136, 137, 1671, 1787, 1788, 1790, 1792, 1794, 1795, 1888, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 74, 75, 76, 133, 1789, 1793, 2049, 2050, 2051)</t>
+    <t xml:space="preserve">c(59, 74, 75, 76, 133, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1793, 1794, 1888, 2049, 2050, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 61, 77, 134, 1792, 1795, 2052, 2262)</t>
   </si>
   <si>
     <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 59, 61, 74, 75, 134, 135, 136, 1671, 1787, 1789, 1794, 1795, 1888, 2049, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 76, 77, 133, 137, 1788, 1790, 1792, 1793, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 74, 75, 76, 133, 134, 135, 136, 1671, 1788, 1789, 1790, 1792, 1793, 1795, 2049, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 61, 77, 137, 1787, 1794, 1888, 2050, 2053)</t>
+    <t xml:space="preserve">c(51, 58, 61, 75, 76, 77, 133, 134, 135, 137, 1671, 1788, 1790, 1792, 1794, 1795, 1888, 2050, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 74, 136, 1787, 1789, 1793, 2049, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 75, 76, 77, 133, 134, 136, 137, 1787, 1788, 1789, 1790, 1792, 1795, 2049, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 61, 74, 135, 1671, 1793, 1794, 1888, 2050, 2053)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
@@ -107,1366 +107,1360 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 123, 124, 183, 184, 185, 186, 1747, 1749, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 125, 1748, 1892, 2006, 2007, 2008)</t>
+    <t xml:space="preserve">c(78, 79, 80, 124, 125, 183, 184, 185, 186, 1747, 1748, 1890, 1891, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 122, 123, 1749, 1892, 2006, 2007)</t>
   </si>
   <si>
     <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 183, 184, 185, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(80, 81, 82, 122, 124, 125, 183, 184, 1747, 1749, 1890, 1891, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 123, 185, 186, 1748, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 82, 123, 124, 125, 185, 186, 1749, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 122, 183, 184, 1747, 1748, 1890)</t>
+    <t xml:space="preserve">c(79, 80, 81, 122, 123, 124, 183, 184, 186, 1749, 1891, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 125, 185, 1747, 1748, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 82, 122, 124, 125, 183, 184, 185, 1748, 1749, 1890, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 123, 186, 1747, 1891, 1892, 2007)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1980, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1833, 1834, 1979, 2145)</t>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 1834, 2146, 2147)</t>
   </si>
   <si>
     <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1834, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1979, 1980, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1833, 1834, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1834, 1979, 1980, 2144, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1832, 1833, 2146)</t>
+    <t xml:space="preserve">c(1828, 1829, 1832, 1833, 1979, 1980, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1834, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1833, 1980, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1834, 1979, 2145, 2147)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(100, 101, 103, 104, 105, 107, 108, 111, 114, 115, 117, 118, 1646, 1648, 1676, 1677, 2211, 2212, 2213, 2297, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 106, 109, 110, 112, 113, 116, 1645, 1647, 2296, 2322, 2323)</t>
+    <t xml:space="preserve">c(100, 101, 102, 104, 105, 107, 109, 110, 112, 113, 115, 116, 118, 1645, 1646, 1647, 1676, 2211, 2213, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 106, 108, 111, 114, 117, 1648, 1677, 2212, 2296, 2297, 2322)</t>
   </si>
   <si>
     <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(100, 102, 104, 106, 107, 109, 110, 111, 112, 114, 115, 117, 1645, 1647, 1676, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 103, 105, 108, 113, 116, 118, 1646, 1648, 1677, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 105, 107, 109, 110, 111, 112, 113, 114, 115, 116, 117, 1645, 1647, 1676, 1677, 2213, 2296, 2297, 2298, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 104, 106, 108, 118, 1646, 1648, 2211, 2212, 2299, 2322)</t>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 106, 109, 112, 113, 115, 116, 117, 118, 1648, 1677, 2211, 2213, 2296, 2297, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(105, 107, 108, 110, 111, 114, 1645, 1646, 1647, 1676, 2212, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 107, 109, 113, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 2211, 2212, 2213, 2296, 2297, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 105, 106, 108, 110, 111, 112, 114, 1677, 2299, 2321)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 77, 134, 136, 137, 1671, 1787, 1789, 1790, 1792, 1793, 1794, 1888, 2049, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 74, 75, 76, 133, 135, 1788, 1795, 2050, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 61, 74, 75, 76, 133, 134, 136, 1671, 1787, 1788, 1789, 1792, 1793, 1794, 1795, 1888, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 77, 135, 137, 1790, 2049, 2050, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 74, 76, 77, 133, 134, 137, 1790, 1792, 1793, 1794, 1795, 1888, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 75, 135, 136, 1671, 1787, 1788, 1789, 2049, 2053)</t>
+    <t xml:space="preserve">c(59, 61, 74, 77, 133, 134, 135, 137, 1671, 1787, 1788, 1790, 1792, 1793, 1794, 1795, 2049, 2050, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 75, 76, 136, 1789, 1888, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 75, 77, 133, 134, 136, 137, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 74, 76, 135, 1671, 1787, 2050, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 74, 75, 77, 133, 135, 136, 1787, 1790, 1793, 1794, 1888, 2049, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 76, 134, 137, 1671, 1788, 1789, 1792, 1795, 2052)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(80, 81, 124, 125, 184, 185, 186, 1748, 1749, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 82, 122, 123, 183, 1747, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 122, 124, 183, 185, 186, 1747, 1748, 1890, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 82, 123, 125, 184, 1749, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 122, 124, 184, 186, 1748, 1749, 1890, 1891, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 82, 123, 125, 183, 185, 1747, 2006)</t>
+    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 124, 125, 185, 186, 1749, 1890, 1891, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 183, 184, 1747, 1748, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 123, 125, 183, 186, 1748, 1890, 1891, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 122, 124, 184, 185, 1747, 1749, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 122, 123, 125, 184, 185, 186, 1748, 1891, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 124, 183, 1747, 1749, 1890, 2007, 2008)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1979, 1980, 2144, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 1834, 2145, 2148)</t>
-  </si>
-  <si>
     <t xml:space="preserve">c(1829, 1830, 1833, 1834, 1980, 2144, 2145, 2146, 2148)</t>
   </si>
   <si>
     <t xml:space="preserve">c(1828, 1831, 1832, 1979, 2147)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1834, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1979, 1980, 2144, 2145, 2147)</t>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1834, 1980, 2144, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1833, 1979, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1979, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1833, 1834, 1980, 2148)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(100, 101, 102, 108, 109, 110, 111, 114, 115, 117, 118, 1645, 1646, 1676, 2211, 2212, 2213, 2296, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 104, 105, 106, 107, 112, 113, 116, 1647, 1648, 1677, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 105, 106, 107, 108, 110, 111, 112, 114, 115, 116, 117, 1645, 1646, 1647, 1648, 1676, 1677, 2212, 2213, 2297)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 104, 109, 113, 118, 2211, 2296, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 106, 107, 110, 111, 112, 113, 114, 117, 118, 1646, 1647, 1676, 1677, 2211, 2212, 2213, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 104, 105, 108, 109, 115, 116, 1645, 1648, 2296, 2297, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 74, 75, 77, 134, 135, 136, 1671, 1787, 1788, 1790, 1794, 1795, 1888, 2049, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 76, 133, 137, 1789, 1792, 1793, 2050, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 134, 136, 1671, 1787, 1788, 1789, 1790, 1793, 1794, 1795, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(76, 77, 133, 135, 137, 1792, 1888, 2049, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 61, 76, 133, 134, 135, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 2049, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 74, 75, 77, 136, 1795, 1888, 2050, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 125, 184, 185, 1747, 1748, 1749, 1891, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(82, 123, 124, 183, 186, 1890, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 82, 122, 123, 124, 183, 184, 185, 186, 1747, 1749, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 125, 1748, 1891, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 82, 123, 124, 125, 183, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 122, 184, 185, 186, 1747)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1832, 1833, 1979, 1980, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1834, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1833, 1979, 1980, 2144, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1834, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1834, 1979, 1980, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1833, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 107, 108, 110, 111, 114, 115, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2296, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 105, 106, 109, 112, 113, 116, 117, 118, 2297, 2298, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 106, 107, 108, 109, 110, 111, 114, 115, 116, 117, 1646, 1648, 1676, 1677, 2212, 2213, 2297, 2298, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 105, 112, 113, 118, 1645, 1647, 2211, 2296, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 103, 104, 109, 111, 112, 114, 115, 116, 117, 118, 1645, 1646, 1647, 2211, 2212, 2213, 2296, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 105, 106, 107, 108, 110, 113, 1648, 1676, 1677, 2297, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 75, 77, 133, 134, 135, 136, 137, 1787, 1788, 1790, 1792, 1793, 1794, 1795, 2049, 2050, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 61, 74, 76, 1671, 1789, 1888, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 74, 76, 77, 133, 134, 135, 136, 137, 1788, 1792, 1793, 1794, 1888, 2049, 2050, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 75, 1671, 1787, 1789, 1790, 1795, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 74, 75, 76, 77, 134, 135, 136, 137, 1671, 1787, 1790, 1795, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 133, 1788, 1789, 1792, 1793, 1794, 1888, 2049, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 82, 122, 123, 125, 185, 186, 1747, 1890, 1891, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 124, 183, 184, 1748, 1749, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 125, 183, 184, 186, 1890, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(122, 123, 124, 185, 1747, 1748, 1749, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 123, 125, 183, 186, 1747, 1748, 1749, 1890, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 82, 122, 124, 184, 185, 1891, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 1833, 1834, 1979, 1980, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1833, 1979, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1832, 1834, 1980, 2144)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1833, 1834, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1832, 1979, 1980, 2144)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 105, 106, 107, 108, 109, 110, 111, 112, 117, 1645, 1647, 1648, 1676, 2211, 2213, 2296, 2297, 2298, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 104, 113, 114, 115, 116, 118, 1646, 1677, 2212, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 105, 106, 108, 109, 110, 112, 116, 117, 118, 1645, 1647, 1676, 1677, 2211, 2296, 2297, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 107, 111, 113, 114, 115, 1646, 1648, 2212, 2213, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 104, 106, 107, 108, 109, 110, 111, 114, 115, 118, 1645, 1646, 1647, 1677, 2212, 2213, 2297, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 105, 112, 113, 116, 117, 1648, 1676, 2211, 2296, 2322)</t>
+    <t xml:space="preserve">c(103, 104, 105, 107, 108, 109, 110, 113, 115, 117, 118, 1646, 1647, 1676, 1677, 2211, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 106, 111, 112, 114, 116, 1645, 1648, 2212, 2213)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 108, 109, 111, 112, 115, 116, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2213, 2296, 2298, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(106, 107, 110, 113, 114, 117, 118, 2212, 2297, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 108, 109, 110, 111, 112, 113, 116, 1645, 1646, 1647, 1676, 1677, 2213, 2297, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 107, 114, 115, 117, 118, 1648, 2211, 2212, 2296, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 61, 75, 77, 135, 136, 137, 1787, 1788, 1789, 1792, 1793, 1794, 1795, 1888, 2049, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 74, 76, 133, 134, 1671, 1790, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 61, 75, 77, 133, 136, 137, 1671, 1787, 1788, 1790, 1794, 1888, 2049, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 74, 76, 134, 135, 1789, 1792, 1793, 1795, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 76, 77, 133, 137, 1671, 1787, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 61, 74, 75, 134, 135, 136, 1788, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 122, 125, 185, 186, 1748, 1890, 1891, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 123, 124, 183, 184, 1747, 1749, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 122, 124, 183, 184, 1748, 1749, 1890, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(82, 123, 125, 185, 186, 1747, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 82, 123, 124, 125, 184, 186, 1747, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 122, 183, 185, 1748, 1749, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1834, 1979, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1832, 1833, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1979, 1980, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1833, 1834, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1979, 1980, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 1834, 2144, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 104, 105, 106, 108, 112, 116, 117, 118, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2297, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 107, 109, 110, 111, 113, 114, 115, 1645, 2296, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 105, 106, 107, 108, 110, 111, 113, 114, 115, 116, 118, 1645, 1647, 1648, 1677, 2212, 2297, 2298, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 104, 109, 112, 117, 1646, 1676, 2211, 2213, 2296, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 106, 107, 108, 109, 110, 111, 114, 116, 1645, 1646, 1647, 1676, 1677, 2212, 2296, 2297, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 104, 105, 112, 113, 115, 117, 118, 1648, 2211, 2213, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 76, 77, 134, 1787, 1788, 1789, 1792, 1794, 1795, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 75, 133, 135, 136, 137, 1671, 1790, 1793, 1888)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 74, 75, 76, 77, 134, 135, 136, 137, 1787, 1789, 1792, 1793, 1794, 1795, 1888, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 61, 133, 1671, 1788, 1790, 2049, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 74, 75, 76, 77, 133, 134, 135, 137, 1671, 1787, 1789, 1790, 1794, 1888, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 61, 136, 1788, 1792, 1793, 1795, 2049, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 122, 124, 125, 183, 186, 1747, 1748, 1749, 1891, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 82, 123, 184, 185, 1890, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 124, 125, 183, 185, 186, 1748, 1749, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 82, 122, 123, 184, 1747, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 82, 124, 183, 184, 185, 1747, 1748, 1890, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 122, 123, 125, 186, 1749, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 1834, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1979, 1980, 2144, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1834, 1979, 1980, 2144, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1833, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1834, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1979, 1980, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 106, 107, 108, 112, 114, 116, 117, 1646, 1647, 1676, 1677, 2211, 2212, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 105, 109, 110, 111, 113, 115, 118, 1645, 1648, 2213, 2296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 105, 106, 107, 109, 110, 111, 112, 113, 114, 115, 117, 118, 2211, 2213, 2297, 2298, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 108, 116, 1645, 1646, 1647, 1648, 1676, 1677, 2212, 2296, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 107, 108, 109, 110, 111, 114, 115, 116, 117, 118, 1645, 1646, 1648, 1676, 1677, 2212, 2213, 2296, 2297, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 104, 105, 106, 112, 113, 1647, 2211, 2298, 2299, 2321, 2323)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 61, 74, 76, 77, 133, 134, 136, 137, 1671, 1787, 1788, 1789, 1790, 1793, 1795, 1888, 2049, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 75, 135, 1792, 1794, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 61, 74, 76, 77, 133, 135, 136, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1795, 1888, 2049, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 75, 134, 137, 1794, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 61, 74, 76, 77, 134, 135, 136, 137, 1671, 1788, 1789, 1790, 1792, 1794, 1795, 1888, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 75, 133, 1787, 1793, 2049, 2050, 2051, 2053)</t>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 76, 77, 137, 1671, 1787, 1788, 1789, 1790, 1793, 1794, 2049, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 75, 133, 134, 135, 136, 1792, 1795, 1888, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 61, 74, 76, 77, 133, 136, 137, 1671, 1787, 1789, 1790, 1793, 1794, 1795, 1888, 2049, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 75, 134, 135, 1788, 1792, 2050, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 76, 77, 133, 134, 137, 1787, 1788, 1789, 1794, 1795, 1888, 2049, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(75, 135, 136, 1671, 1790, 1792, 1793, 2050, 2051, 2262)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 123, 124, 125, 184, 186, 1747, 1748, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 183, 185, 1749, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 82, 123, 125, 183, 184, 185, 186, 1890, 1891, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 122, 124, 1747, 1748, 1749, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 122, 123, 124, 184, 186, 1747, 1749, 1890, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 82, 125, 183, 185, 1748, 1891, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1832, 1834, 1979, 1980, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1833, 2144, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1833, 1834, 1980, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1832, 1979, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833, 1979, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1834, 1980, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 105, 106, 107, 108, 110, 112, 113, 115, 117, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2213, 2297, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 109, 111, 114, 116, 2212, 2296, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 107, 108, 111, 112, 113, 116, 118, 1646, 1647, 1648, 1676, 1677, 2211, 2213, 2296, 2297, 2298, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 105, 106, 109, 110, 114, 115, 117, 1645, 2212, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 104, 105, 106, 109, 110, 112, 113, 116, 117, 118, 1645, 1646, 1648, 1677, 2211, 2212, 2213, 2296, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 107, 108, 111, 114, 115, 1647, 1676, 2297, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 76, 77, 134, 135, 136, 137, 1788, 1789, 1792, 1793, 1795, 1888, 2049, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(75, 133, 1671, 1787, 1790, 1794, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 74, 75, 76, 77, 133, 134, 137, 1788, 1789, 1790, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 135, 136, 1671, 1787, 1792, 1793)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 75, 76, 133, 134, 136, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1795, 1888, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 61, 74, 77, 135, 137, 1794, 2049, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 82, 122, 123, 125, 185, 186, 1747, 1748, 1890, 1891, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 124, 183, 184, 1749, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 82, 122, 124, 185, 186, 1747, 1748, 1749, 1890, 1891, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 123, 125, 183, 184, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 123, 124, 125, 183, 184, 186, 1747, 1748, 1749, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 185, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 1834, 1980, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1979, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1832, 1834, 1979, 1980, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1833, 2144, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1832, 1833, 1834, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1979, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 104, 106, 108, 109, 112, 113, 114, 115, 116, 118, 1645, 1647, 1648, 1676, 1677, 2212, 2213, 2296, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 105, 107, 110, 111, 117, 1646, 2211, 2297, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 106, 107, 108, 111, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1676, 1677, 2213, 2296, 2297, 2298, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 105, 109, 110, 112, 1648, 2211, 2212, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 104, 107, 108, 110, 111, 112, 113, 114, 115, 116, 118, 1645, 1646, 1677, 2212, 2296, 2297, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 105, 106, 109, 117, 1647, 1648, 1676, 2211, 2213, 2322)</t>
+    <t xml:space="preserve">c(78, 79, 80, 81, 122, 124, 125, 183, 184, 185, 1748, 1890, 1891, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(82, 123, 186, 1747, 1749, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 125, 183, 184, 186, 1748, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(123, 124, 185, 1747, 1749, 1890, 1891, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 122, 124, 125, 183, 184, 185, 1747, 1749, 1890, 1891, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 82, 123, 186, 1748, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1979, 2144, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1834, 1980, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833, 1834, 1979, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1980, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1834, 1979, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 108, 109, 110, 111, 112, 113, 114, 118, 1647, 1676, 1677, 2211, 2213, 2297, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(106, 107, 115, 116, 117, 1645, 1646, 1648, 2212, 2296, 2298, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 104, 106, 107, 108, 110, 111, 112, 113, 114, 116, 118, 1646, 1647, 1648, 1676, 1677, 2296, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 105, 109, 115, 117, 1645, 2211, 2212, 2213, 2297)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 106, 108, 110, 111, 112, 113, 114, 115, 117, 118, 1646, 1648, 1676, 1677, 2211, 2212, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 105, 107, 109, 116, 1645, 1647, 2213, 2296, 2297, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 61, 75, 76, 133, 134, 135, 137, 1671, 1787, 1789, 1792, 1794, 1888, 2049, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 74, 77, 136, 1788, 1790, 1793, 1795, 2050, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 75, 76, 134, 135, 136, 137, 1671, 1787, 1788, 1790, 1793, 1795, 1888, 2049, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 74, 77, 133, 1789, 1792, 1794, 2050, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 61, 74, 75, 77, 134, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1794, 1795, 2049, 2050, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 76, 133, 135, 1793, 1888, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 122, 124, 125, 183, 184, 185, 186, 1747, 1748, 1749, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 123, 1890, 1891, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 122, 124, 183, 184, 185, 186, 1747, 1748, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 82, 123, 125, 1749, 1890, 1891, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 122, 124, 125, 184, 186, 1747, 1748, 1749, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 123, 183, 185, 1890, 1891, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1834, 1979, 1980, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1833, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1834, 1979, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 1980, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1832, 1833, 1979, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1834, 1980, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 106, 107, 108, 109, 113, 114, 116, 118, 1645, 1646, 1647, 1648, 1676, 2211, 2212, 2296, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 104, 105, 110, 111, 112, 115, 117, 1677, 2213, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 105, 106, 107, 108, 109, 111, 113, 114, 115, 116, 117, 1646, 1677, 2213, 2296, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(104, 110, 112, 118, 1645, 1647, 1648, 1676, 2211, 2212, 2297, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 105, 107, 109, 111, 115, 118, 1645, 1646, 1647, 1648, 1676, 2211, 2213, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 106, 108, 110, 112, 113, 114, 116, 117, 1677, 2212, 2296)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 75, 76, 77, 134, 136, 1671, 1787, 1788, 1790, 1792, 1795, 1888, 2049, 2050, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 74, 133, 135, 137, 1789, 1793, 1794, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 75, 76, 133, 135, 136, 137, 1671, 1787, 1788, 1790, 1793, 1888, 2049, 2050, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 74, 77, 134, 1789, 1792, 1794, 1795, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 76, 133, 135, 136, 1671, 1787, 1788, 1789, 1793, 1794, 1888, 2049, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 75, 77, 134, 137, 1790, 1792, 1795, 2051, 2262)</t>
+    <t xml:space="preserve">c(51, 58, 60, 61, 75, 77, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1793, 1794, 1795, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 74, 76, 1789, 1790, 1792, 1888, 2049, 2050, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 75, 76, 77, 134, 136, 1787, 1788, 1790, 1792, 1793, 1795, 1888, 2049, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 74, 133, 135, 137, 1671, 1789, 1794, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 75, 76, 77, 133, 134, 135, 136, 1788, 1789, 1792, 1794, 1795, 2049, 2050, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 74, 137, 1671, 1787, 1790, 1793, 1888, 2052, 2262)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 1892)</t>
+    <t xml:space="preserve">c(78, 79, 80, 122, 124, 125, 1748, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 123, 1747, 1749)</t>
   </si>
   <si>
     <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 79, 82, 123, 124, 125, 1747, 1748, 1749, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 122, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 82, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 122, 123, 124)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1834, 1980, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1832, 1833, 1979, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1832, 1833, 1834, 1980, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1979, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1979, 1980, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1833, 1834, 2144, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 108, 109, 110, 113, 114, 115, 117, 118, 1647, 1648, 1676, 2211, 2212, 2296, 2298, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(106, 107, 111, 112, 116, 1645, 1646, 1677, 2213, 2297, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 104, 105, 106, 108, 110, 111, 112, 113, 114, 116, 1645, 1646, 1648, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 107, 109, 115, 117, 118, 1647, 1676, 1677, 2211, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 103, 104, 105, 106, 107, 108, 110, 111, 112, 113, 115, 116, 117, 118, 1646, 1648, 1676, 1677, 2211, 2212, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 109, 114, 1645, 1647, 2213, 2296, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 77, 133, 134, 136, 137, 1671, 1787, 1790, 1792, 1793, 2049, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 76, 135, 1788, 1789, 1794, 1795, 1888, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 61, 74, 77, 134, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1795, 1888, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 75, 76, 133, 135, 1794, 2049, 2050, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 76, 77, 133, 134, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1795, 2049, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 74, 75, 135, 136, 1793, 1794, 1888, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 123, 124, 125, 1748, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 1747, 1749, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 122, 125, 1747, 1748, 1749, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 123, 124, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 122, 124, 125, 1748, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 123, 1747, 1749, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1832, 1833, 1834, 1979, 1980, 2144, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1834, 1979, 1980, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1834, 1979, 1980, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 1833, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 105, 106, 109, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2297, 2298, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 107, 108, 110, 111, 112, 113, 2213, 2296, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 107, 109, 110, 111, 113, 114, 115, 116, 1645, 1647, 1648, 1676, 2211, 2212, 2298, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(106, 108, 112, 117, 118, 1646, 1677, 2213, 2296, 2297, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 107, 109, 111, 112, 113, 114, 115, 1645, 1676, 1677, 2211, 2213, 2296, 2297, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 108, 110, 116, 117, 118, 1646, 1647, 1648, 2212, 2299, 2321)</t>
+    <t xml:space="preserve">c(80, 81, 82, 122, 124, 125, 1747, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 123, 1748, 1749)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 82, 122, 123, 124, 125, 1747, 1749, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 1748, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1979, 1980, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1834, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1832, 1833, 1834, 1979, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1980, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1832, 1834, 1979, 1980, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1833, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 104, 105, 107, 108, 110, 111, 113, 114, 116, 1645, 1648, 1676, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 106, 109, 112, 115, 117, 118, 1646, 1647, 1677, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 110, 111, 117, 118, 1645, 1646, 1648, 1677, 2213, 2297, 2298, 2299, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(109, 112, 113, 114, 115, 116, 1647, 1676, 2211, 2212, 2296, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 106, 109, 110, 111, 112, 114, 116, 117, 118, 1646, 1647, 1676, 2211, 2212, 2296, 2297, 2298, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 105, 107, 108, 113, 115, 1645, 1648, 1677, 2213, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 74, 76, 77, 133, 134, 135, 136, 1671, 1787, 1788, 1790, 1792, 1793, 1794, 2049, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 75, 137, 1789, 1795, 1888, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 74, 76, 77, 134, 135, 136, 1671, 1787, 1789, 1792, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 75, 133, 137, 1788, 1790, 1793, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 61, 75, 77, 133, 135, 137, 1671, 1787, 1789, 1793, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 74, 76, 134, 136, 1788, 1790, 1792, 1794)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 122, 123, 124, 1747, 1749, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 82, 125, 1748, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 123, 124, 125, 1747, 1748, 1749, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 82, 122, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1833, 1834, 2144, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1979, 1980, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1979, 1980, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 1833, 1834, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1834, 1979, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1832, 1833, 1980, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 106, 107, 108, 109, 111, 112, 115, 116, 117, 118, 1645, 1646, 1647, 1676, 2211, 2213, 2296, 2297, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 104, 105, 110, 113, 114, 1648, 1677, 2212, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 105, 107, 109, 111, 112, 113, 114, 115, 116, 117, 118, 1676, 1677, 2211, 2212, 2213, 2297, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 104, 106, 108, 110, 1645, 1646, 1647, 1648, 2296, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 104, 106, 108, 109, 110, 111, 112, 114, 115, 116, 1645, 1647, 1648, 1676, 1677, 2211, 2213, 2296, 2297, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 105, 107, 113, 117, 118, 1646, 2212, 2298, 2299, 2321)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(58, 74, 75, 76, 134, 136, 137, 1671, 1787, 1788, 1790, 1792, 1793, 1794, 1795, 2049, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 77, 133, 135, 1789, 1888, 2050)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 74, 77, 133, 135, 136, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 75, 76, 134, 137, 1671, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 74, 76, 77, 133, 134, 135, 136, 1787, 1788, 1790, 1792, 1794, 1888, 2049, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 61, 75, 137, 1671, 1789, 1793, 1795, 2052)</t>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 133, 135, 137, 1787, 1788, 1792, 1794, 1795, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(134, 136, 1671, 1789, 1790, 1793, 1888, 2049, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 61, 74, 76, 133, 134, 135, 1671, 1790, 1792, 1793, 1794, 1888, 2049, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 75, 77, 136, 137, 1787, 1788, 1789, 1795, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 75, 76, 77, 134, 135, 136, 137, 1671, 1788, 1789, 1792, 1793, 1888, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 74, 133, 1787, 1790, 1794, 1795, 2049, 2052)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(79, 82, 122, 123, 124, 125, 184, 185, 186, 1748, 1749, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 183, 1747, 1890, 1891, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 82, 122, 124, 125, 183, 185, 1890, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 123, 184, 186, 1747, 1748, 1749, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 82, 123, 124, 125, 184, 185, 1747, 1748, 1749, 1890, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 122, 183, 186, 1891, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1834, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 1979, 1980, 2144)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1832, 1833, 1834, 1980, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1979, 2144, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1832, 1833, 1834, 1979, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1980, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 107, 111, 112, 114, 115, 116, 118, 1645, 1647, 1648, 1676, 2211, 2213, 2296, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 108, 109, 110, 113, 117, 1646, 1677, 2212, 2297, 2298, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 105, 106, 108, 109, 110, 111, 112, 114, 115, 116, 117, 1647, 1648, 1677, 2211, 2213, 2296, 2297, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 104, 107, 113, 118, 1645, 1646, 1676, 2212, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 105, 106, 108, 110, 111, 112, 114, 116, 117, 118, 1645, 1646, 1648, 2212, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 104, 107, 109, 113, 115, 1647, 1676, 1677, 2211, 2213)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 136, 137, 1671, 1787, 1788, 1792, 1793, 1888, 2049, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 77, 133, 134, 135, 1789, 1790, 1794, 1795, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 137, 1671, 1788, 1789, 1792, 1793, 1794, 1888, 2050, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 134, 135, 136, 1787, 1790, 1795, 2049, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 61, 74, 75, 77, 134, 136, 137, 1787, 1788, 1789, 1790, 1792, 1795, 1888, 2049, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 76, 133, 135, 1671, 1793, 1794, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 82, 122, 123, 124, 183, 185, 1748, 1749, 1890, 1891, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 125, 184, 186, 1747, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 82, 123, 124, 125, 183, 186, 1747, 1749, 1890, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 122, 184, 185, 1748, 1891, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 82, 122, 123, 124, 183, 184, 185, 1747, 1748, 1891, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 125, 186, 1749, 1890, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1833, 1980, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1834, 1979, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1834, 1979, 1980, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 2144, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1833, 1979, 1980, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1832, 1834, 2144, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(105, 106, 107, 108, 110, 111, 112, 113, 114, 115, 116, 117, 1645, 1646, 1648, 1676, 1677, 2211, 2212, 2297, 2298, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 109, 118, 1647, 2213, 2296, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 107, 108, 109, 110, 111, 112, 113, 114, 116, 118, 1645, 1646, 1648, 1677, 2212, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(104, 105, 106, 115, 117, 1647, 1676, 2211, 2213, 2296, 2297, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 104, 105, 106, 107, 109, 110, 112, 113, 114, 116, 117, 1645, 1646, 1676, 1677, 2212, 2296, 2297, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 108, 111, 115, 118, 1647, 1648, 2211, 2213, 2298, 2322)</t>
+    <t xml:space="preserve">c(79, 80, 81, 82, 124, 183, 184, 185, 186, 1747, 1748, 1890, 1891, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 123, 125, 1749, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1749, 1890, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(183, 184, 185, 186, 1748, 1891, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(82, 123, 124, 125, 184, 185, 186, 1748, 1749, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 122, 183, 1747, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1833, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1834, 1979, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 1979, 1980, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 2144, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 104, 107, 108, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 2211, 2212, 2213, 2297, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 105, 106, 109, 1648, 1676, 1677, 2296, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 108, 109, 113, 114, 117, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2296, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 107, 110, 111, 112, 115, 116, 118, 1645, 2297, 2298, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 104, 106, 107, 109, 110, 111, 115, 116, 117, 118, 1647, 1648, 1677, 2211, 2296, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 105, 108, 112, 113, 114, 1645, 1646, 1676, 2212, 2213, 2297)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 133, 135, 137, 1671, 1787, 1789, 1792, 1793, 1794, 1795, 1888, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 75, 76, 77, 134, 136, 1788, 1790, 2049, 2050)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 77, 135, 1671, 1788, 1789, 1790, 1794, 1795, 1888, 2049, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(76, 133, 134, 136, 137, 1787, 1792, 1793, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 61, 74, 76, 77, 133, 134, 135, 136, 1787, 1788, 1792, 1793, 1795, 1888, 2049, 2050, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 60, 75, 137, 1671, 1789, 1790, 1794, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 123, 124, 185, 186, 1748, 1749, 1890, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 122, 125, 183, 184, 1747, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 123, 124, 125, 185, 1747, 1748, 1749, 1891, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 183, 184, 186, 1890, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 123, 125, 183, 186, 1749, 1890, 1891, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 124, 184, 185, 1747, 1748, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1832, 1833, 1834, 2144, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1979, 1980, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1979, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1834, 1980, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1833, 1834, 1979, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1832, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 107, 109, 110, 111, 112, 114, 115, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2297, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 104, 105, 106, 108, 113, 116, 117, 2296, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 104, 110, 111, 113, 115, 116, 118, 1645, 1647, 1648, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 105, 106, 107, 108, 109, 112, 114, 117, 1646, 1676, 1677)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 105, 106, 107, 108, 110, 111, 113, 114, 115, 116, 118, 1645, 1646, 1647, 1676, 2212, 2213, 2296, 2297, 2298, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 103, 104, 109, 112, 117, 1648, 1677, 2211, 2321, 2322, 2323)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(58, 59, 60, 75, 77, 133, 134, 135, 1788, 1789, 1790, 1792, 1795, 1888, 2049, 2050, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 74, 76, 136, 137, 1787, 1793, 1794, 2051, 2053)</t>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 134, 135, 136, 137, 1788, 1888, 2049, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(77, 133, 1787, 1789, 1790, 1792, 1793, 1794, 1795, 2262)</t>
   </si>
   <si>
     <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 135, 137, 1787, 1789, 1792, 1794, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 134, 136, 1788, 1790, 1793, 1795, 1888, 2049, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 61, 75, 76, 77, 133, 136, 137, 1790, 1792, 1794, 1795, 1888, 2049, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 74, 134, 135, 1787, 1788, 1789, 1793, 2051, 2262)</t>
+    <t xml:space="preserve">c(58, 75, 76, 77, 133, 134, 135, 136, 137, 1788, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 61, 74, 1787, 1789, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 135, 137, 1789, 1792, 1793, 1794, 1795, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(133, 134, 136, 1787, 1788, 1790, 1888, 2049, 2051, 2262)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 79, 81, 123, 124, 125, 183, 185, 186, 1747, 1749, 1890, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 82, 122, 184, 1748, 1891, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 82, 122, 183, 184, 185, 186, 1747, 1890, 1891, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 123, 124, 125, 1748, 1749, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 82, 123, 124, 125, 183, 185, 186, 1748, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 122, 184, 1747, 1749, 1890, 1891, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1980, 2144, 2146, 2148)</t>
+    <t xml:space="preserve">c(79, 80, 123, 124, 125, 183, 186, 1747, 1748, 1890, 1891, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 82, 122, 184, 185, 1749, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 122, 124, 184, 185, 186, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 123, 125, 183, 1747, 1748, 1749)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 122, 123, 125, 183, 186, 1747, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 82, 124, 184, 185, 1748, 1749)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1979)</t>
   </si>
   <si>
     <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1980, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1979, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1980, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1979, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 104, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1676, 1677, 2297, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 105, 1648, 2211, 2212, 2213, 2296, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 105, 106, 107, 108, 111, 113, 114, 115, 116, 1645, 1647, 1677, 2211, 2212, 2213, 2296, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 103, 104, 109, 110, 112, 117, 118, 1646, 1648, 1676, 2297)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(104, 105, 106, 107, 109, 111, 113, 114, 116, 117, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2297, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 108, 110, 112, 115, 118, 1645, 2213, 2296)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 61, 74, 75, 76, 133, 134, 135, 136, 137, 1787, 1789, 1794, 2049, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 77, 1788, 1790, 1792, 1793, 1795, 1888, 2050, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 61, 74, 77, 133, 134, 135, 136, 1787, 1788, 1789, 1790, 1792, 2049, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 75, 76, 137, 1793, 1794, 1795, 1888, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 61, 74, 75, 76, 136, 1788, 1789, 1790, 1794, 1795, 1888, 2049, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 77, 133, 134, 135, 137, 1787, 1792, 1793, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 123, 124, 183, 185, 1747, 1749, 1890, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(82, 125, 184, 186, 1748, 1891, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 123, 124, 184, 186, 1747, 1748, 1749, 1890, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 82, 122, 125, 183, 185, 1891, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 82, 122, 124, 183, 184, 185, 186, 1748, 1749, 1890, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 123, 125, 1747, 1891, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2144:2147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1980, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1979, 2144, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1979, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 105, 106, 108, 110, 111, 113, 114, 117, 118, 1645, 1647, 1648, 1676, 1677, 2212, 2213, 2297, 2298, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 107, 109, 112, 115, 116, 1646, 2211, 2296, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 107, 109, 110, 111, 112, 114, 115, 116, 117, 118, 1645, 1648, 1676, 2212, 2213, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(106, 108, 113, 1646, 1647, 1677, 2211, 2296, 2297, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 105, 106, 108, 109, 111, 112, 113, 114, 116, 118, 1645, 1646, 1647, 2212, 2296, 2297, 2298, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 104, 107, 110, 115, 117, 1648, 1676, 1677, 2211, 2213, 2323)</t>
+    <t xml:space="preserve">c(1829, 1830, 1831, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1979, 1980, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1979, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1980, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 105, 107, 108, 109, 111, 112, 113, 115, 1646, 1647, 1648, 1676, 2211, 2212, 2213, 2296, 2298, 2299, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 106, 110, 114, 116, 117, 118, 1645, 1677, 2297, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 104, 106, 107, 108, 109, 112, 114, 116, 117, 118, 1645, 1646, 1677, 2213, 2296, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 105, 110, 111, 113, 115, 1647, 1648, 1676, 2211, 2212, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 106, 107, 108, 109, 111, 112, 113, 114, 116, 1647, 1676, 2211, 2296, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(105, 110, 115, 117, 118, 1645, 1646, 1648, 1677, 2212, 2213, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 61, 74, 76, 77, 133, 134, 135, 136, 137, 1787, 1790, 1792, 1794, 1795, 2049, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 75, 1788, 1789, 1793, 1888, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 74, 77, 133, 134, 135, 136, 137, 1787, 1788, 1790, 1792, 1793, 1795, 1888, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 75, 76, 1789, 1794, 2049, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 74, 75, 76, 77, 133, 134, 136, 1788, 1789, 1792, 1793, 1888, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 135, 137, 1787, 1790, 1794, 1795, 2049)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 122, 123, 124, 185, 186, 1747, 1748, 1749, 1891, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 125, 183, 184, 1890, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 122, 123, 124, 125, 184, 186, 1747, 1749, 1890, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 183, 185, 1748, 1891, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 122, 124, 125, 184, 186, 1748, 1749, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 123, 183, 185, 1747, 1890, 1891, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1980, 2144, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1979, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1979, 1980, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1980, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1979, 2144, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 104, 105, 106, 108, 110, 111, 112, 113, 114, 116, 117, 1646, 1647, 1648, 1677, 2211, 2212, 2213, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 107, 109, 115, 118, 1645, 1676, 2296, 2297, 2298, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 104, 105, 107, 108, 109, 111, 112, 113, 114, 116, 117, 118, 1645, 1646, 1647, 1648, 2296, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 106, 110, 115, 1676, 1677, 2211, 2212, 2213, 2297, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 109, 110, 111, 112, 113, 114, 115, 117, 1645, 1646, 1648, 1677, 2211, 2212, 2213, 2297, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(104, 105, 106, 107, 108, 116, 118, 1647, 1676, 2296, 2321, 2322)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 74, 76, 77, 1888, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 75, 1671, 2049, 2050, 2262)</t>
+    <t xml:space="preserve">c(58, 60, 61, 75, 77, 1671, 1888, 2049, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 74, 76, 2050, 2051)</t>
   </si>
   <si>
     <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 59, 61, 75, 76, 77, 1888, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 74, 1671, 2049, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 75, 76, 77, 1888, 2049, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 74, 1671, 2052, 2053, 2262)</t>
+    <t xml:space="preserve">c(74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 74, 76, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 75, 77, 1671, 1888, 2049)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 79, 122, 123, 124, 1747, 1748, 1749, 1891, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 82, 125, 1890, 2007)</t>
+    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 125, 1749, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 124, 1747, 1748, 1890, 1891)</t>
   </si>
   <si>
     <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(79, 81, 123, 124, 125, 1747, 1748, 1890, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 82, 122, 1749, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 82, 122, 123, 125, 1747, 1748, 1890, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 124, 1749, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1834, 1979, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 1980, 2144, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1832, 1834, 1979, 1980, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1833, 2144, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1832, 1833, 1979, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1834, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 118, 2212, 2213, 2296, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 1676, 1677, 2211, 2297, 2298)</t>
+    <t xml:space="preserve">c(78, 81, 122, 123, 124, 1747, 1749, 1890, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 125, 1748, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 122, 123, 125, 1747, 1749, 1890, 1891, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 82, 124, 1748, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 2144, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 1834, 1979, 1980, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833, 1834, 1980, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1979, 2144, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1834, 1980, 2144, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 1979, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 2211, 2212, 2296, 2297, 2298, 2299, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 118, 1676, 1677, 2213, 2323)</t>
   </si>
   <si>
     <t xml:space="preserve">c(115, 116, 117, 118, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(116, 118, 1676, 1677, 2211, 2296, 2297, 2298, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 2212, 2213, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 118, 1677, 2211, 2212, 2213, 2298, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 1676, 2296, 2297, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 74, 75, 76, 77, 1671, 2049, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 61, 1888, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 77, 1671, 1888, 2049, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 74, 75, 76, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 61, 74, 75, 76, 77, 1671, 2049, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 1888, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 82, 122, 123, 124, 125, 1748, 1749, 1891, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 1747, 1890, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 122, 125, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 82, 123, 124, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 124, 125, 1748, 1890, 1891, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 123, 1747, 1749, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1833, 1834, 1979, 1980, 2144, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1832, 1833, 1834, 1980, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1979, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1833, 1834, 1979, 1980, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1832, 2144, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 1677, 2211, 2212, 2296, 2298, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 118, 1676, 2213, 2297, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 118, 1676, 1677, 2211, 2212, 2213, 2297, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 2296, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 118, 1676, 1677, 2211, 2296, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 2212, 2213, 2297, 2322, 2323)</t>
+    <t xml:space="preserve">c(115, 116, 117, 118, 1677, 2212, 2296, 2298, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1676, 2211, 2213, 2297, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 1676, 2211, 2212, 2296, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 118, 1677, 2213, 2297, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 74, 75, 77, 1671, 2049, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 61, 76, 1888, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 61, 74, 75, 77, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 76, 1671, 1888, 2049, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 61, 77, 1671, 1888, 2049, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 74, 75, 76, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 82, 122, 124, 125, 1747, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 123, 1748, 1749, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 122, 123, 125, 1747, 1748, 1749, 1890, 1891, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 124, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 124, 125, 1747, 1748, 1890, 1891, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 123, 1749, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 1979, 2144, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1834, 1980, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1832, 1834, 1979, 1980, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1833, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1832, 1834, 1979, 1980, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1833, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 2211, 2213, 2297, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1677, 2212, 2296, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 1676, 2211, 2296, 2297, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(118, 1677, 2212, 2213, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 117, 1676, 1677, 2211, 2212, 2213, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 118, 2296, 2297, 2298, 2321)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 77, 1888, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(75, 76, 1671, 2049, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 74, 75, 76, 77, 1671, 2049, 2050, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 61, 1888, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 76, 77, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 75, 1671, 1888, 2049, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 124, 125, 1747, 1890, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 1748, 1749, 1891, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 1747, 1748, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(123, 124, 125, 1749, 1890, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 122, 123, 124, 1748, 1749, 1890, 1891, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 82, 125, 1747, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1834, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1833, 1979, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1832, 1833, 1979, 1980, 2144, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1834, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1834, 1980, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1833, 1979, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 1676, 2211, 2212, 2213, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 118, 1677, 2296, 2297, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 1677, 2212, 2213, 2296, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(118, 1676, 2211, 2297, 2298, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 118, 1677, 2211, 2297, 2298, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1676, 2212, 2213, 2296, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 61, 76, 1671, 1888, 2049, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 74, 75, 77, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 61, 74, 77, 1888, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 75, 76, 1671, 2049)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 74, 75, 77, 1671, 1888, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 76, 2049, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 125, 1747, 1748, 1890, 1891, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(82, 122, 123, 124, 1749, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 123, 125, 1748, 1749, 1891, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 122, 124, 1747, 1890, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 122, 123, 125, 1748, 1890, 1891, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 124, 1747, 1749, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1832, 1833, 1834, 1979, 1980, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1832, 1834, 1979, 1980, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1833, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1833, 1834, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1979, 1980, 2144, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 1676, 2212, 2297, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(118, 1677, 2211, 2213, 2296, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 1677, 2211, 2212, 2213, 2296, 2297, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 118, 1676, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 1677, 2211, 2213, 2297, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(118, 1676, 2212, 2296, 2298, 2299)</t>
+    <t xml:space="preserve">c(51, 59, 60, 61, 75, 76, 1671, 1888, 2050, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 74, 77, 2049, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 61, 74, 75, 76, 77, 2049, 2050, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 60, 1671, 1888, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 61, 77, 1671, 1888, 2049, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 60, 74, 75, 76, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 122, 124, 1747, 1748, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 123, 125, 1749, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 82, 123, 124, 1748, 1749, 1890, 1891, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 122, 125, 1747, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 123, 124, 1747, 1748, 1890, 1891, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 125, 1749, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833, 1979, 1980, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1834, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1832, 1834, 1980, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1833, 1979, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1980, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1834, 1979, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 118, 1677, 2211, 2212, 2213, 2296, 2297, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 1676, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 2213, 2296, 2298, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1677, 2211, 2212, 2297, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 1676, 1677, 2211, 2213, 2296, 2298, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 118, 2212, 2297, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 61, 74, 76, 77, 1671, 1888, 2049, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 75, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 60, 61, 74, 75, 77, 2049, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 76, 1671, 1888, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 75, 76, 77, 1671, 2049, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 74, 1888, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 123, 124, 1748, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 122, 125, 1747, 1749)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 82, 125, 1747, 1748, 1749, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 122, 123, 124, 1890, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 122, 123, 124, 1747, 1748, 1890, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 125, 1749, 1891, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1832, 1833, 1834, 1980, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1979, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1833, 1834, 1979, 1980, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1834, 2144, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1833, 1979, 1980, 2145)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 1676, 1677, 2212, 2213, 2298, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 118, 2211, 2296, 2297, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 118, 1676, 2213, 2296, 2297, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 1677, 2211, 2212, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 1677, 2211, 2213, 2296, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 118, 1676, 2212, 2297, 2298)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(59, 60, 61, 75, 76, 1888, 2049, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 74, 77, 2050, 2051)</t>
+    <t xml:space="preserve">c(60, 61, 75, 77, 1888, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 74, 76, 2049)</t>
   </si>
   <si>
     <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(59, 60, 61, 74, 75, 76, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 77, 1888, 2049, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 74, 75, 77, 1888, 2049, 2050, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 61, 76, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 123, 1748, 1890, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(122, 124, 125, 1747, 1749, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 82, 122, 123, 124, 125, 1748, 1749, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 1747, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 122, 123, 124, 125, 1749, 1890, 1891, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 82, 1747, 1748, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1979, 1980, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1979, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1980, 2144, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1979, 1980, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 2211, 2212, 2213, 2296, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 118, 1676, 1677, 2297)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 118, 1676, 2211, 2296, 2297, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 1677, 2212, 2213, 2298, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 118, 1677, 2212, 2213, 2296, 2298, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 1676, 2211, 2297, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 76, 2049, 2050, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(75, 77, 1888, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 61, 74, 75, 2049, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 76, 77, 1888, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 74, 75, 77, 1888, 2049, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 76, 2050, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 125, 1747, 1748, 1749, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(82, 122, 123, 124, 1890, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 124, 1747, 1748, 1749, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 125, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 122, 123, 125, 1747, 1890, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 124, 1748, 1749, 1891, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1979, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1979, 2144, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1980, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1980, 2144, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1979, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 1677, 2211, 2297, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(2212, 2213, 2296, 2298, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(118, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 2298, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 1677, 2211, 2212, 2213, 2296, 2298, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 118, 1676, 2297, 2323)</t>
+    <t xml:space="preserve">c(60, 61, 74, 75, 76, 77, 1888, 2049, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 74, 75, 76, 77, 1888, 2049, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 61, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 122, 1747, 1748, 1749, 1890, 1891, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 123, 124, 125, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 122, 125, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 123, 124, 1747, 1748, 1749)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 123, 125, 1747, 1748, 1749, 1891, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 124, 1890, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1980, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1979, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 2144, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1980, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2145:2148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 118, 1676, 1677, 2213, 2297, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 2211, 2212, 2296, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 1676, 2211, 2212, 2296, 2297, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 118, 1677, 2213, 2298, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 1677, 2211, 2213, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 118, 1676, 2212, 2296, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 75, 77, 1888, 2049, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 74, 76, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 75, 1888, 2049, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(61, 74, 76, 77, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 75, 76, 1888, 2049, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 74, 77, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 122, 124, 125, 1747, 1749, 1890, 1891, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 82, 123, 1748, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 123, 125, 1748, 1749, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 122, 124, 1747, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 82, 124, 1747, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 122, 123, 125, 1748)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1979, 1980, 2144, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1980, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1979, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1979, 1980, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 2144, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 1676, 1677, 2211, 2296, 2297, 2298, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 118, 2212, 2213, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 118, 1676, 2211, 2212, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(117, 1677, 2213, 2296, 2297, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 117, 1676, 1677, 2211, 2212, 2297, 2298, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(116, 118, 2213, 2296, 2299, 2322)</t>
   </si>
 </sst>
 </file>
@@ -7713,13 +7707,13 @@
         <v>3</v>
       </c>
       <c r="M106" t="s">
-        <v>249</v>
+        <v>42</v>
       </c>
       <c r="N106" t="n">
         <v>9</v>
       </c>
       <c r="O106" t="s">
-        <v>250</v>
+        <v>43</v>
       </c>
       <c r="P106" t="n">
         <v>5</v>
@@ -7769,13 +7763,13 @@
         <v>1</v>
       </c>
       <c r="M107" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="N107" t="n">
         <v>23</v>
       </c>
       <c r="O107" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P107" t="n">
         <v>12</v>
@@ -7825,13 +7819,13 @@
         <v>2</v>
       </c>
       <c r="M108" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="N108" t="n">
         <v>23</v>
       </c>
       <c r="O108" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P108" t="n">
         <v>12</v>
@@ -7881,13 +7875,13 @@
         <v>3</v>
       </c>
       <c r="M109" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="N109" t="n">
         <v>23</v>
       </c>
       <c r="O109" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="P109" t="n">
         <v>12</v>
@@ -7937,13 +7931,13 @@
         <v>1</v>
       </c>
       <c r="M110" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N110" t="n">
         <v>20</v>
       </c>
       <c r="O110" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P110" t="n">
         <v>10</v>
@@ -7993,13 +7987,13 @@
         <v>2</v>
       </c>
       <c r="M111" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="N111" t="n">
         <v>20</v>
       </c>
       <c r="O111" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P111" t="n">
         <v>10</v>
@@ -8049,13 +8043,13 @@
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="N112" t="n">
         <v>20</v>
       </c>
       <c r="O112" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P112" t="n">
         <v>10</v>
@@ -8105,13 +8099,13 @@
         <v>1</v>
       </c>
       <c r="M113" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N113" t="n">
         <v>14</v>
       </c>
       <c r="O113" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P113" t="n">
         <v>8</v>
@@ -8161,13 +8155,13 @@
         <v>2</v>
       </c>
       <c r="M114" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N114" t="n">
         <v>14</v>
       </c>
       <c r="O114" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P114" t="n">
         <v>8</v>
@@ -8217,13 +8211,13 @@
         <v>3</v>
       </c>
       <c r="M115" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="N115" t="n">
         <v>14</v>
       </c>
       <c r="O115" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P115" t="n">
         <v>8</v>
@@ -8273,13 +8267,13 @@
         <v>1</v>
       </c>
       <c r="M116" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N116" t="n">
         <v>9</v>
       </c>
       <c r="O116" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P116" t="n">
         <v>5</v>
@@ -8329,13 +8323,13 @@
         <v>2</v>
       </c>
       <c r="M117" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N117" t="n">
         <v>9</v>
       </c>
       <c r="O117" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P117" t="n">
         <v>5</v>
@@ -8385,13 +8379,13 @@
         <v>3</v>
       </c>
       <c r="M118" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="N118" t="n">
         <v>9</v>
       </c>
       <c r="O118" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="P118" t="n">
         <v>5</v>
@@ -8441,13 +8435,13 @@
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N119" t="n">
         <v>23</v>
       </c>
       <c r="O119" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P119" t="n">
         <v>12</v>
@@ -8497,13 +8491,13 @@
         <v>2</v>
       </c>
       <c r="M120" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N120" t="n">
         <v>23</v>
       </c>
       <c r="O120" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P120" t="n">
         <v>12</v>
@@ -8553,13 +8547,13 @@
         <v>3</v>
       </c>
       <c r="M121" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="N121" t="n">
         <v>23</v>
       </c>
       <c r="O121" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P121" t="n">
         <v>12</v>
@@ -8603,28 +8597,28 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
+        <v>279</v>
+      </c>
+      <c r="L122" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" t="s">
+        <v>280</v>
+      </c>
+      <c r="N122" t="n">
+        <v>18</v>
+      </c>
+      <c r="O122" t="s">
         <v>281</v>
-      </c>
-      <c r="L122" t="n">
-        <v>1</v>
-      </c>
-      <c r="M122" t="s">
-        <v>282</v>
-      </c>
-      <c r="N122" t="n">
-        <v>18</v>
-      </c>
-      <c r="O122" t="s">
-        <v>283</v>
       </c>
       <c r="P122" t="n">
         <v>10</v>
       </c>
       <c r="Q122" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="R122" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="123">
@@ -8659,28 +8653,28 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N123" t="n">
         <v>18</v>
       </c>
       <c r="O123" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="P123" t="n">
         <v>10</v>
       </c>
       <c r="Q123" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="R123" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="124">
@@ -8715,28 +8709,28 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="N124" t="n">
         <v>18</v>
       </c>
       <c r="O124" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P124" t="n">
         <v>10</v>
       </c>
       <c r="Q124" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="R124" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="125">
@@ -8771,19 +8765,19 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="N125" t="n">
         <v>14</v>
       </c>
       <c r="O125" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="P125" t="n">
         <v>8</v>
@@ -8827,19 +8821,19 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
       </c>
       <c r="M126" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="N126" t="n">
         <v>14</v>
       </c>
       <c r="O126" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P126" t="n">
         <v>8</v>
@@ -8883,19 +8877,19 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
       </c>
       <c r="M127" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N127" t="n">
         <v>14</v>
       </c>
       <c r="O127" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P127" t="n">
         <v>8</v>
@@ -8939,28 +8933,28 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="N128" t="n">
         <v>7</v>
       </c>
       <c r="O128" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P128" t="n">
         <v>4</v>
       </c>
       <c r="Q128" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R128" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="129">
@@ -8995,28 +8989,28 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="N129" t="n">
         <v>7</v>
       </c>
       <c r="O129" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="P129" t="n">
         <v>4</v>
       </c>
       <c r="Q129" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R129" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="130">
@@ -9051,28 +9045,28 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="N130" t="n">
         <v>7</v>
       </c>
       <c r="O130" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P130" t="n">
         <v>4</v>
       </c>
       <c r="Q130" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R130" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="131">
@@ -9107,19 +9101,19 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="N131" t="n">
         <v>23</v>
       </c>
       <c r="O131" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P131" t="n">
         <v>12</v>
@@ -9163,19 +9157,19 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N132" t="n">
         <v>23</v>
       </c>
       <c r="O132" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="P132" t="n">
         <v>12</v>
@@ -9219,19 +9213,19 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="N133" t="n">
         <v>23</v>
       </c>
       <c r="O133" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P133" t="n">
         <v>12</v>
@@ -9275,28 +9269,28 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="N134" t="n">
         <v>18</v>
       </c>
       <c r="O134" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="P134" t="n">
         <v>10</v>
       </c>
       <c r="Q134" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="R134" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="135">
@@ -9331,28 +9325,28 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="N135" t="n">
         <v>18</v>
       </c>
       <c r="O135" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="P135" t="n">
         <v>10</v>
       </c>
       <c r="Q135" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="R135" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="136">
@@ -9387,28 +9381,28 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="N136" t="n">
         <v>18</v>
       </c>
       <c r="O136" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="P136" t="n">
         <v>10</v>
       </c>
       <c r="Q136" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="R136" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="137">
@@ -9443,19 +9437,19 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N137" t="n">
         <v>14</v>
       </c>
       <c r="O137" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="P137" t="n">
         <v>8</v>
@@ -9499,19 +9493,19 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="N138" t="n">
         <v>14</v>
       </c>
       <c r="O138" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="P138" t="n">
         <v>8</v>
@@ -9555,19 +9549,19 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="N139" t="n">
         <v>14</v>
       </c>
       <c r="O139" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="P139" t="n">
         <v>8</v>
@@ -9611,28 +9605,28 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="N140" t="n">
         <v>7</v>
       </c>
       <c r="O140" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P140" t="n">
         <v>4</v>
       </c>
       <c r="Q140" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R140" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="141">
@@ -9667,28 +9661,28 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N141" t="n">
         <v>7</v>
       </c>
       <c r="O141" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="P141" t="n">
         <v>4</v>
       </c>
       <c r="Q141" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R141" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="142">
@@ -9723,28 +9717,28 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="N142" t="n">
         <v>7</v>
       </c>
       <c r="O142" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="P142" t="n">
         <v>4</v>
       </c>
       <c r="Q142" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R142" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="143">
@@ -9779,19 +9773,19 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N143" t="n">
         <v>23</v>
       </c>
       <c r="O143" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="P143" t="n">
         <v>12</v>
@@ -9835,19 +9829,19 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N144" t="n">
         <v>23</v>
       </c>
       <c r="O144" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="P144" t="n">
         <v>12</v>
@@ -9891,19 +9885,19 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="N145" t="n">
         <v>23</v>
       </c>
       <c r="O145" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="P145" t="n">
         <v>12</v>
@@ -9947,28 +9941,28 @@
         <v>3</v>
       </c>
       <c r="K146" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L146" t="n">
         <v>1</v>
       </c>
       <c r="M146" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="N146" t="n">
         <v>11</v>
       </c>
       <c r="O146" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P146" t="n">
         <v>6</v>
       </c>
       <c r="Q146" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="R146" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="147">
@@ -10003,28 +9997,28 @@
         <v>3</v>
       </c>
       <c r="K147" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L147" t="n">
         <v>2</v>
       </c>
       <c r="M147" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="N147" t="n">
         <v>11</v>
       </c>
       <c r="O147" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="P147" t="n">
         <v>6</v>
       </c>
       <c r="Q147" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="R147" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="148">
@@ -10059,28 +10053,28 @@
         <v>3</v>
       </c>
       <c r="K148" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L148" t="n">
         <v>3</v>
       </c>
       <c r="M148" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="N148" t="n">
         <v>11</v>
       </c>
       <c r="O148" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="P148" t="n">
         <v>6</v>
       </c>
       <c r="Q148" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="R148" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="149">
@@ -10115,28 +10109,28 @@
         <v>3</v>
       </c>
       <c r="K149" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L149" t="n">
         <v>1</v>
       </c>
       <c r="M149" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="N149" t="n">
         <v>12</v>
       </c>
       <c r="O149" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="P149" t="n">
         <v>6</v>
       </c>
       <c r="Q149" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R149" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="150">
@@ -10171,28 +10165,28 @@
         <v>3</v>
       </c>
       <c r="K150" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L150" t="n">
         <v>2</v>
       </c>
       <c r="M150" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="N150" t="n">
         <v>12</v>
       </c>
       <c r="O150" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="P150" t="n">
         <v>6</v>
       </c>
       <c r="Q150" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R150" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="151">
@@ -10227,28 +10221,28 @@
         <v>3</v>
       </c>
       <c r="K151" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L151" t="n">
         <v>3</v>
       </c>
       <c r="M151" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="N151" t="n">
         <v>12</v>
       </c>
       <c r="O151" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="P151" t="n">
         <v>6</v>
       </c>
       <c r="Q151" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R151" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="152">
@@ -10283,19 +10277,19 @@
         <v>3</v>
       </c>
       <c r="K152" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L152" t="n">
         <v>1</v>
       </c>
       <c r="M152" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="N152" t="n">
         <v>9</v>
       </c>
       <c r="O152" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P152" t="n">
         <v>5</v>
@@ -10339,19 +10333,19 @@
         <v>3</v>
       </c>
       <c r="K153" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L153" t="n">
         <v>2</v>
       </c>
       <c r="M153" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="N153" t="n">
         <v>9</v>
       </c>
       <c r="O153" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="P153" t="n">
         <v>5</v>
@@ -10395,19 +10389,19 @@
         <v>3</v>
       </c>
       <c r="K154" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L154" t="n">
         <v>3</v>
       </c>
       <c r="M154" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="N154" t="n">
         <v>9</v>
       </c>
       <c r="O154" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P154" t="n">
         <v>5</v>
@@ -10451,28 +10445,28 @@
         <v>3</v>
       </c>
       <c r="K155" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L155" t="n">
         <v>1</v>
       </c>
       <c r="M155" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="N155" t="n">
         <v>10</v>
       </c>
       <c r="O155" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="P155" t="n">
         <v>6</v>
       </c>
       <c r="Q155" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R155" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="156">
@@ -10507,28 +10501,28 @@
         <v>3</v>
       </c>
       <c r="K156" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L156" t="n">
         <v>2</v>
       </c>
       <c r="M156" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N156" t="n">
         <v>10</v>
       </c>
       <c r="O156" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="P156" t="n">
         <v>6</v>
       </c>
       <c r="Q156" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R156" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="157">
@@ -10563,28 +10557,28 @@
         <v>3</v>
       </c>
       <c r="K157" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L157" t="n">
         <v>3</v>
       </c>
       <c r="M157" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="N157" t="n">
         <v>10</v>
       </c>
       <c r="O157" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="P157" t="n">
         <v>6</v>
       </c>
       <c r="Q157" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R157" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="158">
@@ -10619,28 +10613,28 @@
         <v>3</v>
       </c>
       <c r="K158" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="N158" t="n">
         <v>11</v>
       </c>
       <c r="O158" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="P158" t="n">
         <v>6</v>
       </c>
       <c r="Q158" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="R158" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="159">
@@ -10675,28 +10669,28 @@
         <v>3</v>
       </c>
       <c r="K159" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L159" t="n">
         <v>2</v>
       </c>
       <c r="M159" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="N159" t="n">
         <v>11</v>
       </c>
       <c r="O159" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="P159" t="n">
         <v>6</v>
       </c>
       <c r="Q159" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="R159" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="160">
@@ -10731,28 +10725,28 @@
         <v>3</v>
       </c>
       <c r="K160" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
       </c>
       <c r="M160" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N160" t="n">
         <v>11</v>
       </c>
       <c r="O160" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="P160" t="n">
         <v>6</v>
       </c>
       <c r="Q160" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="R160" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="161">
@@ -10787,28 +10781,28 @@
         <v>3</v>
       </c>
       <c r="K161" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L161" t="n">
         <v>1</v>
       </c>
       <c r="M161" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="N161" t="n">
         <v>12</v>
       </c>
       <c r="O161" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="P161" t="n">
         <v>6</v>
       </c>
       <c r="Q161" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R161" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="162">
@@ -10843,28 +10837,28 @@
         <v>3</v>
       </c>
       <c r="K162" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L162" t="n">
         <v>2</v>
       </c>
       <c r="M162" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="N162" t="n">
         <v>12</v>
       </c>
       <c r="O162" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="P162" t="n">
         <v>6</v>
       </c>
       <c r="Q162" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R162" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="163">
@@ -10899,28 +10893,28 @@
         <v>3</v>
       </c>
       <c r="K163" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
       </c>
       <c r="M163" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="N163" t="n">
         <v>12</v>
       </c>
       <c r="O163" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P163" t="n">
         <v>6</v>
       </c>
       <c r="Q163" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R163" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="164">
@@ -10955,19 +10949,19 @@
         <v>3</v>
       </c>
       <c r="K164" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L164" t="n">
         <v>1</v>
       </c>
       <c r="M164" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="N164" t="n">
         <v>9</v>
       </c>
       <c r="O164" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="P164" t="n">
         <v>5</v>
@@ -11011,19 +11005,19 @@
         <v>3</v>
       </c>
       <c r="K165" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L165" t="n">
         <v>2</v>
       </c>
       <c r="M165" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="N165" t="n">
         <v>9</v>
       </c>
       <c r="O165" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="P165" t="n">
         <v>5</v>
@@ -11067,19 +11061,19 @@
         <v>3</v>
       </c>
       <c r="K166" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
       </c>
       <c r="M166" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="N166" t="n">
         <v>9</v>
       </c>
       <c r="O166" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="P166" t="n">
         <v>5</v>
@@ -11123,28 +11117,28 @@
         <v>3</v>
       </c>
       <c r="K167" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L167" t="n">
         <v>1</v>
       </c>
       <c r="M167" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="N167" t="n">
         <v>10</v>
       </c>
       <c r="O167" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P167" t="n">
         <v>6</v>
       </c>
       <c r="Q167" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R167" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="168">
@@ -11179,28 +11173,28 @@
         <v>3</v>
       </c>
       <c r="K168" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L168" t="n">
         <v>2</v>
       </c>
       <c r="M168" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="N168" t="n">
         <v>10</v>
       </c>
       <c r="O168" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="P168" t="n">
         <v>6</v>
       </c>
       <c r="Q168" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R168" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="169">
@@ -11235,28 +11229,28 @@
         <v>3</v>
       </c>
       <c r="K169" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
       </c>
       <c r="M169" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="N169" t="n">
         <v>10</v>
       </c>
       <c r="O169" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="P169" t="n">
         <v>6</v>
       </c>
       <c r="Q169" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R169" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="170">
@@ -11291,28 +11285,28 @@
         <v>3</v>
       </c>
       <c r="K170" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L170" t="n">
         <v>1</v>
       </c>
       <c r="M170" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="N170" t="n">
         <v>11</v>
       </c>
       <c r="O170" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P170" t="n">
         <v>6</v>
       </c>
       <c r="Q170" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="R170" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="171">
@@ -11347,28 +11341,28 @@
         <v>3</v>
       </c>
       <c r="K171" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L171" t="n">
         <v>2</v>
       </c>
       <c r="M171" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="N171" t="n">
         <v>11</v>
       </c>
       <c r="O171" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P171" t="n">
         <v>6</v>
       </c>
       <c r="Q171" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="R171" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="172">
@@ -11403,28 +11397,28 @@
         <v>3</v>
       </c>
       <c r="K172" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
       </c>
       <c r="M172" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="N172" t="n">
         <v>11</v>
       </c>
       <c r="O172" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P172" t="n">
         <v>6</v>
       </c>
       <c r="Q172" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="R172" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="173">
@@ -11459,28 +11453,28 @@
         <v>3</v>
       </c>
       <c r="K173" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L173" t="n">
         <v>1</v>
       </c>
       <c r="M173" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="N173" t="n">
         <v>12</v>
       </c>
       <c r="O173" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P173" t="n">
         <v>6</v>
       </c>
       <c r="Q173" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R173" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="174">
@@ -11515,28 +11509,28 @@
         <v>3</v>
       </c>
       <c r="K174" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L174" t="n">
         <v>2</v>
       </c>
       <c r="M174" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="N174" t="n">
         <v>12</v>
       </c>
       <c r="O174" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="P174" t="n">
         <v>6</v>
       </c>
       <c r="Q174" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R174" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="175">
@@ -11571,28 +11565,28 @@
         <v>3</v>
       </c>
       <c r="K175" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L175" t="n">
         <v>3</v>
       </c>
       <c r="M175" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="N175" t="n">
         <v>12</v>
       </c>
       <c r="O175" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P175" t="n">
         <v>6</v>
       </c>
       <c r="Q175" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R175" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="176">
@@ -11627,19 +11621,19 @@
         <v>3</v>
       </c>
       <c r="K176" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L176" t="n">
         <v>1</v>
       </c>
       <c r="M176" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N176" t="n">
         <v>9</v>
       </c>
       <c r="O176" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P176" t="n">
         <v>5</v>
@@ -11683,19 +11677,19 @@
         <v>3</v>
       </c>
       <c r="K177" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L177" t="n">
         <v>2</v>
       </c>
       <c r="M177" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="N177" t="n">
         <v>9</v>
       </c>
       <c r="O177" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P177" t="n">
         <v>5</v>
@@ -11739,19 +11733,19 @@
         <v>3</v>
       </c>
       <c r="K178" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L178" t="n">
         <v>3</v>
       </c>
       <c r="M178" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N178" t="n">
         <v>9</v>
       </c>
       <c r="O178" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="P178" t="n">
         <v>5</v>
@@ -11795,28 +11789,28 @@
         <v>3</v>
       </c>
       <c r="K179" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L179" t="n">
         <v>1</v>
       </c>
       <c r="M179" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="N179" t="n">
         <v>10</v>
       </c>
       <c r="O179" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="P179" t="n">
         <v>6</v>
       </c>
       <c r="Q179" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R179" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="180">
@@ -11851,28 +11845,28 @@
         <v>3</v>
       </c>
       <c r="K180" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L180" t="n">
         <v>2</v>
       </c>
       <c r="M180" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="N180" t="n">
         <v>10</v>
       </c>
       <c r="O180" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="P180" t="n">
         <v>6</v>
       </c>
       <c r="Q180" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R180" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="181">
@@ -11907,28 +11901,28 @@
         <v>3</v>
       </c>
       <c r="K181" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L181" t="n">
         <v>3</v>
       </c>
       <c r="M181" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N181" t="n">
         <v>10</v>
       </c>
       <c r="O181" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P181" t="n">
         <v>6</v>
       </c>
       <c r="Q181" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R181" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="182">
@@ -11963,28 +11957,28 @@
         <v>3</v>
       </c>
       <c r="K182" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L182" t="n">
         <v>1</v>
       </c>
       <c r="M182" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N182" t="n">
         <v>11</v>
       </c>
       <c r="O182" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="P182" t="n">
         <v>6</v>
       </c>
       <c r="Q182" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="R182" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="183">
@@ -12019,28 +12013,28 @@
         <v>3</v>
       </c>
       <c r="K183" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L183" t="n">
         <v>2</v>
       </c>
       <c r="M183" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="N183" t="n">
         <v>11</v>
       </c>
       <c r="O183" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P183" t="n">
         <v>6</v>
       </c>
       <c r="Q183" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="R183" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="184">
@@ -12075,28 +12069,28 @@
         <v>3</v>
       </c>
       <c r="K184" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L184" t="n">
         <v>3</v>
       </c>
       <c r="M184" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="N184" t="n">
         <v>11</v>
       </c>
       <c r="O184" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="P184" t="n">
         <v>6</v>
       </c>
       <c r="Q184" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="R184" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="185">
@@ -12131,28 +12125,28 @@
         <v>3</v>
       </c>
       <c r="K185" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L185" t="n">
         <v>1</v>
       </c>
       <c r="M185" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N185" t="n">
         <v>12</v>
       </c>
       <c r="O185" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="P185" t="n">
         <v>6</v>
       </c>
       <c r="Q185" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R185" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="186">
@@ -12187,28 +12181,28 @@
         <v>3</v>
       </c>
       <c r="K186" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L186" t="n">
         <v>2</v>
       </c>
       <c r="M186" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="N186" t="n">
         <v>12</v>
       </c>
       <c r="O186" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P186" t="n">
         <v>6</v>
       </c>
       <c r="Q186" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R186" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="187">
@@ -12243,28 +12237,28 @@
         <v>3</v>
       </c>
       <c r="K187" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L187" t="n">
         <v>3</v>
       </c>
       <c r="M187" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N187" t="n">
         <v>12</v>
       </c>
       <c r="O187" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="P187" t="n">
         <v>6</v>
       </c>
       <c r="Q187" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R187" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="188">
@@ -12299,19 +12293,19 @@
         <v>3</v>
       </c>
       <c r="K188" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L188" t="n">
         <v>1</v>
       </c>
       <c r="M188" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="N188" t="n">
         <v>9</v>
       </c>
       <c r="O188" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P188" t="n">
         <v>5</v>
@@ -12355,19 +12349,19 @@
         <v>3</v>
       </c>
       <c r="K189" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L189" t="n">
         <v>2</v>
       </c>
       <c r="M189" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="N189" t="n">
         <v>9</v>
       </c>
       <c r="O189" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="P189" t="n">
         <v>5</v>
@@ -12411,19 +12405,19 @@
         <v>3</v>
       </c>
       <c r="K190" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L190" t="n">
         <v>3</v>
       </c>
       <c r="M190" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N190" t="n">
         <v>9</v>
       </c>
       <c r="O190" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="P190" t="n">
         <v>5</v>
@@ -12467,28 +12461,28 @@
         <v>3</v>
       </c>
       <c r="K191" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L191" t="n">
         <v>1</v>
       </c>
       <c r="M191" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="N191" t="n">
         <v>10</v>
       </c>
       <c r="O191" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P191" t="n">
         <v>6</v>
       </c>
       <c r="Q191" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R191" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="192">
@@ -12523,28 +12517,28 @@
         <v>3</v>
       </c>
       <c r="K192" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L192" t="n">
         <v>2</v>
       </c>
       <c r="M192" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="N192" t="n">
         <v>10</v>
       </c>
       <c r="O192" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="P192" t="n">
         <v>6</v>
       </c>
       <c r="Q192" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R192" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="193">
@@ -12579,28 +12573,28 @@
         <v>3</v>
       </c>
       <c r="K193" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L193" t="n">
         <v>3</v>
       </c>
       <c r="M193" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="N193" t="n">
         <v>10</v>
       </c>
       <c r="O193" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="P193" t="n">
         <v>6</v>
       </c>
       <c r="Q193" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R193" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="194">
@@ -12635,28 +12629,28 @@
         <v>3</v>
       </c>
       <c r="K194" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L194" t="n">
         <v>1</v>
       </c>
       <c r="M194" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="N194" t="n">
         <v>10</v>
       </c>
       <c r="O194" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="P194" t="n">
         <v>5</v>
       </c>
       <c r="Q194" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="R194" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195">
@@ -12691,28 +12685,28 @@
         <v>3</v>
       </c>
       <c r="K195" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L195" t="n">
         <v>2</v>
       </c>
       <c r="M195" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="N195" t="n">
         <v>10</v>
       </c>
       <c r="O195" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="P195" t="n">
         <v>5</v>
       </c>
       <c r="Q195" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="R195" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="196">
@@ -12747,28 +12741,28 @@
         <v>3</v>
       </c>
       <c r="K196" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L196" t="n">
         <v>3</v>
       </c>
       <c r="M196" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="N196" t="n">
         <v>10</v>
       </c>
       <c r="O196" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="P196" t="n">
         <v>5</v>
       </c>
       <c r="Q196" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="R196" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="197">
@@ -12803,28 +12797,28 @@
         <v>3</v>
       </c>
       <c r="K197" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L197" t="n">
         <v>1</v>
       </c>
       <c r="M197" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="N197" t="n">
         <v>12</v>
       </c>
       <c r="O197" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="P197" t="n">
         <v>6</v>
       </c>
       <c r="Q197" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R197" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="198">
@@ -12859,28 +12853,28 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L198" t="n">
         <v>2</v>
       </c>
       <c r="M198" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="N198" t="n">
         <v>12</v>
       </c>
       <c r="O198" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P198" t="n">
         <v>6</v>
       </c>
       <c r="Q198" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R198" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="199">
@@ -12915,28 +12909,28 @@
         <v>3</v>
       </c>
       <c r="K199" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L199" t="n">
         <v>3</v>
       </c>
       <c r="M199" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="N199" t="n">
         <v>12</v>
       </c>
       <c r="O199" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P199" t="n">
         <v>6</v>
       </c>
       <c r="Q199" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R199" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="200">
@@ -12971,28 +12965,28 @@
         <v>3</v>
       </c>
       <c r="K200" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L200" t="n">
         <v>1</v>
       </c>
       <c r="M200" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N200" t="n">
         <v>7</v>
       </c>
       <c r="O200" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P200" t="n">
         <v>4</v>
       </c>
       <c r="Q200" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R200" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="201">
@@ -13027,28 +13021,28 @@
         <v>3</v>
       </c>
       <c r="K201" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L201" t="n">
         <v>2</v>
       </c>
       <c r="M201" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="N201" t="n">
         <v>7</v>
       </c>
       <c r="O201" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P201" t="n">
         <v>4</v>
       </c>
       <c r="Q201" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R201" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="202">
@@ -13083,28 +13077,28 @@
         <v>3</v>
       </c>
       <c r="K202" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L202" t="n">
         <v>3</v>
       </c>
       <c r="M202" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="N202" t="n">
         <v>7</v>
       </c>
       <c r="O202" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="P202" t="n">
         <v>4</v>
       </c>
       <c r="Q202" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R202" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="203">
@@ -13139,28 +13133,28 @@
         <v>3</v>
       </c>
       <c r="K203" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L203" t="n">
         <v>1</v>
       </c>
       <c r="M203" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="N203" t="n">
         <v>10</v>
       </c>
       <c r="O203" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P203" t="n">
         <v>6</v>
       </c>
       <c r="Q203" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R203" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="204">
@@ -13195,28 +13189,28 @@
         <v>3</v>
       </c>
       <c r="K204" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L204" t="n">
         <v>2</v>
       </c>
       <c r="M204" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="N204" t="n">
         <v>10</v>
       </c>
       <c r="O204" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="P204" t="n">
         <v>6</v>
       </c>
       <c r="Q204" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R204" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="205">
@@ -13251,28 +13245,28 @@
         <v>3</v>
       </c>
       <c r="K205" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L205" t="n">
         <v>3</v>
       </c>
       <c r="M205" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="N205" t="n">
         <v>10</v>
       </c>
       <c r="O205" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="P205" t="n">
         <v>6</v>
       </c>
       <c r="Q205" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R205" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="206">
@@ -13307,28 +13301,28 @@
         <v>3</v>
       </c>
       <c r="K206" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N206" t="n">
         <v>10</v>
       </c>
       <c r="O206" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P206" t="n">
         <v>5</v>
       </c>
       <c r="Q206" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="R206" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="207">
@@ -13363,28 +13357,28 @@
         <v>3</v>
       </c>
       <c r="K207" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L207" t="n">
         <v>2</v>
       </c>
       <c r="M207" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N207" t="n">
         <v>10</v>
       </c>
       <c r="O207" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P207" t="n">
         <v>5</v>
       </c>
       <c r="Q207" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="R207" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="208">
@@ -13419,28 +13413,28 @@
         <v>3</v>
       </c>
       <c r="K208" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L208" t="n">
         <v>3</v>
       </c>
       <c r="M208" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N208" t="n">
         <v>10</v>
       </c>
       <c r="O208" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="P208" t="n">
         <v>5</v>
       </c>
       <c r="Q208" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="R208" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="209">
@@ -13475,28 +13469,28 @@
         <v>3</v>
       </c>
       <c r="K209" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L209" t="n">
         <v>1</v>
       </c>
       <c r="M209" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N209" t="n">
         <v>12</v>
       </c>
       <c r="O209" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="P209" t="n">
         <v>6</v>
       </c>
       <c r="Q209" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R209" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="210">
@@ -13531,28 +13525,28 @@
         <v>3</v>
       </c>
       <c r="K210" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L210" t="n">
         <v>2</v>
       </c>
       <c r="M210" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="N210" t="n">
         <v>12</v>
       </c>
       <c r="O210" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="P210" t="n">
         <v>6</v>
       </c>
       <c r="Q210" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R210" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="211">
@@ -13587,28 +13581,28 @@
         <v>3</v>
       </c>
       <c r="K211" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L211" t="n">
         <v>3</v>
       </c>
       <c r="M211" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="N211" t="n">
         <v>12</v>
       </c>
       <c r="O211" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="P211" t="n">
         <v>6</v>
       </c>
       <c r="Q211" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="R211" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="212">
@@ -13643,28 +13637,28 @@
         <v>3</v>
       </c>
       <c r="K212" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L212" t="n">
         <v>1</v>
       </c>
       <c r="M212" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="N212" t="n">
         <v>7</v>
       </c>
       <c r="O212" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="P212" t="n">
         <v>4</v>
       </c>
       <c r="Q212" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R212" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="213">
@@ -13699,28 +13693,28 @@
         <v>3</v>
       </c>
       <c r="K213" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L213" t="n">
         <v>2</v>
       </c>
       <c r="M213" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="N213" t="n">
         <v>7</v>
       </c>
       <c r="O213" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="P213" t="n">
         <v>4</v>
       </c>
       <c r="Q213" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R213" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="214">
@@ -13755,28 +13749,28 @@
         <v>3</v>
       </c>
       <c r="K214" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L214" t="n">
         <v>3</v>
       </c>
       <c r="M214" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N214" t="n">
         <v>7</v>
       </c>
       <c r="O214" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P214" t="n">
         <v>4</v>
       </c>
       <c r="Q214" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R214" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="215">
@@ -13811,28 +13805,28 @@
         <v>3</v>
       </c>
       <c r="K215" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L215" t="n">
         <v>1</v>
       </c>
       <c r="M215" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="N215" t="n">
         <v>10</v>
       </c>
       <c r="O215" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="P215" t="n">
         <v>6</v>
       </c>
       <c r="Q215" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R215" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="216">
@@ -13867,28 +13861,28 @@
         <v>3</v>
       </c>
       <c r="K216" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L216" t="n">
         <v>2</v>
       </c>
       <c r="M216" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="N216" t="n">
         <v>10</v>
       </c>
       <c r="O216" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="P216" t="n">
         <v>6</v>
       </c>
       <c r="Q216" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R216" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="217">
@@ -13923,28 +13917,28 @@
         <v>3</v>
       </c>
       <c r="K217" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L217" t="n">
         <v>3</v>
       </c>
       <c r="M217" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="N217" t="n">
         <v>10</v>
       </c>
       <c r="O217" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="P217" t="n">
         <v>6</v>
       </c>
       <c r="Q217" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R217" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_lon_fold_sets.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_lon_fold_sets.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -77,1390 +77,940 @@
     <t xml:space="preserve">1.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 74, 75, 76, 133, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1793, 1794, 1888, 2049, 2050, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 77, 134, 1792, 1795, 2052, 2262)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 76, 77, 133, 134, 135, 1671, 1787, 1788, 1789, 1790, 1793, 1794, 2049, 2050, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 74, 75, 136, 137, 1792, 1795, 1888, 2052, 2053)</t>
   </si>
   <si>
     <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 61, 75, 76, 77, 133, 134, 135, 137, 1671, 1788, 1790, 1792, 1794, 1795, 1888, 2050, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 74, 136, 1787, 1789, 1793, 2049, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 75, 76, 77, 133, 134, 136, 137, 1787, 1788, 1789, 1790, 1792, 1795, 2049, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 61, 74, 135, 1671, 1793, 1794, 1888, 2050, 2053)</t>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 76, 77, 133, 134, 135, 136, 137, 1787, 1792, 1793, 1794, 1888, 2049, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 75, 1671, 1788, 1789, 1790, 1795, 2050, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 74, 75, 77, 134, 135, 136, 137, 1790, 1792, 1793, 1794, 1795, 1888, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 61, 76, 133, 1671, 1787, 1788, 1789, 2049, 2051)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 124, 125, 183, 184, 185, 186, 1747, 1748, 1890, 1891, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 122, 123, 1749, 1892, 2006, 2007)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 82, 122, 124, 125, 184, 186, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 123, 183, 185, 1747, 1748, 1749, 1890)</t>
   </si>
   <si>
     <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 183, 184, 185, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(79, 80, 81, 122, 123, 124, 183, 184, 186, 1749, 1891, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 82, 125, 185, 1747, 1748, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 82, 122, 124, 125, 183, 184, 185, 1748, 1749, 1890, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 123, 186, 1747, 1891, 1892, 2007)</t>
+    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 125, 183, 186, 1747, 1748, 1749, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 124, 184, 185, 1890, 1891, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 122, 123, 124, 183, 184, 185, 186, 1748, 1890, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 125, 1747, 1749, 1891, 1892, 2006)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1833, 1834, 2146, 2147)</t>
+    <t xml:space="preserve">c(1829, 1834, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833)</t>
   </si>
   <si>
     <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1834, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1829, 1832, 1833, 1979, 1980, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1834, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1833, 1980, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1834, 1979, 2145, 2147)</t>
+    <t xml:space="preserve">c(1828, 1832, 1833, 1979, 1980, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1834, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 1834, 1979, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1980, 2144, 2147, 2148)</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 105, 107, 109, 110, 112, 113, 115, 116, 118, 1645, 1646, 1647, 1676, 2211, 2213, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 106, 108, 111, 114, 117, 1648, 1677, 2212, 2296, 2297, 2322)</t>
+    <t xml:space="preserve">c(100, 102, 103, 109, 111, 112, 113, 115, 116, 117, 118, 1645, 1647, 1648, 1676, 2211, 2212, 2213, 2297, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 104, 105, 106, 107, 108, 110, 114, 1646, 1677, 2296, 2299)</t>
   </si>
   <si>
     <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 106, 109, 112, 113, 115, 116, 117, 118, 1648, 1677, 2211, 2213, 2296, 2297, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(105, 107, 108, 110, 111, 114, 1645, 1646, 1647, 1676, 2212, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 107, 109, 113, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 2211, 2212, 2213, 2296, 2297, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 105, 106, 108, 110, 111, 112, 114, 1677, 2299, 2321)</t>
+    <t xml:space="preserve">c(102, 104, 105, 106, 107, 108, 109, 110, 111, 112, 114, 115, 117, 1645, 1676, 2211, 2212, 2213, 2296, 2297, 2298, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 113, 116, 118, 1646, 1647, 1648, 1677, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 105, 106, 108, 109, 110, 111, 114, 116, 117, 118, 1645, 1646, 1648, 1676, 1677, 2212, 2296, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 104, 107, 112, 113, 115, 1647, 2211, 2213, 2297, 2298, 2321)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(59, 61, 74, 77, 133, 134, 135, 137, 1671, 1787, 1788, 1790, 1792, 1793, 1794, 1795, 2049, 2050, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 75, 76, 136, 1789, 1888, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 75, 77, 133, 134, 136, 137, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 74, 76, 135, 1671, 1787, 2050, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 74, 75, 77, 133, 135, 136, 1787, 1790, 1793, 1794, 1888, 2049, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 76, 134, 137, 1671, 1788, 1789, 1792, 1795, 2052)</t>
+    <t xml:space="preserve">c(51, 60, 61, 74, 77, 133, 134, 135, 137, 1671, 1788, 1790, 1793, 1794, 1795, 1888, 2049, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 75, 76, 136, 1787, 1789, 1792, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 74, 75, 76, 77, 133, 135, 136, 137, 1671, 1787, 1790, 1792, 1793, 1794, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 134, 1788, 1789, 1795, 1888, 2049, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 61, 75, 76, 77, 133, 134, 136, 137, 1787, 1788, 1789, 1790, 1792, 1794, 1795, 2049, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 74, 135, 1671, 1793, 1888, 2050, 2053)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 124, 125, 185, 186, 1749, 1890, 1891, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 183, 184, 1747, 1748, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 123, 125, 183, 186, 1748, 1890, 1891, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 122, 124, 184, 185, 1747, 1749, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 82, 122, 123, 125, 184, 185, 186, 1748, 1891, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 124, 183, 1747, 1749, 1890, 2007, 2008)</t>
+    <t xml:space="preserve">c(79, 80, 82, 123, 124, 125, 184, 185, 186, 1748, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 122, 183, 1747, 1749, 1890, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 125, 183, 184, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 82, 122, 123, 124, 185, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 123, 124, 186, 1747, 1748, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 122, 125, 183, 184, 185, 1749)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1829, 1830, 1833, 1834, 1980, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1832, 1979, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1834, 1980, 2144, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1833, 1979, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1979, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1833, 1834, 1980, 2148)</t>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1833, 1980, 2144, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1832, 1834, 1979, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1833, 1979, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1834, 1980, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1832, 1833, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1834, 1979, 1980, 2148)</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(103, 104, 105, 107, 108, 109, 110, 113, 115, 117, 118, 1646, 1647, 1676, 1677, 2211, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 106, 111, 112, 114, 116, 1645, 1648, 2212, 2213)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 108, 109, 111, 112, 115, 116, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2213, 2296, 2298, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(106, 107, 110, 113, 114, 117, 118, 2212, 2297, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 108, 109, 110, 111, 112, 113, 116, 1645, 1646, 1647, 1676, 1677, 2213, 2297, 2298, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 107, 114, 115, 117, 118, 1648, 2211, 2212, 2296, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 61, 75, 77, 135, 136, 137, 1787, 1788, 1789, 1792, 1793, 1794, 1795, 1888, 2049, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 74, 76, 133, 134, 1671, 1790, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 61, 75, 77, 133, 136, 137, 1671, 1787, 1788, 1790, 1794, 1888, 2049, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 74, 76, 134, 135, 1789, 1792, 1793, 1795, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 76, 77, 133, 137, 1671, 1787, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 61, 74, 75, 134, 135, 136, 1788, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 82, 122, 125, 185, 186, 1748, 1890, 1891, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 123, 124, 183, 184, 1747, 1749, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 124, 183, 184, 1748, 1749, 1890, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(82, 123, 125, 185, 186, 1747, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 82, 123, 124, 125, 184, 186, 1747, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 122, 183, 185, 1748, 1749, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1834, 1979, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1832, 1833, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1979, 1980, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1833, 1834, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1979, 1980, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 1834, 2144, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 105, 106, 108, 112, 116, 117, 118, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2297, 2298, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 107, 109, 110, 111, 113, 114, 115, 1645, 2296, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 105, 106, 107, 108, 110, 111, 113, 114, 115, 116, 118, 1645, 1647, 1648, 1677, 2212, 2297, 2298, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 104, 109, 112, 117, 1646, 1676, 2211, 2213, 2296, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 106, 107, 108, 109, 110, 111, 114, 116, 1645, 1646, 1647, 1676, 1677, 2212, 2296, 2297, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 104, 105, 112, 113, 115, 117, 118, 1648, 2211, 2213, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 76, 77, 134, 1787, 1788, 1789, 1792, 1794, 1795, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 75, 133, 135, 136, 137, 1671, 1790, 1793, 1888)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 74, 75, 76, 77, 134, 135, 136, 137, 1787, 1789, 1792, 1793, 1794, 1795, 1888, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 61, 133, 1671, 1788, 1790, 2049, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 74, 75, 76, 77, 133, 134, 135, 137, 1671, 1787, 1789, 1790, 1794, 1888, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 61, 136, 1788, 1792, 1793, 1795, 2049, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 122, 124, 125, 183, 186, 1747, 1748, 1749, 1891, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 82, 123, 184, 185, 1890, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 124, 125, 183, 185, 186, 1748, 1749, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 82, 122, 123, 184, 1747, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 82, 124, 183, 184, 185, 1747, 1748, 1890, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 122, 123, 125, 186, 1749, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 1834, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1979, 1980, 2144, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1834, 1979, 1980, 2144, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1833, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1834, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1979, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 106, 107, 108, 112, 114, 116, 117, 1646, 1647, 1676, 1677, 2211, 2212, 2297, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 105, 109, 110, 111, 113, 115, 118, 1645, 1648, 2213, 2296)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 105, 106, 107, 109, 110, 111, 112, 113, 114, 115, 117, 118, 2211, 2213, 2297, 2298, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 108, 116, 1645, 1646, 1647, 1648, 1676, 1677, 2212, 2296, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 107, 108, 109, 110, 111, 114, 115, 116, 117, 118, 1645, 1646, 1648, 1676, 1677, 2212, 2213, 2296, 2297, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 104, 105, 106, 112, 113, 1647, 2211, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 76, 77, 137, 1671, 1787, 1788, 1789, 1790, 1793, 1794, 2049, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74, 75, 133, 134, 135, 136, 1792, 1795, 1888, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 61, 74, 76, 77, 133, 136, 137, 1671, 1787, 1789, 1790, 1793, 1794, 1795, 1888, 2049, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 75, 134, 135, 1788, 1792, 2050, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 76, 77, 133, 134, 137, 1787, 1788, 1789, 1794, 1795, 1888, 2049, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(75, 135, 136, 1671, 1790, 1792, 1793, 2050, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 124, 125, 183, 184, 185, 1748, 1890, 1891, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(82, 123, 186, 1747, 1749, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 125, 183, 184, 186, 1748, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(123, 124, 185, 1747, 1749, 1890, 1891, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 122, 124, 125, 183, 184, 185, 1747, 1749, 1890, 1891, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 82, 123, 186, 1748, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1979, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1834, 1980, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833, 1834, 1979, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1980, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1834, 1979, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 108, 109, 110, 111, 112, 113, 114, 118, 1647, 1676, 1677, 2211, 2213, 2297, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(106, 107, 115, 116, 117, 1645, 1646, 1648, 2212, 2296, 2298, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 104, 106, 107, 108, 110, 111, 112, 113, 114, 116, 118, 1646, 1647, 1648, 1676, 1677, 2296, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 103, 105, 109, 115, 117, 1645, 2211, 2212, 2213, 2297)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 106, 108, 110, 111, 112, 113, 114, 115, 117, 118, 1646, 1648, 1676, 1677, 2211, 2212, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 105, 107, 109, 116, 1645, 1647, 2213, 2296, 2297, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 75, 76, 133, 134, 135, 137, 1671, 1787, 1789, 1792, 1794, 1888, 2049, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 74, 77, 136, 1788, 1790, 1793, 1795, 2050, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 75, 76, 134, 135, 136, 137, 1671, 1787, 1788, 1790, 1793, 1795, 1888, 2049, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 74, 77, 133, 1789, 1792, 1794, 2050, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 61, 74, 75, 77, 134, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1794, 1795, 2049, 2050, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 76, 133, 135, 1793, 1888, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 82, 122, 124, 125, 183, 184, 185, 186, 1747, 1748, 1749, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 123, 1890, 1891, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 122, 124, 183, 184, 185, 186, 1747, 1748, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 82, 123, 125, 1749, 1890, 1891, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 122, 124, 125, 184, 186, 1747, 1748, 1749, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 82, 123, 183, 185, 1890, 1891, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1834, 1979, 1980, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1833, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1834, 1979, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 1980, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1832, 1833, 1979, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1834, 1980, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 106, 107, 108, 109, 113, 114, 116, 118, 1645, 1646, 1647, 1648, 1676, 2211, 2212, 2296, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 104, 105, 110, 111, 112, 115, 117, 1677, 2213, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 105, 106, 107, 108, 109, 111, 113, 114, 115, 116, 117, 1646, 1677, 2213, 2296, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(104, 110, 112, 118, 1645, 1647, 1648, 1676, 2211, 2212, 2297, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 104, 105, 107, 109, 111, 115, 118, 1645, 1646, 1647, 1648, 1676, 2211, 2213, 2297, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(103, 106, 108, 110, 112, 113, 114, 116, 117, 1677, 2212, 2296)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 75, 77, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1793, 1794, 1795, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 74, 76, 1789, 1790, 1792, 1888, 2049, 2050, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 75, 76, 77, 134, 136, 1787, 1788, 1790, 1792, 1793, 1795, 1888, 2049, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 74, 133, 135, 137, 1671, 1789, 1794, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 75, 76, 77, 133, 134, 135, 136, 1788, 1789, 1792, 1794, 1795, 2049, 2050, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 74, 137, 1671, 1787, 1790, 1793, 1888, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 124, 125, 1748, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 123, 1747, 1749)</t>
+    <t xml:space="preserve">c(100, 102, 105, 106, 107, 108, 109, 111, 112, 113, 1646, 1647, 1648, 1676, 2211, 2212, 2213, 2296, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 103, 104, 110, 114, 115, 116, 117, 118, 1645, 1677, 2297)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 108, 109, 110, 111, 112, 113, 117, 118, 1645, 2211, 2212, 2297, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(107, 114, 115, 116, 1646, 1647, 1648, 1676, 1677, 2213, 2296, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 104, 105, 106, 107, 108, 110, 111, 112, 114, 115, 116, 117, 1645, 1647, 1648, 1676, 1677, 2211, 2213, 2296, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 109, 113, 118, 1646, 2212, 2297, 2298, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 61, 75, 76, 77, 133, 135, 1787, 1788, 1789, 1792, 1793, 1795, 1888, 2049, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 74, 134, 136, 137, 1671, 1790, 1794, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 61, 74, 75, 77, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1792, 1793, 1795, 1888, 2049, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 76, 133, 1790, 1794, 2050, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 74, 75, 77, 133, 135, 136, 137, 1787, 1788, 1789, 1790, 1793, 1795, 1888, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 61, 76, 134, 1671, 1792, 1794, 2049, 2050, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 123, 124, 183, 184, 185, 186, 1748, 1749, 1890, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 122, 125, 1747, 1891, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 122, 183, 184, 185, 186, 1748, 1749, 1890, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 123, 124, 125, 1747, 1891, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 125, 183, 184, 185, 186, 1749, 1890, 1891, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 123, 124, 1747, 1748, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1834, 1979, 1980, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1833, 1834, 2144, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1832, 1979, 1980)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833, 1834, 1979, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1980, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 105, 106, 107, 108, 109, 110, 111, 113, 115, 116, 117, 1646, 1647, 1648, 1676, 1677, 2212, 2297, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 104, 112, 114, 118, 1645, 2211, 2213, 2296, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 106, 107, 108, 109, 110, 111, 112, 115, 117, 118, 1646, 1648, 2211, 2212, 2213, 2296, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(104, 105, 113, 114, 116, 1645, 1647, 1676, 1677, 2297, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 105, 106, 107, 109, 111, 112, 113, 114, 116, 117, 118, 1647, 1648, 1676, 2211, 2212, 2213, 2296, 2297, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 104, 108, 110, 115, 1645, 1646, 1677, 2298, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 61, 75, 76, 77, 133, 134, 136, 137, 1671, 1787, 1788, 1790, 1888, 2049, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 74, 135, 1789, 1792, 1793, 1794, 1795, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 76, 77, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1793, 1795, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 74, 75, 133, 1790, 1792, 1794, 1888, 2049, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 74, 76, 77, 137, 1671, 1787, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 61, 75, 133, 134, 135, 136, 1788, 2051, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 122, 123, 124, 183, 184, 185, 186, 1747, 1749, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 82, 125, 1748, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 123, 184, 185, 186, 1747, 1748, 1749, 1890, 1891, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 122, 124, 125, 183, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 122, 124, 183, 184, 185, 186, 1749, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 123, 125, 1747, 1748, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1832, 1834, 1979, 2144, 2145, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1833, 1980, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1834, 1979, 1980, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1834, 1979, 1980, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 105, 106, 108, 110, 111, 113, 114, 115, 116, 117, 118, 1645, 1646, 1648, 1676, 1677, 2296, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 104, 107, 109, 112, 1647, 2211, 2212, 2213, 2297, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 107, 110, 113, 114, 115, 117, 118, 1645, 1646, 1647, 1648, 1676, 2211, 2212, 2213, 2296, 2297, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(105, 106, 108, 109, 111, 112, 116, 1677, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 105, 106, 107, 108, 109, 110, 111, 114, 115, 116, 1646, 1647, 1648, 1676, 1677, 2213, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 112, 113, 117, 118, 1645, 2211, 2212, 2296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 74, 75, 76, 77, 133, 134, 135, 137, 1671, 1787, 1788, 1790, 1792, 1793, 1794, 2049, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 61, 136, 1789, 1795, 1888, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 61, 74, 75, 76, 77, 133, 135, 137, 1787, 1788, 1789, 1790, 1794, 1795, 1888, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 134, 136, 1671, 1792, 1793, 2049, 2050, 2051, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 76, 77, 134, 135, 136, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1888, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 61, 74, 75, 133, 137, 1794, 1795, 2049, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 183, 184, 1747, 1748, 1749, 1890, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(122, 123, 124, 125, 185, 186, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 123, 124, 125, 183, 185, 186, 1747, 1748, 1749, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 82, 122, 184, 1890, 1891, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 123, 125, 183, 184, 185, 186, 1747, 1748, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(122, 124, 1749, 1890, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1832, 1833, 1979, 1980, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1834, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1832, 1833, 1834)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1832, 1833, 1979, 1980, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1834, 2144, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 104, 106, 107, 109, 110, 111, 113, 115, 116, 117, 118, 1646, 1647, 1648, 1676, 1677, 2212, 2296, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 105, 108, 112, 114, 1645, 2211, 2213, 2297, 2298, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 105, 106, 108, 110, 111, 112, 114, 116, 117, 118, 1645, 1646, 2211, 2212, 2296, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 104, 107, 109, 113, 115, 1647, 1648, 1676, 1677, 2213, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 105, 106, 107, 110, 111, 112, 113, 1645, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2296, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 104, 108, 109, 114, 115, 116, 117, 118, 1646, 2297)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 135, 136, 137, 1787, 1788, 1789, 1790, 1794, 2049, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(77, 133, 134, 1671, 1792, 1793, 1795, 1888, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 75, 133, 134, 136, 137, 1787, 1789, 1792, 1793, 1794, 1795, 1888, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 74, 76, 77, 135, 1671, 1788, 1790, 2049, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 60, 61, 74, 76, 77, 133, 134, 1671, 1787, 1788, 1789, 1790, 1793, 1794, 1795, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 75, 135, 136, 137, 1792, 1888, 2049, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 124, 125, 184, 185, 186, 1748, 1749, 1890, 1891, 1892, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 122, 123, 183, 1747, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 122, 123, 125, 183, 184, 185, 1890, 1891, 1892, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 124, 186, 1747, 1748, 1749, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 125, 183, 184, 1747, 1748, 1749, 1890, 1891, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 123, 124, 185, 186, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1832, 1833, 1834, 1979, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1980, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1834, 1979, 1980, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1832, 1833, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1831, 1832, 1834, 1979, 1980, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1833, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 105, 107, 111, 113, 115, 116, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2296, 2297, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 106, 108, 109, 110, 112, 114, 117, 2213, 2298, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 105, 106, 109, 111, 112, 113, 115, 116, 117, 118, 1646, 1647, 1648, 1676, 1677, 2211, 2296, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 104, 107, 108, 110, 114, 1645, 2212, 2213, 2297, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 105, 107, 108, 109, 110, 112, 114, 115, 116, 117, 1646, 1647, 1677, 2211, 2296, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 104, 106, 111, 113, 118, 1645, 1648, 1676, 2212, 2213, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + CP_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 74, 76, 77, 133, 134, 135, 136, 137, 1671, 1787, 1789, 1795, 1888, 2049, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 61, 75, 1788, 1790, 1792, 1793, 1794, 2050)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 76, 77, 133, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1795, 1888, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 61, 74, 75, 134, 135, 1794, 2049, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 61, 74, 75, 76, 133, 134, 135, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2050, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 77, 136, 137, 1671, 1787, 2049, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 123, 124, 1748, 1749, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 125, 1747, 1891)</t>
   </si>
   <si>
     <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(80, 81, 82, 122, 124, 125, 1747, 1890, 1891, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 123, 1748, 1749)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 82, 122, 123, 124, 125, 1747, 1749, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 1748, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1832, 1833, 1979, 1980, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1834, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1832, 1833, 1834, 1979, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1980, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1832, 1834, 1979, 1980, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1833, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 105, 107, 108, 110, 111, 113, 114, 116, 1645, 1648, 1676, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 106, 109, 112, 115, 117, 118, 1646, 1647, 1677, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 110, 111, 117, 118, 1645, 1646, 1648, 1677, 2213, 2297, 2298, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(109, 112, 113, 114, 115, 116, 1647, 1676, 2211, 2212, 2296, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 106, 109, 110, 111, 112, 114, 116, 117, 118, 1646, 1647, 1676, 2211, 2212, 2296, 2297, 2298, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 105, 107, 108, 113, 115, 1645, 1648, 1677, 2213, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 74, 76, 77, 133, 134, 135, 136, 1671, 1787, 1788, 1790, 1792, 1793, 1794, 2049, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 75, 137, 1789, 1795, 1888, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 74, 76, 77, 134, 135, 136, 1671, 1787, 1789, 1792, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 75, 133, 137, 1788, 1790, 1793, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 61, 75, 77, 133, 135, 137, 1671, 1787, 1789, 1793, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 74, 76, 134, 136, 1788, 1790, 1792, 1794)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 122, 123, 124, 1747, 1749, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 82, 125, 1748, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 123, 124, 125, 1747, 1748, 1749, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 82, 122, 1890, 1892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1833, 1834, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1979, 1980, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1979, 1980, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 1833, 1834, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1834, 1979, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1832, 1833, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 106, 107, 108, 109, 111, 112, 115, 116, 117, 118, 1645, 1646, 1647, 1676, 2211, 2213, 2296, 2297, 2298, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 104, 105, 110, 113, 114, 1648, 1677, 2212, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 105, 107, 109, 111, 112, 113, 114, 115, 116, 117, 118, 1676, 1677, 2211, 2212, 2213, 2297, 2298, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 104, 106, 108, 110, 1645, 1646, 1647, 1648, 2296, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 104, 106, 108, 109, 110, 111, 112, 114, 115, 116, 1645, 1647, 1648, 1676, 1677, 2211, 2213, 2296, 2297, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 105, 107, 113, 117, 118, 1646, 2212, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 133, 135, 137, 1787, 1788, 1792, 1794, 1795, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(134, 136, 1671, 1789, 1790, 1793, 1888, 2049, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 61, 74, 76, 133, 134, 135, 1671, 1790, 1792, 1793, 1794, 1888, 2049, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 75, 77, 136, 137, 1787, 1788, 1789, 1795, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 75, 76, 77, 134, 135, 136, 137, 1671, 1788, 1789, 1792, 1793, 1888, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 74, 133, 1787, 1790, 1794, 1795, 2049, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 124, 183, 184, 185, 186, 1747, 1748, 1890, 1891, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 123, 125, 1749, 1892, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1749, 1890, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(183, 184, 185, 186, 1748, 1891, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(82, 123, 124, 125, 184, 185, 186, 1748, 1749, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 183, 1747, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1833, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1834, 1979, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 1979, 1980, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 2144, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 104, 107, 108, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 2211, 2212, 2213, 2297, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 105, 106, 109, 1648, 1676, 1677, 2296, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 108, 109, 113, 114, 117, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2296, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 107, 110, 111, 112, 115, 116, 118, 1645, 2297, 2298, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 106, 107, 109, 110, 111, 115, 116, 117, 118, 1647, 1648, 1677, 2211, 2296, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 105, 108, 112, 113, 114, 1645, 1646, 1676, 2212, 2213, 2297)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 133, 135, 137, 1671, 1787, 1789, 1792, 1793, 1794, 1795, 1888, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 75, 76, 77, 134, 136, 1788, 1790, 2049, 2050)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 77, 135, 1671, 1788, 1789, 1790, 1794, 1795, 1888, 2049, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(76, 133, 134, 136, 137, 1787, 1792, 1793, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 61, 74, 76, 77, 133, 134, 135, 136, 1787, 1788, 1792, 1793, 1795, 1888, 2049, 2050, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 75, 137, 1671, 1789, 1790, 1794, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 82, 123, 124, 185, 186, 1748, 1749, 1890, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 122, 125, 183, 184, 1747, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 123, 124, 125, 185, 1747, 1748, 1749, 1891, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 122, 183, 184, 186, 1890, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 123, 125, 183, 186, 1749, 1890, 1891, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 124, 184, 185, 1747, 1748, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1832, 1833, 1834, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1979, 1980, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1979, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1834, 1980, 2144, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1833, 1834, 1979, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1832, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 103, 107, 109, 110, 111, 112, 114, 115, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2297, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 104, 105, 106, 108, 113, 116, 117, 2296, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 103, 104, 110, 111, 113, 115, 116, 118, 1645, 1647, 1648, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 105, 106, 107, 108, 109, 112, 114, 117, 1646, 1676, 1677)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 102, 105, 106, 107, 108, 110, 111, 113, 114, 115, 116, 118, 1645, 1646, 1647, 1676, 2212, 2213, 2296, 2297, 2298, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 103, 104, 109, 112, 117, 1648, 1677, 2211, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 134, 135, 136, 137, 1788, 1888, 2049, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(77, 133, 1787, 1789, 1790, 1792, 1793, 1794, 1795, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 75, 76, 77, 133, 134, 135, 136, 137, 1788, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 61, 74, 1787, 1789, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 135, 137, 1789, 1792, 1793, 1794, 1795, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(133, 134, 136, 1787, 1788, 1790, 1888, 2049, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 123, 124, 125, 183, 186, 1747, 1748, 1890, 1891, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 82, 122, 184, 185, 1749, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 122, 124, 184, 185, 186, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 82, 123, 125, 183, 1747, 1748, 1749)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 122, 123, 125, 183, 186, 1747, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 82, 124, 184, 185, 1748, 1749)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1980, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1979)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1831, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1979, 1980, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1979, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1980, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 105, 107, 108, 109, 111, 112, 113, 115, 1646, 1647, 1648, 1676, 2211, 2212, 2213, 2296, 2298, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 104, 106, 110, 114, 116, 117, 118, 1645, 1677, 2297, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(101, 102, 103, 104, 106, 107, 108, 109, 112, 114, 116, 117, 118, 1645, 1646, 1677, 2213, 2296, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 105, 110, 111, 113, 115, 1647, 1648, 1676, 2211, 2212, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 106, 107, 108, 109, 111, 112, 113, 114, 116, 1647, 1676, 2211, 2296, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(105, 110, 115, 117, 118, 1645, 1646, 1648, 1677, 2212, 2213, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 60, 61, 74, 76, 77, 133, 134, 135, 136, 137, 1787, 1790, 1792, 1794, 1795, 2049, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 75, 1788, 1789, 1793, 1888, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 74, 77, 133, 134, 135, 136, 137, 1787, 1788, 1790, 1792, 1793, 1795, 1888, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 75, 76, 1789, 1794, 2049, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 74, 75, 76, 77, 133, 134, 136, 1788, 1789, 1792, 1793, 1888, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 135, 137, 1787, 1790, 1794, 1795, 2049)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 82, 122, 123, 124, 185, 186, 1747, 1748, 1749, 1891, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 125, 183, 184, 1890, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 82, 122, 123, 124, 125, 184, 186, 1747, 1749, 1890, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 183, 185, 1748, 1891, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 122, 124, 125, 184, 186, 1748, 1749, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 123, 183, 185, 1747, 1890, 1891, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1980, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1979, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1979, 1980, 2144, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 2145, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1980, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1979, 2144, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 103, 104, 105, 106, 108, 110, 111, 112, 113, 114, 116, 117, 1646, 1647, 1648, 1677, 2211, 2212, 2213, 2299, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 107, 109, 115, 118, 1645, 1676, 2296, 2297, 2298, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 103, 104, 105, 107, 108, 109, 111, 112, 113, 114, 116, 117, 118, 1645, 1646, 1647, 1648, 2296, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(102, 106, 110, 115, 1676, 1677, 2211, 2212, 2213, 2297, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 109, 110, 111, 112, 113, 114, 115, 117, 1645, 1646, 1648, 1677, 2211, 2212, 2213, 2297, 2298, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(104, 105, 106, 107, 108, 116, 118, 1647, 1676, 2296, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 61, 75, 77, 1671, 1888, 2049, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 74, 76, 2050, 2051)</t>
+    <t xml:space="preserve">c(78, 80, 81, 82, 123, 124, 1748, 1749, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 122, 125, 1747, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 122, 125, 1747, 1748, 1749, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 123, 124, 1890, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1834, 1979, 1980, 2144, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1832, 1833, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1834, 1979, 1980, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1831, 1832, 1833, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833, 1979, 1980, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1834, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 107, 109, 111, 112, 113, 116, 117, 1645, 1646, 1648, 1677, 2211, 2212, 2213, 2296, 2297, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 105, 106, 108, 110, 114, 115, 118, 1647, 1676, 2298, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 104, 107, 108, 109, 110, 111, 113, 115, 117, 118, 1645, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 105, 106, 112, 114, 116, 1646, 1647, 1648, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 104, 105, 106, 107, 108, 109, 112, 115, 116, 117, 1645, 2211, 2212, 2213, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 110, 111, 113, 114, 118, 1646, 1647, 1648, 1676, 1677, 2296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 77, 133, 134, 135, 137, 1671, 1788, 1789, 1792, 1794, 2050, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(75, 76, 136, 1787, 1790, 1793, 1795, 1888, 2049, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 60, 61, 74, 75, 76, 77, 133, 135, 136, 137, 1787, 1789, 1792, 1793, 1888, 2051, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(59, 134, 1671, 1788, 1790, 1794, 1795, 2049, 2050, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 75, 76, 77, 133, 134, 135, 137, 1787, 1792, 1793, 1795, 1888, 2049, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 61, 74, 136, 1671, 1788, 1789, 1790, 1794, 2050)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 81, 82, 122, 124, 1747, 1748, 1890, 1891)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 123, 125, 1749, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 123, 124, 125, 1747, 1748, 1749, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 122, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 82, 122, 124, 1747, 1748, 1749, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 123, 125, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833, 1834, 1980, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1979, 2144, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1979, 1980, 2144, 2145, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1832, 1833, 1834, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1832, 1833, 1834, 1980, 2144, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1979, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 103, 107, 108, 109, 110, 112, 113, 114, 115, 116, 1645, 1646, 1647, 1648, 1676, 1677, 2212, 2213, 2296, 2297, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 104, 105, 106, 111, 117, 118, 2211, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 104, 105, 107, 109, 111, 113, 115, 116, 117, 118, 1645, 1646, 1648, 1676, 2211, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 103, 106, 108, 110, 112, 114, 1647, 1677, 2212, 2213, 2296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 104, 105, 107, 109, 111, 112, 113, 114, 115, 116, 117, 1645, 1647, 1648, 1676, 2211, 2296, 2297, 2298, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 106, 108, 110, 118, 1646, 1677, 2212, 2213, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + NDF_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 76, 133, 134, 135, 1671, 1787, 1788, 1789, 1790, 1795, 2049, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 75, 77, 136, 137, 1792, 1793, 1794, 1888, 2050)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 61, 74, 75, 133, 134, 135, 136, 1787, 1788, 1790, 1792, 1793, 1794, 1888, 2049, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 76, 77, 137, 1671, 1789, 1795, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 61, 77, 133, 135, 136, 137, 1671, 1787, 1790, 1793, 1794, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 74, 75, 76, 134, 1788, 1789, 1792, 1795)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 82, 123, 125, 183, 185, 186, 1747, 1748, 1890, 1891, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 122, 124, 184, 1749, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 82, 122, 124, 125, 184, 185, 186, 1747, 1748, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(81, 123, 183, 1749, 1890, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 123, 124, 185, 186, 1747, 1748, 1749, 1891, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 125, 183, 184, 1890, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1834, 1979, 1980, 2144, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1832, 1833, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1832, 1833, 1980, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1834, 1979, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 1832, 1834, 1979, 1980, 2144, 2145, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1833, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 104, 105, 106, 107, 109, 110, 111, 112, 113, 117, 118, 1648, 1676, 1677, 2211, 2212, 2296, 2298, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 108, 114, 115, 116, 1645, 1646, 1647, 2213, 2297, 2299, 2321)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 103, 104, 106, 107, 108, 109, 111, 112, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 2211, 2213, 2296, 2297, 2298, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 105, 110, 113, 114, 115, 1677, 2212, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 105, 106, 107, 108, 109, 111, 112, 113, 115, 116, 117, 1645, 1647, 1648, 1676, 1677, 2211, 2297, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 104, 110, 114, 118, 1646, 2212, 2213, 2296, 2298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 60, 61, 74, 75, 76, 133, 134, 137, 1671, 1788, 1789, 1790, 1792, 1795, 1888, 2049, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 77, 135, 136, 1787, 1793, 1794, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 76, 77, 133, 135, 1671, 1787, 1789, 1790, 1792, 1795, 2049, 2050, 2051, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(74, 75, 134, 136, 137, 1788, 1793, 1794, 1888, 2052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 61, 76, 133, 134, 135, 136, 137, 1671, 1792, 1793, 1794, 1888, 2049, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 74, 75, 77, 1787, 1788, 1789, 1790, 1795, 2050)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 123, 124, 125, 183, 185, 1747, 1748, 1891, 1892, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 184, 186, 1749, 1890, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 81, 82, 122, 124, 183, 186, 1747, 1748, 1890, 1891, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 80, 123, 125, 184, 185, 1749, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 82, 122, 124, 125, 184, 1747, 1748, 1890, 1891, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 123, 183, 185, 186, 1749, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1831, 1833, 1980, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1832, 1834, 1979, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1833, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1832, 1834, 1979)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1833, 1834, 1979, 1980, 2144, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1832, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 105, 107, 108, 111, 112, 113, 115, 116, 1647, 1648, 1676, 1677, 2211, 2213, 2296, 2298, 2299, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 106, 109, 110, 114, 117, 118, 1645, 1646, 2212, 2297, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 104, 107, 110, 111, 113, 115, 116, 1645, 1646, 1647, 1648, 1676, 2211, 2212, 2296, 2297, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 105, 106, 108, 109, 112, 114, 117, 118, 1677, 2213, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 105, 106, 108, 109, 112, 113, 115, 117, 118, 1645, 1646, 1647, 1648, 1676, 2211, 2212, 2296, 2297, 2298, 2299, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 104, 107, 110, 111, 114, 116, 1677, 2213, 2321, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + EE_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 61, 74, 75, 77, 1888, 2050, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 76, 1671, 2049, 2051, 2053)</t>
   </si>
   <si>
     <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 74, 76, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 75, 77, 1671, 1888, 2049)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 82, 122, 123, 125, 1749, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 124, 1747, 1748, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 122, 123, 124, 1747, 1749, 1890, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 82, 125, 1748, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 122, 123, 125, 1747, 1749, 1890, 1891, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 82, 124, 1748, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 1834, 1979, 1980, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833, 1834, 1980, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1979, 2144, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1833, 1834, 1980, 2144, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1832, 1979, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 2211, 2212, 2296, 2297, 2298, 2299, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 118, 1676, 1677, 2213, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 118, 1677, 2212, 2296, 2298, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1676, 2211, 2213, 2297, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 1676, 2211, 2212, 2296, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 118, 1677, 2213, 2297, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 74, 75, 77, 1671, 2049, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 61, 76, 1888, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 59, 61, 74, 75, 77, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 76, 1671, 1888, 2049, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 58, 60, 61, 77, 1671, 1888, 2049, 2050, 2052, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 74, 75, 76, 2051, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 82, 122, 124, 125, 1747, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 123, 1748, 1749, 1890)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 81, 122, 123, 125, 1747, 1748, 1749, 1890, 1891, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 82, 124, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 124, 125, 1747, 1748, 1890, 1891, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 123, 1749, 1892, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1833, 1979, 2144, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1832, 1834, 1980, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1831, 1832, 1834, 1979, 1980, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1830, 1833, 2144, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1832, 1834, 1979, 1980, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1833, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 2211, 2213, 2297, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1677, 2212, 2296, 2298, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 1676, 2211, 2296, 2297, 2298, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(118, 1677, 2212, 2213, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 117, 1676, 1677, 2211, 2212, 2213, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 118, 2296, 2297, 2298, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 59, 60, 61, 75, 76, 1671, 1888, 2050, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 74, 77, 2049, 2051, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 61, 74, 75, 76, 77, 2049, 2050, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 1671, 1888, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 61, 77, 1671, 1888, 2049, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 74, 75, 76, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 122, 124, 1747, 1748, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 123, 125, 1749, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 82, 123, 124, 1748, 1749, 1890, 1891, 1892, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 81, 122, 125, 1747, 2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 123, 124, 1747, 1748, 1890, 1891, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 125, 1749, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1831, 1832, 1833, 1979, 1980, 2144, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1834, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1832, 1834, 1980, 2144, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1833, 1979, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1980, 2144, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1834, 1979, 2145, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 118, 1677, 2211, 2212, 2213, 2296, 2297, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 1676, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 2213, 2296, 2298, 2299, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1677, 2211, 2212, 2297, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 1676, 1677, 2211, 2213, 2296, 2298, 2299, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 118, 2212, 2297, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 61, 74, 76, 77, 1671, 1888, 2049, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 75, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 60, 61, 74, 75, 77, 2049, 2050, 2051, 2052, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 76, 1671, 1888, 2053)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 75, 76, 77, 1671, 2049, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(51, 74, 1888, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 80, 81, 123, 124, 1748, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 82, 122, 125, 1747, 1749)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 81, 82, 125, 1747, 1748, 1749, 1891, 1892, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 122, 123, 124, 1890, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 122, 123, 124, 1747, 1748, 1890, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 125, 1749, 1891, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1831, 1832, 1833, 1834, 1980, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1979, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 2144, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1833, 1834, 1979, 1980, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1832, 1834, 2144, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 1833, 1979, 1980, 2145)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 1676, 1677, 2212, 2213, 2298, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 118, 2211, 2296, 2297, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 118, 1676, 2213, 2296, 2297, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 1677, 2211, 2212, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 1677, 2211, 2213, 2296, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 118, 1676, 2212, 2297, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 61, 75, 77, 1888, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 74, 76, 2049)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(60, 61, 74, 75, 76, 77, 1888, 2049, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 2050, 2051, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 74, 75, 76, 77, 1888, 2049, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 61, 2050, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 122, 1747, 1748, 1749, 1890, 1891, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 123, 124, 125, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 122, 125, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 123, 124, 1747, 1748, 1749)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 122, 123, 125, 1747, 1748, 1749, 1891, 2006, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(81, 82, 124, 1890, 1892, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1831, 1980, 2144, 2145, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1830, 1979, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 2144, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1980, 2145, 2146, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2145:2148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 118, 1676, 1677, 2213, 2297, 2298, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 2211, 2212, 2296, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 1676, 2211, 2212, 2296, 2297, 2299, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 118, 1677, 2213, 2298, 2321)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 1677, 2211, 2213, 2297, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 118, 1676, 2212, 2296, 2298)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 75, 77, 1888, 2049, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 74, 76, 2050, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 75, 1888, 2049, 2050, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(61, 74, 76, 77, 2051)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 60, 75, 76, 1888, 2049, 2050, 2051, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(59, 61, 74, 77, 2052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 122, 124, 125, 1747, 1749, 1890, 1891, 1892, 2007)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 82, 123, 1748, 2006, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 80, 81, 82, 123, 125, 1748, 1749, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(79, 122, 124, 1747, 1890, 1891)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(80, 81, 82, 124, 1747, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 122, 123, 125, 1748)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 2145, 2146, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1979, 1980, 2144, 2147)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1830, 1980, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1829, 1831, 1979, 2144)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1979, 1980, 2145, 2146)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1831, 2144, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 1676, 1677, 2211, 2296, 2297, 2298, 2321, 2322)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 118, 2212, 2213, 2299, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 118, 1676, 2211, 2212, 2298, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(117, 1677, 2213, 2296, 2297, 2299)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 117, 1676, 1677, 2211, 2212, 2297, 2298, 2321, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(116, 118, 2213, 2296, 2299, 2322)</t>
+    <t xml:space="preserve">c(58, 60, 61, 75, 77, 1888, 2049, 2050, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 74, 76, 1671, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 74, 76, 77, 1671, 1888, 2050, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 61, 75, 2049, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 124, 183, 186, 1747, 1749, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 123, 125, 184, 185, 1748, 1890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 81, 122, 123, 124, 125, 185, 186, 1747, 1748, 1891, 1892, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 82, 183, 184, 1749, 1890, 2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 82, 123, 124, 125, 184, 186, 1747, 1748, 1891, 2006, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 122, 183, 185, 1749, 1890, 1892, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1830, 1831, 1832, 1833, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1834, 1979, 1980, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1832, 1833, 1834, 1979, 1980, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1830, 1831, 2144, 2145, 2146)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1832, 1833, 1834, 1979, 1980, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 2144)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 103, 104, 106, 108, 109, 110, 111, 112, 113, 114, 115, 116, 1645, 1646, 1648, 1677, 2212, 2213, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 105, 107, 117, 118, 1647, 1676, 2211, 2296, 2297, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 103, 104, 105, 106, 107, 110, 111, 112, 114, 115, 117, 1646, 1647, 1648, 1677, 2211, 2213, 2297, 2298, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 108, 109, 113, 116, 118, 1645, 1676, 2212, 2296, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 102, 104, 105, 106, 107, 108, 113, 115, 116, 117, 1645, 1646, 1647, 1676, 2213, 2296, 2297, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(103, 109, 110, 111, 112, 114, 118, 1648, 1677, 2211, 2212, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 58, 59, 61, 74, 75, 77, 1671, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(60, 76, 1888, 2049, 2050, 2051)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 60, 61, 74, 75, 76, 77, 1888, 2051, 2052, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 59, 1671, 2049, 2050, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 74, 75, 77, 1888, 2049, 2050, 2052, 2053)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(51, 61, 76, 1671, 2051, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 81, 123, 124, 125, 183, 184, 185, 1747, 1748, 1749, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 82, 122, 186, 1890, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 81, 82, 122, 123, 124, 183, 185, 1748, 1890, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(80, 125, 184, 186, 1747, 1749, 1891, 1892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(79, 80, 81, 123, 125, 184, 185, 186, 1748, 1890, 1891, 1892, 2006, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 82, 122, 124, 183, 1747, 1749, 2007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1834, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1832, 1833, 1979)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 1834, 1979, 1980, 2144, 2145, 2146, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1832, 1833, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1830, 1832, 1833, 1834, 1979, 1980, 2145, 2147)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1829, 1831, 2144, 2146, 2148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 102, 103, 105, 106, 108, 109, 110, 111, 112, 113, 114, 115, 1645, 1647, 1676, 2212, 2213, 2297, 2298, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 104, 107, 116, 117, 118, 1646, 1648, 1677, 2211, 2296, 2299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 101, 104, 105, 106, 107, 108, 110, 112, 113, 114, 118, 1645, 1646, 1676, 1677, 2212, 2213, 2296, 2297, 2299, 2321, 2322)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(102, 103, 109, 111, 115, 116, 117, 1647, 1648, 2211, 2298, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(100, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 113, 116, 117, 1645, 1646, 1648, 2211, 2213, 2296, 2297, 2299, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(101, 112, 114, 115, 118, 1647, 1676, 1677, 2212, 2298, 2321, 2322)</t>
   </si>
 </sst>
 </file>
@@ -3221,19 +2771,19 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
       </c>
       <c r="M26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N26" t="n">
         <v>20</v>
       </c>
       <c r="O26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P26" t="n">
         <v>10</v>
@@ -3277,19 +2827,19 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
       </c>
       <c r="M27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N27" t="n">
         <v>20</v>
       </c>
       <c r="O27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P27" t="n">
         <v>10</v>
@@ -3333,19 +2883,19 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
       </c>
       <c r="M28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N28" t="n">
         <v>20</v>
       </c>
       <c r="O28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P28" t="n">
         <v>10</v>
@@ -3395,13 +2945,13 @@
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N29" t="n">
         <v>14</v>
       </c>
       <c r="O29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P29" t="n">
         <v>8</v>
@@ -3451,13 +3001,13 @@
         <v>2</v>
       </c>
       <c r="M30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N30" t="n">
         <v>14</v>
       </c>
       <c r="O30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P30" t="n">
         <v>8</v>
@@ -3507,13 +3057,13 @@
         <v>3</v>
       </c>
       <c r="M31" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N31" t="n">
         <v>14</v>
       </c>
       <c r="O31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P31" t="n">
         <v>8</v>
@@ -3557,19 +3107,19 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N32" t="n">
         <v>9</v>
       </c>
       <c r="O32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P32" t="n">
         <v>5</v>
@@ -3613,19 +3163,19 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
       </c>
       <c r="M33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N33" t="n">
         <v>9</v>
       </c>
       <c r="O33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P33" t="n">
         <v>5</v>
@@ -3669,19 +3219,19 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
       </c>
       <c r="M34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N34" t="n">
         <v>9</v>
       </c>
       <c r="O34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P34" t="n">
         <v>5</v>
@@ -3731,13 +3281,13 @@
         <v>1</v>
       </c>
       <c r="M35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N35" t="n">
         <v>23</v>
       </c>
       <c r="O35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P35" t="n">
         <v>12</v>
@@ -3787,13 +3337,13 @@
         <v>2</v>
       </c>
       <c r="M36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N36" t="n">
         <v>23</v>
       </c>
       <c r="O36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P36" t="n">
         <v>12</v>
@@ -3843,13 +3393,13 @@
         <v>3</v>
       </c>
       <c r="M37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N37" t="n">
         <v>23</v>
       </c>
       <c r="O37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P37" t="n">
         <v>12</v>
@@ -3893,19 +3443,19 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N38" t="n">
         <v>20</v>
       </c>
       <c r="O38" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P38" t="n">
         <v>10</v>
@@ -3949,19 +3499,19 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
       </c>
       <c r="M39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N39" t="n">
         <v>20</v>
       </c>
       <c r="O39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P39" t="n">
         <v>10</v>
@@ -4005,19 +3555,19 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
       </c>
       <c r="M40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N40" t="n">
         <v>20</v>
       </c>
       <c r="O40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P40" t="n">
         <v>10</v>
@@ -4067,13 +3617,13 @@
         <v>1</v>
       </c>
       <c r="M41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N41" t="n">
         <v>14</v>
       </c>
       <c r="O41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P41" t="n">
         <v>8</v>
@@ -4123,13 +3673,13 @@
         <v>2</v>
       </c>
       <c r="M42" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N42" t="n">
         <v>14</v>
       </c>
       <c r="O42" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P42" t="n">
         <v>8</v>
@@ -4179,13 +3729,13 @@
         <v>3</v>
       </c>
       <c r="M43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N43" t="n">
         <v>14</v>
       </c>
       <c r="O43" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P43" t="n">
         <v>8</v>
@@ -4229,19 +3779,19 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
       </c>
       <c r="M44" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N44" t="n">
         <v>9</v>
       </c>
       <c r="O44" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P44" t="n">
         <v>5</v>
@@ -4285,19 +3835,19 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
       </c>
       <c r="M45" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N45" t="n">
         <v>9</v>
       </c>
       <c r="O45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P45" t="n">
         <v>5</v>
@@ -4341,19 +3891,19 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
       </c>
       <c r="M46" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N46" t="n">
         <v>9</v>
       </c>
       <c r="O46" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P46" t="n">
         <v>5</v>
@@ -4403,13 +3953,13 @@
         <v>1</v>
       </c>
       <c r="M47" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N47" t="n">
         <v>23</v>
       </c>
       <c r="O47" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P47" t="n">
         <v>12</v>
@@ -4459,13 +4009,13 @@
         <v>2</v>
       </c>
       <c r="M48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N48" t="n">
         <v>23</v>
       </c>
       <c r="O48" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P48" t="n">
         <v>12</v>
@@ -4515,13 +4065,13 @@
         <v>3</v>
       </c>
       <c r="M49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N49" t="n">
         <v>23</v>
       </c>
       <c r="O49" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P49" t="n">
         <v>12</v>
@@ -4565,19 +4115,19 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N50" t="n">
         <v>20</v>
       </c>
       <c r="O50" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P50" t="n">
         <v>10</v>
@@ -4621,19 +4171,19 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
       </c>
       <c r="M51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N51" t="n">
         <v>20</v>
       </c>
       <c r="O51" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P51" t="n">
         <v>10</v>
@@ -4677,19 +4227,19 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
       </c>
       <c r="M52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N52" t="n">
         <v>20</v>
       </c>
       <c r="O52" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P52" t="n">
         <v>10</v>
@@ -4733,19 +4283,19 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N53" t="n">
         <v>14</v>
       </c>
       <c r="O53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P53" t="n">
         <v>8</v>
@@ -4789,19 +4339,19 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
       </c>
       <c r="M54" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N54" t="n">
         <v>14</v>
       </c>
       <c r="O54" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P54" t="n">
         <v>8</v>
@@ -4845,19 +4395,19 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
       </c>
       <c r="M55" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N55" t="n">
         <v>14</v>
       </c>
       <c r="O55" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P55" t="n">
         <v>8</v>
@@ -4901,19 +4451,19 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
       </c>
       <c r="M56" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N56" t="n">
         <v>9</v>
       </c>
       <c r="O56" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P56" t="n">
         <v>5</v>
@@ -4957,19 +4507,19 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
       </c>
       <c r="M57" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N57" t="n">
         <v>9</v>
       </c>
       <c r="O57" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P57" t="n">
         <v>5</v>
@@ -5013,19 +4563,19 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
       </c>
       <c r="M58" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N58" t="n">
         <v>9</v>
       </c>
       <c r="O58" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P58" t="n">
         <v>5</v>
@@ -5069,19 +4619,19 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
       </c>
       <c r="M59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N59" t="n">
         <v>23</v>
       </c>
       <c r="O59" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P59" t="n">
         <v>12</v>
@@ -5125,19 +4675,19 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
       </c>
       <c r="M60" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N60" t="n">
         <v>23</v>
       </c>
       <c r="O60" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P60" t="n">
         <v>12</v>
@@ -5181,19 +4731,19 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
       </c>
       <c r="M61" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N61" t="n">
         <v>23</v>
       </c>
       <c r="O61" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P61" t="n">
         <v>12</v>
@@ -5237,19 +4787,19 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
       </c>
       <c r="M62" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N62" t="n">
         <v>20</v>
       </c>
       <c r="O62" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P62" t="n">
         <v>10</v>
@@ -5293,19 +4843,19 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
       </c>
       <c r="M63" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N63" t="n">
         <v>20</v>
       </c>
       <c r="O63" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P63" t="n">
         <v>10</v>
@@ -5349,19 +4899,19 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
       </c>
       <c r="M64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N64" t="n">
         <v>20</v>
       </c>
       <c r="O64" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P64" t="n">
         <v>10</v>
@@ -5405,19 +4955,19 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N65" t="n">
         <v>14</v>
       </c>
       <c r="O65" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P65" t="n">
         <v>8</v>
@@ -5461,19 +5011,19 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
       </c>
       <c r="M66" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N66" t="n">
         <v>14</v>
       </c>
       <c r="O66" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P66" t="n">
         <v>8</v>
@@ -5517,19 +5067,19 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
       </c>
       <c r="M67" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N67" t="n">
         <v>14</v>
       </c>
       <c r="O67" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P67" t="n">
         <v>8</v>
@@ -5573,19 +5123,19 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
       </c>
       <c r="M68" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N68" t="n">
         <v>9</v>
       </c>
       <c r="O68" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P68" t="n">
         <v>5</v>
@@ -5629,19 +5179,19 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
       </c>
       <c r="M69" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N69" t="n">
         <v>9</v>
       </c>
       <c r="O69" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P69" t="n">
         <v>5</v>
@@ -5685,19 +5235,19 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
       </c>
       <c r="M70" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N70" t="n">
         <v>9</v>
       </c>
       <c r="O70" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P70" t="n">
         <v>5</v>
@@ -5741,19 +5291,19 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N71" t="n">
         <v>23</v>
       </c>
       <c r="O71" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P71" t="n">
         <v>12</v>
@@ -5797,19 +5347,19 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
       </c>
       <c r="M72" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N72" t="n">
         <v>23</v>
       </c>
       <c r="O72" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P72" t="n">
         <v>12</v>
@@ -5853,19 +5403,19 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
       </c>
       <c r="M73" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N73" t="n">
         <v>23</v>
       </c>
       <c r="O73" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P73" t="n">
         <v>12</v>
@@ -5909,19 +5459,19 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
       </c>
       <c r="M74" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N74" t="n">
         <v>20</v>
       </c>
       <c r="O74" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P74" t="n">
         <v>10</v>
@@ -5965,19 +5515,19 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
       </c>
       <c r="M75" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N75" t="n">
         <v>20</v>
       </c>
       <c r="O75" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P75" t="n">
         <v>10</v>
@@ -6021,19 +5571,19 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
       </c>
       <c r="M76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N76" t="n">
         <v>20</v>
       </c>
       <c r="O76" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P76" t="n">
         <v>10</v>
@@ -6077,28 +5627,28 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N77" t="n">
         <v>10</v>
       </c>
       <c r="O77" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P77" t="n">
         <v>5</v>
       </c>
       <c r="Q77" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R77" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="78">
@@ -6133,28 +5683,28 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N78" t="n">
         <v>10</v>
       </c>
       <c r="O78" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P78" t="n">
         <v>5</v>
       </c>
       <c r="Q78" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R78" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="79">
@@ -6189,28 +5739,28 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N79" t="n">
         <v>10</v>
       </c>
       <c r="O79" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P79" t="n">
         <v>5</v>
       </c>
       <c r="Q79" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R79" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="80">
@@ -6245,19 +5795,19 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
       </c>
       <c r="M80" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N80" t="n">
         <v>9</v>
       </c>
       <c r="O80" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P80" t="n">
         <v>5</v>
@@ -6301,19 +5851,19 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
       </c>
       <c r="M81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N81" t="n">
         <v>9</v>
       </c>
       <c r="O81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P81" t="n">
         <v>5</v>
@@ -6357,19 +5907,19 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
       </c>
       <c r="M82" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N82" t="n">
         <v>9</v>
       </c>
       <c r="O82" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P82" t="n">
         <v>5</v>
@@ -6413,19 +5963,19 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N83" t="n">
         <v>23</v>
       </c>
       <c r="O83" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P83" t="n">
         <v>12</v>
@@ -6469,19 +6019,19 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
       </c>
       <c r="M84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N84" t="n">
         <v>23</v>
       </c>
       <c r="O84" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P84" t="n">
         <v>12</v>
@@ -6525,19 +6075,19 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
       </c>
       <c r="M85" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N85" t="n">
         <v>23</v>
       </c>
       <c r="O85" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P85" t="n">
         <v>12</v>
@@ -6581,19 +6131,19 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
       <c r="M86" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N86" t="n">
         <v>20</v>
       </c>
       <c r="O86" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P86" t="n">
         <v>10</v>
@@ -6637,19 +6187,19 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
       </c>
       <c r="M87" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N87" t="n">
         <v>20</v>
       </c>
       <c r="O87" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P87" t="n">
         <v>10</v>
@@ -6693,19 +6243,19 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
       </c>
       <c r="M88" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N88" t="n">
         <v>20</v>
       </c>
       <c r="O88" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P88" t="n">
         <v>10</v>
@@ -6749,28 +6299,28 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N89" t="n">
         <v>10</v>
       </c>
       <c r="O89" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P89" t="n">
         <v>5</v>
       </c>
       <c r="Q89" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R89" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="90">
@@ -6805,28 +6355,28 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N90" t="n">
         <v>10</v>
       </c>
       <c r="O90" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P90" t="n">
         <v>5</v>
       </c>
       <c r="Q90" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R90" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91">
@@ -6861,28 +6411,28 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N91" t="n">
         <v>10</v>
       </c>
       <c r="O91" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P91" t="n">
         <v>5</v>
       </c>
       <c r="Q91" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R91" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92">
@@ -6917,19 +6467,19 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
       </c>
       <c r="M92" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N92" t="n">
         <v>9</v>
       </c>
       <c r="O92" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P92" t="n">
         <v>5</v>
@@ -6973,19 +6523,19 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
       </c>
       <c r="M93" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N93" t="n">
         <v>9</v>
       </c>
       <c r="O93" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P93" t="n">
         <v>5</v>
@@ -7029,19 +6579,19 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
       </c>
       <c r="M94" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N94" t="n">
         <v>9</v>
       </c>
       <c r="O94" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P94" t="n">
         <v>5</v>
@@ -7085,19 +6635,19 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N95" t="n">
         <v>23</v>
       </c>
       <c r="O95" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P95" t="n">
         <v>12</v>
@@ -7141,19 +6691,19 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
       </c>
       <c r="M96" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N96" t="n">
         <v>23</v>
       </c>
       <c r="O96" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P96" t="n">
         <v>12</v>
@@ -7197,19 +6747,19 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
       </c>
       <c r="M97" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N97" t="n">
         <v>23</v>
       </c>
       <c r="O97" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P97" t="n">
         <v>12</v>
@@ -7253,19 +6803,19 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
       </c>
       <c r="M98" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N98" t="n">
         <v>20</v>
       </c>
       <c r="O98" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P98" t="n">
         <v>10</v>
@@ -7309,19 +6859,19 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
       </c>
       <c r="M99" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N99" t="n">
         <v>20</v>
       </c>
       <c r="O99" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P99" t="n">
         <v>10</v>
@@ -7365,19 +6915,19 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
       </c>
       <c r="M100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N100" t="n">
         <v>20</v>
       </c>
       <c r="O100" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P100" t="n">
         <v>10</v>
@@ -7421,19 +6971,19 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N101" t="n">
         <v>14</v>
       </c>
       <c r="O101" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P101" t="n">
         <v>8</v>
@@ -7477,19 +7027,19 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
       </c>
       <c r="M102" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N102" t="n">
         <v>14</v>
       </c>
       <c r="O102" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P102" t="n">
         <v>8</v>
@@ -7533,19 +7083,19 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
       </c>
       <c r="M103" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N103" t="n">
         <v>14</v>
       </c>
       <c r="O103" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P103" t="n">
         <v>8</v>
@@ -7589,19 +7139,19 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N104" t="n">
         <v>9</v>
       </c>
       <c r="O104" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P104" t="n">
         <v>5</v>
@@ -7645,19 +7195,19 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
       </c>
       <c r="M105" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N105" t="n">
         <v>9</v>
       </c>
       <c r="O105" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P105" t="n">
         <v>5</v>
@@ -7701,19 +7251,19 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
       </c>
       <c r="M106" t="s">
-        <v>42</v>
+        <v>250</v>
       </c>
       <c r="N106" t="n">
         <v>9</v>
       </c>
       <c r="O106" t="s">
-        <v>43</v>
+        <v>251</v>
       </c>
       <c r="P106" t="n">
         <v>5</v>
@@ -7757,19 +7307,19 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="N107" t="n">
         <v>23</v>
       </c>
       <c r="O107" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="P107" t="n">
         <v>12</v>
@@ -7813,19 +7363,19 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
       </c>
       <c r="M108" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N108" t="n">
         <v>23</v>
       </c>
       <c r="O108" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P108" t="n">
         <v>12</v>
@@ -7869,19 +7419,19 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
       </c>
       <c r="M109" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N109" t="n">
         <v>23</v>
       </c>
       <c r="O109" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P109" t="n">
         <v>12</v>
@@ -7925,19 +7475,19 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N110" t="n">
         <v>20</v>
       </c>
       <c r="O110" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P110" t="n">
         <v>10</v>
@@ -7981,19 +7531,19 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
       </c>
       <c r="M111" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N111" t="n">
         <v>20</v>
       </c>
       <c r="O111" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="P111" t="n">
         <v>10</v>
@@ -8037,19 +7587,19 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="N112" t="n">
         <v>20</v>
       </c>
       <c r="O112" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="P112" t="n">
         <v>10</v>
@@ -8093,19 +7643,19 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N113" t="n">
         <v>14</v>
       </c>
       <c r="O113" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="P113" t="n">
         <v>8</v>
@@ -8149,19 +7699,19 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
       </c>
       <c r="M114" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N114" t="n">
         <v>14</v>
       </c>
       <c r="O114" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="P114" t="n">
         <v>8</v>
@@ -8205,19 +7755,19 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
       </c>
       <c r="M115" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N115" t="n">
         <v>14</v>
       </c>
       <c r="O115" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="P115" t="n">
         <v>8</v>
@@ -8261,19 +7811,19 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="N116" t="n">
         <v>9</v>
       </c>
       <c r="O116" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="P116" t="n">
         <v>5</v>
@@ -8317,19 +7867,19 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
       </c>
       <c r="M117" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N117" t="n">
         <v>9</v>
       </c>
       <c r="O117" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P117" t="n">
         <v>5</v>
@@ -8373,19 +7923,19 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
       </c>
       <c r="M118" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="N118" t="n">
         <v>9</v>
       </c>
       <c r="O118" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="P118" t="n">
         <v>5</v>
@@ -8429,19 +7979,19 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="N119" t="n">
         <v>23</v>
       </c>
       <c r="O119" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P119" t="n">
         <v>12</v>
@@ -8485,19 +8035,19 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
       </c>
       <c r="M120" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="N120" t="n">
         <v>23</v>
       </c>
       <c r="O120" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="P120" t="n">
         <v>12</v>
@@ -8541,19 +8091,19 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
       </c>
       <c r="M121" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N121" t="n">
         <v>23</v>
       </c>
       <c r="O121" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="P121" t="n">
         <v>12</v>
@@ -8597,28 +8147,28 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N122" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O122" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="P122" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q122" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="R122" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="123">
@@ -8653,28 +8203,28 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N123" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O123" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="P123" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q123" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="R123" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="124">
@@ -8709,28 +8259,28 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
+        <v>288</v>
+      </c>
+      <c r="N124" t="n">
+        <v>11</v>
+      </c>
+      <c r="O124" t="s">
+        <v>289</v>
+      </c>
+      <c r="P124" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q124" t="s">
         <v>285</v>
       </c>
-      <c r="N124" t="n">
-        <v>18</v>
-      </c>
-      <c r="O124" t="s">
-        <v>286</v>
-      </c>
-      <c r="P124" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q124" t="s">
-        <v>282</v>
-      </c>
       <c r="R124" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="125">
@@ -8765,19 +8315,19 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="N125" t="n">
         <v>14</v>
       </c>
       <c r="O125" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="P125" t="n">
         <v>8</v>
@@ -8821,19 +8371,19 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
       </c>
       <c r="M126" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N126" t="n">
         <v>14</v>
       </c>
       <c r="O126" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="P126" t="n">
         <v>8</v>
@@ -8877,19 +8427,19 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
       </c>
       <c r="M127" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N127" t="n">
         <v>14</v>
       </c>
       <c r="O127" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="P127" t="n">
         <v>8</v>
@@ -8933,28 +8483,28 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="N128" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O128" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="P128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q128" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
       <c r="R128" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
     </row>
     <row r="129">
@@ -8989,28 +8539,28 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N129" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O129" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q129" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
       <c r="R129" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
     </row>
     <row r="130">
@@ -9045,28 +8595,28 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N130" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O130" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q130" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
       <c r="R130" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
     </row>
     <row r="131">
@@ -9101,19 +8651,19 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N131" t="n">
         <v>23</v>
       </c>
       <c r="O131" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P131" t="n">
         <v>12</v>
@@ -9157,19 +8707,19 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N132" t="n">
         <v>23</v>
       </c>
       <c r="O132" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P132" t="n">
         <v>12</v>
@@ -9213,19 +8763,19 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N133" t="n">
         <v>23</v>
       </c>
       <c r="O133" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P133" t="n">
         <v>12</v>
@@ -9269,28 +8819,28 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N134" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O134" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P134" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q134" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="R134" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="135">
@@ -9325,28 +8875,28 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N135" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O135" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P135" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q135" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="R135" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="136">
@@ -9381,28 +8931,28 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N136" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="O136" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="P136" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q136" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="R136" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="137">
@@ -9437,19 +8987,19 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N137" t="n">
         <v>14</v>
       </c>
       <c r="O137" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P137" t="n">
         <v>8</v>
@@ -9493,19 +9043,19 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N138" t="n">
         <v>14</v>
       </c>
       <c r="O138" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P138" t="n">
         <v>8</v>
@@ -9549,19 +9099,19 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N139" t="n">
         <v>14</v>
       </c>
       <c r="O139" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P139" t="n">
         <v>8</v>
@@ -9605,28 +9155,28 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N140" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O140" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P140" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q140" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
       <c r="R140" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
     </row>
     <row r="141">
@@ -9661,28 +9211,28 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N141" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O141" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P141" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q141" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
       <c r="R141" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
     </row>
     <row r="142">
@@ -9717,28 +9267,28 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N142" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O142" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P142" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q142" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
       <c r="R142" t="s">
-        <v>296</v>
+        <v>41</v>
       </c>
     </row>
     <row r="143">
@@ -9773,19 +9323,19 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N143" t="n">
         <v>23</v>
       </c>
       <c r="O143" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="P143" t="n">
         <v>12</v>
@@ -9829,19 +9379,19 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N144" t="n">
         <v>23</v>
       </c>
       <c r="O144" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P144" t="n">
         <v>12</v>
@@ -9885,19 +9435,19 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N145" t="n">
         <v>23</v>
       </c>
       <c r="O145" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P145" t="n">
         <v>12</v>
@@ -9907,4038 +9457,6 @@
       </c>
       <c r="R145" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>289</v>
-      </c>
-      <c r="B146" t="b">
-        <v>0</v>
-      </c>
-      <c r="C146" t="s">
-        <v>18</v>
-      </c>
-      <c r="D146" t="s">
-        <v>19</v>
-      </c>
-      <c r="E146" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" t="n">
-        <v>1</v>
-      </c>
-      <c r="H146" t="s">
-        <v>20</v>
-      </c>
-      <c r="I146" t="n">
-        <v>7</v>
-      </c>
-      <c r="J146" t="n">
-        <v>3</v>
-      </c>
-      <c r="K146" t="s">
-        <v>331</v>
-      </c>
-      <c r="L146" t="n">
-        <v>1</v>
-      </c>
-      <c r="M146" t="s">
-        <v>332</v>
-      </c>
-      <c r="N146" t="n">
-        <v>11</v>
-      </c>
-      <c r="O146" t="s">
-        <v>333</v>
-      </c>
-      <c r="P146" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q146" t="s">
-        <v>334</v>
-      </c>
-      <c r="R146" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>290</v>
-      </c>
-      <c r="B147" t="b">
-        <v>0</v>
-      </c>
-      <c r="C147" t="s">
-        <v>18</v>
-      </c>
-      <c r="D147" t="s">
-        <v>19</v>
-      </c>
-      <c r="E147" t="n">
-        <v>1</v>
-      </c>
-      <c r="F147" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" t="n">
-        <v>1</v>
-      </c>
-      <c r="H147" t="s">
-        <v>20</v>
-      </c>
-      <c r="I147" t="n">
-        <v>7</v>
-      </c>
-      <c r="J147" t="n">
-        <v>3</v>
-      </c>
-      <c r="K147" t="s">
-        <v>331</v>
-      </c>
-      <c r="L147" t="n">
-        <v>2</v>
-      </c>
-      <c r="M147" t="s">
-        <v>335</v>
-      </c>
-      <c r="N147" t="n">
-        <v>11</v>
-      </c>
-      <c r="O147" t="s">
-        <v>336</v>
-      </c>
-      <c r="P147" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q147" t="s">
-        <v>334</v>
-      </c>
-      <c r="R147" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>291</v>
-      </c>
-      <c r="B148" t="b">
-        <v>0</v>
-      </c>
-      <c r="C148" t="s">
-        <v>18</v>
-      </c>
-      <c r="D148" t="s">
-        <v>19</v>
-      </c>
-      <c r="E148" t="n">
-        <v>1</v>
-      </c>
-      <c r="F148" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" t="n">
-        <v>1</v>
-      </c>
-      <c r="H148" t="s">
-        <v>20</v>
-      </c>
-      <c r="I148" t="n">
-        <v>7</v>
-      </c>
-      <c r="J148" t="n">
-        <v>3</v>
-      </c>
-      <c r="K148" t="s">
-        <v>331</v>
-      </c>
-      <c r="L148" t="n">
-        <v>3</v>
-      </c>
-      <c r="M148" t="s">
-        <v>337</v>
-      </c>
-      <c r="N148" t="n">
-        <v>11</v>
-      </c>
-      <c r="O148" t="s">
-        <v>338</v>
-      </c>
-      <c r="P148" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q148" t="s">
-        <v>334</v>
-      </c>
-      <c r="R148" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>295</v>
-      </c>
-      <c r="B149" t="b">
-        <v>0</v>
-      </c>
-      <c r="C149" t="s">
-        <v>18</v>
-      </c>
-      <c r="D149" t="s">
-        <v>19</v>
-      </c>
-      <c r="E149" t="n">
-        <v>1</v>
-      </c>
-      <c r="F149" t="n">
-        <v>2</v>
-      </c>
-      <c r="G149" t="n">
-        <v>1</v>
-      </c>
-      <c r="H149" t="s">
-        <v>29</v>
-      </c>
-      <c r="I149" t="n">
-        <v>7</v>
-      </c>
-      <c r="J149" t="n">
-        <v>3</v>
-      </c>
-      <c r="K149" t="s">
-        <v>339</v>
-      </c>
-      <c r="L149" t="n">
-        <v>1</v>
-      </c>
-      <c r="M149" t="s">
-        <v>340</v>
-      </c>
-      <c r="N149" t="n">
-        <v>12</v>
-      </c>
-      <c r="O149" t="s">
-        <v>341</v>
-      </c>
-      <c r="P149" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q149" t="s">
-        <v>342</v>
-      </c>
-      <c r="R149" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>296</v>
-      </c>
-      <c r="B150" t="b">
-        <v>0</v>
-      </c>
-      <c r="C150" t="s">
-        <v>18</v>
-      </c>
-      <c r="D150" t="s">
-        <v>19</v>
-      </c>
-      <c r="E150" t="n">
-        <v>1</v>
-      </c>
-      <c r="F150" t="n">
-        <v>2</v>
-      </c>
-      <c r="G150" t="n">
-        <v>1</v>
-      </c>
-      <c r="H150" t="s">
-        <v>29</v>
-      </c>
-      <c r="I150" t="n">
-        <v>7</v>
-      </c>
-      <c r="J150" t="n">
-        <v>3</v>
-      </c>
-      <c r="K150" t="s">
-        <v>339</v>
-      </c>
-      <c r="L150" t="n">
-        <v>2</v>
-      </c>
-      <c r="M150" t="s">
-        <v>343</v>
-      </c>
-      <c r="N150" t="n">
-        <v>12</v>
-      </c>
-      <c r="O150" t="s">
-        <v>344</v>
-      </c>
-      <c r="P150" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q150" t="s">
-        <v>342</v>
-      </c>
-      <c r="R150" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>297</v>
-      </c>
-      <c r="B151" t="b">
-        <v>0</v>
-      </c>
-      <c r="C151" t="s">
-        <v>18</v>
-      </c>
-      <c r="D151" t="s">
-        <v>19</v>
-      </c>
-      <c r="E151" t="n">
-        <v>1</v>
-      </c>
-      <c r="F151" t="n">
-        <v>2</v>
-      </c>
-      <c r="G151" t="n">
-        <v>1</v>
-      </c>
-      <c r="H151" t="s">
-        <v>29</v>
-      </c>
-      <c r="I151" t="n">
-        <v>7</v>
-      </c>
-      <c r="J151" t="n">
-        <v>3</v>
-      </c>
-      <c r="K151" t="s">
-        <v>339</v>
-      </c>
-      <c r="L151" t="n">
-        <v>3</v>
-      </c>
-      <c r="M151" t="s">
-        <v>345</v>
-      </c>
-      <c r="N151" t="n">
-        <v>12</v>
-      </c>
-      <c r="O151" t="s">
-        <v>346</v>
-      </c>
-      <c r="P151" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q151" t="s">
-        <v>342</v>
-      </c>
-      <c r="R151" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>301</v>
-      </c>
-      <c r="B152" t="b">
-        <v>0</v>
-      </c>
-      <c r="C152" t="s">
-        <v>18</v>
-      </c>
-      <c r="D152" t="s">
-        <v>19</v>
-      </c>
-      <c r="E152" t="n">
-        <v>2</v>
-      </c>
-      <c r="F152" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" t="n">
-        <v>1</v>
-      </c>
-      <c r="H152" t="s">
-        <v>38</v>
-      </c>
-      <c r="I152" t="n">
-        <v>7</v>
-      </c>
-      <c r="J152" t="n">
-        <v>3</v>
-      </c>
-      <c r="K152" t="s">
-        <v>331</v>
-      </c>
-      <c r="L152" t="n">
-        <v>1</v>
-      </c>
-      <c r="M152" t="s">
-        <v>347</v>
-      </c>
-      <c r="N152" t="n">
-        <v>9</v>
-      </c>
-      <c r="O152" t="s">
-        <v>348</v>
-      </c>
-      <c r="P152" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q152" t="s">
-        <v>41</v>
-      </c>
-      <c r="R152" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>302</v>
-      </c>
-      <c r="B153" t="b">
-        <v>0</v>
-      </c>
-      <c r="C153" t="s">
-        <v>18</v>
-      </c>
-      <c r="D153" t="s">
-        <v>19</v>
-      </c>
-      <c r="E153" t="n">
-        <v>2</v>
-      </c>
-      <c r="F153" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" t="n">
-        <v>1</v>
-      </c>
-      <c r="H153" t="s">
-        <v>38</v>
-      </c>
-      <c r="I153" t="n">
-        <v>7</v>
-      </c>
-      <c r="J153" t="n">
-        <v>3</v>
-      </c>
-      <c r="K153" t="s">
-        <v>331</v>
-      </c>
-      <c r="L153" t="n">
-        <v>2</v>
-      </c>
-      <c r="M153" t="s">
-        <v>349</v>
-      </c>
-      <c r="N153" t="n">
-        <v>9</v>
-      </c>
-      <c r="O153" t="s">
-        <v>350</v>
-      </c>
-      <c r="P153" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q153" t="s">
-        <v>41</v>
-      </c>
-      <c r="R153" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>303</v>
-      </c>
-      <c r="B154" t="b">
-        <v>0</v>
-      </c>
-      <c r="C154" t="s">
-        <v>18</v>
-      </c>
-      <c r="D154" t="s">
-        <v>19</v>
-      </c>
-      <c r="E154" t="n">
-        <v>2</v>
-      </c>
-      <c r="F154" t="n">
-        <v>1</v>
-      </c>
-      <c r="G154" t="n">
-        <v>1</v>
-      </c>
-      <c r="H154" t="s">
-        <v>38</v>
-      </c>
-      <c r="I154" t="n">
-        <v>7</v>
-      </c>
-      <c r="J154" t="n">
-        <v>3</v>
-      </c>
-      <c r="K154" t="s">
-        <v>331</v>
-      </c>
-      <c r="L154" t="n">
-        <v>3</v>
-      </c>
-      <c r="M154" t="s">
-        <v>351</v>
-      </c>
-      <c r="N154" t="n">
-        <v>9</v>
-      </c>
-      <c r="O154" t="s">
-        <v>352</v>
-      </c>
-      <c r="P154" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q154" t="s">
-        <v>41</v>
-      </c>
-      <c r="R154" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>307</v>
-      </c>
-      <c r="B155" t="b">
-        <v>0</v>
-      </c>
-      <c r="C155" t="s">
-        <v>18</v>
-      </c>
-      <c r="D155" t="s">
-        <v>19</v>
-      </c>
-      <c r="E155" t="n">
-        <v>2</v>
-      </c>
-      <c r="F155" t="n">
-        <v>2</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1</v>
-      </c>
-      <c r="H155" t="s">
-        <v>46</v>
-      </c>
-      <c r="I155" t="n">
-        <v>7</v>
-      </c>
-      <c r="J155" t="n">
-        <v>3</v>
-      </c>
-      <c r="K155" t="s">
-        <v>339</v>
-      </c>
-      <c r="L155" t="n">
-        <v>1</v>
-      </c>
-      <c r="M155" t="s">
-        <v>353</v>
-      </c>
-      <c r="N155" t="n">
-        <v>10</v>
-      </c>
-      <c r="O155" t="s">
-        <v>354</v>
-      </c>
-      <c r="P155" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q155" t="s">
-        <v>355</v>
-      </c>
-      <c r="R155" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>308</v>
-      </c>
-      <c r="B156" t="b">
-        <v>0</v>
-      </c>
-      <c r="C156" t="s">
-        <v>18</v>
-      </c>
-      <c r="D156" t="s">
-        <v>19</v>
-      </c>
-      <c r="E156" t="n">
-        <v>2</v>
-      </c>
-      <c r="F156" t="n">
-        <v>2</v>
-      </c>
-      <c r="G156" t="n">
-        <v>1</v>
-      </c>
-      <c r="H156" t="s">
-        <v>46</v>
-      </c>
-      <c r="I156" t="n">
-        <v>7</v>
-      </c>
-      <c r="J156" t="n">
-        <v>3</v>
-      </c>
-      <c r="K156" t="s">
-        <v>339</v>
-      </c>
-      <c r="L156" t="n">
-        <v>2</v>
-      </c>
-      <c r="M156" t="s">
-        <v>356</v>
-      </c>
-      <c r="N156" t="n">
-        <v>10</v>
-      </c>
-      <c r="O156" t="s">
-        <v>357</v>
-      </c>
-      <c r="P156" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q156" t="s">
-        <v>355</v>
-      </c>
-      <c r="R156" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>309</v>
-      </c>
-      <c r="B157" t="b">
-        <v>0</v>
-      </c>
-      <c r="C157" t="s">
-        <v>18</v>
-      </c>
-      <c r="D157" t="s">
-        <v>19</v>
-      </c>
-      <c r="E157" t="n">
-        <v>2</v>
-      </c>
-      <c r="F157" t="n">
-        <v>2</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1</v>
-      </c>
-      <c r="H157" t="s">
-        <v>46</v>
-      </c>
-      <c r="I157" t="n">
-        <v>7</v>
-      </c>
-      <c r="J157" t="n">
-        <v>3</v>
-      </c>
-      <c r="K157" t="s">
-        <v>339</v>
-      </c>
-      <c r="L157" t="n">
-        <v>3</v>
-      </c>
-      <c r="M157" t="s">
-        <v>358</v>
-      </c>
-      <c r="N157" t="n">
-        <v>10</v>
-      </c>
-      <c r="O157" t="s">
-        <v>359</v>
-      </c>
-      <c r="P157" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q157" t="s">
-        <v>355</v>
-      </c>
-      <c r="R157" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>313</v>
-      </c>
-      <c r="B158" t="b">
-        <v>0</v>
-      </c>
-      <c r="C158" t="s">
-        <v>18</v>
-      </c>
-      <c r="D158" t="s">
-        <v>19</v>
-      </c>
-      <c r="E158" t="n">
-        <v>1</v>
-      </c>
-      <c r="F158" t="n">
-        <v>1</v>
-      </c>
-      <c r="G158" t="n">
-        <v>2</v>
-      </c>
-      <c r="H158" t="s">
-        <v>54</v>
-      </c>
-      <c r="I158" t="n">
-        <v>7</v>
-      </c>
-      <c r="J158" t="n">
-        <v>3</v>
-      </c>
-      <c r="K158" t="s">
-        <v>331</v>
-      </c>
-      <c r="L158" t="n">
-        <v>1</v>
-      </c>
-      <c r="M158" t="s">
-        <v>360</v>
-      </c>
-      <c r="N158" t="n">
-        <v>11</v>
-      </c>
-      <c r="O158" t="s">
-        <v>361</v>
-      </c>
-      <c r="P158" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q158" t="s">
-        <v>334</v>
-      </c>
-      <c r="R158" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>314</v>
-      </c>
-      <c r="B159" t="b">
-        <v>0</v>
-      </c>
-      <c r="C159" t="s">
-        <v>18</v>
-      </c>
-      <c r="D159" t="s">
-        <v>19</v>
-      </c>
-      <c r="E159" t="n">
-        <v>1</v>
-      </c>
-      <c r="F159" t="n">
-        <v>1</v>
-      </c>
-      <c r="G159" t="n">
-        <v>2</v>
-      </c>
-      <c r="H159" t="s">
-        <v>54</v>
-      </c>
-      <c r="I159" t="n">
-        <v>7</v>
-      </c>
-      <c r="J159" t="n">
-        <v>3</v>
-      </c>
-      <c r="K159" t="s">
-        <v>331</v>
-      </c>
-      <c r="L159" t="n">
-        <v>2</v>
-      </c>
-      <c r="M159" t="s">
-        <v>362</v>
-      </c>
-      <c r="N159" t="n">
-        <v>11</v>
-      </c>
-      <c r="O159" t="s">
-        <v>363</v>
-      </c>
-      <c r="P159" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q159" t="s">
-        <v>334</v>
-      </c>
-      <c r="R159" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>315</v>
-      </c>
-      <c r="B160" t="b">
-        <v>0</v>
-      </c>
-      <c r="C160" t="s">
-        <v>18</v>
-      </c>
-      <c r="D160" t="s">
-        <v>19</v>
-      </c>
-      <c r="E160" t="n">
-        <v>1</v>
-      </c>
-      <c r="F160" t="n">
-        <v>1</v>
-      </c>
-      <c r="G160" t="n">
-        <v>2</v>
-      </c>
-      <c r="H160" t="s">
-        <v>54</v>
-      </c>
-      <c r="I160" t="n">
-        <v>7</v>
-      </c>
-      <c r="J160" t="n">
-        <v>3</v>
-      </c>
-      <c r="K160" t="s">
-        <v>331</v>
-      </c>
-      <c r="L160" t="n">
-        <v>3</v>
-      </c>
-      <c r="M160" t="s">
-        <v>364</v>
-      </c>
-      <c r="N160" t="n">
-        <v>11</v>
-      </c>
-      <c r="O160" t="s">
-        <v>365</v>
-      </c>
-      <c r="P160" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q160" t="s">
-        <v>334</v>
-      </c>
-      <c r="R160" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>319</v>
-      </c>
-      <c r="B161" t="b">
-        <v>0</v>
-      </c>
-      <c r="C161" t="s">
-        <v>18</v>
-      </c>
-      <c r="D161" t="s">
-        <v>19</v>
-      </c>
-      <c r="E161" t="n">
-        <v>1</v>
-      </c>
-      <c r="F161" t="n">
-        <v>2</v>
-      </c>
-      <c r="G161" t="n">
-        <v>2</v>
-      </c>
-      <c r="H161" t="s">
-        <v>61</v>
-      </c>
-      <c r="I161" t="n">
-        <v>7</v>
-      </c>
-      <c r="J161" t="n">
-        <v>3</v>
-      </c>
-      <c r="K161" t="s">
-        <v>339</v>
-      </c>
-      <c r="L161" t="n">
-        <v>1</v>
-      </c>
-      <c r="M161" t="s">
-        <v>366</v>
-      </c>
-      <c r="N161" t="n">
-        <v>12</v>
-      </c>
-      <c r="O161" t="s">
-        <v>367</v>
-      </c>
-      <c r="P161" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q161" t="s">
-        <v>342</v>
-      </c>
-      <c r="R161" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>320</v>
-      </c>
-      <c r="B162" t="b">
-        <v>0</v>
-      </c>
-      <c r="C162" t="s">
-        <v>18</v>
-      </c>
-      <c r="D162" t="s">
-        <v>19</v>
-      </c>
-      <c r="E162" t="n">
-        <v>1</v>
-      </c>
-      <c r="F162" t="n">
-        <v>2</v>
-      </c>
-      <c r="G162" t="n">
-        <v>2</v>
-      </c>
-      <c r="H162" t="s">
-        <v>61</v>
-      </c>
-      <c r="I162" t="n">
-        <v>7</v>
-      </c>
-      <c r="J162" t="n">
-        <v>3</v>
-      </c>
-      <c r="K162" t="s">
-        <v>339</v>
-      </c>
-      <c r="L162" t="n">
-        <v>2</v>
-      </c>
-      <c r="M162" t="s">
-        <v>368</v>
-      </c>
-      <c r="N162" t="n">
-        <v>12</v>
-      </c>
-      <c r="O162" t="s">
-        <v>369</v>
-      </c>
-      <c r="P162" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q162" t="s">
-        <v>342</v>
-      </c>
-      <c r="R162" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>321</v>
-      </c>
-      <c r="B163" t="b">
-        <v>0</v>
-      </c>
-      <c r="C163" t="s">
-        <v>18</v>
-      </c>
-      <c r="D163" t="s">
-        <v>19</v>
-      </c>
-      <c r="E163" t="n">
-        <v>1</v>
-      </c>
-      <c r="F163" t="n">
-        <v>2</v>
-      </c>
-      <c r="G163" t="n">
-        <v>2</v>
-      </c>
-      <c r="H163" t="s">
-        <v>61</v>
-      </c>
-      <c r="I163" t="n">
-        <v>7</v>
-      </c>
-      <c r="J163" t="n">
-        <v>3</v>
-      </c>
-      <c r="K163" t="s">
-        <v>339</v>
-      </c>
-      <c r="L163" t="n">
-        <v>3</v>
-      </c>
-      <c r="M163" t="s">
-        <v>370</v>
-      </c>
-      <c r="N163" t="n">
-        <v>12</v>
-      </c>
-      <c r="O163" t="s">
-        <v>371</v>
-      </c>
-      <c r="P163" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q163" t="s">
-        <v>342</v>
-      </c>
-      <c r="R163" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>325</v>
-      </c>
-      <c r="B164" t="b">
-        <v>0</v>
-      </c>
-      <c r="C164" t="s">
-        <v>18</v>
-      </c>
-      <c r="D164" t="s">
-        <v>19</v>
-      </c>
-      <c r="E164" t="n">
-        <v>2</v>
-      </c>
-      <c r="F164" t="n">
-        <v>1</v>
-      </c>
-      <c r="G164" t="n">
-        <v>2</v>
-      </c>
-      <c r="H164" t="s">
-        <v>68</v>
-      </c>
-      <c r="I164" t="n">
-        <v>7</v>
-      </c>
-      <c r="J164" t="n">
-        <v>3</v>
-      </c>
-      <c r="K164" t="s">
-        <v>331</v>
-      </c>
-      <c r="L164" t="n">
-        <v>1</v>
-      </c>
-      <c r="M164" t="s">
-        <v>372</v>
-      </c>
-      <c r="N164" t="n">
-        <v>9</v>
-      </c>
-      <c r="O164" t="s">
-        <v>373</v>
-      </c>
-      <c r="P164" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q164" t="s">
-        <v>41</v>
-      </c>
-      <c r="R164" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>326</v>
-      </c>
-      <c r="B165" t="b">
-        <v>0</v>
-      </c>
-      <c r="C165" t="s">
-        <v>18</v>
-      </c>
-      <c r="D165" t="s">
-        <v>19</v>
-      </c>
-      <c r="E165" t="n">
-        <v>2</v>
-      </c>
-      <c r="F165" t="n">
-        <v>1</v>
-      </c>
-      <c r="G165" t="n">
-        <v>2</v>
-      </c>
-      <c r="H165" t="s">
-        <v>68</v>
-      </c>
-      <c r="I165" t="n">
-        <v>7</v>
-      </c>
-      <c r="J165" t="n">
-        <v>3</v>
-      </c>
-      <c r="K165" t="s">
-        <v>331</v>
-      </c>
-      <c r="L165" t="n">
-        <v>2</v>
-      </c>
-      <c r="M165" t="s">
-        <v>374</v>
-      </c>
-      <c r="N165" t="n">
-        <v>9</v>
-      </c>
-      <c r="O165" t="s">
-        <v>375</v>
-      </c>
-      <c r="P165" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q165" t="s">
-        <v>41</v>
-      </c>
-      <c r="R165" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>327</v>
-      </c>
-      <c r="B166" t="b">
-        <v>0</v>
-      </c>
-      <c r="C166" t="s">
-        <v>18</v>
-      </c>
-      <c r="D166" t="s">
-        <v>19</v>
-      </c>
-      <c r="E166" t="n">
-        <v>2</v>
-      </c>
-      <c r="F166" t="n">
-        <v>1</v>
-      </c>
-      <c r="G166" t="n">
-        <v>2</v>
-      </c>
-      <c r="H166" t="s">
-        <v>68</v>
-      </c>
-      <c r="I166" t="n">
-        <v>7</v>
-      </c>
-      <c r="J166" t="n">
-        <v>3</v>
-      </c>
-      <c r="K166" t="s">
-        <v>331</v>
-      </c>
-      <c r="L166" t="n">
-        <v>3</v>
-      </c>
-      <c r="M166" t="s">
-        <v>376</v>
-      </c>
-      <c r="N166" t="n">
-        <v>9</v>
-      </c>
-      <c r="O166" t="s">
-        <v>377</v>
-      </c>
-      <c r="P166" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q166" t="s">
-        <v>41</v>
-      </c>
-      <c r="R166" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>331</v>
-      </c>
-      <c r="B167" t="b">
-        <v>0</v>
-      </c>
-      <c r="C167" t="s">
-        <v>18</v>
-      </c>
-      <c r="D167" t="s">
-        <v>19</v>
-      </c>
-      <c r="E167" t="n">
-        <v>2</v>
-      </c>
-      <c r="F167" t="n">
-        <v>2</v>
-      </c>
-      <c r="G167" t="n">
-        <v>2</v>
-      </c>
-      <c r="H167" t="s">
-        <v>75</v>
-      </c>
-      <c r="I167" t="n">
-        <v>7</v>
-      </c>
-      <c r="J167" t="n">
-        <v>3</v>
-      </c>
-      <c r="K167" t="s">
-        <v>339</v>
-      </c>
-      <c r="L167" t="n">
-        <v>1</v>
-      </c>
-      <c r="M167" t="s">
-        <v>378</v>
-      </c>
-      <c r="N167" t="n">
-        <v>10</v>
-      </c>
-      <c r="O167" t="s">
-        <v>379</v>
-      </c>
-      <c r="P167" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q167" t="s">
-        <v>355</v>
-      </c>
-      <c r="R167" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>332</v>
-      </c>
-      <c r="B168" t="b">
-        <v>0</v>
-      </c>
-      <c r="C168" t="s">
-        <v>18</v>
-      </c>
-      <c r="D168" t="s">
-        <v>19</v>
-      </c>
-      <c r="E168" t="n">
-        <v>2</v>
-      </c>
-      <c r="F168" t="n">
-        <v>2</v>
-      </c>
-      <c r="G168" t="n">
-        <v>2</v>
-      </c>
-      <c r="H168" t="s">
-        <v>75</v>
-      </c>
-      <c r="I168" t="n">
-        <v>7</v>
-      </c>
-      <c r="J168" t="n">
-        <v>3</v>
-      </c>
-      <c r="K168" t="s">
-        <v>339</v>
-      </c>
-      <c r="L168" t="n">
-        <v>2</v>
-      </c>
-      <c r="M168" t="s">
-        <v>380</v>
-      </c>
-      <c r="N168" t="n">
-        <v>10</v>
-      </c>
-      <c r="O168" t="s">
-        <v>381</v>
-      </c>
-      <c r="P168" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q168" t="s">
-        <v>355</v>
-      </c>
-      <c r="R168" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>333</v>
-      </c>
-      <c r="B169" t="b">
-        <v>0</v>
-      </c>
-      <c r="C169" t="s">
-        <v>18</v>
-      </c>
-      <c r="D169" t="s">
-        <v>19</v>
-      </c>
-      <c r="E169" t="n">
-        <v>2</v>
-      </c>
-      <c r="F169" t="n">
-        <v>2</v>
-      </c>
-      <c r="G169" t="n">
-        <v>2</v>
-      </c>
-      <c r="H169" t="s">
-        <v>75</v>
-      </c>
-      <c r="I169" t="n">
-        <v>7</v>
-      </c>
-      <c r="J169" t="n">
-        <v>3</v>
-      </c>
-      <c r="K169" t="s">
-        <v>339</v>
-      </c>
-      <c r="L169" t="n">
-        <v>3</v>
-      </c>
-      <c r="M169" t="s">
-        <v>382</v>
-      </c>
-      <c r="N169" t="n">
-        <v>10</v>
-      </c>
-      <c r="O169" t="s">
-        <v>383</v>
-      </c>
-      <c r="P169" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q169" t="s">
-        <v>355</v>
-      </c>
-      <c r="R169" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>337</v>
-      </c>
-      <c r="B170" t="b">
-        <v>0</v>
-      </c>
-      <c r="C170" t="s">
-        <v>18</v>
-      </c>
-      <c r="D170" t="s">
-        <v>19</v>
-      </c>
-      <c r="E170" t="n">
-        <v>1</v>
-      </c>
-      <c r="F170" t="n">
-        <v>1</v>
-      </c>
-      <c r="G170" t="n">
-        <v>1</v>
-      </c>
-      <c r="H170" t="s">
-        <v>20</v>
-      </c>
-      <c r="I170" t="n">
-        <v>8</v>
-      </c>
-      <c r="J170" t="n">
-        <v>3</v>
-      </c>
-      <c r="K170" t="s">
-        <v>384</v>
-      </c>
-      <c r="L170" t="n">
-        <v>1</v>
-      </c>
-      <c r="M170" t="s">
-        <v>385</v>
-      </c>
-      <c r="N170" t="n">
-        <v>11</v>
-      </c>
-      <c r="O170" t="s">
-        <v>386</v>
-      </c>
-      <c r="P170" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q170" t="s">
-        <v>334</v>
-      </c>
-      <c r="R170" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>338</v>
-      </c>
-      <c r="B171" t="b">
-        <v>0</v>
-      </c>
-      <c r="C171" t="s">
-        <v>18</v>
-      </c>
-      <c r="D171" t="s">
-        <v>19</v>
-      </c>
-      <c r="E171" t="n">
-        <v>1</v>
-      </c>
-      <c r="F171" t="n">
-        <v>1</v>
-      </c>
-      <c r="G171" t="n">
-        <v>1</v>
-      </c>
-      <c r="H171" t="s">
-        <v>20</v>
-      </c>
-      <c r="I171" t="n">
-        <v>8</v>
-      </c>
-      <c r="J171" t="n">
-        <v>3</v>
-      </c>
-      <c r="K171" t="s">
-        <v>384</v>
-      </c>
-      <c r="L171" t="n">
-        <v>2</v>
-      </c>
-      <c r="M171" t="s">
-        <v>387</v>
-      </c>
-      <c r="N171" t="n">
-        <v>11</v>
-      </c>
-      <c r="O171" t="s">
-        <v>388</v>
-      </c>
-      <c r="P171" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q171" t="s">
-        <v>334</v>
-      </c>
-      <c r="R171" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>339</v>
-      </c>
-      <c r="B172" t="b">
-        <v>0</v>
-      </c>
-      <c r="C172" t="s">
-        <v>18</v>
-      </c>
-      <c r="D172" t="s">
-        <v>19</v>
-      </c>
-      <c r="E172" t="n">
-        <v>1</v>
-      </c>
-      <c r="F172" t="n">
-        <v>1</v>
-      </c>
-      <c r="G172" t="n">
-        <v>1</v>
-      </c>
-      <c r="H172" t="s">
-        <v>20</v>
-      </c>
-      <c r="I172" t="n">
-        <v>8</v>
-      </c>
-      <c r="J172" t="n">
-        <v>3</v>
-      </c>
-      <c r="K172" t="s">
-        <v>384</v>
-      </c>
-      <c r="L172" t="n">
-        <v>3</v>
-      </c>
-      <c r="M172" t="s">
-        <v>389</v>
-      </c>
-      <c r="N172" t="n">
-        <v>11</v>
-      </c>
-      <c r="O172" t="s">
-        <v>390</v>
-      </c>
-      <c r="P172" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q172" t="s">
-        <v>334</v>
-      </c>
-      <c r="R172" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>343</v>
-      </c>
-      <c r="B173" t="b">
-        <v>0</v>
-      </c>
-      <c r="C173" t="s">
-        <v>18</v>
-      </c>
-      <c r="D173" t="s">
-        <v>19</v>
-      </c>
-      <c r="E173" t="n">
-        <v>1</v>
-      </c>
-      <c r="F173" t="n">
-        <v>2</v>
-      </c>
-      <c r="G173" t="n">
-        <v>1</v>
-      </c>
-      <c r="H173" t="s">
-        <v>29</v>
-      </c>
-      <c r="I173" t="n">
-        <v>8</v>
-      </c>
-      <c r="J173" t="n">
-        <v>3</v>
-      </c>
-      <c r="K173" t="s">
-        <v>339</v>
-      </c>
-      <c r="L173" t="n">
-        <v>1</v>
-      </c>
-      <c r="M173" t="s">
-        <v>391</v>
-      </c>
-      <c r="N173" t="n">
-        <v>12</v>
-      </c>
-      <c r="O173" t="s">
-        <v>392</v>
-      </c>
-      <c r="P173" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q173" t="s">
-        <v>342</v>
-      </c>
-      <c r="R173" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>344</v>
-      </c>
-      <c r="B174" t="b">
-        <v>0</v>
-      </c>
-      <c r="C174" t="s">
-        <v>18</v>
-      </c>
-      <c r="D174" t="s">
-        <v>19</v>
-      </c>
-      <c r="E174" t="n">
-        <v>1</v>
-      </c>
-      <c r="F174" t="n">
-        <v>2</v>
-      </c>
-      <c r="G174" t="n">
-        <v>1</v>
-      </c>
-      <c r="H174" t="s">
-        <v>29</v>
-      </c>
-      <c r="I174" t="n">
-        <v>8</v>
-      </c>
-      <c r="J174" t="n">
-        <v>3</v>
-      </c>
-      <c r="K174" t="s">
-        <v>339</v>
-      </c>
-      <c r="L174" t="n">
-        <v>2</v>
-      </c>
-      <c r="M174" t="s">
-        <v>393</v>
-      </c>
-      <c r="N174" t="n">
-        <v>12</v>
-      </c>
-      <c r="O174" t="s">
-        <v>394</v>
-      </c>
-      <c r="P174" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q174" t="s">
-        <v>342</v>
-      </c>
-      <c r="R174" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>345</v>
-      </c>
-      <c r="B175" t="b">
-        <v>0</v>
-      </c>
-      <c r="C175" t="s">
-        <v>18</v>
-      </c>
-      <c r="D175" t="s">
-        <v>19</v>
-      </c>
-      <c r="E175" t="n">
-        <v>1</v>
-      </c>
-      <c r="F175" t="n">
-        <v>2</v>
-      </c>
-      <c r="G175" t="n">
-        <v>1</v>
-      </c>
-      <c r="H175" t="s">
-        <v>29</v>
-      </c>
-      <c r="I175" t="n">
-        <v>8</v>
-      </c>
-      <c r="J175" t="n">
-        <v>3</v>
-      </c>
-      <c r="K175" t="s">
-        <v>339</v>
-      </c>
-      <c r="L175" t="n">
-        <v>3</v>
-      </c>
-      <c r="M175" t="s">
-        <v>395</v>
-      </c>
-      <c r="N175" t="n">
-        <v>12</v>
-      </c>
-      <c r="O175" t="s">
-        <v>396</v>
-      </c>
-      <c r="P175" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q175" t="s">
-        <v>342</v>
-      </c>
-      <c r="R175" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>349</v>
-      </c>
-      <c r="B176" t="b">
-        <v>0</v>
-      </c>
-      <c r="C176" t="s">
-        <v>18</v>
-      </c>
-      <c r="D176" t="s">
-        <v>19</v>
-      </c>
-      <c r="E176" t="n">
-        <v>2</v>
-      </c>
-      <c r="F176" t="n">
-        <v>1</v>
-      </c>
-      <c r="G176" t="n">
-        <v>1</v>
-      </c>
-      <c r="H176" t="s">
-        <v>38</v>
-      </c>
-      <c r="I176" t="n">
-        <v>8</v>
-      </c>
-      <c r="J176" t="n">
-        <v>3</v>
-      </c>
-      <c r="K176" t="s">
-        <v>384</v>
-      </c>
-      <c r="L176" t="n">
-        <v>1</v>
-      </c>
-      <c r="M176" t="s">
-        <v>397</v>
-      </c>
-      <c r="N176" t="n">
-        <v>9</v>
-      </c>
-      <c r="O176" t="s">
-        <v>398</v>
-      </c>
-      <c r="P176" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q176" t="s">
-        <v>41</v>
-      </c>
-      <c r="R176" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>350</v>
-      </c>
-      <c r="B177" t="b">
-        <v>0</v>
-      </c>
-      <c r="C177" t="s">
-        <v>18</v>
-      </c>
-      <c r="D177" t="s">
-        <v>19</v>
-      </c>
-      <c r="E177" t="n">
-        <v>2</v>
-      </c>
-      <c r="F177" t="n">
-        <v>1</v>
-      </c>
-      <c r="G177" t="n">
-        <v>1</v>
-      </c>
-      <c r="H177" t="s">
-        <v>38</v>
-      </c>
-      <c r="I177" t="n">
-        <v>8</v>
-      </c>
-      <c r="J177" t="n">
-        <v>3</v>
-      </c>
-      <c r="K177" t="s">
-        <v>384</v>
-      </c>
-      <c r="L177" t="n">
-        <v>2</v>
-      </c>
-      <c r="M177" t="s">
-        <v>399</v>
-      </c>
-      <c r="N177" t="n">
-        <v>9</v>
-      </c>
-      <c r="O177" t="s">
-        <v>400</v>
-      </c>
-      <c r="P177" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q177" t="s">
-        <v>41</v>
-      </c>
-      <c r="R177" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>351</v>
-      </c>
-      <c r="B178" t="b">
-        <v>0</v>
-      </c>
-      <c r="C178" t="s">
-        <v>18</v>
-      </c>
-      <c r="D178" t="s">
-        <v>19</v>
-      </c>
-      <c r="E178" t="n">
-        <v>2</v>
-      </c>
-      <c r="F178" t="n">
-        <v>1</v>
-      </c>
-      <c r="G178" t="n">
-        <v>1</v>
-      </c>
-      <c r="H178" t="s">
-        <v>38</v>
-      </c>
-      <c r="I178" t="n">
-        <v>8</v>
-      </c>
-      <c r="J178" t="n">
-        <v>3</v>
-      </c>
-      <c r="K178" t="s">
-        <v>384</v>
-      </c>
-      <c r="L178" t="n">
-        <v>3</v>
-      </c>
-      <c r="M178" t="s">
-        <v>401</v>
-      </c>
-      <c r="N178" t="n">
-        <v>9</v>
-      </c>
-      <c r="O178" t="s">
-        <v>402</v>
-      </c>
-      <c r="P178" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q178" t="s">
-        <v>41</v>
-      </c>
-      <c r="R178" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>355</v>
-      </c>
-      <c r="B179" t="b">
-        <v>0</v>
-      </c>
-      <c r="C179" t="s">
-        <v>18</v>
-      </c>
-      <c r="D179" t="s">
-        <v>19</v>
-      </c>
-      <c r="E179" t="n">
-        <v>2</v>
-      </c>
-      <c r="F179" t="n">
-        <v>2</v>
-      </c>
-      <c r="G179" t="n">
-        <v>1</v>
-      </c>
-      <c r="H179" t="s">
-        <v>46</v>
-      </c>
-      <c r="I179" t="n">
-        <v>8</v>
-      </c>
-      <c r="J179" t="n">
-        <v>3</v>
-      </c>
-      <c r="K179" t="s">
-        <v>339</v>
-      </c>
-      <c r="L179" t="n">
-        <v>1</v>
-      </c>
-      <c r="M179" t="s">
-        <v>403</v>
-      </c>
-      <c r="N179" t="n">
-        <v>10</v>
-      </c>
-      <c r="O179" t="s">
-        <v>404</v>
-      </c>
-      <c r="P179" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q179" t="s">
-        <v>355</v>
-      </c>
-      <c r="R179" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>356</v>
-      </c>
-      <c r="B180" t="b">
-        <v>0</v>
-      </c>
-      <c r="C180" t="s">
-        <v>18</v>
-      </c>
-      <c r="D180" t="s">
-        <v>19</v>
-      </c>
-      <c r="E180" t="n">
-        <v>2</v>
-      </c>
-      <c r="F180" t="n">
-        <v>2</v>
-      </c>
-      <c r="G180" t="n">
-        <v>1</v>
-      </c>
-      <c r="H180" t="s">
-        <v>46</v>
-      </c>
-      <c r="I180" t="n">
-        <v>8</v>
-      </c>
-      <c r="J180" t="n">
-        <v>3</v>
-      </c>
-      <c r="K180" t="s">
-        <v>339</v>
-      </c>
-      <c r="L180" t="n">
-        <v>2</v>
-      </c>
-      <c r="M180" t="s">
-        <v>405</v>
-      </c>
-      <c r="N180" t="n">
-        <v>10</v>
-      </c>
-      <c r="O180" t="s">
-        <v>406</v>
-      </c>
-      <c r="P180" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q180" t="s">
-        <v>355</v>
-      </c>
-      <c r="R180" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>357</v>
-      </c>
-      <c r="B181" t="b">
-        <v>0</v>
-      </c>
-      <c r="C181" t="s">
-        <v>18</v>
-      </c>
-      <c r="D181" t="s">
-        <v>19</v>
-      </c>
-      <c r="E181" t="n">
-        <v>2</v>
-      </c>
-      <c r="F181" t="n">
-        <v>2</v>
-      </c>
-      <c r="G181" t="n">
-        <v>1</v>
-      </c>
-      <c r="H181" t="s">
-        <v>46</v>
-      </c>
-      <c r="I181" t="n">
-        <v>8</v>
-      </c>
-      <c r="J181" t="n">
-        <v>3</v>
-      </c>
-      <c r="K181" t="s">
-        <v>339</v>
-      </c>
-      <c r="L181" t="n">
-        <v>3</v>
-      </c>
-      <c r="M181" t="s">
-        <v>407</v>
-      </c>
-      <c r="N181" t="n">
-        <v>10</v>
-      </c>
-      <c r="O181" t="s">
-        <v>408</v>
-      </c>
-      <c r="P181" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q181" t="s">
-        <v>355</v>
-      </c>
-      <c r="R181" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>361</v>
-      </c>
-      <c r="B182" t="b">
-        <v>0</v>
-      </c>
-      <c r="C182" t="s">
-        <v>18</v>
-      </c>
-      <c r="D182" t="s">
-        <v>19</v>
-      </c>
-      <c r="E182" t="n">
-        <v>1</v>
-      </c>
-      <c r="F182" t="n">
-        <v>1</v>
-      </c>
-      <c r="G182" t="n">
-        <v>2</v>
-      </c>
-      <c r="H182" t="s">
-        <v>54</v>
-      </c>
-      <c r="I182" t="n">
-        <v>8</v>
-      </c>
-      <c r="J182" t="n">
-        <v>3</v>
-      </c>
-      <c r="K182" t="s">
-        <v>384</v>
-      </c>
-      <c r="L182" t="n">
-        <v>1</v>
-      </c>
-      <c r="M182" t="s">
-        <v>409</v>
-      </c>
-      <c r="N182" t="n">
-        <v>11</v>
-      </c>
-      <c r="O182" t="s">
-        <v>410</v>
-      </c>
-      <c r="P182" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q182" t="s">
-        <v>334</v>
-      </c>
-      <c r="R182" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>362</v>
-      </c>
-      <c r="B183" t="b">
-        <v>0</v>
-      </c>
-      <c r="C183" t="s">
-        <v>18</v>
-      </c>
-      <c r="D183" t="s">
-        <v>19</v>
-      </c>
-      <c r="E183" t="n">
-        <v>1</v>
-      </c>
-      <c r="F183" t="n">
-        <v>1</v>
-      </c>
-      <c r="G183" t="n">
-        <v>2</v>
-      </c>
-      <c r="H183" t="s">
-        <v>54</v>
-      </c>
-      <c r="I183" t="n">
-        <v>8</v>
-      </c>
-      <c r="J183" t="n">
-        <v>3</v>
-      </c>
-      <c r="K183" t="s">
-        <v>384</v>
-      </c>
-      <c r="L183" t="n">
-        <v>2</v>
-      </c>
-      <c r="M183" t="s">
-        <v>411</v>
-      </c>
-      <c r="N183" t="n">
-        <v>11</v>
-      </c>
-      <c r="O183" t="s">
-        <v>412</v>
-      </c>
-      <c r="P183" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q183" t="s">
-        <v>334</v>
-      </c>
-      <c r="R183" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>363</v>
-      </c>
-      <c r="B184" t="b">
-        <v>0</v>
-      </c>
-      <c r="C184" t="s">
-        <v>18</v>
-      </c>
-      <c r="D184" t="s">
-        <v>19</v>
-      </c>
-      <c r="E184" t="n">
-        <v>1</v>
-      </c>
-      <c r="F184" t="n">
-        <v>1</v>
-      </c>
-      <c r="G184" t="n">
-        <v>2</v>
-      </c>
-      <c r="H184" t="s">
-        <v>54</v>
-      </c>
-      <c r="I184" t="n">
-        <v>8</v>
-      </c>
-      <c r="J184" t="n">
-        <v>3</v>
-      </c>
-      <c r="K184" t="s">
-        <v>384</v>
-      </c>
-      <c r="L184" t="n">
-        <v>3</v>
-      </c>
-      <c r="M184" t="s">
-        <v>413</v>
-      </c>
-      <c r="N184" t="n">
-        <v>11</v>
-      </c>
-      <c r="O184" t="s">
-        <v>414</v>
-      </c>
-      <c r="P184" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q184" t="s">
-        <v>334</v>
-      </c>
-      <c r="R184" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>367</v>
-      </c>
-      <c r="B185" t="b">
-        <v>0</v>
-      </c>
-      <c r="C185" t="s">
-        <v>18</v>
-      </c>
-      <c r="D185" t="s">
-        <v>19</v>
-      </c>
-      <c r="E185" t="n">
-        <v>1</v>
-      </c>
-      <c r="F185" t="n">
-        <v>2</v>
-      </c>
-      <c r="G185" t="n">
-        <v>2</v>
-      </c>
-      <c r="H185" t="s">
-        <v>61</v>
-      </c>
-      <c r="I185" t="n">
-        <v>8</v>
-      </c>
-      <c r="J185" t="n">
-        <v>3</v>
-      </c>
-      <c r="K185" t="s">
-        <v>339</v>
-      </c>
-      <c r="L185" t="n">
-        <v>1</v>
-      </c>
-      <c r="M185" t="s">
-        <v>415</v>
-      </c>
-      <c r="N185" t="n">
-        <v>12</v>
-      </c>
-      <c r="O185" t="s">
-        <v>416</v>
-      </c>
-      <c r="P185" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q185" t="s">
-        <v>342</v>
-      </c>
-      <c r="R185" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>368</v>
-      </c>
-      <c r="B186" t="b">
-        <v>0</v>
-      </c>
-      <c r="C186" t="s">
-        <v>18</v>
-      </c>
-      <c r="D186" t="s">
-        <v>19</v>
-      </c>
-      <c r="E186" t="n">
-        <v>1</v>
-      </c>
-      <c r="F186" t="n">
-        <v>2</v>
-      </c>
-      <c r="G186" t="n">
-        <v>2</v>
-      </c>
-      <c r="H186" t="s">
-        <v>61</v>
-      </c>
-      <c r="I186" t="n">
-        <v>8</v>
-      </c>
-      <c r="J186" t="n">
-        <v>3</v>
-      </c>
-      <c r="K186" t="s">
-        <v>339</v>
-      </c>
-      <c r="L186" t="n">
-        <v>2</v>
-      </c>
-      <c r="M186" t="s">
-        <v>417</v>
-      </c>
-      <c r="N186" t="n">
-        <v>12</v>
-      </c>
-      <c r="O186" t="s">
-        <v>418</v>
-      </c>
-      <c r="P186" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q186" t="s">
-        <v>342</v>
-      </c>
-      <c r="R186" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>369</v>
-      </c>
-      <c r="B187" t="b">
-        <v>0</v>
-      </c>
-      <c r="C187" t="s">
-        <v>18</v>
-      </c>
-      <c r="D187" t="s">
-        <v>19</v>
-      </c>
-      <c r="E187" t="n">
-        <v>1</v>
-      </c>
-      <c r="F187" t="n">
-        <v>2</v>
-      </c>
-      <c r="G187" t="n">
-        <v>2</v>
-      </c>
-      <c r="H187" t="s">
-        <v>61</v>
-      </c>
-      <c r="I187" t="n">
-        <v>8</v>
-      </c>
-      <c r="J187" t="n">
-        <v>3</v>
-      </c>
-      <c r="K187" t="s">
-        <v>339</v>
-      </c>
-      <c r="L187" t="n">
-        <v>3</v>
-      </c>
-      <c r="M187" t="s">
-        <v>419</v>
-      </c>
-      <c r="N187" t="n">
-        <v>12</v>
-      </c>
-      <c r="O187" t="s">
-        <v>420</v>
-      </c>
-      <c r="P187" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q187" t="s">
-        <v>342</v>
-      </c>
-      <c r="R187" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>373</v>
-      </c>
-      <c r="B188" t="b">
-        <v>0</v>
-      </c>
-      <c r="C188" t="s">
-        <v>18</v>
-      </c>
-      <c r="D188" t="s">
-        <v>19</v>
-      </c>
-      <c r="E188" t="n">
-        <v>2</v>
-      </c>
-      <c r="F188" t="n">
-        <v>1</v>
-      </c>
-      <c r="G188" t="n">
-        <v>2</v>
-      </c>
-      <c r="H188" t="s">
-        <v>68</v>
-      </c>
-      <c r="I188" t="n">
-        <v>8</v>
-      </c>
-      <c r="J188" t="n">
-        <v>3</v>
-      </c>
-      <c r="K188" t="s">
-        <v>384</v>
-      </c>
-      <c r="L188" t="n">
-        <v>1</v>
-      </c>
-      <c r="M188" t="s">
-        <v>421</v>
-      </c>
-      <c r="N188" t="n">
-        <v>9</v>
-      </c>
-      <c r="O188" t="s">
-        <v>422</v>
-      </c>
-      <c r="P188" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q188" t="s">
-        <v>41</v>
-      </c>
-      <c r="R188" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>374</v>
-      </c>
-      <c r="B189" t="b">
-        <v>0</v>
-      </c>
-      <c r="C189" t="s">
-        <v>18</v>
-      </c>
-      <c r="D189" t="s">
-        <v>19</v>
-      </c>
-      <c r="E189" t="n">
-        <v>2</v>
-      </c>
-      <c r="F189" t="n">
-        <v>1</v>
-      </c>
-      <c r="G189" t="n">
-        <v>2</v>
-      </c>
-      <c r="H189" t="s">
-        <v>68</v>
-      </c>
-      <c r="I189" t="n">
-        <v>8</v>
-      </c>
-      <c r="J189" t="n">
-        <v>3</v>
-      </c>
-      <c r="K189" t="s">
-        <v>384</v>
-      </c>
-      <c r="L189" t="n">
-        <v>2</v>
-      </c>
-      <c r="M189" t="s">
-        <v>423</v>
-      </c>
-      <c r="N189" t="n">
-        <v>9</v>
-      </c>
-      <c r="O189" t="s">
-        <v>424</v>
-      </c>
-      <c r="P189" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q189" t="s">
-        <v>41</v>
-      </c>
-      <c r="R189" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>375</v>
-      </c>
-      <c r="B190" t="b">
-        <v>0</v>
-      </c>
-      <c r="C190" t="s">
-        <v>18</v>
-      </c>
-      <c r="D190" t="s">
-        <v>19</v>
-      </c>
-      <c r="E190" t="n">
-        <v>2</v>
-      </c>
-      <c r="F190" t="n">
-        <v>1</v>
-      </c>
-      <c r="G190" t="n">
-        <v>2</v>
-      </c>
-      <c r="H190" t="s">
-        <v>68</v>
-      </c>
-      <c r="I190" t="n">
-        <v>8</v>
-      </c>
-      <c r="J190" t="n">
-        <v>3</v>
-      </c>
-      <c r="K190" t="s">
-        <v>384</v>
-      </c>
-      <c r="L190" t="n">
-        <v>3</v>
-      </c>
-      <c r="M190" t="s">
-        <v>425</v>
-      </c>
-      <c r="N190" t="n">
-        <v>9</v>
-      </c>
-      <c r="O190" t="s">
-        <v>426</v>
-      </c>
-      <c r="P190" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q190" t="s">
-        <v>41</v>
-      </c>
-      <c r="R190" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>379</v>
-      </c>
-      <c r="B191" t="b">
-        <v>0</v>
-      </c>
-      <c r="C191" t="s">
-        <v>18</v>
-      </c>
-      <c r="D191" t="s">
-        <v>19</v>
-      </c>
-      <c r="E191" t="n">
-        <v>2</v>
-      </c>
-      <c r="F191" t="n">
-        <v>2</v>
-      </c>
-      <c r="G191" t="n">
-        <v>2</v>
-      </c>
-      <c r="H191" t="s">
-        <v>75</v>
-      </c>
-      <c r="I191" t="n">
-        <v>8</v>
-      </c>
-      <c r="J191" t="n">
-        <v>3</v>
-      </c>
-      <c r="K191" t="s">
-        <v>339</v>
-      </c>
-      <c r="L191" t="n">
-        <v>1</v>
-      </c>
-      <c r="M191" t="s">
-        <v>427</v>
-      </c>
-      <c r="N191" t="n">
-        <v>10</v>
-      </c>
-      <c r="O191" t="s">
-        <v>428</v>
-      </c>
-      <c r="P191" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q191" t="s">
-        <v>355</v>
-      </c>
-      <c r="R191" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>380</v>
-      </c>
-      <c r="B192" t="b">
-        <v>0</v>
-      </c>
-      <c r="C192" t="s">
-        <v>18</v>
-      </c>
-      <c r="D192" t="s">
-        <v>19</v>
-      </c>
-      <c r="E192" t="n">
-        <v>2</v>
-      </c>
-      <c r="F192" t="n">
-        <v>2</v>
-      </c>
-      <c r="G192" t="n">
-        <v>2</v>
-      </c>
-      <c r="H192" t="s">
-        <v>75</v>
-      </c>
-      <c r="I192" t="n">
-        <v>8</v>
-      </c>
-      <c r="J192" t="n">
-        <v>3</v>
-      </c>
-      <c r="K192" t="s">
-        <v>339</v>
-      </c>
-      <c r="L192" t="n">
-        <v>2</v>
-      </c>
-      <c r="M192" t="s">
-        <v>429</v>
-      </c>
-      <c r="N192" t="n">
-        <v>10</v>
-      </c>
-      <c r="O192" t="s">
-        <v>430</v>
-      </c>
-      <c r="P192" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q192" t="s">
-        <v>355</v>
-      </c>
-      <c r="R192" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>381</v>
-      </c>
-      <c r="B193" t="b">
-        <v>0</v>
-      </c>
-      <c r="C193" t="s">
-        <v>18</v>
-      </c>
-      <c r="D193" t="s">
-        <v>19</v>
-      </c>
-      <c r="E193" t="n">
-        <v>2</v>
-      </c>
-      <c r="F193" t="n">
-        <v>2</v>
-      </c>
-      <c r="G193" t="n">
-        <v>2</v>
-      </c>
-      <c r="H193" t="s">
-        <v>75</v>
-      </c>
-      <c r="I193" t="n">
-        <v>8</v>
-      </c>
-      <c r="J193" t="n">
-        <v>3</v>
-      </c>
-      <c r="K193" t="s">
-        <v>339</v>
-      </c>
-      <c r="L193" t="n">
-        <v>3</v>
-      </c>
-      <c r="M193" t="s">
-        <v>431</v>
-      </c>
-      <c r="N193" t="n">
-        <v>10</v>
-      </c>
-      <c r="O193" t="s">
-        <v>432</v>
-      </c>
-      <c r="P193" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q193" t="s">
-        <v>355</v>
-      </c>
-      <c r="R193" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>385</v>
-      </c>
-      <c r="B194" t="b">
-        <v>0</v>
-      </c>
-      <c r="C194" t="s">
-        <v>18</v>
-      </c>
-      <c r="D194" t="s">
-        <v>19</v>
-      </c>
-      <c r="E194" t="n">
-        <v>1</v>
-      </c>
-      <c r="F194" t="n">
-        <v>1</v>
-      </c>
-      <c r="G194" t="n">
-        <v>1</v>
-      </c>
-      <c r="H194" t="s">
-        <v>20</v>
-      </c>
-      <c r="I194" t="n">
-        <v>9</v>
-      </c>
-      <c r="J194" t="n">
-        <v>3</v>
-      </c>
-      <c r="K194" t="s">
-        <v>433</v>
-      </c>
-      <c r="L194" t="n">
-        <v>1</v>
-      </c>
-      <c r="M194" t="s">
-        <v>434</v>
-      </c>
-      <c r="N194" t="n">
-        <v>10</v>
-      </c>
-      <c r="O194" t="s">
-        <v>435</v>
-      </c>
-      <c r="P194" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q194" t="s">
-        <v>436</v>
-      </c>
-      <c r="R194" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>386</v>
-      </c>
-      <c r="B195" t="b">
-        <v>0</v>
-      </c>
-      <c r="C195" t="s">
-        <v>18</v>
-      </c>
-      <c r="D195" t="s">
-        <v>19</v>
-      </c>
-      <c r="E195" t="n">
-        <v>1</v>
-      </c>
-      <c r="F195" t="n">
-        <v>1</v>
-      </c>
-      <c r="G195" t="n">
-        <v>1</v>
-      </c>
-      <c r="H195" t="s">
-        <v>20</v>
-      </c>
-      <c r="I195" t="n">
-        <v>9</v>
-      </c>
-      <c r="J195" t="n">
-        <v>3</v>
-      </c>
-      <c r="K195" t="s">
-        <v>433</v>
-      </c>
-      <c r="L195" t="n">
-        <v>2</v>
-      </c>
-      <c r="M195" t="s">
-        <v>437</v>
-      </c>
-      <c r="N195" t="n">
-        <v>10</v>
-      </c>
-      <c r="O195" t="s">
-        <v>438</v>
-      </c>
-      <c r="P195" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q195" t="s">
-        <v>436</v>
-      </c>
-      <c r="R195" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>387</v>
-      </c>
-      <c r="B196" t="b">
-        <v>0</v>
-      </c>
-      <c r="C196" t="s">
-        <v>18</v>
-      </c>
-      <c r="D196" t="s">
-        <v>19</v>
-      </c>
-      <c r="E196" t="n">
-        <v>1</v>
-      </c>
-      <c r="F196" t="n">
-        <v>1</v>
-      </c>
-      <c r="G196" t="n">
-        <v>1</v>
-      </c>
-      <c r="H196" t="s">
-        <v>20</v>
-      </c>
-      <c r="I196" t="n">
-        <v>9</v>
-      </c>
-      <c r="J196" t="n">
-        <v>3</v>
-      </c>
-      <c r="K196" t="s">
-        <v>433</v>
-      </c>
-      <c r="L196" t="n">
-        <v>3</v>
-      </c>
-      <c r="M196" t="s">
-        <v>439</v>
-      </c>
-      <c r="N196" t="n">
-        <v>10</v>
-      </c>
-      <c r="O196" t="s">
-        <v>440</v>
-      </c>
-      <c r="P196" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q196" t="s">
-        <v>436</v>
-      </c>
-      <c r="R196" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>391</v>
-      </c>
-      <c r="B197" t="b">
-        <v>0</v>
-      </c>
-      <c r="C197" t="s">
-        <v>18</v>
-      </c>
-      <c r="D197" t="s">
-        <v>19</v>
-      </c>
-      <c r="E197" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" t="n">
-        <v>2</v>
-      </c>
-      <c r="G197" t="n">
-        <v>1</v>
-      </c>
-      <c r="H197" t="s">
-        <v>29</v>
-      </c>
-      <c r="I197" t="n">
-        <v>9</v>
-      </c>
-      <c r="J197" t="n">
-        <v>3</v>
-      </c>
-      <c r="K197" t="s">
-        <v>339</v>
-      </c>
-      <c r="L197" t="n">
-        <v>1</v>
-      </c>
-      <c r="M197" t="s">
-        <v>441</v>
-      </c>
-      <c r="N197" t="n">
-        <v>12</v>
-      </c>
-      <c r="O197" t="s">
-        <v>442</v>
-      </c>
-      <c r="P197" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q197" t="s">
-        <v>342</v>
-      </c>
-      <c r="R197" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>392</v>
-      </c>
-      <c r="B198" t="b">
-        <v>0</v>
-      </c>
-      <c r="C198" t="s">
-        <v>18</v>
-      </c>
-      <c r="D198" t="s">
-        <v>19</v>
-      </c>
-      <c r="E198" t="n">
-        <v>1</v>
-      </c>
-      <c r="F198" t="n">
-        <v>2</v>
-      </c>
-      <c r="G198" t="n">
-        <v>1</v>
-      </c>
-      <c r="H198" t="s">
-        <v>29</v>
-      </c>
-      <c r="I198" t="n">
-        <v>9</v>
-      </c>
-      <c r="J198" t="n">
-        <v>3</v>
-      </c>
-      <c r="K198" t="s">
-        <v>339</v>
-      </c>
-      <c r="L198" t="n">
-        <v>2</v>
-      </c>
-      <c r="M198" t="s">
-        <v>443</v>
-      </c>
-      <c r="N198" t="n">
-        <v>12</v>
-      </c>
-      <c r="O198" t="s">
-        <v>444</v>
-      </c>
-      <c r="P198" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q198" t="s">
-        <v>342</v>
-      </c>
-      <c r="R198" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>393</v>
-      </c>
-      <c r="B199" t="b">
-        <v>0</v>
-      </c>
-      <c r="C199" t="s">
-        <v>18</v>
-      </c>
-      <c r="D199" t="s">
-        <v>19</v>
-      </c>
-      <c r="E199" t="n">
-        <v>1</v>
-      </c>
-      <c r="F199" t="n">
-        <v>2</v>
-      </c>
-      <c r="G199" t="n">
-        <v>1</v>
-      </c>
-      <c r="H199" t="s">
-        <v>29</v>
-      </c>
-      <c r="I199" t="n">
-        <v>9</v>
-      </c>
-      <c r="J199" t="n">
-        <v>3</v>
-      </c>
-      <c r="K199" t="s">
-        <v>339</v>
-      </c>
-      <c r="L199" t="n">
-        <v>3</v>
-      </c>
-      <c r="M199" t="s">
-        <v>445</v>
-      </c>
-      <c r="N199" t="n">
-        <v>12</v>
-      </c>
-      <c r="O199" t="s">
-        <v>446</v>
-      </c>
-      <c r="P199" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q199" t="s">
-        <v>342</v>
-      </c>
-      <c r="R199" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>397</v>
-      </c>
-      <c r="B200" t="b">
-        <v>0</v>
-      </c>
-      <c r="C200" t="s">
-        <v>18</v>
-      </c>
-      <c r="D200" t="s">
-        <v>19</v>
-      </c>
-      <c r="E200" t="n">
-        <v>2</v>
-      </c>
-      <c r="F200" t="n">
-        <v>1</v>
-      </c>
-      <c r="G200" t="n">
-        <v>1</v>
-      </c>
-      <c r="H200" t="s">
-        <v>38</v>
-      </c>
-      <c r="I200" t="n">
-        <v>9</v>
-      </c>
-      <c r="J200" t="n">
-        <v>3</v>
-      </c>
-      <c r="K200" t="s">
-        <v>433</v>
-      </c>
-      <c r="L200" t="n">
-        <v>1</v>
-      </c>
-      <c r="M200" t="s">
-        <v>447</v>
-      </c>
-      <c r="N200" t="n">
-        <v>7</v>
-      </c>
-      <c r="O200" t="s">
-        <v>448</v>
-      </c>
-      <c r="P200" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q200" t="s">
-        <v>296</v>
-      </c>
-      <c r="R200" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>398</v>
-      </c>
-      <c r="B201" t="b">
-        <v>0</v>
-      </c>
-      <c r="C201" t="s">
-        <v>18</v>
-      </c>
-      <c r="D201" t="s">
-        <v>19</v>
-      </c>
-      <c r="E201" t="n">
-        <v>2</v>
-      </c>
-      <c r="F201" t="n">
-        <v>1</v>
-      </c>
-      <c r="G201" t="n">
-        <v>1</v>
-      </c>
-      <c r="H201" t="s">
-        <v>38</v>
-      </c>
-      <c r="I201" t="n">
-        <v>9</v>
-      </c>
-      <c r="J201" t="n">
-        <v>3</v>
-      </c>
-      <c r="K201" t="s">
-        <v>433</v>
-      </c>
-      <c r="L201" t="n">
-        <v>2</v>
-      </c>
-      <c r="M201" t="s">
-        <v>449</v>
-      </c>
-      <c r="N201" t="n">
-        <v>7</v>
-      </c>
-      <c r="O201" t="s">
-        <v>450</v>
-      </c>
-      <c r="P201" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q201" t="s">
-        <v>296</v>
-      </c>
-      <c r="R201" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>399</v>
-      </c>
-      <c r="B202" t="b">
-        <v>0</v>
-      </c>
-      <c r="C202" t="s">
-        <v>18</v>
-      </c>
-      <c r="D202" t="s">
-        <v>19</v>
-      </c>
-      <c r="E202" t="n">
-        <v>2</v>
-      </c>
-      <c r="F202" t="n">
-        <v>1</v>
-      </c>
-      <c r="G202" t="n">
-        <v>1</v>
-      </c>
-      <c r="H202" t="s">
-        <v>38</v>
-      </c>
-      <c r="I202" t="n">
-        <v>9</v>
-      </c>
-      <c r="J202" t="n">
-        <v>3</v>
-      </c>
-      <c r="K202" t="s">
-        <v>433</v>
-      </c>
-      <c r="L202" t="n">
-        <v>3</v>
-      </c>
-      <c r="M202" t="s">
-        <v>451</v>
-      </c>
-      <c r="N202" t="n">
-        <v>7</v>
-      </c>
-      <c r="O202" t="s">
-        <v>452</v>
-      </c>
-      <c r="P202" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q202" t="s">
-        <v>296</v>
-      </c>
-      <c r="R202" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>403</v>
-      </c>
-      <c r="B203" t="b">
-        <v>0</v>
-      </c>
-      <c r="C203" t="s">
-        <v>18</v>
-      </c>
-      <c r="D203" t="s">
-        <v>19</v>
-      </c>
-      <c r="E203" t="n">
-        <v>2</v>
-      </c>
-      <c r="F203" t="n">
-        <v>2</v>
-      </c>
-      <c r="G203" t="n">
-        <v>1</v>
-      </c>
-      <c r="H203" t="s">
-        <v>46</v>
-      </c>
-      <c r="I203" t="n">
-        <v>9</v>
-      </c>
-      <c r="J203" t="n">
-        <v>3</v>
-      </c>
-      <c r="K203" t="s">
-        <v>339</v>
-      </c>
-      <c r="L203" t="n">
-        <v>1</v>
-      </c>
-      <c r="M203" t="s">
-        <v>453</v>
-      </c>
-      <c r="N203" t="n">
-        <v>10</v>
-      </c>
-      <c r="O203" t="s">
-        <v>454</v>
-      </c>
-      <c r="P203" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q203" t="s">
-        <v>355</v>
-      </c>
-      <c r="R203" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>404</v>
-      </c>
-      <c r="B204" t="b">
-        <v>0</v>
-      </c>
-      <c r="C204" t="s">
-        <v>18</v>
-      </c>
-      <c r="D204" t="s">
-        <v>19</v>
-      </c>
-      <c r="E204" t="n">
-        <v>2</v>
-      </c>
-      <c r="F204" t="n">
-        <v>2</v>
-      </c>
-      <c r="G204" t="n">
-        <v>1</v>
-      </c>
-      <c r="H204" t="s">
-        <v>46</v>
-      </c>
-      <c r="I204" t="n">
-        <v>9</v>
-      </c>
-      <c r="J204" t="n">
-        <v>3</v>
-      </c>
-      <c r="K204" t="s">
-        <v>339</v>
-      </c>
-      <c r="L204" t="n">
-        <v>2</v>
-      </c>
-      <c r="M204" t="s">
-        <v>455</v>
-      </c>
-      <c r="N204" t="n">
-        <v>10</v>
-      </c>
-      <c r="O204" t="s">
-        <v>456</v>
-      </c>
-      <c r="P204" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q204" t="s">
-        <v>355</v>
-      </c>
-      <c r="R204" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>405</v>
-      </c>
-      <c r="B205" t="b">
-        <v>0</v>
-      </c>
-      <c r="C205" t="s">
-        <v>18</v>
-      </c>
-      <c r="D205" t="s">
-        <v>19</v>
-      </c>
-      <c r="E205" t="n">
-        <v>2</v>
-      </c>
-      <c r="F205" t="n">
-        <v>2</v>
-      </c>
-      <c r="G205" t="n">
-        <v>1</v>
-      </c>
-      <c r="H205" t="s">
-        <v>46</v>
-      </c>
-      <c r="I205" t="n">
-        <v>9</v>
-      </c>
-      <c r="J205" t="n">
-        <v>3</v>
-      </c>
-      <c r="K205" t="s">
-        <v>339</v>
-      </c>
-      <c r="L205" t="n">
-        <v>3</v>
-      </c>
-      <c r="M205" t="s">
-        <v>457</v>
-      </c>
-      <c r="N205" t="n">
-        <v>10</v>
-      </c>
-      <c r="O205" t="s">
-        <v>458</v>
-      </c>
-      <c r="P205" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q205" t="s">
-        <v>355</v>
-      </c>
-      <c r="R205" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>409</v>
-      </c>
-      <c r="B206" t="b">
-        <v>0</v>
-      </c>
-      <c r="C206" t="s">
-        <v>18</v>
-      </c>
-      <c r="D206" t="s">
-        <v>19</v>
-      </c>
-      <c r="E206" t="n">
-        <v>1</v>
-      </c>
-      <c r="F206" t="n">
-        <v>1</v>
-      </c>
-      <c r="G206" t="n">
-        <v>2</v>
-      </c>
-      <c r="H206" t="s">
-        <v>54</v>
-      </c>
-      <c r="I206" t="n">
-        <v>9</v>
-      </c>
-      <c r="J206" t="n">
-        <v>3</v>
-      </c>
-      <c r="K206" t="s">
-        <v>433</v>
-      </c>
-      <c r="L206" t="n">
-        <v>1</v>
-      </c>
-      <c r="M206" t="s">
-        <v>459</v>
-      </c>
-      <c r="N206" t="n">
-        <v>10</v>
-      </c>
-      <c r="O206" t="s">
-        <v>460</v>
-      </c>
-      <c r="P206" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q206" t="s">
-        <v>436</v>
-      </c>
-      <c r="R206" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>410</v>
-      </c>
-      <c r="B207" t="b">
-        <v>0</v>
-      </c>
-      <c r="C207" t="s">
-        <v>18</v>
-      </c>
-      <c r="D207" t="s">
-        <v>19</v>
-      </c>
-      <c r="E207" t="n">
-        <v>1</v>
-      </c>
-      <c r="F207" t="n">
-        <v>1</v>
-      </c>
-      <c r="G207" t="n">
-        <v>2</v>
-      </c>
-      <c r="H207" t="s">
-        <v>54</v>
-      </c>
-      <c r="I207" t="n">
-        <v>9</v>
-      </c>
-      <c r="J207" t="n">
-        <v>3</v>
-      </c>
-      <c r="K207" t="s">
-        <v>433</v>
-      </c>
-      <c r="L207" t="n">
-        <v>2</v>
-      </c>
-      <c r="M207" t="s">
-        <v>461</v>
-      </c>
-      <c r="N207" t="n">
-        <v>10</v>
-      </c>
-      <c r="O207" t="s">
-        <v>462</v>
-      </c>
-      <c r="P207" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q207" t="s">
-        <v>436</v>
-      </c>
-      <c r="R207" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
-        <v>411</v>
-      </c>
-      <c r="B208" t="b">
-        <v>0</v>
-      </c>
-      <c r="C208" t="s">
-        <v>18</v>
-      </c>
-      <c r="D208" t="s">
-        <v>19</v>
-      </c>
-      <c r="E208" t="n">
-        <v>1</v>
-      </c>
-      <c r="F208" t="n">
-        <v>1</v>
-      </c>
-      <c r="G208" t="n">
-        <v>2</v>
-      </c>
-      <c r="H208" t="s">
-        <v>54</v>
-      </c>
-      <c r="I208" t="n">
-        <v>9</v>
-      </c>
-      <c r="J208" t="n">
-        <v>3</v>
-      </c>
-      <c r="K208" t="s">
-        <v>433</v>
-      </c>
-      <c r="L208" t="n">
-        <v>3</v>
-      </c>
-      <c r="M208" t="s">
-        <v>463</v>
-      </c>
-      <c r="N208" t="n">
-        <v>10</v>
-      </c>
-      <c r="O208" t="s">
-        <v>464</v>
-      </c>
-      <c r="P208" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q208" t="s">
-        <v>436</v>
-      </c>
-      <c r="R208" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
-        <v>415</v>
-      </c>
-      <c r="B209" t="b">
-        <v>0</v>
-      </c>
-      <c r="C209" t="s">
-        <v>18</v>
-      </c>
-      <c r="D209" t="s">
-        <v>19</v>
-      </c>
-      <c r="E209" t="n">
-        <v>1</v>
-      </c>
-      <c r="F209" t="n">
-        <v>2</v>
-      </c>
-      <c r="G209" t="n">
-        <v>2</v>
-      </c>
-      <c r="H209" t="s">
-        <v>61</v>
-      </c>
-      <c r="I209" t="n">
-        <v>9</v>
-      </c>
-      <c r="J209" t="n">
-        <v>3</v>
-      </c>
-      <c r="K209" t="s">
-        <v>339</v>
-      </c>
-      <c r="L209" t="n">
-        <v>1</v>
-      </c>
-      <c r="M209" t="s">
-        <v>465</v>
-      </c>
-      <c r="N209" t="n">
-        <v>12</v>
-      </c>
-      <c r="O209" t="s">
-        <v>466</v>
-      </c>
-      <c r="P209" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q209" t="s">
-        <v>342</v>
-      </c>
-      <c r="R209" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>416</v>
-      </c>
-      <c r="B210" t="b">
-        <v>0</v>
-      </c>
-      <c r="C210" t="s">
-        <v>18</v>
-      </c>
-      <c r="D210" t="s">
-        <v>19</v>
-      </c>
-      <c r="E210" t="n">
-        <v>1</v>
-      </c>
-      <c r="F210" t="n">
-        <v>2</v>
-      </c>
-      <c r="G210" t="n">
-        <v>2</v>
-      </c>
-      <c r="H210" t="s">
-        <v>61</v>
-      </c>
-      <c r="I210" t="n">
-        <v>9</v>
-      </c>
-      <c r="J210" t="n">
-        <v>3</v>
-      </c>
-      <c r="K210" t="s">
-        <v>339</v>
-      </c>
-      <c r="L210" t="n">
-        <v>2</v>
-      </c>
-      <c r="M210" t="s">
-        <v>467</v>
-      </c>
-      <c r="N210" t="n">
-        <v>12</v>
-      </c>
-      <c r="O210" t="s">
-        <v>468</v>
-      </c>
-      <c r="P210" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q210" t="s">
-        <v>342</v>
-      </c>
-      <c r="R210" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>417</v>
-      </c>
-      <c r="B211" t="b">
-        <v>0</v>
-      </c>
-      <c r="C211" t="s">
-        <v>18</v>
-      </c>
-      <c r="D211" t="s">
-        <v>19</v>
-      </c>
-      <c r="E211" t="n">
-        <v>1</v>
-      </c>
-      <c r="F211" t="n">
-        <v>2</v>
-      </c>
-      <c r="G211" t="n">
-        <v>2</v>
-      </c>
-      <c r="H211" t="s">
-        <v>61</v>
-      </c>
-      <c r="I211" t="n">
-        <v>9</v>
-      </c>
-      <c r="J211" t="n">
-        <v>3</v>
-      </c>
-      <c r="K211" t="s">
-        <v>339</v>
-      </c>
-      <c r="L211" t="n">
-        <v>3</v>
-      </c>
-      <c r="M211" t="s">
-        <v>469</v>
-      </c>
-      <c r="N211" t="n">
-        <v>12</v>
-      </c>
-      <c r="O211" t="s">
-        <v>470</v>
-      </c>
-      <c r="P211" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q211" t="s">
-        <v>342</v>
-      </c>
-      <c r="R211" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>421</v>
-      </c>
-      <c r="B212" t="b">
-        <v>0</v>
-      </c>
-      <c r="C212" t="s">
-        <v>18</v>
-      </c>
-      <c r="D212" t="s">
-        <v>19</v>
-      </c>
-      <c r="E212" t="n">
-        <v>2</v>
-      </c>
-      <c r="F212" t="n">
-        <v>1</v>
-      </c>
-      <c r="G212" t="n">
-        <v>2</v>
-      </c>
-      <c r="H212" t="s">
-        <v>68</v>
-      </c>
-      <c r="I212" t="n">
-        <v>9</v>
-      </c>
-      <c r="J212" t="n">
-        <v>3</v>
-      </c>
-      <c r="K212" t="s">
-        <v>433</v>
-      </c>
-      <c r="L212" t="n">
-        <v>1</v>
-      </c>
-      <c r="M212" t="s">
-        <v>471</v>
-      </c>
-      <c r="N212" t="n">
-        <v>7</v>
-      </c>
-      <c r="O212" t="s">
-        <v>472</v>
-      </c>
-      <c r="P212" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q212" t="s">
-        <v>296</v>
-      </c>
-      <c r="R212" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>422</v>
-      </c>
-      <c r="B213" t="b">
-        <v>0</v>
-      </c>
-      <c r="C213" t="s">
-        <v>18</v>
-      </c>
-      <c r="D213" t="s">
-        <v>19</v>
-      </c>
-      <c r="E213" t="n">
-        <v>2</v>
-      </c>
-      <c r="F213" t="n">
-        <v>1</v>
-      </c>
-      <c r="G213" t="n">
-        <v>2</v>
-      </c>
-      <c r="H213" t="s">
-        <v>68</v>
-      </c>
-      <c r="I213" t="n">
-        <v>9</v>
-      </c>
-      <c r="J213" t="n">
-        <v>3</v>
-      </c>
-      <c r="K213" t="s">
-        <v>433</v>
-      </c>
-      <c r="L213" t="n">
-        <v>2</v>
-      </c>
-      <c r="M213" t="s">
-        <v>473</v>
-      </c>
-      <c r="N213" t="n">
-        <v>7</v>
-      </c>
-      <c r="O213" t="s">
-        <v>474</v>
-      </c>
-      <c r="P213" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q213" t="s">
-        <v>296</v>
-      </c>
-      <c r="R213" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>423</v>
-      </c>
-      <c r="B214" t="b">
-        <v>0</v>
-      </c>
-      <c r="C214" t="s">
-        <v>18</v>
-      </c>
-      <c r="D214" t="s">
-        <v>19</v>
-      </c>
-      <c r="E214" t="n">
-        <v>2</v>
-      </c>
-      <c r="F214" t="n">
-        <v>1</v>
-      </c>
-      <c r="G214" t="n">
-        <v>2</v>
-      </c>
-      <c r="H214" t="s">
-        <v>68</v>
-      </c>
-      <c r="I214" t="n">
-        <v>9</v>
-      </c>
-      <c r="J214" t="n">
-        <v>3</v>
-      </c>
-      <c r="K214" t="s">
-        <v>433</v>
-      </c>
-      <c r="L214" t="n">
-        <v>3</v>
-      </c>
-      <c r="M214" t="s">
-        <v>475</v>
-      </c>
-      <c r="N214" t="n">
-        <v>7</v>
-      </c>
-      <c r="O214" t="s">
-        <v>476</v>
-      </c>
-      <c r="P214" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q214" t="s">
-        <v>296</v>
-      </c>
-      <c r="R214" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>427</v>
-      </c>
-      <c r="B215" t="b">
-        <v>0</v>
-      </c>
-      <c r="C215" t="s">
-        <v>18</v>
-      </c>
-      <c r="D215" t="s">
-        <v>19</v>
-      </c>
-      <c r="E215" t="n">
-        <v>2</v>
-      </c>
-      <c r="F215" t="n">
-        <v>2</v>
-      </c>
-      <c r="G215" t="n">
-        <v>2</v>
-      </c>
-      <c r="H215" t="s">
-        <v>75</v>
-      </c>
-      <c r="I215" t="n">
-        <v>9</v>
-      </c>
-      <c r="J215" t="n">
-        <v>3</v>
-      </c>
-      <c r="K215" t="s">
-        <v>339</v>
-      </c>
-      <c r="L215" t="n">
-        <v>1</v>
-      </c>
-      <c r="M215" t="s">
-        <v>477</v>
-      </c>
-      <c r="N215" t="n">
-        <v>10</v>
-      </c>
-      <c r="O215" t="s">
-        <v>478</v>
-      </c>
-      <c r="P215" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q215" t="s">
-        <v>355</v>
-      </c>
-      <c r="R215" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>428</v>
-      </c>
-      <c r="B216" t="b">
-        <v>0</v>
-      </c>
-      <c r="C216" t="s">
-        <v>18</v>
-      </c>
-      <c r="D216" t="s">
-        <v>19</v>
-      </c>
-      <c r="E216" t="n">
-        <v>2</v>
-      </c>
-      <c r="F216" t="n">
-        <v>2</v>
-      </c>
-      <c r="G216" t="n">
-        <v>2</v>
-      </c>
-      <c r="H216" t="s">
-        <v>75</v>
-      </c>
-      <c r="I216" t="n">
-        <v>9</v>
-      </c>
-      <c r="J216" t="n">
-        <v>3</v>
-      </c>
-      <c r="K216" t="s">
-        <v>339</v>
-      </c>
-      <c r="L216" t="n">
-        <v>2</v>
-      </c>
-      <c r="M216" t="s">
-        <v>479</v>
-      </c>
-      <c r="N216" t="n">
-        <v>10</v>
-      </c>
-      <c r="O216" t="s">
-        <v>480</v>
-      </c>
-      <c r="P216" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q216" t="s">
-        <v>355</v>
-      </c>
-      <c r="R216" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>429</v>
-      </c>
-      <c r="B217" t="b">
-        <v>0</v>
-      </c>
-      <c r="C217" t="s">
-        <v>18</v>
-      </c>
-      <c r="D217" t="s">
-        <v>19</v>
-      </c>
-      <c r="E217" t="n">
-        <v>2</v>
-      </c>
-      <c r="F217" t="n">
-        <v>2</v>
-      </c>
-      <c r="G217" t="n">
-        <v>2</v>
-      </c>
-      <c r="H217" t="s">
-        <v>75</v>
-      </c>
-      <c r="I217" t="n">
-        <v>9</v>
-      </c>
-      <c r="J217" t="n">
-        <v>3</v>
-      </c>
-      <c r="K217" t="s">
-        <v>339</v>
-      </c>
-      <c r="L217" t="n">
-        <v>3</v>
-      </c>
-      <c r="M217" t="s">
-        <v>481</v>
-      </c>
-      <c r="N217" t="n">
-        <v>10</v>
-      </c>
-      <c r="O217" t="s">
-        <v>482</v>
-      </c>
-      <c r="P217" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q217" t="s">
-        <v>355</v>
-      </c>
-      <c r="R217" t="s">
-        <v>355</v>
       </c>
     </row>
   </sheetData>
